--- a/pages/apps/uprn-service/config.xlsx
+++ b/pages/apps/uprn-service/config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NDSH\GitHub\dsh-content\dev\pages\apps\uprn-service\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NDSH\GitHub\dsh-content\pages\apps\uprn-service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1586C45E-DEA8-4DBF-87D5-695904905001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B79A0EB-7146-4C10-9515-8E76BD80662D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="132" windowWidth="23040" windowHeight="12024" tabRatio="388" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="388" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="folders" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5582" uniqueCount="2411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5603" uniqueCount="2431">
   <si>
     <t>DbId</t>
   </si>
@@ -7261,6 +7261,66 @@
   </si>
   <si>
     <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/AQREAN/Annual/SL/air_temperature/info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/AQREAN/Annual/SL/daily_aqi_nitrogen_dioxide/info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/AQREAN/Annual/SL/mc_ammonium_in_pm2p5_dry_aerosol_in_air/info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/AQREAN/Annual/SL/mc_ammonium_nitrate_in_pm2p5_dry_aerosol_in_air/info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/AQREAN/Annual/SL/mc_black_carbon_in_pm2p5_dry_aerosol_in_air/info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/AQREAN/Annual/SL/mc_ammonium_sulfate_in_pm2p5_dry_aerosol_in_air/info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/AQREAN/Annual/SL/mc_biomass_burning_aerosol_in_pm2p5_dry_aerosol_in_air/info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/AQREAN/Annual/SL/mc_dust_in_pm2p5_dry_aerosol_in_air/info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/AQREAN/Annual/SL/mc_sulfate_in_pm2p5_dry_aerosol_in_air/info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/AQREAN/Annual/SL/mc_nitrate_in_pm2p5_dry_aerosol_in_air/info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/AQREAN/Annual/SL/mc_nitrogen_dioxide_in_air/info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/AQREAN/Annual/SL/mc_nox_expressed_as_nitrogen_dioxide_in_air/info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/AQREAN/Annual/SL/mc_organic_carbon_from_fossil_fuel_combustion_in_pm2p5_dry_aerosol_in_air/info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/AQREAN/Annual/SL/mc_pm2p5_dry_aerosol_in_air/info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/AQREAN/Annual/SL/mc_secondary_particulate_organic_matter_in_pm2p5_dry_aerosol_in_air/info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/AQREAN/Annual/SL/relative_humidity/info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/AQREAN/Annual/SL_BC/mc_pm2p5_dry_aerosol_in_air/info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/AQREAN/Annual/SL_BC/daily_aqi_nitrogen_dioxide/info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/AQREAN/Annual/SL_BC/daily_aqi_pm2p5_dry_aerosol/info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/AQREAN/Annual/SL_BC/mc_nitrogen_dioxide_in_air/info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/AQREAN/Annual/SL_BC/mc_nox_expressed_as_nitrogen_dioxide_in_air/info.json</t>
   </si>
 </sst>
 </file>
@@ -10354,7 +10414,9 @@
       <c r="M43">
         <v>7002</v>
       </c>
-      <c r="O43" s="3"/>
+      <c r="O43" s="3" t="s">
+        <v>2411</v>
+      </c>
       <c r="P43">
         <v>2</v>
       </c>
@@ -10411,6 +10473,9 @@
       <c r="M44">
         <v>7003</v>
       </c>
+      <c r="O44" s="3" t="s">
+        <v>2411</v>
+      </c>
       <c r="P44">
         <v>2</v>
       </c>
@@ -10526,6 +10591,9 @@
       <c r="M46">
         <v>7005</v>
       </c>
+      <c r="O46" s="3" t="s">
+        <v>2412</v>
+      </c>
       <c r="P46">
         <v>2</v>
       </c>
@@ -10582,6 +10650,9 @@
       <c r="M47">
         <v>7006</v>
       </c>
+      <c r="O47" s="3" t="s">
+        <v>2413</v>
+      </c>
       <c r="P47">
         <v>2</v>
       </c>
@@ -10638,6 +10709,9 @@
       <c r="M48">
         <v>7007</v>
       </c>
+      <c r="O48" s="3" t="s">
+        <v>2415</v>
+      </c>
       <c r="P48">
         <v>2</v>
       </c>
@@ -10694,6 +10768,9 @@
       <c r="M49">
         <v>7008</v>
       </c>
+      <c r="O49" s="3" t="s">
+        <v>2416</v>
+      </c>
       <c r="P49">
         <v>2</v>
       </c>
@@ -10750,6 +10827,9 @@
       <c r="M50">
         <v>7009</v>
       </c>
+      <c r="O50" s="3" t="s">
+        <v>2414</v>
+      </c>
       <c r="P50">
         <v>2</v>
       </c>
@@ -10806,6 +10886,9 @@
       <c r="M51">
         <v>7010</v>
       </c>
+      <c r="O51" s="3" t="s">
+        <v>2417</v>
+      </c>
       <c r="P51">
         <v>2</v>
       </c>
@@ -10862,6 +10945,9 @@
       <c r="M52">
         <v>7011</v>
       </c>
+      <c r="O52" s="3" t="s">
+        <v>2419</v>
+      </c>
       <c r="P52">
         <v>2</v>
       </c>
@@ -10918,6 +11004,9 @@
       <c r="M53">
         <v>7012</v>
       </c>
+      <c r="O53" s="3" t="s">
+        <v>2420</v>
+      </c>
       <c r="P53">
         <v>2</v>
       </c>
@@ -10974,6 +11063,9 @@
       <c r="M54">
         <v>7013</v>
       </c>
+      <c r="O54" s="3" t="s">
+        <v>2421</v>
+      </c>
       <c r="P54">
         <v>2</v>
       </c>
@@ -11030,6 +11122,9 @@
       <c r="M55">
         <v>7014</v>
       </c>
+      <c r="O55" s="3" t="s">
+        <v>2425</v>
+      </c>
       <c r="P55">
         <v>2</v>
       </c>
@@ -11086,6 +11181,9 @@
       <c r="M56">
         <v>7015</v>
       </c>
+      <c r="O56" s="3" t="s">
+        <v>2424</v>
+      </c>
       <c r="P56">
         <v>2</v>
       </c>
@@ -11142,6 +11240,9 @@
       <c r="M57">
         <v>7016</v>
       </c>
+      <c r="O57" s="3" t="s">
+        <v>2418</v>
+      </c>
       <c r="P57">
         <v>2</v>
       </c>
@@ -11198,6 +11299,9 @@
       <c r="M58">
         <v>7017</v>
       </c>
+      <c r="O58" s="3" t="s">
+        <v>2422</v>
+      </c>
       <c r="P58">
         <v>2</v>
       </c>
@@ -11254,6 +11358,9 @@
       <c r="M59">
         <v>7018</v>
       </c>
+      <c r="O59" s="3" t="s">
+        <v>2423</v>
+      </c>
       <c r="P59">
         <v>2</v>
       </c>
@@ -11307,6 +11414,7 @@
       <c r="M60">
         <v>8001</v>
       </c>
+      <c r="O60" s="3"/>
       <c r="P60">
         <v>2</v>
       </c>
@@ -11363,6 +11471,9 @@
       <c r="M61">
         <v>8002</v>
       </c>
+      <c r="O61" s="3" t="s">
+        <v>2427</v>
+      </c>
       <c r="P61">
         <v>2</v>
       </c>
@@ -11419,6 +11530,9 @@
       <c r="M62">
         <v>8003</v>
       </c>
+      <c r="O62" s="3" t="s">
+        <v>2428</v>
+      </c>
       <c r="P62">
         <v>2</v>
       </c>
@@ -11475,6 +11589,9 @@
       <c r="M63">
         <v>8004</v>
       </c>
+      <c r="O63" s="3" t="s">
+        <v>2429</v>
+      </c>
       <c r="P63">
         <v>2</v>
       </c>
@@ -11531,6 +11648,9 @@
       <c r="M64">
         <v>8005</v>
       </c>
+      <c r="O64" s="3" t="s">
+        <v>2430</v>
+      </c>
       <c r="P64">
         <v>2</v>
       </c>
@@ -11586,6 +11706,9 @@
       </c>
       <c r="M65">
         <v>8006</v>
+      </c>
+      <c r="O65" s="3" t="s">
+        <v>2426</v>
       </c>
       <c r="P65">
         <v>2</v>
@@ -11616,6 +11739,28 @@
     <hyperlink ref="O38" r:id="rId8" xr:uid="{71FF0051-ABE5-4973-9ED9-91F5EC5E19E7}"/>
     <hyperlink ref="O40" r:id="rId9" xr:uid="{356432AE-63BD-45AD-AFAA-748A8876906A}"/>
     <hyperlink ref="O45" r:id="rId10" xr:uid="{4252AAA9-D643-4DFB-8757-57BF2C62AF79}"/>
+    <hyperlink ref="O43" r:id="rId11" xr:uid="{4252AAA9-D643-4DFB-8757-57BF2C62AF79}"/>
+    <hyperlink ref="O44" r:id="rId12" xr:uid="{4900D3BB-243B-40FF-9C55-6C4BFE9C0CFE}"/>
+    <hyperlink ref="O46" r:id="rId13" xr:uid="{25DCD23B-0B79-462D-8B8E-F58EC597A07D}"/>
+    <hyperlink ref="O47" r:id="rId14" xr:uid="{D25B6B7C-9BDB-4B88-A91C-C8F4749825FC}"/>
+    <hyperlink ref="O48" r:id="rId15" xr:uid="{3F61F8D5-D025-47EA-9E46-A33CD2A748C3}"/>
+    <hyperlink ref="O49" r:id="rId16" xr:uid="{7413B110-AA8C-4D1F-B232-EC9D2676EC03}"/>
+    <hyperlink ref="O50" r:id="rId17" xr:uid="{A8941504-CE22-4FFF-8C72-0C327A3F35E7}"/>
+    <hyperlink ref="O51" r:id="rId18" xr:uid="{4A006016-10C1-42ED-80E8-802F405B4AE4}"/>
+    <hyperlink ref="O52" r:id="rId19" xr:uid="{7E9F5DD0-1FF6-476A-A906-2A44F86A1D11}"/>
+    <hyperlink ref="O53" r:id="rId20" xr:uid="{1AD16DE8-1400-4B84-9B62-7205C096E12F}"/>
+    <hyperlink ref="O54" r:id="rId21" xr:uid="{C3A01C21-E8E2-417F-B950-130AACEE76C2}"/>
+    <hyperlink ref="O58" r:id="rId22" xr:uid="{76E42F68-0A71-40AC-B534-0BF58052A7AA}"/>
+    <hyperlink ref="O59" r:id="rId23" xr:uid="{32748E37-142E-4E11-B188-229CC5F68817}"/>
+    <hyperlink ref="O56" r:id="rId24" xr:uid="{9ED538C0-DBAB-4F32-B43E-BD185D1D322C}"/>
+    <hyperlink ref="O57" r:id="rId25" xr:uid="{57C56A3D-FC73-437B-BCB9-F35C624A7AC4}"/>
+    <hyperlink ref="O55" r:id="rId26" xr:uid="{D04C60CD-E9F0-40B2-BFF1-8E0AB7A9A0EF}"/>
+    <hyperlink ref="O61" r:id="rId27" xr:uid="{DD24637B-8A52-4477-BD1C-DE472004863A}"/>
+    <hyperlink ref="O62:O64" r:id="rId28" display="https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/AQREAN/Annual/SL_BC/daily_aqi_nitrogen_dioxide/info.json" xr:uid="{955E32ED-9CFA-41A4-9D09-5B1D66C2A966}"/>
+    <hyperlink ref="O65" r:id="rId29" xr:uid="{039F5F3E-0910-4EE6-9FE0-7654E10CABAD}"/>
+    <hyperlink ref="O62" r:id="rId30" xr:uid="{373745D5-336B-46AD-BEF0-FF285433016E}"/>
+    <hyperlink ref="O63" r:id="rId31" xr:uid="{356CAD23-03AB-460F-AFCA-EC4BDE2D8AE0}"/>
+    <hyperlink ref="O64" r:id="rId32" xr:uid="{4F6B4081-E0D1-4EF1-825D-2153F4EE3414}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pages/apps/uprn-service/config.xlsx
+++ b/pages/apps/uprn-service/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NDSH\GitHub\dsh-content\pages\apps\uprn-service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39287A48-5298-454A-A7BC-F539CE481AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86DC6B3F-E098-4B35-A206-8FD8BC4483DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="388" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7299,54 +7299,6 @@
     <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/AQREAN/Annual/SL/daily_aqi_nitrogen_dioxide/2011info.json</t>
   </si>
   <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2019info.xml</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2018info.xml</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2017info.xml</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2016info.xml</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2015info.xml</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2014info.xml</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2012info.xml</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2011info.xml</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2010info.xml</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2009info.xml</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2008info.xml</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2007info.xml</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2006info.xml</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2005info.xml</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2004info.xml</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2003info.xml</t>
-  </si>
-  <si>
     <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/AQREAN/Annual/SL/daily_aqi_nitrogen_dioxide/2010info.json</t>
   </si>
   <si>
@@ -8344,6 +8296,54 @@
   </si>
   <si>
     <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/AQREAN/Annual/SL_BC/mc_pm2p5_dry_aerosol_in_air/2003info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2019info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2018info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2017info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2016info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2015info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2014info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2012info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2011info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2010info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2009info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2008info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2007info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2006info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2005info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2004info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/DSH/Annual/SL/daily_aqi_nitrogen_dioxide/2003info.json</t>
   </si>
 </sst>
 </file>
@@ -60348,7 +60348,7 @@
       </c>
       <c r="J1159" s="6"/>
       <c r="L1159" s="3" t="s">
-        <v>2423</v>
+        <v>2756</v>
       </c>
       <c r="M1159">
         <v>2</v>
@@ -60394,7 +60394,7 @@
       </c>
       <c r="J1160" s="6"/>
       <c r="L1160" s="3" t="s">
-        <v>2424</v>
+        <v>2757</v>
       </c>
       <c r="M1160">
         <v>2</v>
@@ -60440,7 +60440,7 @@
       </c>
       <c r="J1161" s="6"/>
       <c r="L1161" s="3" t="s">
-        <v>2425</v>
+        <v>2758</v>
       </c>
       <c r="M1161">
         <v>2</v>
@@ -60486,7 +60486,7 @@
       </c>
       <c r="J1162" s="6"/>
       <c r="L1162" s="3" t="s">
-        <v>2426</v>
+        <v>2759</v>
       </c>
       <c r="M1162">
         <v>2</v>
@@ -60532,7 +60532,7 @@
       </c>
       <c r="J1163" s="6"/>
       <c r="L1163" s="3" t="s">
-        <v>2427</v>
+        <v>2760</v>
       </c>
       <c r="M1163">
         <v>2</v>
@@ -60578,7 +60578,7 @@
       </c>
       <c r="J1164" s="6"/>
       <c r="L1164" s="3" t="s">
-        <v>2428</v>
+        <v>2761</v>
       </c>
       <c r="M1164">
         <v>2</v>
@@ -60624,7 +60624,7 @@
       </c>
       <c r="J1165" s="6"/>
       <c r="L1165" s="3" t="s">
-        <v>2429</v>
+        <v>2762</v>
       </c>
       <c r="M1165">
         <v>2</v>
@@ -60670,7 +60670,7 @@
       </c>
       <c r="J1166" s="6"/>
       <c r="L1166" s="3" t="s">
-        <v>2430</v>
+        <v>2763</v>
       </c>
       <c r="M1166">
         <v>2</v>
@@ -60716,7 +60716,7 @@
       </c>
       <c r="J1167" s="6"/>
       <c r="L1167" s="3" t="s">
-        <v>2431</v>
+        <v>2764</v>
       </c>
       <c r="M1167">
         <v>2</v>
@@ -60762,7 +60762,7 @@
       </c>
       <c r="J1168" s="6"/>
       <c r="L1168" s="3" t="s">
-        <v>2432</v>
+        <v>2765</v>
       </c>
       <c r="M1168">
         <v>2</v>
@@ -60808,7 +60808,7 @@
       </c>
       <c r="J1169" s="6"/>
       <c r="L1169" s="3" t="s">
-        <v>2433</v>
+        <v>2766</v>
       </c>
       <c r="M1169">
         <v>2</v>
@@ -60854,7 +60854,7 @@
       </c>
       <c r="J1170" s="6"/>
       <c r="L1170" s="3" t="s">
-        <v>2434</v>
+        <v>2767</v>
       </c>
       <c r="M1170">
         <v>2</v>
@@ -60900,7 +60900,7 @@
       </c>
       <c r="J1171" s="6"/>
       <c r="L1171" s="3" t="s">
-        <v>2435</v>
+        <v>2768</v>
       </c>
       <c r="M1171">
         <v>2</v>
@@ -60946,7 +60946,7 @@
       </c>
       <c r="J1172" s="6"/>
       <c r="L1172" s="3" t="s">
-        <v>2436</v>
+        <v>2769</v>
       </c>
       <c r="M1172">
         <v>2</v>
@@ -60992,7 +60992,7 @@
       </c>
       <c r="J1173" s="6"/>
       <c r="L1173" s="3" t="s">
-        <v>2437</v>
+        <v>2770</v>
       </c>
       <c r="M1173">
         <v>2</v>
@@ -61038,7 +61038,7 @@
       </c>
       <c r="J1174" s="6"/>
       <c r="L1174" s="3" t="s">
-        <v>2438</v>
+        <v>2771</v>
       </c>
       <c r="M1174">
         <v>2</v>
@@ -61452,7 +61452,7 @@
       </c>
       <c r="J1183" s="6"/>
       <c r="L1183" s="3" t="s">
-        <v>2439</v>
+        <v>2423</v>
       </c>
       <c r="M1183">
         <v>2</v>
@@ -61498,7 +61498,7 @@
       </c>
       <c r="J1184" s="6"/>
       <c r="L1184" s="3" t="s">
-        <v>2440</v>
+        <v>2424</v>
       </c>
       <c r="M1184">
         <v>2</v>
@@ -61544,7 +61544,7 @@
       </c>
       <c r="J1185" s="6"/>
       <c r="L1185" s="3" t="s">
-        <v>2441</v>
+        <v>2425</v>
       </c>
       <c r="M1185">
         <v>2</v>
@@ -61590,7 +61590,7 @@
       </c>
       <c r="J1186" s="6"/>
       <c r="L1186" s="3" t="s">
-        <v>2442</v>
+        <v>2426</v>
       </c>
       <c r="M1186">
         <v>2</v>
@@ -61636,7 +61636,7 @@
       </c>
       <c r="J1187" s="6"/>
       <c r="L1187" s="3" t="s">
-        <v>2443</v>
+        <v>2427</v>
       </c>
       <c r="M1187">
         <v>2</v>
@@ -61682,7 +61682,7 @@
       </c>
       <c r="J1188" s="6"/>
       <c r="L1188" s="3" t="s">
-        <v>2444</v>
+        <v>2428</v>
       </c>
       <c r="M1188">
         <v>2</v>
@@ -61728,7 +61728,7 @@
       </c>
       <c r="J1189" s="6"/>
       <c r="L1189" s="3" t="s">
-        <v>2445</v>
+        <v>2429</v>
       </c>
       <c r="M1189">
         <v>2</v>
@@ -61774,7 +61774,7 @@
       </c>
       <c r="J1190" s="6"/>
       <c r="L1190" s="3" t="s">
-        <v>2446</v>
+        <v>2430</v>
       </c>
       <c r="M1190">
         <v>2</v>
@@ -61820,7 +61820,7 @@
       </c>
       <c r="J1191" s="6"/>
       <c r="L1191" s="3" t="s">
-        <v>2447</v>
+        <v>2431</v>
       </c>
       <c r="M1191">
         <v>2</v>
@@ -61866,7 +61866,7 @@
       </c>
       <c r="J1192" s="6"/>
       <c r="L1192" s="3" t="s">
-        <v>2448</v>
+        <v>2432</v>
       </c>
       <c r="M1192">
         <v>2</v>
@@ -61912,7 +61912,7 @@
       </c>
       <c r="J1193" s="6"/>
       <c r="L1193" s="3" t="s">
-        <v>2449</v>
+        <v>2433</v>
       </c>
       <c r="M1193">
         <v>2</v>
@@ -61958,7 +61958,7 @@
       </c>
       <c r="J1194" s="6"/>
       <c r="L1194" s="3" t="s">
-        <v>2450</v>
+        <v>2434</v>
       </c>
       <c r="M1194">
         <v>2</v>
@@ -62004,7 +62004,7 @@
       </c>
       <c r="J1195" s="6"/>
       <c r="L1195" s="3" t="s">
-        <v>2451</v>
+        <v>2435</v>
       </c>
       <c r="M1195">
         <v>2</v>
@@ -62050,7 +62050,7 @@
       </c>
       <c r="J1196" s="6"/>
       <c r="L1196" s="3" t="s">
-        <v>2452</v>
+        <v>2436</v>
       </c>
       <c r="M1196">
         <v>2</v>
@@ -62096,7 +62096,7 @@
       </c>
       <c r="J1197" s="6"/>
       <c r="L1197" s="3" t="s">
-        <v>2453</v>
+        <v>2437</v>
       </c>
       <c r="M1197">
         <v>2</v>
@@ -62142,7 +62142,7 @@
       </c>
       <c r="J1198" s="6"/>
       <c r="L1198" s="3" t="s">
-        <v>2454</v>
+        <v>2438</v>
       </c>
       <c r="M1198">
         <v>2</v>
@@ -62188,7 +62188,7 @@
       </c>
       <c r="J1199" s="6"/>
       <c r="L1199" s="3" t="s">
-        <v>2455</v>
+        <v>2439</v>
       </c>
       <c r="M1199">
         <v>2</v>
@@ -62234,7 +62234,7 @@
       </c>
       <c r="J1200" s="6"/>
       <c r="L1200" s="3" t="s">
-        <v>2456</v>
+        <v>2440</v>
       </c>
       <c r="M1200">
         <v>2</v>
@@ -62280,7 +62280,7 @@
       </c>
       <c r="J1201" s="6"/>
       <c r="L1201" s="3" t="s">
-        <v>2457</v>
+        <v>2441</v>
       </c>
       <c r="M1201">
         <v>2</v>
@@ -62326,7 +62326,7 @@
       </c>
       <c r="J1202" s="6"/>
       <c r="L1202" s="3" t="s">
-        <v>2458</v>
+        <v>2442</v>
       </c>
       <c r="M1202">
         <v>2</v>
@@ -62372,7 +62372,7 @@
       </c>
       <c r="J1203" s="6"/>
       <c r="L1203" s="3" t="s">
-        <v>2459</v>
+        <v>2443</v>
       </c>
       <c r="M1203">
         <v>2</v>
@@ -62418,7 +62418,7 @@
       </c>
       <c r="J1204" s="6"/>
       <c r="L1204" s="3" t="s">
-        <v>2460</v>
+        <v>2444</v>
       </c>
       <c r="M1204">
         <v>2</v>
@@ -62464,7 +62464,7 @@
       </c>
       <c r="J1205" s="6"/>
       <c r="L1205" s="3" t="s">
-        <v>2461</v>
+        <v>2445</v>
       </c>
       <c r="M1205">
         <v>2</v>
@@ -62510,7 +62510,7 @@
       </c>
       <c r="J1206" s="6"/>
       <c r="L1206" s="3" t="s">
-        <v>2462</v>
+        <v>2446</v>
       </c>
       <c r="M1206">
         <v>2</v>
@@ -62556,7 +62556,7 @@
       </c>
       <c r="J1207" s="6"/>
       <c r="L1207" s="3" t="s">
-        <v>2463</v>
+        <v>2447</v>
       </c>
       <c r="M1207">
         <v>2</v>
@@ -62602,7 +62602,7 @@
       </c>
       <c r="J1208" s="6"/>
       <c r="L1208" s="3" t="s">
-        <v>2464</v>
+        <v>2448</v>
       </c>
       <c r="M1208">
         <v>2</v>
@@ -62648,7 +62648,7 @@
       </c>
       <c r="J1209" s="6"/>
       <c r="L1209" s="3" t="s">
-        <v>2465</v>
+        <v>2449</v>
       </c>
       <c r="M1209">
         <v>2</v>
@@ -62694,7 +62694,7 @@
       </c>
       <c r="J1210" s="6"/>
       <c r="L1210" s="3" t="s">
-        <v>2466</v>
+        <v>2450</v>
       </c>
       <c r="M1210">
         <v>2</v>
@@ -62740,7 +62740,7 @@
       </c>
       <c r="J1211" s="6"/>
       <c r="L1211" s="3" t="s">
-        <v>2467</v>
+        <v>2451</v>
       </c>
       <c r="M1211">
         <v>2</v>
@@ -62786,7 +62786,7 @@
       </c>
       <c r="J1212" s="6"/>
       <c r="L1212" s="3" t="s">
-        <v>2468</v>
+        <v>2452</v>
       </c>
       <c r="M1212">
         <v>2</v>
@@ -62832,7 +62832,7 @@
       </c>
       <c r="J1213" s="6"/>
       <c r="L1213" s="3" t="s">
-        <v>2469</v>
+        <v>2453</v>
       </c>
       <c r="M1213">
         <v>2</v>
@@ -62878,7 +62878,7 @@
       </c>
       <c r="J1214" s="6"/>
       <c r="L1214" s="3" t="s">
-        <v>2470</v>
+        <v>2454</v>
       </c>
       <c r="M1214">
         <v>2</v>
@@ -62924,7 +62924,7 @@
       </c>
       <c r="J1215" s="6"/>
       <c r="L1215" s="3" t="s">
-        <v>2471</v>
+        <v>2455</v>
       </c>
       <c r="M1215">
         <v>2</v>
@@ -62970,7 +62970,7 @@
       </c>
       <c r="J1216" s="6"/>
       <c r="L1216" s="3" t="s">
-        <v>2472</v>
+        <v>2456</v>
       </c>
       <c r="M1216">
         <v>2</v>
@@ -63016,7 +63016,7 @@
       </c>
       <c r="J1217" s="6"/>
       <c r="L1217" s="3" t="s">
-        <v>2473</v>
+        <v>2457</v>
       </c>
       <c r="M1217">
         <v>2</v>
@@ -63062,7 +63062,7 @@
       </c>
       <c r="J1218" s="6"/>
       <c r="L1218" s="3" t="s">
-        <v>2474</v>
+        <v>2458</v>
       </c>
       <c r="M1218">
         <v>2</v>
@@ -63108,7 +63108,7 @@
       </c>
       <c r="J1219" s="6"/>
       <c r="L1219" s="3" t="s">
-        <v>2475</v>
+        <v>2459</v>
       </c>
       <c r="M1219">
         <v>2</v>
@@ -63154,7 +63154,7 @@
       </c>
       <c r="J1220" s="6"/>
       <c r="L1220" s="3" t="s">
-        <v>2476</v>
+        <v>2460</v>
       </c>
       <c r="M1220">
         <v>2</v>
@@ -63200,7 +63200,7 @@
       </c>
       <c r="J1221" s="6"/>
       <c r="L1221" s="3" t="s">
-        <v>2477</v>
+        <v>2461</v>
       </c>
       <c r="M1221">
         <v>2</v>
@@ -63246,7 +63246,7 @@
       </c>
       <c r="J1222" s="6"/>
       <c r="L1222" s="3" t="s">
-        <v>2478</v>
+        <v>2462</v>
       </c>
       <c r="M1222">
         <v>2</v>
@@ -63292,7 +63292,7 @@
       </c>
       <c r="J1223" s="6"/>
       <c r="L1223" s="3" t="s">
-        <v>2479</v>
+        <v>2463</v>
       </c>
       <c r="M1223">
         <v>2</v>
@@ -63338,7 +63338,7 @@
       </c>
       <c r="J1224" s="6"/>
       <c r="L1224" s="3" t="s">
-        <v>2484</v>
+        <v>2468</v>
       </c>
       <c r="M1224">
         <v>2</v>
@@ -63384,7 +63384,7 @@
       </c>
       <c r="J1225" s="6"/>
       <c r="L1225" s="3" t="s">
-        <v>2485</v>
+        <v>2469</v>
       </c>
       <c r="M1225">
         <v>2</v>
@@ -63430,7 +63430,7 @@
       </c>
       <c r="J1226" s="6"/>
       <c r="L1226" s="3" t="s">
-        <v>2486</v>
+        <v>2470</v>
       </c>
       <c r="M1226">
         <v>2</v>
@@ -63476,7 +63476,7 @@
       </c>
       <c r="J1227" s="6"/>
       <c r="L1227" s="3" t="s">
-        <v>2487</v>
+        <v>2471</v>
       </c>
       <c r="M1227">
         <v>2</v>
@@ -63522,7 +63522,7 @@
       </c>
       <c r="J1228" s="6"/>
       <c r="L1228" s="3" t="s">
-        <v>2480</v>
+        <v>2464</v>
       </c>
       <c r="M1228">
         <v>2</v>
@@ -63568,7 +63568,7 @@
       </c>
       <c r="J1229" s="6"/>
       <c r="L1229" s="3" t="s">
-        <v>2481</v>
+        <v>2465</v>
       </c>
       <c r="M1229">
         <v>2</v>
@@ -63614,7 +63614,7 @@
       </c>
       <c r="J1230" s="6"/>
       <c r="L1230" s="3" t="s">
-        <v>2482</v>
+        <v>2466</v>
       </c>
       <c r="M1230">
         <v>2</v>
@@ -63660,7 +63660,7 @@
       </c>
       <c r="J1231" s="6"/>
       <c r="L1231" s="3" t="s">
-        <v>2483</v>
+        <v>2467</v>
       </c>
       <c r="M1231">
         <v>2</v>
@@ -63706,7 +63706,7 @@
       </c>
       <c r="J1232" s="6"/>
       <c r="L1232" s="3" t="s">
-        <v>2488</v>
+        <v>2472</v>
       </c>
       <c r="M1232">
         <v>2</v>
@@ -63752,7 +63752,7 @@
       </c>
       <c r="J1233" s="6"/>
       <c r="L1233" s="3" t="s">
-        <v>2489</v>
+        <v>2473</v>
       </c>
       <c r="M1233">
         <v>2</v>
@@ -63798,7 +63798,7 @@
       </c>
       <c r="J1234" s="6"/>
       <c r="L1234" s="3" t="s">
-        <v>2490</v>
+        <v>2474</v>
       </c>
       <c r="M1234">
         <v>2</v>
@@ -63844,7 +63844,7 @@
       </c>
       <c r="J1235" s="6"/>
       <c r="L1235" s="3" t="s">
-        <v>2491</v>
+        <v>2475</v>
       </c>
       <c r="M1235">
         <v>2</v>
@@ -63890,7 +63890,7 @@
       </c>
       <c r="J1236" s="6"/>
       <c r="L1236" s="3" t="s">
-        <v>2492</v>
+        <v>2476</v>
       </c>
       <c r="M1236">
         <v>2</v>
@@ -63936,7 +63936,7 @@
       </c>
       <c r="J1237" s="6"/>
       <c r="L1237" s="3" t="s">
-        <v>2493</v>
+        <v>2477</v>
       </c>
       <c r="M1237">
         <v>2</v>
@@ -63982,7 +63982,7 @@
       </c>
       <c r="J1238" s="6"/>
       <c r="L1238" s="3" t="s">
-        <v>2494</v>
+        <v>2478</v>
       </c>
       <c r="M1238">
         <v>2</v>
@@ -64028,7 +64028,7 @@
       </c>
       <c r="J1239" s="6"/>
       <c r="L1239" s="3" t="s">
-        <v>2495</v>
+        <v>2479</v>
       </c>
       <c r="M1239">
         <v>2</v>
@@ -64074,7 +64074,7 @@
       </c>
       <c r="J1240" s="6"/>
       <c r="L1240" s="3" t="s">
-        <v>2496</v>
+        <v>2480</v>
       </c>
       <c r="M1240">
         <v>2</v>
@@ -64120,7 +64120,7 @@
       </c>
       <c r="J1241" s="6"/>
       <c r="L1241" s="3" t="s">
-        <v>2499</v>
+        <v>2483</v>
       </c>
       <c r="M1241">
         <v>2</v>
@@ -64166,7 +64166,7 @@
       </c>
       <c r="J1242" s="6"/>
       <c r="L1242" s="3" t="s">
-        <v>2500</v>
+        <v>2484</v>
       </c>
       <c r="M1242">
         <v>2</v>
@@ -64212,7 +64212,7 @@
       </c>
       <c r="J1243" s="6"/>
       <c r="L1243" s="3" t="s">
-        <v>2501</v>
+        <v>2485</v>
       </c>
       <c r="M1243">
         <v>2</v>
@@ -64258,7 +64258,7 @@
       </c>
       <c r="J1244" s="6"/>
       <c r="L1244" s="3" t="s">
-        <v>2502</v>
+        <v>2486</v>
       </c>
       <c r="M1244">
         <v>2</v>
@@ -64304,7 +64304,7 @@
       </c>
       <c r="J1245" s="6"/>
       <c r="L1245" s="3" t="s">
-        <v>2503</v>
+        <v>2487</v>
       </c>
       <c r="M1245">
         <v>2</v>
@@ -64350,7 +64350,7 @@
       </c>
       <c r="J1246" s="6"/>
       <c r="L1246" s="3" t="s">
-        <v>2504</v>
+        <v>2488</v>
       </c>
       <c r="M1246">
         <v>2</v>
@@ -64396,7 +64396,7 @@
       </c>
       <c r="J1247" s="6"/>
       <c r="L1247" s="3" t="s">
-        <v>2505</v>
+        <v>2489</v>
       </c>
       <c r="M1247">
         <v>2</v>
@@ -64442,7 +64442,7 @@
       </c>
       <c r="J1248" s="6"/>
       <c r="L1248" s="3" t="s">
-        <v>2497</v>
+        <v>2481</v>
       </c>
       <c r="M1248">
         <v>2</v>
@@ -64488,7 +64488,7 @@
       </c>
       <c r="J1249" s="6"/>
       <c r="L1249" s="3" t="s">
-        <v>2498</v>
+        <v>2482</v>
       </c>
       <c r="M1249">
         <v>2</v>
@@ -64534,7 +64534,7 @@
       </c>
       <c r="J1250" s="6"/>
       <c r="L1250" s="3" t="s">
-        <v>2506</v>
+        <v>2490</v>
       </c>
       <c r="M1250">
         <v>2</v>
@@ -64580,7 +64580,7 @@
       </c>
       <c r="J1251" s="6"/>
       <c r="L1251" s="3" t="s">
-        <v>2507</v>
+        <v>2491</v>
       </c>
       <c r="M1251">
         <v>2</v>
@@ -64626,7 +64626,7 @@
       </c>
       <c r="J1252" s="6"/>
       <c r="L1252" s="3" t="s">
-        <v>2508</v>
+        <v>2492</v>
       </c>
       <c r="M1252">
         <v>2</v>
@@ -64672,7 +64672,7 @@
       </c>
       <c r="J1253" s="6"/>
       <c r="L1253" s="3" t="s">
-        <v>2509</v>
+        <v>2493</v>
       </c>
       <c r="M1253">
         <v>2</v>
@@ -64718,7 +64718,7 @@
       </c>
       <c r="J1254" s="6"/>
       <c r="L1254" s="3" t="s">
-        <v>2510</v>
+        <v>2494</v>
       </c>
       <c r="M1254">
         <v>2</v>
@@ -64764,7 +64764,7 @@
       </c>
       <c r="J1255" s="6"/>
       <c r="L1255" s="3" t="s">
-        <v>2511</v>
+        <v>2495</v>
       </c>
       <c r="M1255">
         <v>2</v>
@@ -64810,7 +64810,7 @@
       </c>
       <c r="J1256" s="6"/>
       <c r="L1256" s="3" t="s">
-        <v>2516</v>
+        <v>2500</v>
       </c>
       <c r="M1256">
         <v>2</v>
@@ -64856,7 +64856,7 @@
       </c>
       <c r="J1257" s="6"/>
       <c r="L1257" s="3" t="s">
-        <v>2517</v>
+        <v>2501</v>
       </c>
       <c r="M1257">
         <v>2</v>
@@ -64902,7 +64902,7 @@
       </c>
       <c r="J1258" s="6"/>
       <c r="L1258" s="3" t="s">
-        <v>2518</v>
+        <v>2502</v>
       </c>
       <c r="M1258">
         <v>2</v>
@@ -64948,7 +64948,7 @@
       </c>
       <c r="J1259" s="6"/>
       <c r="L1259" s="3" t="s">
-        <v>2519</v>
+        <v>2503</v>
       </c>
       <c r="M1259">
         <v>2</v>
@@ -64994,7 +64994,7 @@
       </c>
       <c r="J1260" s="6"/>
       <c r="L1260" s="3" t="s">
-        <v>2512</v>
+        <v>2496</v>
       </c>
       <c r="M1260">
         <v>2</v>
@@ -65040,7 +65040,7 @@
       </c>
       <c r="J1261" s="6"/>
       <c r="L1261" s="3" t="s">
-        <v>2513</v>
+        <v>2497</v>
       </c>
       <c r="M1261">
         <v>2</v>
@@ -65086,7 +65086,7 @@
       </c>
       <c r="J1262" s="6"/>
       <c r="L1262" s="3" t="s">
-        <v>2514</v>
+        <v>2498</v>
       </c>
       <c r="M1262">
         <v>2</v>
@@ -65132,7 +65132,7 @@
       </c>
       <c r="J1263" s="6"/>
       <c r="L1263" s="3" t="s">
-        <v>2515</v>
+        <v>2499</v>
       </c>
       <c r="M1263">
         <v>2</v>
@@ -65178,7 +65178,7 @@
       </c>
       <c r="J1264" s="6"/>
       <c r="L1264" s="3" t="s">
-        <v>2520</v>
+        <v>2504</v>
       </c>
       <c r="M1264">
         <v>2</v>
@@ -65224,7 +65224,7 @@
       </c>
       <c r="J1265" s="6"/>
       <c r="L1265" s="3" t="s">
-        <v>2521</v>
+        <v>2505</v>
       </c>
       <c r="M1265">
         <v>2</v>
@@ -65270,7 +65270,7 @@
       </c>
       <c r="J1266" s="6"/>
       <c r="L1266" s="3" t="s">
-        <v>2522</v>
+        <v>2506</v>
       </c>
       <c r="M1266">
         <v>2</v>
@@ -65316,7 +65316,7 @@
       </c>
       <c r="J1267" s="6"/>
       <c r="L1267" s="3" t="s">
-        <v>2523</v>
+        <v>2507</v>
       </c>
       <c r="M1267">
         <v>2</v>
@@ -65362,7 +65362,7 @@
       </c>
       <c r="J1268" s="6"/>
       <c r="L1268" s="3" t="s">
-        <v>2524</v>
+        <v>2508</v>
       </c>
       <c r="M1268">
         <v>2</v>
@@ -65408,7 +65408,7 @@
       </c>
       <c r="J1269" s="6"/>
       <c r="L1269" s="3" t="s">
-        <v>2525</v>
+        <v>2509</v>
       </c>
       <c r="M1269">
         <v>2</v>
@@ -65454,7 +65454,7 @@
       </c>
       <c r="J1270" s="6"/>
       <c r="L1270" s="3" t="s">
-        <v>2526</v>
+        <v>2510</v>
       </c>
       <c r="M1270">
         <v>2</v>
@@ -65500,7 +65500,7 @@
       </c>
       <c r="J1271" s="6"/>
       <c r="L1271" s="3" t="s">
-        <v>2527</v>
+        <v>2511</v>
       </c>
       <c r="M1271">
         <v>2</v>
@@ -65546,7 +65546,7 @@
       </c>
       <c r="J1272" s="6"/>
       <c r="L1272" s="3" t="s">
-        <v>2528</v>
+        <v>2512</v>
       </c>
       <c r="M1272">
         <v>2</v>
@@ -65592,7 +65592,7 @@
       </c>
       <c r="J1273" s="6"/>
       <c r="L1273" s="3" t="s">
-        <v>2529</v>
+        <v>2513</v>
       </c>
       <c r="M1273">
         <v>2</v>
@@ -65638,7 +65638,7 @@
       </c>
       <c r="J1274" s="6"/>
       <c r="L1274" s="3" t="s">
-        <v>2530</v>
+        <v>2514</v>
       </c>
       <c r="M1274">
         <v>2</v>
@@ -65684,7 +65684,7 @@
       </c>
       <c r="J1275" s="6"/>
       <c r="L1275" s="3" t="s">
-        <v>2531</v>
+        <v>2515</v>
       </c>
       <c r="M1275">
         <v>2</v>
@@ -65730,7 +65730,7 @@
       </c>
       <c r="J1276" s="6"/>
       <c r="L1276" s="3" t="s">
-        <v>2532</v>
+        <v>2516</v>
       </c>
       <c r="M1276">
         <v>2</v>
@@ -65776,7 +65776,7 @@
       </c>
       <c r="J1277" s="6"/>
       <c r="L1277" s="3" t="s">
-        <v>2533</v>
+        <v>2517</v>
       </c>
       <c r="M1277">
         <v>2</v>
@@ -65822,7 +65822,7 @@
       </c>
       <c r="J1278" s="6"/>
       <c r="L1278" s="3" t="s">
-        <v>2534</v>
+        <v>2518</v>
       </c>
       <c r="M1278">
         <v>2</v>
@@ -65868,7 +65868,7 @@
       </c>
       <c r="J1279" s="6"/>
       <c r="L1279" s="3" t="s">
-        <v>2535</v>
+        <v>2519</v>
       </c>
       <c r="M1279">
         <v>2</v>
@@ -65914,7 +65914,7 @@
       </c>
       <c r="J1280" s="6"/>
       <c r="L1280" s="3" t="s">
-        <v>2536</v>
+        <v>2520</v>
       </c>
       <c r="M1280">
         <v>2</v>
@@ -65960,7 +65960,7 @@
       </c>
       <c r="J1281" s="6"/>
       <c r="L1281" s="3" t="s">
-        <v>2537</v>
+        <v>2521</v>
       </c>
       <c r="M1281">
         <v>2</v>
@@ -66006,7 +66006,7 @@
       </c>
       <c r="J1282" s="6"/>
       <c r="L1282" s="3" t="s">
-        <v>2538</v>
+        <v>2522</v>
       </c>
       <c r="M1282">
         <v>2</v>
@@ -66052,7 +66052,7 @@
       </c>
       <c r="J1283" s="6"/>
       <c r="L1283" s="3" t="s">
-        <v>2539</v>
+        <v>2523</v>
       </c>
       <c r="M1283">
         <v>2</v>
@@ -66098,7 +66098,7 @@
       </c>
       <c r="J1284" s="6"/>
       <c r="L1284" s="3" t="s">
-        <v>2540</v>
+        <v>2524</v>
       </c>
       <c r="M1284">
         <v>2</v>
@@ -66144,7 +66144,7 @@
       </c>
       <c r="J1285" s="6"/>
       <c r="L1285" s="3" t="s">
-        <v>2541</v>
+        <v>2525</v>
       </c>
       <c r="M1285">
         <v>2</v>
@@ -66190,7 +66190,7 @@
       </c>
       <c r="J1286" s="6"/>
       <c r="L1286" s="3" t="s">
-        <v>2542</v>
+        <v>2526</v>
       </c>
       <c r="M1286">
         <v>2</v>
@@ -66236,7 +66236,7 @@
       </c>
       <c r="J1287" s="6"/>
       <c r="L1287" s="3" t="s">
-        <v>2543</v>
+        <v>2527</v>
       </c>
       <c r="M1287">
         <v>2</v>
@@ -66282,7 +66282,7 @@
       </c>
       <c r="J1288" s="6"/>
       <c r="L1288" s="3" t="s">
-        <v>2544</v>
+        <v>2528</v>
       </c>
       <c r="M1288">
         <v>2</v>
@@ -66328,7 +66328,7 @@
       </c>
       <c r="J1289" s="6"/>
       <c r="L1289" s="3" t="s">
-        <v>2545</v>
+        <v>2529</v>
       </c>
       <c r="M1289">
         <v>2</v>
@@ -66374,7 +66374,7 @@
       </c>
       <c r="J1290" s="6"/>
       <c r="L1290" s="3" t="s">
-        <v>2546</v>
+        <v>2530</v>
       </c>
       <c r="M1290">
         <v>2</v>
@@ -66420,7 +66420,7 @@
       </c>
       <c r="J1291" s="6"/>
       <c r="L1291" s="3" t="s">
-        <v>2547</v>
+        <v>2531</v>
       </c>
       <c r="M1291">
         <v>2</v>
@@ -66466,7 +66466,7 @@
       </c>
       <c r="J1292" s="6"/>
       <c r="L1292" s="3" t="s">
-        <v>2548</v>
+        <v>2532</v>
       </c>
       <c r="M1292">
         <v>2</v>
@@ -66512,7 +66512,7 @@
       </c>
       <c r="J1293" s="6"/>
       <c r="L1293" s="3" t="s">
-        <v>2549</v>
+        <v>2533</v>
       </c>
       <c r="M1293">
         <v>2</v>
@@ -66558,7 +66558,7 @@
       </c>
       <c r="J1294" s="6"/>
       <c r="L1294" s="3" t="s">
-        <v>2550</v>
+        <v>2534</v>
       </c>
       <c r="M1294">
         <v>2</v>
@@ -66604,7 +66604,7 @@
       </c>
       <c r="J1295" s="6"/>
       <c r="L1295" s="3" t="s">
-        <v>2558</v>
+        <v>2542</v>
       </c>
       <c r="M1295">
         <v>2</v>
@@ -66650,7 +66650,7 @@
       </c>
       <c r="J1296" s="6"/>
       <c r="L1296" s="3" t="s">
-        <v>2551</v>
+        <v>2535</v>
       </c>
       <c r="M1296">
         <v>2</v>
@@ -66696,7 +66696,7 @@
       </c>
       <c r="J1297" s="6"/>
       <c r="L1297" s="3" t="s">
-        <v>2552</v>
+        <v>2536</v>
       </c>
       <c r="M1297">
         <v>2</v>
@@ -66742,7 +66742,7 @@
       </c>
       <c r="J1298" s="6"/>
       <c r="L1298" s="3" t="s">
-        <v>2553</v>
+        <v>2537</v>
       </c>
       <c r="M1298">
         <v>2</v>
@@ -66788,7 +66788,7 @@
       </c>
       <c r="J1299" s="6"/>
       <c r="L1299" s="3" t="s">
-        <v>2554</v>
+        <v>2538</v>
       </c>
       <c r="M1299">
         <v>2</v>
@@ -66834,7 +66834,7 @@
       </c>
       <c r="J1300" s="6"/>
       <c r="L1300" s="3" t="s">
-        <v>2555</v>
+        <v>2539</v>
       </c>
       <c r="M1300">
         <v>2</v>
@@ -66880,7 +66880,7 @@
       </c>
       <c r="J1301" s="6"/>
       <c r="L1301" s="3" t="s">
-        <v>2556</v>
+        <v>2540</v>
       </c>
       <c r="M1301">
         <v>2</v>
@@ -66926,7 +66926,7 @@
       </c>
       <c r="J1302" s="6"/>
       <c r="L1302" s="3" t="s">
-        <v>2557</v>
+        <v>2541</v>
       </c>
       <c r="M1302">
         <v>2</v>
@@ -66972,7 +66972,7 @@
       </c>
       <c r="J1303" s="6"/>
       <c r="L1303" s="3" t="s">
-        <v>2559</v>
+        <v>2543</v>
       </c>
       <c r="M1303">
         <v>2</v>
@@ -67018,7 +67018,7 @@
       </c>
       <c r="J1304" s="6"/>
       <c r="L1304" s="3" t="s">
-        <v>2560</v>
+        <v>2544</v>
       </c>
       <c r="M1304">
         <v>2</v>
@@ -67064,7 +67064,7 @@
       </c>
       <c r="J1305" s="6"/>
       <c r="L1305" s="3" t="s">
-        <v>2561</v>
+        <v>2545</v>
       </c>
       <c r="M1305">
         <v>2</v>
@@ -67110,7 +67110,7 @@
       </c>
       <c r="J1306" s="6"/>
       <c r="L1306" s="3" t="s">
-        <v>2562</v>
+        <v>2546</v>
       </c>
       <c r="M1306">
         <v>2</v>
@@ -67156,7 +67156,7 @@
       </c>
       <c r="J1307" s="6"/>
       <c r="L1307" s="3" t="s">
-        <v>2563</v>
+        <v>2547</v>
       </c>
       <c r="M1307">
         <v>2</v>
@@ -67202,7 +67202,7 @@
       </c>
       <c r="J1308" s="6"/>
       <c r="L1308" s="3" t="s">
-        <v>2564</v>
+        <v>2548</v>
       </c>
       <c r="M1308">
         <v>2</v>
@@ -67248,7 +67248,7 @@
       </c>
       <c r="J1309" s="6"/>
       <c r="L1309" s="3" t="s">
-        <v>2565</v>
+        <v>2549</v>
       </c>
       <c r="M1309">
         <v>2</v>
@@ -67294,7 +67294,7 @@
       </c>
       <c r="J1310" s="6"/>
       <c r="L1310" s="3" t="s">
-        <v>2566</v>
+        <v>2550</v>
       </c>
       <c r="M1310">
         <v>2</v>
@@ -67340,7 +67340,7 @@
       </c>
       <c r="J1311" s="6"/>
       <c r="L1311" s="3" t="s">
-        <v>2567</v>
+        <v>2551</v>
       </c>
       <c r="M1311">
         <v>2</v>
@@ -67386,7 +67386,7 @@
       </c>
       <c r="J1312" s="6"/>
       <c r="L1312" s="3" t="s">
-        <v>2568</v>
+        <v>2552</v>
       </c>
       <c r="M1312">
         <v>2</v>
@@ -67432,7 +67432,7 @@
       </c>
       <c r="J1313" s="6"/>
       <c r="L1313" s="3" t="s">
-        <v>2569</v>
+        <v>2553</v>
       </c>
       <c r="M1313">
         <v>2</v>
@@ -67478,7 +67478,7 @@
       </c>
       <c r="J1314" s="6"/>
       <c r="L1314" s="3" t="s">
-        <v>2570</v>
+        <v>2554</v>
       </c>
       <c r="M1314">
         <v>2</v>
@@ -67524,7 +67524,7 @@
       </c>
       <c r="J1315" s="6"/>
       <c r="L1315" s="3" t="s">
-        <v>2571</v>
+        <v>2555</v>
       </c>
       <c r="M1315">
         <v>2</v>
@@ -67570,7 +67570,7 @@
       </c>
       <c r="J1316" s="6"/>
       <c r="L1316" s="3" t="s">
-        <v>2572</v>
+        <v>2556</v>
       </c>
       <c r="M1316">
         <v>2</v>
@@ -67616,7 +67616,7 @@
       </c>
       <c r="J1317" s="6"/>
       <c r="L1317" s="3" t="s">
-        <v>2573</v>
+        <v>2557</v>
       </c>
       <c r="M1317">
         <v>2</v>
@@ -67662,7 +67662,7 @@
       </c>
       <c r="J1318" s="6"/>
       <c r="L1318" s="3" t="s">
-        <v>2574</v>
+        <v>2558</v>
       </c>
       <c r="M1318">
         <v>2</v>
@@ -67708,7 +67708,7 @@
       </c>
       <c r="J1319" s="6"/>
       <c r="L1319" s="3" t="s">
-        <v>2575</v>
+        <v>2559</v>
       </c>
       <c r="M1319">
         <v>2</v>
@@ -67754,7 +67754,7 @@
       </c>
       <c r="J1320" s="6"/>
       <c r="L1320" s="3" t="s">
-        <v>2576</v>
+        <v>2560</v>
       </c>
       <c r="M1320">
         <v>2</v>
@@ -67800,7 +67800,7 @@
       </c>
       <c r="J1321" s="6"/>
       <c r="L1321" s="3" t="s">
-        <v>2577</v>
+        <v>2561</v>
       </c>
       <c r="M1321">
         <v>2</v>
@@ -67846,7 +67846,7 @@
       </c>
       <c r="J1322" s="6"/>
       <c r="L1322" s="3" t="s">
-        <v>2578</v>
+        <v>2562</v>
       </c>
       <c r="M1322">
         <v>2</v>
@@ -67892,7 +67892,7 @@
       </c>
       <c r="J1323" s="6"/>
       <c r="L1323" s="3" t="s">
-        <v>2579</v>
+        <v>2563</v>
       </c>
       <c r="M1323">
         <v>2</v>
@@ -67938,7 +67938,7 @@
       </c>
       <c r="J1324" s="6"/>
       <c r="L1324" s="3" t="s">
-        <v>2580</v>
+        <v>2564</v>
       </c>
       <c r="M1324">
         <v>2</v>
@@ -67984,7 +67984,7 @@
       </c>
       <c r="J1325" s="6"/>
       <c r="L1325" s="3" t="s">
-        <v>2581</v>
+        <v>2565</v>
       </c>
       <c r="M1325">
         <v>2</v>
@@ -68030,7 +68030,7 @@
       </c>
       <c r="J1326" s="6"/>
       <c r="L1326" s="3" t="s">
-        <v>2582</v>
+        <v>2566</v>
       </c>
       <c r="M1326">
         <v>2</v>
@@ -68076,7 +68076,7 @@
       </c>
       <c r="J1327" s="6"/>
       <c r="L1327" s="3" t="s">
-        <v>2588</v>
+        <v>2572</v>
       </c>
       <c r="M1327">
         <v>2</v>
@@ -68122,7 +68122,7 @@
       </c>
       <c r="J1328" s="6"/>
       <c r="L1328" s="3" t="s">
-        <v>2583</v>
+        <v>2567</v>
       </c>
       <c r="M1328">
         <v>2</v>
@@ -68168,7 +68168,7 @@
       </c>
       <c r="J1329" s="6"/>
       <c r="L1329" s="3" t="s">
-        <v>2584</v>
+        <v>2568</v>
       </c>
       <c r="M1329">
         <v>2</v>
@@ -68214,7 +68214,7 @@
       </c>
       <c r="J1330" s="6"/>
       <c r="L1330" s="3" t="s">
-        <v>2585</v>
+        <v>2569</v>
       </c>
       <c r="M1330">
         <v>2</v>
@@ -68260,7 +68260,7 @@
       </c>
       <c r="J1331" s="6"/>
       <c r="L1331" s="3" t="s">
-        <v>2586</v>
+        <v>2570</v>
       </c>
       <c r="M1331">
         <v>2</v>
@@ -68306,7 +68306,7 @@
       </c>
       <c r="J1332" s="6"/>
       <c r="L1332" s="3" t="s">
-        <v>2587</v>
+        <v>2571</v>
       </c>
       <c r="M1332">
         <v>2</v>
@@ -68352,7 +68352,7 @@
       </c>
       <c r="J1333" s="6"/>
       <c r="L1333" s="3" t="s">
-        <v>2589</v>
+        <v>2573</v>
       </c>
       <c r="M1333">
         <v>2</v>
@@ -68398,7 +68398,7 @@
       </c>
       <c r="J1334" s="6"/>
       <c r="L1334" s="3" t="s">
-        <v>2590</v>
+        <v>2574</v>
       </c>
       <c r="M1334">
         <v>2</v>
@@ -68444,7 +68444,7 @@
       </c>
       <c r="J1335" s="6"/>
       <c r="L1335" s="3" t="s">
-        <v>2591</v>
+        <v>2575</v>
       </c>
       <c r="M1335">
         <v>2</v>
@@ -68490,7 +68490,7 @@
       </c>
       <c r="J1336" s="6"/>
       <c r="L1336" s="3" t="s">
-        <v>2592</v>
+        <v>2576</v>
       </c>
       <c r="M1336">
         <v>2</v>
@@ -68536,7 +68536,7 @@
       </c>
       <c r="J1337" s="6"/>
       <c r="L1337" s="3" t="s">
-        <v>2601</v>
+        <v>2585</v>
       </c>
       <c r="M1337">
         <v>2</v>
@@ -68582,7 +68582,7 @@
       </c>
       <c r="J1338" s="6"/>
       <c r="L1338" s="3" t="s">
-        <v>2602</v>
+        <v>2586</v>
       </c>
       <c r="M1338">
         <v>2</v>
@@ -68628,7 +68628,7 @@
       </c>
       <c r="J1339" s="6"/>
       <c r="L1339" s="3" t="s">
-        <v>2603</v>
+        <v>2587</v>
       </c>
       <c r="M1339">
         <v>2</v>
@@ -68674,7 +68674,7 @@
       </c>
       <c r="J1340" s="6"/>
       <c r="L1340" s="3" t="s">
-        <v>2604</v>
+        <v>2588</v>
       </c>
       <c r="M1340">
         <v>2</v>
@@ -68720,7 +68720,7 @@
       </c>
       <c r="J1341" s="6"/>
       <c r="L1341" s="3" t="s">
-        <v>2605</v>
+        <v>2589</v>
       </c>
       <c r="M1341">
         <v>2</v>
@@ -68766,7 +68766,7 @@
       </c>
       <c r="J1342" s="6"/>
       <c r="L1342" s="3" t="s">
-        <v>2606</v>
+        <v>2590</v>
       </c>
       <c r="M1342">
         <v>2</v>
@@ -68812,7 +68812,7 @@
       </c>
       <c r="J1343" s="6"/>
       <c r="L1343" s="3" t="s">
-        <v>2593</v>
+        <v>2577</v>
       </c>
       <c r="M1343">
         <v>2</v>
@@ -68858,7 +68858,7 @@
       </c>
       <c r="J1344" s="6"/>
       <c r="L1344" s="3" t="s">
-        <v>2594</v>
+        <v>2578</v>
       </c>
       <c r="M1344">
         <v>2</v>
@@ -68904,7 +68904,7 @@
       </c>
       <c r="J1345" s="6"/>
       <c r="L1345" s="3" t="s">
-        <v>2595</v>
+        <v>2579</v>
       </c>
       <c r="M1345">
         <v>2</v>
@@ -68950,7 +68950,7 @@
       </c>
       <c r="J1346" s="6"/>
       <c r="L1346" s="3" t="s">
-        <v>2596</v>
+        <v>2580</v>
       </c>
       <c r="M1346">
         <v>2</v>
@@ -68996,7 +68996,7 @@
       </c>
       <c r="J1347" s="6"/>
       <c r="L1347" s="3" t="s">
-        <v>2597</v>
+        <v>2581</v>
       </c>
       <c r="M1347">
         <v>2</v>
@@ -69042,7 +69042,7 @@
       </c>
       <c r="J1348" s="6"/>
       <c r="L1348" s="3" t="s">
-        <v>2598</v>
+        <v>2582</v>
       </c>
       <c r="M1348">
         <v>2</v>
@@ -69088,7 +69088,7 @@
       </c>
       <c r="J1349" s="6"/>
       <c r="L1349" s="3" t="s">
-        <v>2599</v>
+        <v>2583</v>
       </c>
       <c r="M1349">
         <v>2</v>
@@ -69134,7 +69134,7 @@
       </c>
       <c r="J1350" s="6"/>
       <c r="L1350" s="3" t="s">
-        <v>2600</v>
+        <v>2584</v>
       </c>
       <c r="M1350">
         <v>2</v>
@@ -69180,7 +69180,7 @@
       </c>
       <c r="J1351" s="6"/>
       <c r="L1351" s="3" t="s">
-        <v>2607</v>
+        <v>2591</v>
       </c>
       <c r="M1351">
         <v>2</v>
@@ -69226,7 +69226,7 @@
       </c>
       <c r="J1352" s="6"/>
       <c r="L1352" s="3" t="s">
-        <v>2608</v>
+        <v>2592</v>
       </c>
       <c r="M1352">
         <v>2</v>
@@ -69272,7 +69272,7 @@
       </c>
       <c r="J1353" s="6"/>
       <c r="L1353" s="3" t="s">
-        <v>2611</v>
+        <v>2595</v>
       </c>
       <c r="M1353">
         <v>2</v>
@@ -69318,7 +69318,7 @@
       </c>
       <c r="J1354" s="6"/>
       <c r="L1354" s="3" t="s">
-        <v>2612</v>
+        <v>2596</v>
       </c>
       <c r="M1354">
         <v>2</v>
@@ -69364,7 +69364,7 @@
       </c>
       <c r="J1355" s="6"/>
       <c r="L1355" s="3" t="s">
-        <v>2613</v>
+        <v>2597</v>
       </c>
       <c r="M1355">
         <v>2</v>
@@ -69410,7 +69410,7 @@
       </c>
       <c r="J1356" s="6"/>
       <c r="L1356" s="3" t="s">
-        <v>2614</v>
+        <v>2598</v>
       </c>
       <c r="M1356">
         <v>2</v>
@@ -69456,7 +69456,7 @@
       </c>
       <c r="J1357" s="6"/>
       <c r="L1357" s="3" t="s">
-        <v>2615</v>
+        <v>2599</v>
       </c>
       <c r="M1357">
         <v>2</v>
@@ -69502,7 +69502,7 @@
       </c>
       <c r="J1358" s="6"/>
       <c r="L1358" s="3" t="s">
-        <v>2616</v>
+        <v>2600</v>
       </c>
       <c r="M1358">
         <v>2</v>
@@ -69548,7 +69548,7 @@
       </c>
       <c r="J1359" s="6"/>
       <c r="L1359" s="3" t="s">
-        <v>2609</v>
+        <v>2593</v>
       </c>
       <c r="M1359">
         <v>2</v>
@@ -69594,7 +69594,7 @@
       </c>
       <c r="J1360" s="6"/>
       <c r="L1360" s="3" t="s">
-        <v>2610</v>
+        <v>2594</v>
       </c>
       <c r="M1360">
         <v>2</v>
@@ -69640,7 +69640,7 @@
       </c>
       <c r="J1361" s="6"/>
       <c r="L1361" s="3" t="s">
-        <v>2617</v>
+        <v>2601</v>
       </c>
       <c r="M1361">
         <v>2</v>
@@ -69686,7 +69686,7 @@
       </c>
       <c r="J1362" s="6"/>
       <c r="L1362" s="3" t="s">
-        <v>2618</v>
+        <v>2602</v>
       </c>
       <c r="M1362">
         <v>2</v>
@@ -69732,7 +69732,7 @@
       </c>
       <c r="J1363" s="6"/>
       <c r="L1363" s="3" t="s">
-        <v>2619</v>
+        <v>2603</v>
       </c>
       <c r="M1363">
         <v>2</v>
@@ -69778,7 +69778,7 @@
       </c>
       <c r="J1364" s="6"/>
       <c r="L1364" s="3" t="s">
-        <v>2620</v>
+        <v>2604</v>
       </c>
       <c r="M1364">
         <v>2</v>
@@ -69824,7 +69824,7 @@
       </c>
       <c r="J1365" s="6"/>
       <c r="L1365" s="3" t="s">
-        <v>2621</v>
+        <v>2605</v>
       </c>
       <c r="M1365">
         <v>2</v>
@@ -69870,7 +69870,7 @@
       </c>
       <c r="J1366" s="6"/>
       <c r="L1366" s="3" t="s">
-        <v>2622</v>
+        <v>2606</v>
       </c>
       <c r="M1366">
         <v>2</v>
@@ -69916,7 +69916,7 @@
       </c>
       <c r="J1367" s="6"/>
       <c r="L1367" s="3" t="s">
-        <v>2623</v>
+        <v>2607</v>
       </c>
       <c r="M1367">
         <v>2</v>
@@ -69962,7 +69962,7 @@
       </c>
       <c r="J1368" s="6"/>
       <c r="L1368" s="3" t="s">
-        <v>2624</v>
+        <v>2608</v>
       </c>
       <c r="M1368">
         <v>2</v>
@@ -70008,7 +70008,7 @@
       </c>
       <c r="J1369" s="6"/>
       <c r="L1369" s="3" t="s">
-        <v>2625</v>
+        <v>2609</v>
       </c>
       <c r="M1369">
         <v>2</v>
@@ -70054,7 +70054,7 @@
       </c>
       <c r="J1370" s="6"/>
       <c r="L1370" s="3" t="s">
-        <v>2626</v>
+        <v>2610</v>
       </c>
       <c r="M1370">
         <v>2</v>
@@ -70100,7 +70100,7 @@
       </c>
       <c r="J1371" s="6"/>
       <c r="L1371" s="3" t="s">
-        <v>2627</v>
+        <v>2611</v>
       </c>
       <c r="M1371">
         <v>2</v>
@@ -70146,7 +70146,7 @@
       </c>
       <c r="J1372" s="6"/>
       <c r="L1372" s="3" t="s">
-        <v>2628</v>
+        <v>2612</v>
       </c>
       <c r="M1372">
         <v>2</v>
@@ -70192,7 +70192,7 @@
       </c>
       <c r="J1373" s="6"/>
       <c r="L1373" s="3" t="s">
-        <v>2629</v>
+        <v>2613</v>
       </c>
       <c r="M1373">
         <v>2</v>
@@ -70238,7 +70238,7 @@
       </c>
       <c r="J1374" s="6"/>
       <c r="L1374" s="3" t="s">
-        <v>2630</v>
+        <v>2614</v>
       </c>
       <c r="M1374">
         <v>2</v>
@@ -70284,7 +70284,7 @@
       </c>
       <c r="J1375" s="6"/>
       <c r="L1375" s="3" t="s">
-        <v>2631</v>
+        <v>2615</v>
       </c>
       <c r="M1375">
         <v>2</v>
@@ -70330,7 +70330,7 @@
       </c>
       <c r="J1376" s="6"/>
       <c r="L1376" s="3" t="s">
-        <v>2632</v>
+        <v>2616</v>
       </c>
       <c r="M1376">
         <v>2</v>
@@ -70376,7 +70376,7 @@
       </c>
       <c r="J1377" s="6"/>
       <c r="L1377" s="3" t="s">
-        <v>2633</v>
+        <v>2617</v>
       </c>
       <c r="M1377">
         <v>2</v>
@@ -70422,7 +70422,7 @@
       </c>
       <c r="J1378" s="6"/>
       <c r="L1378" s="3" t="s">
-        <v>2635</v>
+        <v>2619</v>
       </c>
       <c r="M1378">
         <v>2</v>
@@ -70468,7 +70468,7 @@
       </c>
       <c r="J1379" s="6"/>
       <c r="L1379" s="3" t="s">
-        <v>2636</v>
+        <v>2620</v>
       </c>
       <c r="M1379">
         <v>2</v>
@@ -70514,7 +70514,7 @@
       </c>
       <c r="J1380" s="6"/>
       <c r="L1380" s="3" t="s">
-        <v>2637</v>
+        <v>2621</v>
       </c>
       <c r="M1380">
         <v>2</v>
@@ -70560,7 +70560,7 @@
       </c>
       <c r="J1381" s="6"/>
       <c r="L1381" s="3" t="s">
-        <v>2638</v>
+        <v>2622</v>
       </c>
       <c r="M1381">
         <v>2</v>
@@ -70606,7 +70606,7 @@
       </c>
       <c r="J1382" s="6"/>
       <c r="L1382" s="3" t="s">
-        <v>2634</v>
+        <v>2618</v>
       </c>
       <c r="M1382">
         <v>2</v>
@@ -70652,7 +70652,7 @@
       </c>
       <c r="J1383" s="6"/>
       <c r="L1383" s="3" t="s">
-        <v>2639</v>
+        <v>2623</v>
       </c>
       <c r="M1383">
         <v>2</v>
@@ -70698,7 +70698,7 @@
       </c>
       <c r="J1384" s="6"/>
       <c r="L1384" s="3" t="s">
-        <v>2640</v>
+        <v>2624</v>
       </c>
       <c r="M1384">
         <v>2</v>
@@ -70744,7 +70744,7 @@
       </c>
       <c r="J1385" s="6"/>
       <c r="L1385" s="3" t="s">
-        <v>2649</v>
+        <v>2633</v>
       </c>
       <c r="M1385">
         <v>2</v>
@@ -70790,7 +70790,7 @@
       </c>
       <c r="J1386" s="6"/>
       <c r="L1386" s="3" t="s">
-        <v>2650</v>
+        <v>2634</v>
       </c>
       <c r="M1386">
         <v>2</v>
@@ -70836,7 +70836,7 @@
       </c>
       <c r="J1387" s="6"/>
       <c r="L1387" s="3" t="s">
-        <v>2651</v>
+        <v>2635</v>
       </c>
       <c r="M1387">
         <v>2</v>
@@ -70882,7 +70882,7 @@
       </c>
       <c r="J1388" s="6"/>
       <c r="L1388" s="3" t="s">
-        <v>2652</v>
+        <v>2636</v>
       </c>
       <c r="M1388">
         <v>2</v>
@@ -70928,7 +70928,7 @@
       </c>
       <c r="J1389" s="6"/>
       <c r="L1389" s="3" t="s">
-        <v>2653</v>
+        <v>2637</v>
       </c>
       <c r="M1389">
         <v>2</v>
@@ -70974,7 +70974,7 @@
       </c>
       <c r="J1390" s="6"/>
       <c r="L1390" s="3" t="s">
-        <v>2654</v>
+        <v>2638</v>
       </c>
       <c r="M1390">
         <v>2</v>
@@ -71020,7 +71020,7 @@
       </c>
       <c r="J1391" s="6"/>
       <c r="L1391" s="3" t="s">
-        <v>2641</v>
+        <v>2625</v>
       </c>
       <c r="M1391">
         <v>2</v>
@@ -71066,7 +71066,7 @@
       </c>
       <c r="J1392" s="6"/>
       <c r="L1392" s="3" t="s">
-        <v>2642</v>
+        <v>2626</v>
       </c>
       <c r="M1392">
         <v>2</v>
@@ -71112,7 +71112,7 @@
       </c>
       <c r="J1393" s="6"/>
       <c r="L1393" s="3" t="s">
-        <v>2643</v>
+        <v>2627</v>
       </c>
       <c r="M1393">
         <v>2</v>
@@ -71158,7 +71158,7 @@
       </c>
       <c r="J1394" s="6"/>
       <c r="L1394" s="3" t="s">
-        <v>2644</v>
+        <v>2628</v>
       </c>
       <c r="M1394">
         <v>2</v>
@@ -71204,7 +71204,7 @@
       </c>
       <c r="J1395" s="6"/>
       <c r="L1395" s="3" t="s">
-        <v>2645</v>
+        <v>2629</v>
       </c>
       <c r="M1395">
         <v>2</v>
@@ -71250,7 +71250,7 @@
       </c>
       <c r="J1396" s="6"/>
       <c r="L1396" s="3" t="s">
-        <v>2646</v>
+        <v>2630</v>
       </c>
       <c r="M1396">
         <v>2</v>
@@ -71296,7 +71296,7 @@
       </c>
       <c r="J1397" s="6"/>
       <c r="L1397" s="3" t="s">
-        <v>2647</v>
+        <v>2631</v>
       </c>
       <c r="M1397">
         <v>2</v>
@@ -71342,7 +71342,7 @@
       </c>
       <c r="J1398" s="6"/>
       <c r="L1398" s="3" t="s">
-        <v>2648</v>
+        <v>2632</v>
       </c>
       <c r="M1398">
         <v>2</v>
@@ -71388,7 +71388,7 @@
       </c>
       <c r="J1399" s="6"/>
       <c r="L1399" s="3" t="s">
-        <v>2655</v>
+        <v>2639</v>
       </c>
       <c r="M1399">
         <v>2</v>
@@ -71434,7 +71434,7 @@
       </c>
       <c r="J1400" s="6"/>
       <c r="L1400" s="3" t="s">
-        <v>2656</v>
+        <v>2640</v>
       </c>
       <c r="M1400">
         <v>2</v>
@@ -71480,7 +71480,7 @@
       </c>
       <c r="J1401" s="6"/>
       <c r="L1401" s="3" t="s">
-        <v>2657</v>
+        <v>2641</v>
       </c>
       <c r="M1401">
         <v>2</v>
@@ -71526,7 +71526,7 @@
       </c>
       <c r="J1402" s="6"/>
       <c r="L1402" s="3" t="s">
-        <v>2658</v>
+        <v>2642</v>
       </c>
       <c r="M1402">
         <v>2</v>
@@ -71572,7 +71572,7 @@
       </c>
       <c r="J1403" s="6"/>
       <c r="L1403" s="3" t="s">
-        <v>2659</v>
+        <v>2643</v>
       </c>
       <c r="M1403">
         <v>2</v>
@@ -71618,7 +71618,7 @@
       </c>
       <c r="J1404" s="6"/>
       <c r="L1404" s="3" t="s">
-        <v>2660</v>
+        <v>2644</v>
       </c>
       <c r="M1404">
         <v>2</v>
@@ -71664,7 +71664,7 @@
       </c>
       <c r="J1405" s="6"/>
       <c r="L1405" s="3" t="s">
-        <v>2664</v>
+        <v>2648</v>
       </c>
       <c r="M1405">
         <v>2</v>
@@ -71710,7 +71710,7 @@
       </c>
       <c r="J1406" s="6"/>
       <c r="L1406" s="3" t="s">
-        <v>2665</v>
+        <v>2649</v>
       </c>
       <c r="M1406">
         <v>2</v>
@@ -71756,7 +71756,7 @@
       </c>
       <c r="J1407" s="6"/>
       <c r="L1407" s="3" t="s">
-        <v>2666</v>
+        <v>2650</v>
       </c>
       <c r="M1407">
         <v>2</v>
@@ -71802,7 +71802,7 @@
       </c>
       <c r="J1408" s="6"/>
       <c r="L1408" s="3" t="s">
-        <v>2661</v>
+        <v>2645</v>
       </c>
       <c r="M1408">
         <v>2</v>
@@ -71848,7 +71848,7 @@
       </c>
       <c r="J1409" s="6"/>
       <c r="L1409" s="3" t="s">
-        <v>2662</v>
+        <v>2646</v>
       </c>
       <c r="M1409">
         <v>2</v>
@@ -71894,7 +71894,7 @@
       </c>
       <c r="J1410" s="6"/>
       <c r="L1410" s="3" t="s">
-        <v>2663</v>
+        <v>2647</v>
       </c>
       <c r="M1410">
         <v>2</v>
@@ -71940,7 +71940,7 @@
       </c>
       <c r="J1411" s="6"/>
       <c r="L1411" s="3" t="s">
-        <v>2668</v>
+        <v>2652</v>
       </c>
       <c r="M1411">
         <v>2</v>
@@ -71986,7 +71986,7 @@
       </c>
       <c r="J1412" s="6"/>
       <c r="L1412" s="3" t="s">
-        <v>2669</v>
+        <v>2653</v>
       </c>
       <c r="M1412">
         <v>2</v>
@@ -72032,7 +72032,7 @@
       </c>
       <c r="J1413" s="6"/>
       <c r="L1413" s="3" t="s">
-        <v>2670</v>
+        <v>2654</v>
       </c>
       <c r="M1413">
         <v>2</v>
@@ -72078,7 +72078,7 @@
       </c>
       <c r="J1414" s="6"/>
       <c r="L1414" s="3" t="s">
-        <v>2667</v>
+        <v>2651</v>
       </c>
       <c r="M1414">
         <v>2</v>
@@ -72124,7 +72124,7 @@
       </c>
       <c r="J1415" s="6"/>
       <c r="L1415" s="3" t="s">
-        <v>2671</v>
+        <v>2655</v>
       </c>
       <c r="M1415">
         <v>2</v>
@@ -72170,7 +72170,7 @@
       </c>
       <c r="J1416" s="6"/>
       <c r="L1416" s="3" t="s">
-        <v>2672</v>
+        <v>2656</v>
       </c>
       <c r="M1416">
         <v>2</v>
@@ -72216,7 +72216,7 @@
       </c>
       <c r="J1417" s="6"/>
       <c r="L1417" s="3" t="s">
-        <v>2677</v>
+        <v>2661</v>
       </c>
       <c r="M1417">
         <v>2</v>
@@ -72262,7 +72262,7 @@
       </c>
       <c r="J1418" s="6"/>
       <c r="L1418" s="3" t="s">
-        <v>2678</v>
+        <v>2662</v>
       </c>
       <c r="M1418">
         <v>2</v>
@@ -72308,7 +72308,7 @@
       </c>
       <c r="J1419" s="6"/>
       <c r="L1419" s="3" t="s">
-        <v>2679</v>
+        <v>2663</v>
       </c>
       <c r="M1419">
         <v>2</v>
@@ -72354,7 +72354,7 @@
       </c>
       <c r="J1420" s="6"/>
       <c r="L1420" s="3" t="s">
-        <v>2680</v>
+        <v>2664</v>
       </c>
       <c r="M1420">
         <v>2</v>
@@ -72400,7 +72400,7 @@
       </c>
       <c r="J1421" s="6"/>
       <c r="L1421" s="3" t="s">
-        <v>2681</v>
+        <v>2665</v>
       </c>
       <c r="M1421">
         <v>2</v>
@@ -72446,7 +72446,7 @@
       </c>
       <c r="J1422" s="6"/>
       <c r="L1422" s="3" t="s">
-        <v>2673</v>
+        <v>2657</v>
       </c>
       <c r="M1422">
         <v>2</v>
@@ -72492,7 +72492,7 @@
       </c>
       <c r="J1423" s="6"/>
       <c r="L1423" s="3" t="s">
-        <v>2674</v>
+        <v>2658</v>
       </c>
       <c r="M1423">
         <v>2</v>
@@ -72538,7 +72538,7 @@
       </c>
       <c r="J1424" s="6"/>
       <c r="L1424" s="3" t="s">
-        <v>2675</v>
+        <v>2659</v>
       </c>
       <c r="M1424">
         <v>2</v>
@@ -72584,7 +72584,7 @@
       </c>
       <c r="J1425" s="6"/>
       <c r="L1425" s="3" t="s">
-        <v>2676</v>
+        <v>2660</v>
       </c>
       <c r="M1425">
         <v>2</v>
@@ -72630,7 +72630,7 @@
       </c>
       <c r="J1426" s="6"/>
       <c r="L1426" s="3" t="s">
-        <v>2684</v>
+        <v>2668</v>
       </c>
       <c r="M1426">
         <v>2</v>
@@ -72676,7 +72676,7 @@
       </c>
       <c r="J1427" s="6"/>
       <c r="L1427" s="3" t="s">
-        <v>2685</v>
+        <v>2669</v>
       </c>
       <c r="M1427">
         <v>2</v>
@@ -72722,7 +72722,7 @@
       </c>
       <c r="J1428" s="6"/>
       <c r="L1428" s="3" t="s">
-        <v>2686</v>
+        <v>2670</v>
       </c>
       <c r="M1428">
         <v>2</v>
@@ -72768,7 +72768,7 @@
       </c>
       <c r="J1429" s="6"/>
       <c r="L1429" s="3" t="s">
-        <v>2682</v>
+        <v>2666</v>
       </c>
       <c r="M1429">
         <v>2</v>
@@ -72814,7 +72814,7 @@
       </c>
       <c r="J1430" s="6"/>
       <c r="L1430" s="3" t="s">
-        <v>2683</v>
+        <v>2667</v>
       </c>
       <c r="M1430">
         <v>2</v>
@@ -72860,7 +72860,7 @@
       </c>
       <c r="J1431" s="6"/>
       <c r="L1431" s="3" t="s">
-        <v>2687</v>
+        <v>2671</v>
       </c>
       <c r="M1431">
         <v>2</v>
@@ -72906,7 +72906,7 @@
       </c>
       <c r="J1432" s="6"/>
       <c r="L1432" s="3" t="s">
-        <v>2688</v>
+        <v>2672</v>
       </c>
       <c r="M1432">
         <v>2</v>
@@ -72952,7 +72952,7 @@
       </c>
       <c r="J1433" s="6"/>
       <c r="L1433" s="3" t="s">
-        <v>2689</v>
+        <v>2673</v>
       </c>
       <c r="M1433">
         <v>2</v>
@@ -72998,7 +72998,7 @@
       </c>
       <c r="J1434" s="6"/>
       <c r="L1434" s="3" t="s">
-        <v>2690</v>
+        <v>2674</v>
       </c>
       <c r="M1434">
         <v>2</v>
@@ -73044,7 +73044,7 @@
       </c>
       <c r="J1435" s="6"/>
       <c r="L1435" s="3" t="s">
-        <v>2691</v>
+        <v>2675</v>
       </c>
       <c r="M1435">
         <v>2</v>
@@ -73090,7 +73090,7 @@
       </c>
       <c r="J1436" s="6"/>
       <c r="L1436" s="3" t="s">
-        <v>2692</v>
+        <v>2676</v>
       </c>
       <c r="M1436">
         <v>2</v>
@@ -73136,7 +73136,7 @@
       </c>
       <c r="J1437" s="6"/>
       <c r="L1437" s="3" t="s">
-        <v>2693</v>
+        <v>2677</v>
       </c>
       <c r="M1437">
         <v>2</v>
@@ -73182,7 +73182,7 @@
       </c>
       <c r="J1438" s="6"/>
       <c r="L1438" s="3" t="s">
-        <v>2694</v>
+        <v>2678</v>
       </c>
       <c r="M1438">
         <v>2</v>
@@ -73228,7 +73228,7 @@
       </c>
       <c r="J1439" s="6"/>
       <c r="L1439" s="3" t="s">
-        <v>2695</v>
+        <v>2679</v>
       </c>
       <c r="M1439">
         <v>2</v>
@@ -73274,7 +73274,7 @@
       </c>
       <c r="J1440" s="6"/>
       <c r="L1440" s="3" t="s">
-        <v>2696</v>
+        <v>2680</v>
       </c>
       <c r="M1440">
         <v>2</v>
@@ -73320,7 +73320,7 @@
       </c>
       <c r="J1441" s="6"/>
       <c r="L1441" s="3" t="s">
-        <v>2697</v>
+        <v>2681</v>
       </c>
       <c r="M1441">
         <v>2</v>
@@ -73366,7 +73366,7 @@
       </c>
       <c r="J1442" s="6"/>
       <c r="L1442" s="3" t="s">
-        <v>2698</v>
+        <v>2682</v>
       </c>
       <c r="M1442">
         <v>2</v>
@@ -73412,7 +73412,7 @@
       </c>
       <c r="J1443" s="6"/>
       <c r="L1443" s="3" t="s">
-        <v>2699</v>
+        <v>2683</v>
       </c>
       <c r="M1443">
         <v>2</v>
@@ -73458,7 +73458,7 @@
       </c>
       <c r="J1444" s="6"/>
       <c r="L1444" s="3" t="s">
-        <v>2700</v>
+        <v>2684</v>
       </c>
       <c r="M1444">
         <v>2</v>
@@ -73504,7 +73504,7 @@
       </c>
       <c r="J1445" s="6"/>
       <c r="L1445" s="3" t="s">
-        <v>2701</v>
+        <v>2685</v>
       </c>
       <c r="M1445">
         <v>2</v>
@@ -73550,7 +73550,7 @@
       </c>
       <c r="J1446" s="6"/>
       <c r="L1446" s="3" t="s">
-        <v>2702</v>
+        <v>2686</v>
       </c>
       <c r="M1446">
         <v>2</v>
@@ -73596,7 +73596,7 @@
       </c>
       <c r="J1447" s="6"/>
       <c r="L1447" s="3" t="s">
-        <v>2703</v>
+        <v>2687</v>
       </c>
       <c r="M1447">
         <v>2</v>
@@ -73642,7 +73642,7 @@
       </c>
       <c r="J1448" s="6"/>
       <c r="L1448" s="3" t="s">
-        <v>2704</v>
+        <v>2688</v>
       </c>
       <c r="M1448">
         <v>2</v>
@@ -73688,7 +73688,7 @@
       </c>
       <c r="J1449" s="6"/>
       <c r="L1449" s="3" t="s">
-        <v>2705</v>
+        <v>2689</v>
       </c>
       <c r="M1449">
         <v>2</v>
@@ -73734,7 +73734,7 @@
       </c>
       <c r="J1450" s="6"/>
       <c r="L1450" s="3" t="s">
-        <v>2706</v>
+        <v>2690</v>
       </c>
       <c r="M1450">
         <v>2</v>
@@ -73780,7 +73780,7 @@
       </c>
       <c r="J1451" s="6"/>
       <c r="L1451" s="3" t="s">
-        <v>2707</v>
+        <v>2691</v>
       </c>
       <c r="M1451">
         <v>2</v>
@@ -73826,7 +73826,7 @@
       </c>
       <c r="J1452" s="6"/>
       <c r="L1452" s="3" t="s">
-        <v>2708</v>
+        <v>2692</v>
       </c>
       <c r="M1452">
         <v>2</v>
@@ -73872,7 +73872,7 @@
       </c>
       <c r="J1453" s="6"/>
       <c r="L1453" s="3" t="s">
-        <v>2709</v>
+        <v>2693</v>
       </c>
       <c r="M1453">
         <v>2</v>
@@ -73918,7 +73918,7 @@
       </c>
       <c r="J1454" s="6"/>
       <c r="L1454" s="3" t="s">
-        <v>2710</v>
+        <v>2694</v>
       </c>
       <c r="M1454">
         <v>2</v>
@@ -73964,7 +73964,7 @@
       </c>
       <c r="J1455" s="6"/>
       <c r="L1455" s="3" t="s">
-        <v>2711</v>
+        <v>2695</v>
       </c>
       <c r="M1455">
         <v>2</v>
@@ -74010,7 +74010,7 @@
       </c>
       <c r="J1456" s="6"/>
       <c r="L1456" s="3" t="s">
-        <v>2712</v>
+        <v>2696</v>
       </c>
       <c r="M1456">
         <v>2</v>
@@ -74056,7 +74056,7 @@
       </c>
       <c r="J1457" s="6"/>
       <c r="L1457" s="3" t="s">
-        <v>2713</v>
+        <v>2697</v>
       </c>
       <c r="M1457">
         <v>2</v>
@@ -74102,7 +74102,7 @@
       </c>
       <c r="J1458" s="6"/>
       <c r="L1458" s="3" t="s">
-        <v>2714</v>
+        <v>2698</v>
       </c>
       <c r="M1458">
         <v>2</v>
@@ -74148,7 +74148,7 @@
       </c>
       <c r="J1459" s="6"/>
       <c r="L1459" s="3" t="s">
-        <v>2715</v>
+        <v>2699</v>
       </c>
       <c r="M1459">
         <v>2</v>
@@ -74194,7 +74194,7 @@
       </c>
       <c r="J1460" s="6"/>
       <c r="L1460" s="3" t="s">
-        <v>2716</v>
+        <v>2700</v>
       </c>
       <c r="M1460">
         <v>2</v>
@@ -74240,7 +74240,7 @@
       </c>
       <c r="J1461" s="6"/>
       <c r="L1461" s="3" t="s">
-        <v>2717</v>
+        <v>2701</v>
       </c>
       <c r="M1461">
         <v>2</v>
@@ -74286,7 +74286,7 @@
       </c>
       <c r="J1462" s="6"/>
       <c r="L1462" s="3" t="s">
-        <v>2718</v>
+        <v>2702</v>
       </c>
       <c r="M1462">
         <v>2</v>
@@ -74332,7 +74332,7 @@
       </c>
       <c r="J1463" s="6"/>
       <c r="L1463" s="3" t="s">
-        <v>2719</v>
+        <v>2703</v>
       </c>
       <c r="M1463">
         <v>2</v>
@@ -74378,7 +74378,7 @@
       </c>
       <c r="J1464" s="6"/>
       <c r="L1464" s="3" t="s">
-        <v>2720</v>
+        <v>2704</v>
       </c>
       <c r="M1464">
         <v>2</v>
@@ -74424,7 +74424,7 @@
       </c>
       <c r="J1465" s="6"/>
       <c r="L1465" s="3" t="s">
-        <v>2721</v>
+        <v>2705</v>
       </c>
       <c r="M1465">
         <v>2</v>
@@ -74470,7 +74470,7 @@
       </c>
       <c r="J1466" s="6"/>
       <c r="L1466" s="3" t="s">
-        <v>2722</v>
+        <v>2706</v>
       </c>
       <c r="M1466">
         <v>2</v>
@@ -74516,7 +74516,7 @@
       </c>
       <c r="J1467" s="6"/>
       <c r="L1467" s="3" t="s">
-        <v>2726</v>
+        <v>2710</v>
       </c>
       <c r="M1467">
         <v>2</v>
@@ -74562,7 +74562,7 @@
       </c>
       <c r="J1468" s="6"/>
       <c r="L1468" s="3" t="s">
-        <v>2727</v>
+        <v>2711</v>
       </c>
       <c r="M1468">
         <v>2</v>
@@ -74608,7 +74608,7 @@
       </c>
       <c r="J1469" s="6"/>
       <c r="L1469" s="3" t="s">
-        <v>2728</v>
+        <v>2712</v>
       </c>
       <c r="M1469">
         <v>2</v>
@@ -74654,7 +74654,7 @@
       </c>
       <c r="J1470" s="6"/>
       <c r="L1470" s="3" t="s">
-        <v>2723</v>
+        <v>2707</v>
       </c>
       <c r="M1470">
         <v>2</v>
@@ -74700,7 +74700,7 @@
       </c>
       <c r="J1471" s="6"/>
       <c r="L1471" s="3" t="s">
-        <v>2724</v>
+        <v>2708</v>
       </c>
       <c r="M1471">
         <v>2</v>
@@ -74746,7 +74746,7 @@
       </c>
       <c r="J1472" s="6"/>
       <c r="L1472" s="3" t="s">
-        <v>2725</v>
+        <v>2709</v>
       </c>
       <c r="M1472">
         <v>2</v>
@@ -74792,7 +74792,7 @@
       </c>
       <c r="J1473" s="6"/>
       <c r="L1473" s="3" t="s">
-        <v>2729</v>
+        <v>2713</v>
       </c>
       <c r="M1473">
         <v>2</v>
@@ -74838,7 +74838,7 @@
       </c>
       <c r="J1474" s="6"/>
       <c r="L1474" s="3" t="s">
-        <v>2730</v>
+        <v>2714</v>
       </c>
       <c r="M1474">
         <v>2</v>
@@ -74884,7 +74884,7 @@
       </c>
       <c r="J1475" s="6"/>
       <c r="L1475" s="3" t="s">
-        <v>2731</v>
+        <v>2715</v>
       </c>
       <c r="M1475">
         <v>2</v>
@@ -74930,7 +74930,7 @@
       </c>
       <c r="J1476" s="6"/>
       <c r="L1476" s="3" t="s">
-        <v>2732</v>
+        <v>2716</v>
       </c>
       <c r="M1476">
         <v>2</v>
@@ -74976,7 +74976,7 @@
       </c>
       <c r="J1477" s="6"/>
       <c r="L1477" s="3" t="s">
-        <v>2733</v>
+        <v>2717</v>
       </c>
       <c r="M1477">
         <v>2</v>
@@ -75022,7 +75022,7 @@
       </c>
       <c r="J1478" s="6"/>
       <c r="L1478" s="3" t="s">
-        <v>2734</v>
+        <v>2718</v>
       </c>
       <c r="M1478">
         <v>2</v>
@@ -75068,7 +75068,7 @@
       </c>
       <c r="J1479" s="6"/>
       <c r="L1479" s="3" t="s">
-        <v>2735</v>
+        <v>2719</v>
       </c>
       <c r="M1479">
         <v>2</v>
@@ -75114,7 +75114,7 @@
       </c>
       <c r="J1480" s="6"/>
       <c r="L1480" s="3" t="s">
-        <v>2736</v>
+        <v>2720</v>
       </c>
       <c r="M1480">
         <v>2</v>
@@ -75160,7 +75160,7 @@
       </c>
       <c r="J1481" s="6"/>
       <c r="L1481" s="3" t="s">
-        <v>2737</v>
+        <v>2721</v>
       </c>
       <c r="M1481">
         <v>2</v>
@@ -75206,7 +75206,7 @@
       </c>
       <c r="J1482" s="6"/>
       <c r="L1482" s="3" t="s">
-        <v>2738</v>
+        <v>2722</v>
       </c>
       <c r="M1482">
         <v>2</v>
@@ -75252,7 +75252,7 @@
       </c>
       <c r="J1483" s="6"/>
       <c r="L1483" s="3" t="s">
-        <v>2739</v>
+        <v>2723</v>
       </c>
       <c r="M1483">
         <v>2</v>
@@ -75298,7 +75298,7 @@
       </c>
       <c r="J1484" s="6"/>
       <c r="L1484" s="3" t="s">
-        <v>2740</v>
+        <v>2724</v>
       </c>
       <c r="M1484">
         <v>2</v>
@@ -75344,7 +75344,7 @@
       </c>
       <c r="J1485" s="6"/>
       <c r="L1485" s="3" t="s">
-        <v>2741</v>
+        <v>2725</v>
       </c>
       <c r="M1485">
         <v>2</v>
@@ -75390,7 +75390,7 @@
       </c>
       <c r="J1486" s="6"/>
       <c r="L1486" s="3" t="s">
-        <v>2742</v>
+        <v>2726</v>
       </c>
       <c r="M1486">
         <v>2</v>
@@ -75436,7 +75436,7 @@
       </c>
       <c r="J1487" s="6"/>
       <c r="L1487" s="3" t="s">
-        <v>2743</v>
+        <v>2727</v>
       </c>
       <c r="M1487">
         <v>2</v>
@@ -75482,7 +75482,7 @@
       </c>
       <c r="J1488" s="6"/>
       <c r="L1488" s="3" t="s">
-        <v>2744</v>
+        <v>2728</v>
       </c>
       <c r="M1488">
         <v>2</v>
@@ -75528,7 +75528,7 @@
       </c>
       <c r="J1489" s="6"/>
       <c r="L1489" s="3" t="s">
-        <v>2745</v>
+        <v>2729</v>
       </c>
       <c r="M1489">
         <v>2</v>
@@ -75574,7 +75574,7 @@
       </c>
       <c r="J1490" s="6"/>
       <c r="L1490" s="3" t="s">
-        <v>2746</v>
+        <v>2730</v>
       </c>
       <c r="M1490">
         <v>2</v>
@@ -75620,7 +75620,7 @@
       </c>
       <c r="J1491" s="6"/>
       <c r="L1491" s="3" t="s">
-        <v>2747</v>
+        <v>2731</v>
       </c>
       <c r="M1491">
         <v>2</v>
@@ -75666,7 +75666,7 @@
       </c>
       <c r="J1492" s="6"/>
       <c r="L1492" s="3" t="s">
-        <v>2748</v>
+        <v>2732</v>
       </c>
       <c r="M1492">
         <v>2</v>
@@ -75712,7 +75712,7 @@
       </c>
       <c r="J1493" s="6"/>
       <c r="L1493" s="3" t="s">
-        <v>2749</v>
+        <v>2733</v>
       </c>
       <c r="M1493">
         <v>2</v>
@@ -75758,7 +75758,7 @@
       </c>
       <c r="J1494" s="6"/>
       <c r="L1494" s="3" t="s">
-        <v>2750</v>
+        <v>2734</v>
       </c>
       <c r="M1494">
         <v>2</v>
@@ -75804,7 +75804,7 @@
       </c>
       <c r="J1495" s="6"/>
       <c r="L1495" s="3" t="s">
-        <v>2751</v>
+        <v>2735</v>
       </c>
       <c r="M1495">
         <v>2</v>
@@ -75850,7 +75850,7 @@
       </c>
       <c r="J1496" s="6"/>
       <c r="L1496" s="3" t="s">
-        <v>2752</v>
+        <v>2736</v>
       </c>
       <c r="M1496">
         <v>2</v>
@@ -75896,7 +75896,7 @@
       </c>
       <c r="J1497" s="6"/>
       <c r="L1497" s="3" t="s">
-        <v>2753</v>
+        <v>2737</v>
       </c>
       <c r="M1497">
         <v>2</v>
@@ -75942,7 +75942,7 @@
       </c>
       <c r="J1498" s="6"/>
       <c r="L1498" s="3" t="s">
-        <v>2754</v>
+        <v>2738</v>
       </c>
       <c r="M1498">
         <v>2</v>
@@ -75988,7 +75988,7 @@
       </c>
       <c r="J1499" s="6"/>
       <c r="L1499" s="3" t="s">
-        <v>2755</v>
+        <v>2739</v>
       </c>
       <c r="M1499">
         <v>2</v>
@@ -76034,7 +76034,7 @@
       </c>
       <c r="J1500" s="6"/>
       <c r="L1500" s="3" t="s">
-        <v>2756</v>
+        <v>2740</v>
       </c>
       <c r="M1500">
         <v>2</v>
@@ -76080,7 +76080,7 @@
       </c>
       <c r="J1501" s="6"/>
       <c r="L1501" s="3" t="s">
-        <v>2757</v>
+        <v>2741</v>
       </c>
       <c r="M1501">
         <v>2</v>
@@ -76126,7 +76126,7 @@
       </c>
       <c r="J1502" s="6"/>
       <c r="L1502" s="3" t="s">
-        <v>2758</v>
+        <v>2742</v>
       </c>
       <c r="M1502">
         <v>2</v>
@@ -76172,7 +76172,7 @@
       </c>
       <c r="J1503" s="6"/>
       <c r="L1503" s="3" t="s">
-        <v>2759</v>
+        <v>2743</v>
       </c>
       <c r="M1503">
         <v>2</v>
@@ -76218,7 +76218,7 @@
       </c>
       <c r="J1504" s="6"/>
       <c r="L1504" s="3" t="s">
-        <v>2760</v>
+        <v>2744</v>
       </c>
       <c r="M1504">
         <v>2</v>
@@ -76264,7 +76264,7 @@
       </c>
       <c r="J1505" s="6"/>
       <c r="L1505" s="3" t="s">
-        <v>2761</v>
+        <v>2745</v>
       </c>
       <c r="M1505">
         <v>2</v>
@@ -76310,7 +76310,7 @@
       </c>
       <c r="J1506" s="6"/>
       <c r="L1506" s="3" t="s">
-        <v>2764</v>
+        <v>2748</v>
       </c>
       <c r="M1506">
         <v>2</v>
@@ -76356,7 +76356,7 @@
       </c>
       <c r="J1507" s="6"/>
       <c r="L1507" s="3" t="s">
-        <v>2762</v>
+        <v>2746</v>
       </c>
       <c r="M1507">
         <v>2</v>
@@ -76402,7 +76402,7 @@
       </c>
       <c r="J1508" s="6"/>
       <c r="L1508" s="3" t="s">
-        <v>2763</v>
+        <v>2747</v>
       </c>
       <c r="M1508">
         <v>2</v>
@@ -76448,7 +76448,7 @@
       </c>
       <c r="J1509" s="6"/>
       <c r="L1509" s="3" t="s">
-        <v>2765</v>
+        <v>2749</v>
       </c>
       <c r="M1509">
         <v>2</v>
@@ -76494,7 +76494,7 @@
       </c>
       <c r="J1510" s="6"/>
       <c r="L1510" s="3" t="s">
-        <v>2766</v>
+        <v>2750</v>
       </c>
       <c r="M1510">
         <v>2</v>
@@ -76540,7 +76540,7 @@
       </c>
       <c r="J1511" s="6"/>
       <c r="L1511" s="3" t="s">
-        <v>2767</v>
+        <v>2751</v>
       </c>
       <c r="M1511">
         <v>2</v>
@@ -76586,7 +76586,7 @@
       </c>
       <c r="J1512" s="6"/>
       <c r="L1512" s="3" t="s">
-        <v>2768</v>
+        <v>2752</v>
       </c>
       <c r="M1512">
         <v>2</v>
@@ -76632,7 +76632,7 @@
       </c>
       <c r="J1513" s="6"/>
       <c r="L1513" s="3" t="s">
-        <v>2769</v>
+        <v>2753</v>
       </c>
       <c r="M1513">
         <v>2</v>
@@ -76678,7 +76678,7 @@
       </c>
       <c r="J1514" s="6"/>
       <c r="L1514" s="3" t="s">
-        <v>2770</v>
+        <v>2754</v>
       </c>
       <c r="M1514">
         <v>2</v>
@@ -76724,7 +76724,7 @@
       </c>
       <c r="J1515" s="6"/>
       <c r="L1515" s="3" t="s">
-        <v>2771</v>
+        <v>2755</v>
       </c>
       <c r="M1515">
         <v>2</v>

--- a/pages/apps/uprn-service/config.xlsx
+++ b/pages/apps/uprn-service/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NDSH\GitHub\dsh-content\dev\pages\apps\uprn-service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A972FF9B-E520-47FD-814A-14A692BB127F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BA40EF4-E13E-46B0-8E19-04844816C4E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="388" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5959" uniqueCount="2781">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5959" uniqueCount="2780">
   <si>
     <t>DbId</t>
   </si>
@@ -7159,9 +7159,6 @@
   </si>
   <si>
     <t>UK Air - Modelled Background Pollution</t>
-  </si>
-  <si>
-    <t>AQREAN Surface Level</t>
   </si>
   <si>
     <t>objectid15</t>
@@ -9012,7 +9009,7 @@
         <v>4000</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="I6">
         <v>2</v>
@@ -9023,7 +9020,7 @@
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>2769</v>
+        <v>2768</v>
       </c>
       <c r="C7" t="b">
         <v>1</v>
@@ -9035,7 +9032,7 @@
         <v>79</v>
       </c>
       <c r="F7" t="s">
-        <v>2377</v>
+        <v>2768</v>
       </c>
       <c r="G7">
         <v>7000</v>
@@ -9049,19 +9046,19 @@
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
+        <v>2770</v>
+      </c>
+      <c r="C8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
         <v>2771</v>
       </c>
-      <c r="C8" t="b">
-        <v>1</v>
-      </c>
-      <c r="D8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
-        <v>2772</v>
-      </c>
       <c r="F8" t="s">
-        <v>2771</v>
+        <v>2770</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -9069,7 +9066,7 @@
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>2770</v>
+        <v>2769</v>
       </c>
       <c r="C9" t="b">
         <v>1</v>
@@ -9078,10 +9075,10 @@
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>2772</v>
+        <v>2771</v>
       </c>
       <c r="F9" t="s">
-        <v>2770</v>
+        <v>2769</v>
       </c>
       <c r="G9">
         <v>100</v>
@@ -9095,7 +9092,7 @@
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>2773</v>
+        <v>2772</v>
       </c>
       <c r="C10" t="b">
         <v>1</v>
@@ -9104,15 +9101,15 @@
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>2775</v>
+        <v>2774</v>
       </c>
       <c r="F10" t="s">
-        <v>2773</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>2773</v>
+        <v>2772</v>
       </c>
       <c r="C11" t="b">
         <v>1</v>
@@ -9121,32 +9118,32 @@
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>2776</v>
+        <v>2775</v>
       </c>
       <c r="F11" t="s">
-        <v>2773</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
+        <v>2773</v>
+      </c>
+      <c r="C12" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
         <v>2774</v>
       </c>
-      <c r="C12" t="b">
-        <v>1</v>
-      </c>
-      <c r="D12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
-        <v>2775</v>
-      </c>
       <c r="F12" t="s">
-        <v>2774</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>2774</v>
+        <v>2773</v>
       </c>
       <c r="C13" t="b">
         <v>1</v>
@@ -9155,10 +9152,10 @@
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>2776</v>
+        <v>2775</v>
       </c>
       <c r="F13" t="s">
-        <v>2774</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.3">
@@ -9374,7 +9371,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
@@ -9430,7 +9427,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
@@ -9486,7 +9483,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.3">
@@ -11261,7 +11258,7 @@
         <v>183</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
@@ -11370,7 +11367,7 @@
         <v>194</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -11391,7 +11388,7 @@
         <v>6000</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="P40">
         <v>2</v>
@@ -11488,7 +11485,7 @@
         <v>2</v>
       </c>
       <c r="K42" t="s">
-        <v>2775</v>
+        <v>2774</v>
       </c>
       <c r="L42" t="s">
         <v>204</v>
@@ -11532,7 +11529,7 @@
         <v>208</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -11544,7 +11541,7 @@
         <v>2</v>
       </c>
       <c r="K43" t="s">
-        <v>2777</v>
+        <v>2776</v>
       </c>
       <c r="L43" t="s">
         <v>209</v>
@@ -11553,7 +11550,7 @@
         <v>7002</v>
       </c>
       <c r="O43" s="3" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="P43">
         <v>2</v>
@@ -11591,7 +11588,7 @@
         <v>213</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -11603,7 +11600,7 @@
         <v>2</v>
       </c>
       <c r="K44" t="s">
-        <v>2777</v>
+        <v>2776</v>
       </c>
       <c r="L44" t="s">
         <v>214</v>
@@ -11612,7 +11609,7 @@
         <v>7003</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="P44">
         <v>2</v>
@@ -11650,7 +11647,7 @@
         <v>218</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -11662,7 +11659,7 @@
         <v>2</v>
       </c>
       <c r="K45" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="L45" t="s">
         <v>219</v>
@@ -11671,7 +11668,7 @@
         <v>7004</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
       <c r="P45">
         <v>2</v>
@@ -11709,7 +11706,7 @@
         <v>223</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -11721,7 +11718,7 @@
         <v>2</v>
       </c>
       <c r="K46" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="L46" t="s">
         <v>224</v>
@@ -11730,7 +11727,7 @@
         <v>7005</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
       <c r="P46">
         <v>2</v>
@@ -11768,7 +11765,7 @@
         <v>228</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -11780,7 +11777,7 @@
         <v>2</v>
       </c>
       <c r="K47" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="L47" t="s">
         <v>229</v>
@@ -11789,7 +11786,7 @@
         <v>7006</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="P47">
         <v>2</v>
@@ -11827,7 +11824,7 @@
         <v>233</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -11839,7 +11836,7 @@
         <v>2</v>
       </c>
       <c r="K48" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="L48" t="s">
         <v>234</v>
@@ -11848,7 +11845,7 @@
         <v>7007</v>
       </c>
       <c r="O48" s="3" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="P48">
         <v>2</v>
@@ -11886,7 +11883,7 @@
         <v>238</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -11898,7 +11895,7 @@
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="L49" t="s">
         <v>239</v>
@@ -11907,7 +11904,7 @@
         <v>7008</v>
       </c>
       <c r="O49" s="3" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
       <c r="P49">
         <v>2</v>
@@ -11945,7 +11942,7 @@
         <v>243</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
@@ -11957,7 +11954,7 @@
         <v>2</v>
       </c>
       <c r="K50" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="L50" t="s">
         <v>244</v>
@@ -11966,7 +11963,7 @@
         <v>7009</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="P50">
         <v>2</v>
@@ -12004,7 +12001,7 @@
         <v>248</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -12016,7 +12013,7 @@
         <v>2</v>
       </c>
       <c r="K51" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="L51" t="s">
         <v>249</v>
@@ -12025,7 +12022,7 @@
         <v>7010</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="P51">
         <v>2</v>
@@ -12063,7 +12060,7 @@
         <v>253</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -12075,7 +12072,7 @@
         <v>2</v>
       </c>
       <c r="K52" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="L52" t="s">
         <v>254</v>
@@ -12084,7 +12081,7 @@
         <v>7011</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>2400</v>
+        <v>2399</v>
       </c>
       <c r="P52">
         <v>2</v>
@@ -12122,7 +12119,7 @@
         <v>258</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -12134,7 +12131,7 @@
         <v>2</v>
       </c>
       <c r="K53" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="L53" t="s">
         <v>259</v>
@@ -12143,7 +12140,7 @@
         <v>7012</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
       <c r="P53">
         <v>2</v>
@@ -12181,7 +12178,7 @@
         <v>263</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -12193,7 +12190,7 @@
         <v>2</v>
       </c>
       <c r="K54" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="L54" t="s">
         <v>264</v>
@@ -12202,7 +12199,7 @@
         <v>7013</v>
       </c>
       <c r="O54" s="3" t="s">
-        <v>2402</v>
+        <v>2401</v>
       </c>
       <c r="P54">
         <v>2</v>
@@ -12240,7 +12237,7 @@
         <v>268</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -12252,7 +12249,7 @@
         <v>2</v>
       </c>
       <c r="K55" t="s">
-        <v>2777</v>
+        <v>2776</v>
       </c>
       <c r="L55" t="s">
         <v>269</v>
@@ -12261,7 +12258,7 @@
         <v>7014</v>
       </c>
       <c r="O55" s="3" t="s">
-        <v>2406</v>
+        <v>2405</v>
       </c>
       <c r="P55">
         <v>2</v>
@@ -12299,7 +12296,7 @@
         <v>273</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
@@ -12311,7 +12308,7 @@
         <v>2</v>
       </c>
       <c r="K56" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="L56" t="s">
         <v>274</v>
@@ -12320,7 +12317,7 @@
         <v>7015</v>
       </c>
       <c r="O56" s="3" t="s">
-        <v>2405</v>
+        <v>2404</v>
       </c>
       <c r="P56">
         <v>2</v>
@@ -12358,7 +12355,7 @@
         <v>278</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -12370,7 +12367,7 @@
         <v>2</v>
       </c>
       <c r="K57" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="L57" t="s">
         <v>279</v>
@@ -12379,7 +12376,7 @@
         <v>7016</v>
       </c>
       <c r="O57" s="3" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
       <c r="P57">
         <v>2</v>
@@ -12417,7 +12414,7 @@
         <v>283</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
@@ -12429,7 +12426,7 @@
         <v>2</v>
       </c>
       <c r="K58" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="L58" t="s">
         <v>284</v>
@@ -12438,7 +12435,7 @@
         <v>7017</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>2403</v>
+        <v>2402</v>
       </c>
       <c r="P58">
         <v>2</v>
@@ -12476,7 +12473,7 @@
         <v>288</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
@@ -12488,7 +12485,7 @@
         <v>2</v>
       </c>
       <c r="K59" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="L59" t="s">
         <v>289</v>
@@ -12497,7 +12494,7 @@
         <v>7018</v>
       </c>
       <c r="O59" s="3" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
       <c r="P59">
         <v>2</v>
@@ -12544,7 +12541,7 @@
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>2776</v>
+        <v>2775</v>
       </c>
       <c r="L60" t="s">
         <v>293</v>
@@ -12589,7 +12586,7 @@
         <v>297</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -12601,7 +12598,7 @@
         <v>2</v>
       </c>
       <c r="K61" t="s">
-        <v>2779</v>
+        <v>2778</v>
       </c>
       <c r="L61" t="s">
         <v>298</v>
@@ -12610,7 +12607,7 @@
         <v>8002</v>
       </c>
       <c r="O61" s="3" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
       <c r="P61">
         <v>2</v>
@@ -12648,7 +12645,7 @@
         <v>302</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -12660,7 +12657,7 @@
         <v>2</v>
       </c>
       <c r="K62" t="s">
-        <v>2779</v>
+        <v>2778</v>
       </c>
       <c r="L62" t="s">
         <v>303</v>
@@ -12669,7 +12666,7 @@
         <v>8003</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="P62">
         <v>2</v>
@@ -12707,7 +12704,7 @@
         <v>307</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -12719,7 +12716,7 @@
         <v>2</v>
       </c>
       <c r="K63" t="s">
-        <v>2780</v>
+        <v>2779</v>
       </c>
       <c r="L63" t="s">
         <v>308</v>
@@ -12728,7 +12725,7 @@
         <v>8004</v>
       </c>
       <c r="O63" s="3" t="s">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="P63">
         <v>2</v>
@@ -12766,7 +12763,7 @@
         <v>312</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -12778,7 +12775,7 @@
         <v>2</v>
       </c>
       <c r="K64" t="s">
-        <v>2780</v>
+        <v>2779</v>
       </c>
       <c r="L64" t="s">
         <v>313</v>
@@ -12787,7 +12784,7 @@
         <v>8005</v>
       </c>
       <c r="O64" s="3" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
       <c r="P64">
         <v>2</v>
@@ -12825,7 +12822,7 @@
         <v>317</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -12837,7 +12834,7 @@
         <v>2</v>
       </c>
       <c r="K65" t="s">
-        <v>2780</v>
+        <v>2779</v>
       </c>
       <c r="L65" t="s">
         <v>318</v>
@@ -12846,7 +12843,7 @@
         <v>8006</v>
       </c>
       <c r="O65" s="3" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
       <c r="P65">
         <v>2</v>
@@ -54303,7 +54300,7 @@
         <v>1822</v>
       </c>
       <c r="F1018" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1018" t="b">
         <v>1</v>
@@ -54346,7 +54343,7 @@
         <v>1823</v>
       </c>
       <c r="F1019" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1019" t="b">
         <v>1</v>
@@ -54389,7 +54386,7 @@
         <v>1824</v>
       </c>
       <c r="F1020" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1020" t="b">
         <v>1</v>
@@ -54432,7 +54429,7 @@
         <v>1825</v>
       </c>
       <c r="F1021" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1021" t="b">
         <v>1</v>
@@ -54475,7 +54472,7 @@
         <v>1826</v>
       </c>
       <c r="F1022" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1022" t="b">
         <v>1</v>
@@ -54518,7 +54515,7 @@
         <v>1827</v>
       </c>
       <c r="F1023" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1023" t="b">
         <v>1</v>
@@ -54561,7 +54558,7 @@
         <v>1828</v>
       </c>
       <c r="F1024" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1024" t="b">
         <v>1</v>
@@ -54604,7 +54601,7 @@
         <v>1829</v>
       </c>
       <c r="F1025" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1025" t="b">
         <v>1</v>
@@ -54647,7 +54644,7 @@
         <v>1830</v>
       </c>
       <c r="F1026" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1026" t="b">
         <v>1</v>
@@ -54690,7 +54687,7 @@
         <v>1831</v>
       </c>
       <c r="F1027" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1027" t="b">
         <v>1</v>
@@ -54733,7 +54730,7 @@
         <v>1832</v>
       </c>
       <c r="F1028" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1028" t="b">
         <v>1</v>
@@ -54776,7 +54773,7 @@
         <v>1833</v>
       </c>
       <c r="F1029" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1029" t="b">
         <v>1</v>
@@ -54819,7 +54816,7 @@
         <v>1834</v>
       </c>
       <c r="F1030" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1030" t="b">
         <v>1</v>
@@ -54862,7 +54859,7 @@
         <v>1835</v>
       </c>
       <c r="F1031" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1031" t="b">
         <v>1</v>
@@ -54905,7 +54902,7 @@
         <v>1836</v>
       </c>
       <c r="F1032" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1032" t="b">
         <v>1</v>
@@ -54948,7 +54945,7 @@
         <v>1837</v>
       </c>
       <c r="F1033" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1033" t="b">
         <v>1</v>
@@ -54991,7 +54988,7 @@
         <v>1838</v>
       </c>
       <c r="F1034" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1034" t="b">
         <v>1</v>
@@ -55034,7 +55031,7 @@
         <v>1839</v>
       </c>
       <c r="F1035" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1035" t="b">
         <v>1</v>
@@ -55077,7 +55074,7 @@
         <v>1840</v>
       </c>
       <c r="F1036" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1036" t="b">
         <v>1</v>
@@ -55120,7 +55117,7 @@
         <v>1841</v>
       </c>
       <c r="F1037" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1037" t="b">
         <v>1</v>
@@ -55163,7 +55160,7 @@
         <v>1842</v>
       </c>
       <c r="F1038" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1038" t="b">
         <v>1</v>
@@ -55206,7 +55203,7 @@
         <v>1843</v>
       </c>
       <c r="F1039" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1039" t="b">
         <v>1</v>
@@ -55249,7 +55246,7 @@
         <v>1844</v>
       </c>
       <c r="F1040" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1040" t="b">
         <v>1</v>
@@ -55292,7 +55289,7 @@
         <v>1845</v>
       </c>
       <c r="F1041" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1041" t="b">
         <v>1</v>
@@ -55335,7 +55332,7 @@
         <v>1846</v>
       </c>
       <c r="F1042" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1042" t="b">
         <v>1</v>
@@ -55378,7 +55375,7 @@
         <v>1847</v>
       </c>
       <c r="F1043" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1043" t="b">
         <v>1</v>
@@ -55421,7 +55418,7 @@
         <v>1848</v>
       </c>
       <c r="F1044" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1044" t="b">
         <v>1</v>
@@ -55464,7 +55461,7 @@
         <v>1849</v>
       </c>
       <c r="F1045" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1045" t="b">
         <v>1</v>
@@ -55507,7 +55504,7 @@
         <v>1850</v>
       </c>
       <c r="F1046" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1046" t="b">
         <v>1</v>
@@ -55550,7 +55547,7 @@
         <v>1851</v>
       </c>
       <c r="F1047" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1047" t="b">
         <v>1</v>
@@ -55593,7 +55590,7 @@
         <v>1852</v>
       </c>
       <c r="F1048" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1048" t="b">
         <v>1</v>
@@ -55636,7 +55633,7 @@
         <v>1853</v>
       </c>
       <c r="F1049" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1049" t="b">
         <v>1</v>
@@ -55679,7 +55676,7 @@
         <v>1854</v>
       </c>
       <c r="F1050" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1050" t="b">
         <v>1</v>
@@ -55722,7 +55719,7 @@
         <v>1855</v>
       </c>
       <c r="F1051" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1051" t="b">
         <v>1</v>
@@ -55765,7 +55762,7 @@
         <v>1856</v>
       </c>
       <c r="F1052" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1052" t="b">
         <v>1</v>
@@ -55808,7 +55805,7 @@
         <v>1857</v>
       </c>
       <c r="F1053" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1053" t="b">
         <v>1</v>
@@ -55851,7 +55848,7 @@
         <v>1858</v>
       </c>
       <c r="F1054" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1054" t="b">
         <v>1</v>
@@ -55894,7 +55891,7 @@
         <v>1859</v>
       </c>
       <c r="F1055" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1055" t="b">
         <v>1</v>
@@ -55937,7 +55934,7 @@
         <v>1860</v>
       </c>
       <c r="F1056" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1056" t="b">
         <v>1</v>
@@ -55980,7 +55977,7 @@
         <v>1861</v>
       </c>
       <c r="F1057" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1057" t="b">
         <v>1</v>
@@ -56023,7 +56020,7 @@
         <v>1862</v>
       </c>
       <c r="F1058" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1058" t="b">
         <v>1</v>
@@ -56066,7 +56063,7 @@
         <v>1863</v>
       </c>
       <c r="F1059" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1059" t="b">
         <v>1</v>
@@ -56109,7 +56106,7 @@
         <v>1864</v>
       </c>
       <c r="F1060" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1060" t="b">
         <v>1</v>
@@ -56152,7 +56149,7 @@
         <v>1865</v>
       </c>
       <c r="F1061" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1061" t="b">
         <v>1</v>
@@ -56195,7 +56192,7 @@
         <v>1866</v>
       </c>
       <c r="F1062" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1062" t="b">
         <v>1</v>
@@ -56238,7 +56235,7 @@
         <v>1867</v>
       </c>
       <c r="F1063" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1063" t="b">
         <v>1</v>
@@ -56281,7 +56278,7 @@
         <v>1868</v>
       </c>
       <c r="F1064" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1064" t="b">
         <v>1</v>
@@ -56324,7 +56321,7 @@
         <v>1869</v>
       </c>
       <c r="F1065" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1065" t="b">
         <v>1</v>
@@ -56367,7 +56364,7 @@
         <v>1870</v>
       </c>
       <c r="F1066" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1066" t="b">
         <v>1</v>
@@ -56410,7 +56407,7 @@
         <v>1871</v>
       </c>
       <c r="F1067" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1067" t="b">
         <v>1</v>
@@ -56453,7 +56450,7 @@
         <v>1872</v>
       </c>
       <c r="F1068" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1068" t="b">
         <v>1</v>
@@ -56496,7 +56493,7 @@
         <v>1873</v>
       </c>
       <c r="F1069" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1069" t="b">
         <v>1</v>
@@ -56539,7 +56536,7 @@
         <v>1874</v>
       </c>
       <c r="F1070" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1070" t="b">
         <v>1</v>
@@ -56582,7 +56579,7 @@
         <v>1875</v>
       </c>
       <c r="F1071" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1071" t="b">
         <v>1</v>
@@ -56625,7 +56622,7 @@
         <v>1876</v>
       </c>
       <c r="F1072" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1072" t="b">
         <v>1</v>
@@ -56668,7 +56665,7 @@
         <v>1877</v>
       </c>
       <c r="F1073" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1073" t="b">
         <v>1</v>
@@ -56711,7 +56708,7 @@
         <v>1878</v>
       </c>
       <c r="F1074" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1074" t="b">
         <v>1</v>
@@ -56754,7 +56751,7 @@
         <v>1879</v>
       </c>
       <c r="F1075" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1075" t="b">
         <v>1</v>
@@ -56797,7 +56794,7 @@
         <v>1880</v>
       </c>
       <c r="F1076" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1076" t="b">
         <v>1</v>
@@ -56840,7 +56837,7 @@
         <v>1881</v>
       </c>
       <c r="F1077" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1077" t="b">
         <v>1</v>
@@ -56883,7 +56880,7 @@
         <v>1882</v>
       </c>
       <c r="F1078" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1078" t="b">
         <v>1</v>
@@ -56926,7 +56923,7 @@
         <v>1883</v>
       </c>
       <c r="F1079" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1079" t="b">
         <v>1</v>
@@ -56969,7 +56966,7 @@
         <v>1884</v>
       </c>
       <c r="F1080" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1080" t="b">
         <v>1</v>
@@ -57012,7 +57009,7 @@
         <v>1885</v>
       </c>
       <c r="F1081" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1081" t="b">
         <v>1</v>
@@ -57055,7 +57052,7 @@
         <v>1886</v>
       </c>
       <c r="F1082" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1082" t="b">
         <v>1</v>
@@ -57098,7 +57095,7 @@
         <v>1887</v>
       </c>
       <c r="F1083" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1083" t="b">
         <v>1</v>
@@ -57141,7 +57138,7 @@
         <v>1888</v>
       </c>
       <c r="F1084" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1084" t="b">
         <v>1</v>
@@ -57184,7 +57181,7 @@
         <v>1889</v>
       </c>
       <c r="F1085" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1085" t="b">
         <v>1</v>
@@ -57227,7 +57224,7 @@
         <v>1890</v>
       </c>
       <c r="F1086" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1086" t="b">
         <v>1</v>
@@ -57270,7 +57267,7 @@
         <v>1891</v>
       </c>
       <c r="F1087" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1087" t="b">
         <v>1</v>
@@ -57313,7 +57310,7 @@
         <v>1892</v>
       </c>
       <c r="F1088" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1088" t="b">
         <v>1</v>
@@ -57356,7 +57353,7 @@
         <v>1893</v>
       </c>
       <c r="F1089" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1089" t="b">
         <v>1</v>
@@ -57399,7 +57396,7 @@
         <v>1894</v>
       </c>
       <c r="F1090" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1090" t="b">
         <v>1</v>
@@ -57442,7 +57439,7 @@
         <v>1895</v>
       </c>
       <c r="F1091" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1091" t="b">
         <v>1</v>
@@ -57485,7 +57482,7 @@
         <v>1896</v>
       </c>
       <c r="F1092" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1092" t="b">
         <v>1</v>
@@ -57528,7 +57525,7 @@
         <v>1897</v>
       </c>
       <c r="F1093" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1093" t="b">
         <v>1</v>
@@ -57571,7 +57568,7 @@
         <v>1898</v>
       </c>
       <c r="F1094" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1094" t="b">
         <v>1</v>
@@ -57614,7 +57611,7 @@
         <v>1899</v>
       </c>
       <c r="F1095" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1095" t="b">
         <v>1</v>
@@ -57657,7 +57654,7 @@
         <v>1900</v>
       </c>
       <c r="F1096" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1096" t="b">
         <v>1</v>
@@ -57700,7 +57697,7 @@
         <v>1901</v>
       </c>
       <c r="F1097" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1097" t="b">
         <v>1</v>
@@ -57743,7 +57740,7 @@
         <v>1902</v>
       </c>
       <c r="F1098" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1098" t="b">
         <v>1</v>
@@ -57786,7 +57783,7 @@
         <v>1903</v>
       </c>
       <c r="F1099" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1099" t="b">
         <v>1</v>
@@ -57829,7 +57826,7 @@
         <v>1904</v>
       </c>
       <c r="F1100" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1100" t="b">
         <v>1</v>
@@ -57872,7 +57869,7 @@
         <v>1905</v>
       </c>
       <c r="F1101" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1101" t="b">
         <v>1</v>
@@ -57915,7 +57912,7 @@
         <v>1906</v>
       </c>
       <c r="F1102" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1102" t="b">
         <v>1</v>
@@ -57958,7 +57955,7 @@
         <v>1907</v>
       </c>
       <c r="F1103" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1103" t="b">
         <v>1</v>
@@ -58001,7 +57998,7 @@
         <v>1908</v>
       </c>
       <c r="F1104" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1104" t="b">
         <v>1</v>
@@ -58044,7 +58041,7 @@
         <v>1909</v>
       </c>
       <c r="F1105" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1105" t="b">
         <v>1</v>
@@ -58087,7 +58084,7 @@
         <v>1910</v>
       </c>
       <c r="F1106" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1106" t="b">
         <v>1</v>
@@ -58130,7 +58127,7 @@
         <v>1911</v>
       </c>
       <c r="F1107" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1107" t="b">
         <v>1</v>
@@ -58173,7 +58170,7 @@
         <v>1912</v>
       </c>
       <c r="F1108" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1108" t="b">
         <v>1</v>
@@ -58216,7 +58213,7 @@
         <v>1913</v>
       </c>
       <c r="F1109" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1109" t="b">
         <v>1</v>
@@ -58259,7 +58256,7 @@
         <v>1914</v>
       </c>
       <c r="F1110" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="G1110" t="b">
         <v>1</v>
@@ -58296,7 +58293,7 @@
         <v>0</v>
       </c>
       <c r="D1111" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="E1111" t="s">
         <v>325</v>
@@ -58336,7 +58333,7 @@
         <v>0</v>
       </c>
       <c r="D1112" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="E1112" t="s">
         <v>924</v>
@@ -58376,7 +58373,7 @@
         <v>0</v>
       </c>
       <c r="D1113" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
       <c r="E1113" t="s">
         <v>1915</v>
@@ -58416,7 +58413,7 @@
         <v>0</v>
       </c>
       <c r="D1114" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
       <c r="E1114" t="s">
         <v>1916</v>
@@ -58456,7 +58453,7 @@
         <v>0</v>
       </c>
       <c r="D1115" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="E1115" t="s">
         <v>327</v>
@@ -58502,7 +58499,7 @@
         <v>1917</v>
       </c>
       <c r="F1116" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="G1116" t="b">
         <v>1</v>
@@ -58548,7 +58545,7 @@
         <v>1919</v>
       </c>
       <c r="F1117" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="G1117" t="b">
         <v>1</v>
@@ -58594,7 +58591,7 @@
         <v>1921</v>
       </c>
       <c r="F1118" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="G1118" t="b">
         <v>1</v>
@@ -58640,7 +58637,7 @@
         <v>1923</v>
       </c>
       <c r="F1119" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="G1119" t="b">
         <v>1</v>
@@ -58686,7 +58683,7 @@
         <v>1925</v>
       </c>
       <c r="F1120" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="G1120" t="b">
         <v>1</v>
@@ -58732,7 +58729,7 @@
         <v>1927</v>
       </c>
       <c r="F1121" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="G1121" t="b">
         <v>1</v>
@@ -58778,7 +58775,7 @@
         <v>1929</v>
       </c>
       <c r="F1122" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="G1122" t="b">
         <v>1</v>
@@ -58824,7 +58821,7 @@
         <v>1931</v>
       </c>
       <c r="F1123" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="G1123" t="b">
         <v>1</v>
@@ -58870,7 +58867,7 @@
         <v>1933</v>
       </c>
       <c r="F1124" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="G1124" t="b">
         <v>1</v>
@@ -58916,7 +58913,7 @@
         <v>1935</v>
       </c>
       <c r="F1125" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="G1125" t="b">
         <v>1</v>
@@ -58962,7 +58959,7 @@
         <v>1937</v>
       </c>
       <c r="F1126" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="G1126" t="b">
         <v>1</v>
@@ -59008,7 +59005,7 @@
         <v>1939</v>
       </c>
       <c r="F1127" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="G1127" t="b">
         <v>1</v>
@@ -59054,7 +59051,7 @@
         <v>1941</v>
       </c>
       <c r="F1128" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="G1128" t="b">
         <v>1</v>
@@ -59100,7 +59097,7 @@
         <v>1943</v>
       </c>
       <c r="F1129" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="G1129" t="b">
         <v>1</v>
@@ -59140,7 +59137,7 @@
         <v>0</v>
       </c>
       <c r="D1130" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="E1130" t="s">
         <v>325</v>
@@ -59180,7 +59177,7 @@
         <v>0</v>
       </c>
       <c r="D1131" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="E1131" t="s">
         <v>924</v>
@@ -59220,7 +59217,7 @@
         <v>0</v>
       </c>
       <c r="D1132" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
       <c r="E1132" t="s">
         <v>1915</v>
@@ -59260,7 +59257,7 @@
         <v>0</v>
       </c>
       <c r="D1133" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
       <c r="E1133" t="s">
         <v>1916</v>
@@ -59300,7 +59297,7 @@
         <v>0</v>
       </c>
       <c r="D1134" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="E1134" t="s">
         <v>327</v>
@@ -59346,7 +59343,7 @@
         <v>1945</v>
       </c>
       <c r="F1135" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="G1135" t="b">
         <v>1</v>
@@ -59392,7 +59389,7 @@
         <v>1947</v>
       </c>
       <c r="F1136" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="G1136" t="b">
         <v>1</v>
@@ -59438,7 +59435,7 @@
         <v>1949</v>
       </c>
       <c r="F1137" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="G1137" t="b">
         <v>1</v>
@@ -59484,7 +59481,7 @@
         <v>1951</v>
       </c>
       <c r="F1138" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="G1138" t="b">
         <v>1</v>
@@ -59530,7 +59527,7 @@
         <v>1953</v>
       </c>
       <c r="F1139" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="G1139" t="b">
         <v>1</v>
@@ -59576,7 +59573,7 @@
         <v>1955</v>
       </c>
       <c r="F1140" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="G1140" t="b">
         <v>1</v>
@@ -59622,7 +59619,7 @@
         <v>1957</v>
       </c>
       <c r="F1141" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="G1141" t="b">
         <v>1</v>
@@ -59668,7 +59665,7 @@
         <v>1959</v>
       </c>
       <c r="F1142" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="G1142" t="b">
         <v>1</v>
@@ -59714,7 +59711,7 @@
         <v>1961</v>
       </c>
       <c r="F1143" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="G1143" t="b">
         <v>1</v>
@@ -59760,7 +59757,7 @@
         <v>1963</v>
       </c>
       <c r="F1144" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="G1144" t="b">
         <v>1</v>
@@ -59806,7 +59803,7 @@
         <v>1965</v>
       </c>
       <c r="F1145" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="G1145" t="b">
         <v>1</v>
@@ -59852,7 +59849,7 @@
         <v>1967</v>
       </c>
       <c r="F1146" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="G1146" t="b">
         <v>1</v>
@@ -59898,7 +59895,7 @@
         <v>1969</v>
       </c>
       <c r="F1147" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="G1147" t="b">
         <v>1</v>
@@ -59944,7 +59941,7 @@
         <v>1971</v>
       </c>
       <c r="F1148" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="G1148" t="b">
         <v>1</v>
@@ -59990,7 +59987,7 @@
         <v>1973</v>
       </c>
       <c r="F1149" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="G1149" t="b">
         <v>1</v>
@@ -60036,7 +60033,7 @@
         <v>1975</v>
       </c>
       <c r="F1150" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="G1150" t="b">
         <v>1</v>
@@ -60082,7 +60079,7 @@
         <v>1977</v>
       </c>
       <c r="F1151" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="G1151" t="b">
         <v>1</v>
@@ -60128,7 +60125,7 @@
         <v>1979</v>
       </c>
       <c r="F1152" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="G1152" t="b">
         <v>1</v>
@@ -60174,7 +60171,7 @@
         <v>1981</v>
       </c>
       <c r="F1153" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="G1153" t="b">
         <v>1</v>
@@ -60220,7 +60217,7 @@
         <v>1983</v>
       </c>
       <c r="F1154" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="G1154" t="b">
         <v>1</v>
@@ -60266,7 +60263,7 @@
         <v>1985</v>
       </c>
       <c r="F1155" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="G1155" t="b">
         <v>1</v>
@@ -60312,7 +60309,7 @@
         <v>1987</v>
       </c>
       <c r="F1156" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="G1156" t="b">
         <v>1</v>
@@ -60358,7 +60355,7 @@
         <v>1989</v>
       </c>
       <c r="F1157" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="G1157" t="b">
         <v>1</v>
@@ -60404,7 +60401,7 @@
         <v>1991</v>
       </c>
       <c r="F1158" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="G1158" t="b">
         <v>1</v>
@@ -60450,7 +60447,7 @@
         <v>1993</v>
       </c>
       <c r="F1159" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1159" t="b">
         <v>1</v>
@@ -60463,7 +60460,7 @@
       </c>
       <c r="J1159" s="6"/>
       <c r="L1159" s="3" t="s">
-        <v>2753</v>
+        <v>2752</v>
       </c>
       <c r="M1159">
         <v>2</v>
@@ -60496,7 +60493,7 @@
         <v>1994</v>
       </c>
       <c r="F1160" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1160" t="b">
         <v>1</v>
@@ -60509,7 +60506,7 @@
       </c>
       <c r="J1160" s="6"/>
       <c r="L1160" s="3" t="s">
-        <v>2754</v>
+        <v>2753</v>
       </c>
       <c r="M1160">
         <v>2</v>
@@ -60542,7 +60539,7 @@
         <v>1995</v>
       </c>
       <c r="F1161" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1161" t="b">
         <v>1</v>
@@ -60555,7 +60552,7 @@
       </c>
       <c r="J1161" s="6"/>
       <c r="L1161" s="3" t="s">
-        <v>2755</v>
+        <v>2754</v>
       </c>
       <c r="M1161">
         <v>2</v>
@@ -60588,7 +60585,7 @@
         <v>1996</v>
       </c>
       <c r="F1162" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1162" t="b">
         <v>1</v>
@@ -60601,7 +60598,7 @@
       </c>
       <c r="J1162" s="6"/>
       <c r="L1162" s="3" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="M1162">
         <v>2</v>
@@ -60634,7 +60631,7 @@
         <v>1997</v>
       </c>
       <c r="F1163" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1163" t="b">
         <v>1</v>
@@ -60647,7 +60644,7 @@
       </c>
       <c r="J1163" s="6"/>
       <c r="L1163" s="3" t="s">
-        <v>2757</v>
+        <v>2756</v>
       </c>
       <c r="M1163">
         <v>2</v>
@@ -60680,7 +60677,7 @@
         <v>1998</v>
       </c>
       <c r="F1164" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1164" t="b">
         <v>1</v>
@@ -60693,7 +60690,7 @@
       </c>
       <c r="J1164" s="6"/>
       <c r="L1164" s="3" t="s">
-        <v>2758</v>
+        <v>2757</v>
       </c>
       <c r="M1164">
         <v>2</v>
@@ -60726,7 +60723,7 @@
         <v>1999</v>
       </c>
       <c r="F1165" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1165" t="b">
         <v>1</v>
@@ -60739,7 +60736,7 @@
       </c>
       <c r="J1165" s="6"/>
       <c r="L1165" s="3" t="s">
-        <v>2759</v>
+        <v>2758</v>
       </c>
       <c r="M1165">
         <v>2</v>
@@ -60772,7 +60769,7 @@
         <v>2000</v>
       </c>
       <c r="F1166" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1166" t="b">
         <v>1</v>
@@ -60785,7 +60782,7 @@
       </c>
       <c r="J1166" s="6"/>
       <c r="L1166" s="3" t="s">
-        <v>2760</v>
+        <v>2759</v>
       </c>
       <c r="M1166">
         <v>2</v>
@@ -60818,7 +60815,7 @@
         <v>2001</v>
       </c>
       <c r="F1167" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1167" t="b">
         <v>1</v>
@@ -60831,7 +60828,7 @@
       </c>
       <c r="J1167" s="6"/>
       <c r="L1167" s="3" t="s">
-        <v>2761</v>
+        <v>2760</v>
       </c>
       <c r="M1167">
         <v>2</v>
@@ -60864,7 +60861,7 @@
         <v>2002</v>
       </c>
       <c r="F1168" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1168" t="b">
         <v>1</v>
@@ -60877,7 +60874,7 @@
       </c>
       <c r="J1168" s="6"/>
       <c r="L1168" s="3" t="s">
-        <v>2762</v>
+        <v>2761</v>
       </c>
       <c r="M1168">
         <v>2</v>
@@ -60910,7 +60907,7 @@
         <v>2003</v>
       </c>
       <c r="F1169" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1169" t="b">
         <v>1</v>
@@ -60923,7 +60920,7 @@
       </c>
       <c r="J1169" s="6"/>
       <c r="L1169" s="3" t="s">
-        <v>2763</v>
+        <v>2762</v>
       </c>
       <c r="M1169">
         <v>2</v>
@@ -60956,7 +60953,7 @@
         <v>2004</v>
       </c>
       <c r="F1170" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1170" t="b">
         <v>1</v>
@@ -60969,7 +60966,7 @@
       </c>
       <c r="J1170" s="6"/>
       <c r="L1170" s="3" t="s">
-        <v>2764</v>
+        <v>2763</v>
       </c>
       <c r="M1170">
         <v>2</v>
@@ -61002,7 +60999,7 @@
         <v>2005</v>
       </c>
       <c r="F1171" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1171" t="b">
         <v>1</v>
@@ -61015,7 +61012,7 @@
       </c>
       <c r="J1171" s="6"/>
       <c r="L1171" s="3" t="s">
-        <v>2765</v>
+        <v>2764</v>
       </c>
       <c r="M1171">
         <v>2</v>
@@ -61048,7 +61045,7 @@
         <v>2006</v>
       </c>
       <c r="F1172" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1172" t="b">
         <v>1</v>
@@ -61061,7 +61058,7 @@
       </c>
       <c r="J1172" s="6"/>
       <c r="L1172" s="3" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="M1172">
         <v>2</v>
@@ -61094,7 +61091,7 @@
         <v>2007</v>
       </c>
       <c r="F1173" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1173" t="b">
         <v>1</v>
@@ -61107,7 +61104,7 @@
       </c>
       <c r="J1173" s="6"/>
       <c r="L1173" s="3" t="s">
-        <v>2767</v>
+        <v>2766</v>
       </c>
       <c r="M1173">
         <v>2</v>
@@ -61140,7 +61137,7 @@
         <v>2008</v>
       </c>
       <c r="F1174" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1174" t="b">
         <v>1</v>
@@ -61153,7 +61150,7 @@
       </c>
       <c r="J1174" s="6"/>
       <c r="L1174" s="3" t="s">
-        <v>2768</v>
+        <v>2767</v>
       </c>
       <c r="M1174">
         <v>2</v>
@@ -61186,7 +61183,7 @@
         <v>2009</v>
       </c>
       <c r="F1175" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1175" t="b">
         <v>1</v>
@@ -61199,7 +61196,7 @@
       </c>
       <c r="J1175" s="6"/>
       <c r="L1175" s="3" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
       <c r="M1175">
         <v>2</v>
@@ -61232,7 +61229,7 @@
         <v>2010</v>
       </c>
       <c r="F1176" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1176" t="b">
         <v>1</v>
@@ -61245,7 +61242,7 @@
       </c>
       <c r="J1176" s="6"/>
       <c r="L1176" s="3" t="s">
-        <v>2413</v>
+        <v>2412</v>
       </c>
       <c r="M1176">
         <v>2</v>
@@ -61278,7 +61275,7 @@
         <v>2011</v>
       </c>
       <c r="F1177" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1177" t="b">
         <v>1</v>
@@ -61291,7 +61288,7 @@
       </c>
       <c r="J1177" s="6"/>
       <c r="L1177" s="3" t="s">
-        <v>2414</v>
+        <v>2413</v>
       </c>
       <c r="M1177">
         <v>2</v>
@@ -61324,7 +61321,7 @@
         <v>2012</v>
       </c>
       <c r="F1178" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1178" t="b">
         <v>1</v>
@@ -61337,7 +61334,7 @@
       </c>
       <c r="J1178" s="6"/>
       <c r="L1178" s="3" t="s">
-        <v>2415</v>
+        <v>2414</v>
       </c>
       <c r="M1178">
         <v>2</v>
@@ -61370,7 +61367,7 @@
         <v>2013</v>
       </c>
       <c r="F1179" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1179" t="b">
         <v>1</v>
@@ -61383,7 +61380,7 @@
       </c>
       <c r="J1179" s="6"/>
       <c r="L1179" s="3" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="M1179">
         <v>2</v>
@@ -61416,7 +61413,7 @@
         <v>2014</v>
       </c>
       <c r="F1180" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1180" t="b">
         <v>1</v>
@@ -61429,7 +61426,7 @@
       </c>
       <c r="J1180" s="6"/>
       <c r="L1180" s="3" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
       <c r="M1180">
         <v>2</v>
@@ -61462,7 +61459,7 @@
         <v>2015</v>
       </c>
       <c r="F1181" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1181" t="b">
         <v>1</v>
@@ -61475,7 +61472,7 @@
       </c>
       <c r="J1181" s="6"/>
       <c r="L1181" s="3" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="M1181">
         <v>2</v>
@@ -61508,7 +61505,7 @@
         <v>2016</v>
       </c>
       <c r="F1182" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1182" t="b">
         <v>1</v>
@@ -61521,7 +61518,7 @@
       </c>
       <c r="J1182" s="6"/>
       <c r="L1182" s="3" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="M1182">
         <v>2</v>
@@ -61554,7 +61551,7 @@
         <v>2017</v>
       </c>
       <c r="F1183" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1183" t="b">
         <v>1</v>
@@ -61567,7 +61564,7 @@
       </c>
       <c r="J1183" s="6"/>
       <c r="L1183" s="3" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
       <c r="M1183">
         <v>2</v>
@@ -61600,7 +61597,7 @@
         <v>2018</v>
       </c>
       <c r="F1184" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1184" t="b">
         <v>1</v>
@@ -61613,7 +61610,7 @@
       </c>
       <c r="J1184" s="6"/>
       <c r="L1184" s="3" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="M1184">
         <v>2</v>
@@ -61646,7 +61643,7 @@
         <v>2019</v>
       </c>
       <c r="F1185" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1185" t="b">
         <v>1</v>
@@ -61659,7 +61656,7 @@
       </c>
       <c r="J1185" s="6"/>
       <c r="L1185" s="3" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
       <c r="M1185">
         <v>2</v>
@@ -61692,7 +61689,7 @@
         <v>2020</v>
       </c>
       <c r="F1186" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1186" t="b">
         <v>1</v>
@@ -61705,7 +61702,7 @@
       </c>
       <c r="J1186" s="6"/>
       <c r="L1186" s="3" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="M1186">
         <v>2</v>
@@ -61738,7 +61735,7 @@
         <v>2021</v>
       </c>
       <c r="F1187" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1187" t="b">
         <v>1</v>
@@ -61751,7 +61748,7 @@
       </c>
       <c r="J1187" s="6"/>
       <c r="L1187" s="3" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
       <c r="M1187">
         <v>2</v>
@@ -61784,7 +61781,7 @@
         <v>2022</v>
       </c>
       <c r="F1188" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1188" t="b">
         <v>1</v>
@@ -61797,7 +61794,7 @@
       </c>
       <c r="J1188" s="6"/>
       <c r="L1188" s="3" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="M1188">
         <v>2</v>
@@ -61830,7 +61827,7 @@
         <v>2023</v>
       </c>
       <c r="F1189" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1189" t="b">
         <v>1</v>
@@ -61843,7 +61840,7 @@
       </c>
       <c r="J1189" s="6"/>
       <c r="L1189" s="3" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="M1189">
         <v>2</v>
@@ -61876,7 +61873,7 @@
         <v>2024</v>
       </c>
       <c r="F1190" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1190" t="b">
         <v>1</v>
@@ -61889,7 +61886,7 @@
       </c>
       <c r="J1190" s="6"/>
       <c r="L1190" s="3" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="M1190">
         <v>2</v>
@@ -61922,7 +61919,7 @@
         <v>2025</v>
       </c>
       <c r="F1191" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1191" t="b">
         <v>1</v>
@@ -61935,7 +61932,7 @@
       </c>
       <c r="J1191" s="6"/>
       <c r="L1191" s="3" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
       <c r="M1191">
         <v>2</v>
@@ -61968,7 +61965,7 @@
         <v>2026</v>
       </c>
       <c r="F1192" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1192" t="b">
         <v>1</v>
@@ -61981,7 +61978,7 @@
       </c>
       <c r="J1192" s="6"/>
       <c r="L1192" s="3" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="M1192">
         <v>2</v>
@@ -62014,7 +62011,7 @@
         <v>2027</v>
       </c>
       <c r="F1193" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1193" t="b">
         <v>1</v>
@@ -62027,7 +62024,7 @@
       </c>
       <c r="J1193" s="6"/>
       <c r="L1193" s="3" t="s">
-        <v>2430</v>
+        <v>2429</v>
       </c>
       <c r="M1193">
         <v>2</v>
@@ -62060,7 +62057,7 @@
         <v>2028</v>
       </c>
       <c r="F1194" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1194" t="b">
         <v>1</v>
@@ -62073,7 +62070,7 @@
       </c>
       <c r="J1194" s="6"/>
       <c r="L1194" s="3" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
       <c r="M1194">
         <v>2</v>
@@ -62106,7 +62103,7 @@
         <v>2029</v>
       </c>
       <c r="F1195" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1195" t="b">
         <v>1</v>
@@ -62119,7 +62116,7 @@
       </c>
       <c r="J1195" s="6"/>
       <c r="L1195" s="3" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="M1195">
         <v>2</v>
@@ -62152,7 +62149,7 @@
         <v>2030</v>
       </c>
       <c r="F1196" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1196" t="b">
         <v>1</v>
@@ -62165,7 +62162,7 @@
       </c>
       <c r="J1196" s="6"/>
       <c r="L1196" s="3" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="M1196">
         <v>2</v>
@@ -62198,7 +62195,7 @@
         <v>2031</v>
       </c>
       <c r="F1197" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1197" t="b">
         <v>1</v>
@@ -62211,7 +62208,7 @@
       </c>
       <c r="J1197" s="6"/>
       <c r="L1197" s="3" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
       <c r="M1197">
         <v>2</v>
@@ -62244,7 +62241,7 @@
         <v>2032</v>
       </c>
       <c r="F1198" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1198" t="b">
         <v>1</v>
@@ -62257,7 +62254,7 @@
       </c>
       <c r="J1198" s="6"/>
       <c r="L1198" s="3" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
       <c r="M1198">
         <v>2</v>
@@ -62290,7 +62287,7 @@
         <v>2033</v>
       </c>
       <c r="F1199" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1199" t="b">
         <v>1</v>
@@ -62303,7 +62300,7 @@
       </c>
       <c r="J1199" s="6"/>
       <c r="L1199" s="3" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
       <c r="M1199">
         <v>2</v>
@@ -62336,7 +62333,7 @@
         <v>2034</v>
       </c>
       <c r="F1200" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1200" t="b">
         <v>1</v>
@@ -62349,7 +62346,7 @@
       </c>
       <c r="J1200" s="6"/>
       <c r="L1200" s="3" t="s">
-        <v>2437</v>
+        <v>2436</v>
       </c>
       <c r="M1200">
         <v>2</v>
@@ -62382,7 +62379,7 @@
         <v>2035</v>
       </c>
       <c r="F1201" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1201" t="b">
         <v>1</v>
@@ -62395,7 +62392,7 @@
       </c>
       <c r="J1201" s="6"/>
       <c r="L1201" s="3" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="M1201">
         <v>2</v>
@@ -62428,7 +62425,7 @@
         <v>2036</v>
       </c>
       <c r="F1202" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1202" t="b">
         <v>1</v>
@@ -62441,7 +62438,7 @@
       </c>
       <c r="J1202" s="6"/>
       <c r="L1202" s="3" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
       <c r="M1202">
         <v>2</v>
@@ -62474,7 +62471,7 @@
         <v>2037</v>
       </c>
       <c r="F1203" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1203" t="b">
         <v>1</v>
@@ -62487,7 +62484,7 @@
       </c>
       <c r="J1203" s="6"/>
       <c r="L1203" s="3" t="s">
-        <v>2440</v>
+        <v>2439</v>
       </c>
       <c r="M1203">
         <v>2</v>
@@ -62520,7 +62517,7 @@
         <v>2038</v>
       </c>
       <c r="F1204" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1204" t="b">
         <v>1</v>
@@ -62533,7 +62530,7 @@
       </c>
       <c r="J1204" s="6"/>
       <c r="L1204" s="3" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="M1204">
         <v>2</v>
@@ -62566,7 +62563,7 @@
         <v>2039</v>
       </c>
       <c r="F1205" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1205" t="b">
         <v>1</v>
@@ -62579,7 +62576,7 @@
       </c>
       <c r="J1205" s="6"/>
       <c r="L1205" s="3" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="M1205">
         <v>2</v>
@@ -62612,7 +62609,7 @@
         <v>2040</v>
       </c>
       <c r="F1206" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1206" t="b">
         <v>1</v>
@@ -62625,7 +62622,7 @@
       </c>
       <c r="J1206" s="6"/>
       <c r="L1206" s="3" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="M1206">
         <v>2</v>
@@ -62658,7 +62655,7 @@
         <v>2041</v>
       </c>
       <c r="F1207" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1207" t="b">
         <v>1</v>
@@ -62671,7 +62668,7 @@
       </c>
       <c r="J1207" s="6"/>
       <c r="L1207" s="3" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="M1207">
         <v>2</v>
@@ -62704,7 +62701,7 @@
         <v>2042</v>
       </c>
       <c r="F1208" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1208" t="b">
         <v>1</v>
@@ -62717,7 +62714,7 @@
       </c>
       <c r="J1208" s="6"/>
       <c r="L1208" s="3" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="M1208">
         <v>2</v>
@@ -62750,7 +62747,7 @@
         <v>2043</v>
       </c>
       <c r="F1209" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1209" t="b">
         <v>1</v>
@@ -62763,7 +62760,7 @@
       </c>
       <c r="J1209" s="6"/>
       <c r="L1209" s="3" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="M1209">
         <v>2</v>
@@ -62796,7 +62793,7 @@
         <v>2044</v>
       </c>
       <c r="F1210" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1210" t="b">
         <v>1</v>
@@ -62809,7 +62806,7 @@
       </c>
       <c r="J1210" s="6"/>
       <c r="L1210" s="3" t="s">
-        <v>2447</v>
+        <v>2446</v>
       </c>
       <c r="M1210">
         <v>2</v>
@@ -62842,7 +62839,7 @@
         <v>2045</v>
       </c>
       <c r="F1211" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1211" t="b">
         <v>1</v>
@@ -62855,7 +62852,7 @@
       </c>
       <c r="J1211" s="6"/>
       <c r="L1211" s="3" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="M1211">
         <v>2</v>
@@ -62888,7 +62885,7 @@
         <v>2046</v>
       </c>
       <c r="F1212" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1212" t="b">
         <v>1</v>
@@ -62901,7 +62898,7 @@
       </c>
       <c r="J1212" s="6"/>
       <c r="L1212" s="3" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="M1212">
         <v>2</v>
@@ -62934,7 +62931,7 @@
         <v>2047</v>
       </c>
       <c r="F1213" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1213" t="b">
         <v>1</v>
@@ -62947,7 +62944,7 @@
       </c>
       <c r="J1213" s="6"/>
       <c r="L1213" s="3" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="M1213">
         <v>2</v>
@@ -62980,7 +62977,7 @@
         <v>2048</v>
       </c>
       <c r="F1214" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1214" t="b">
         <v>1</v>
@@ -62993,7 +62990,7 @@
       </c>
       <c r="J1214" s="6"/>
       <c r="L1214" s="3" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="M1214">
         <v>2</v>
@@ -63026,7 +63023,7 @@
         <v>2049</v>
       </c>
       <c r="F1215" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1215" t="b">
         <v>1</v>
@@ -63039,7 +63036,7 @@
       </c>
       <c r="J1215" s="6"/>
       <c r="L1215" s="3" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="M1215">
         <v>2</v>
@@ -63072,7 +63069,7 @@
         <v>2050</v>
       </c>
       <c r="F1216" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1216" t="b">
         <v>1</v>
@@ -63085,7 +63082,7 @@
       </c>
       <c r="J1216" s="6"/>
       <c r="L1216" s="3" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="M1216">
         <v>2</v>
@@ -63118,7 +63115,7 @@
         <v>2051</v>
       </c>
       <c r="F1217" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1217" t="b">
         <v>1</v>
@@ -63131,7 +63128,7 @@
       </c>
       <c r="J1217" s="6"/>
       <c r="L1217" s="3" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="M1217">
         <v>2</v>
@@ -63164,7 +63161,7 @@
         <v>2052</v>
       </c>
       <c r="F1218" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1218" t="b">
         <v>1</v>
@@ -63177,7 +63174,7 @@
       </c>
       <c r="J1218" s="6"/>
       <c r="L1218" s="3" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="M1218">
         <v>2</v>
@@ -63210,7 +63207,7 @@
         <v>2053</v>
       </c>
       <c r="F1219" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1219" t="b">
         <v>1</v>
@@ -63223,7 +63220,7 @@
       </c>
       <c r="J1219" s="6"/>
       <c r="L1219" s="3" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="M1219">
         <v>2</v>
@@ -63256,7 +63253,7 @@
         <v>2054</v>
       </c>
       <c r="F1220" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1220" t="b">
         <v>1</v>
@@ -63269,7 +63266,7 @@
       </c>
       <c r="J1220" s="6"/>
       <c r="L1220" s="3" t="s">
-        <v>2457</v>
+        <v>2456</v>
       </c>
       <c r="M1220">
         <v>2</v>
@@ -63302,7 +63299,7 @@
         <v>2055</v>
       </c>
       <c r="F1221" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1221" t="b">
         <v>1</v>
@@ -63315,7 +63312,7 @@
       </c>
       <c r="J1221" s="6"/>
       <c r="L1221" s="3" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="M1221">
         <v>2</v>
@@ -63348,7 +63345,7 @@
         <v>2056</v>
       </c>
       <c r="F1222" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1222" t="b">
         <v>1</v>
@@ -63361,7 +63358,7 @@
       </c>
       <c r="J1222" s="6"/>
       <c r="L1222" s="3" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="M1222">
         <v>2</v>
@@ -63394,7 +63391,7 @@
         <v>2057</v>
       </c>
       <c r="F1223" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1223" t="b">
         <v>1</v>
@@ -63407,7 +63404,7 @@
       </c>
       <c r="J1223" s="6"/>
       <c r="L1223" s="3" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="M1223">
         <v>2</v>
@@ -63440,7 +63437,7 @@
         <v>2058</v>
       </c>
       <c r="F1224" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1224" t="b">
         <v>1</v>
@@ -63453,7 +63450,7 @@
       </c>
       <c r="J1224" s="6"/>
       <c r="L1224" s="3" t="s">
-        <v>2465</v>
+        <v>2464</v>
       </c>
       <c r="M1224">
         <v>2</v>
@@ -63486,7 +63483,7 @@
         <v>2059</v>
       </c>
       <c r="F1225" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1225" t="b">
         <v>1</v>
@@ -63499,7 +63496,7 @@
       </c>
       <c r="J1225" s="6"/>
       <c r="L1225" s="3" t="s">
-        <v>2466</v>
+        <v>2465</v>
       </c>
       <c r="M1225">
         <v>2</v>
@@ -63532,7 +63529,7 @@
         <v>2060</v>
       </c>
       <c r="F1226" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1226" t="b">
         <v>1</v>
@@ -63545,7 +63542,7 @@
       </c>
       <c r="J1226" s="6"/>
       <c r="L1226" s="3" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="M1226">
         <v>2</v>
@@ -63578,7 +63575,7 @@
         <v>2061</v>
       </c>
       <c r="F1227" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1227" t="b">
         <v>1</v>
@@ -63591,7 +63588,7 @@
       </c>
       <c r="J1227" s="6"/>
       <c r="L1227" s="3" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
       <c r="M1227">
         <v>2</v>
@@ -63624,7 +63621,7 @@
         <v>2062</v>
       </c>
       <c r="F1228" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1228" t="b">
         <v>1</v>
@@ -63637,7 +63634,7 @@
       </c>
       <c r="J1228" s="6"/>
       <c r="L1228" s="3" t="s">
-        <v>2461</v>
+        <v>2460</v>
       </c>
       <c r="M1228">
         <v>2</v>
@@ -63670,7 +63667,7 @@
         <v>2063</v>
       </c>
       <c r="F1229" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1229" t="b">
         <v>1</v>
@@ -63683,7 +63680,7 @@
       </c>
       <c r="J1229" s="6"/>
       <c r="L1229" s="3" t="s">
-        <v>2462</v>
+        <v>2461</v>
       </c>
       <c r="M1229">
         <v>2</v>
@@ -63716,7 +63713,7 @@
         <v>2064</v>
       </c>
       <c r="F1230" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1230" t="b">
         <v>1</v>
@@ -63729,7 +63726,7 @@
       </c>
       <c r="J1230" s="6"/>
       <c r="L1230" s="3" t="s">
-        <v>2463</v>
+        <v>2462</v>
       </c>
       <c r="M1230">
         <v>2</v>
@@ -63762,7 +63759,7 @@
         <v>2065</v>
       </c>
       <c r="F1231" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1231" t="b">
         <v>1</v>
@@ -63775,7 +63772,7 @@
       </c>
       <c r="J1231" s="6"/>
       <c r="L1231" s="3" t="s">
-        <v>2464</v>
+        <v>2463</v>
       </c>
       <c r="M1231">
         <v>2</v>
@@ -63808,7 +63805,7 @@
         <v>2066</v>
       </c>
       <c r="F1232" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1232" t="b">
         <v>1</v>
@@ -63821,7 +63818,7 @@
       </c>
       <c r="J1232" s="6"/>
       <c r="L1232" s="3" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
       <c r="M1232">
         <v>2</v>
@@ -63854,7 +63851,7 @@
         <v>2067</v>
       </c>
       <c r="F1233" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1233" t="b">
         <v>1</v>
@@ -63867,7 +63864,7 @@
       </c>
       <c r="J1233" s="6"/>
       <c r="L1233" s="3" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
       <c r="M1233">
         <v>2</v>
@@ -63900,7 +63897,7 @@
         <v>2068</v>
       </c>
       <c r="F1234" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1234" t="b">
         <v>1</v>
@@ -63913,7 +63910,7 @@
       </c>
       <c r="J1234" s="6"/>
       <c r="L1234" s="3" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="M1234">
         <v>2</v>
@@ -63946,7 +63943,7 @@
         <v>2069</v>
       </c>
       <c r="F1235" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1235" t="b">
         <v>1</v>
@@ -63959,7 +63956,7 @@
       </c>
       <c r="J1235" s="6"/>
       <c r="L1235" s="3" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="M1235">
         <v>2</v>
@@ -63992,7 +63989,7 @@
         <v>2070</v>
       </c>
       <c r="F1236" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1236" t="b">
         <v>1</v>
@@ -64005,7 +64002,7 @@
       </c>
       <c r="J1236" s="6"/>
       <c r="L1236" s="3" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
       <c r="M1236">
         <v>2</v>
@@ -64038,7 +64035,7 @@
         <v>2071</v>
       </c>
       <c r="F1237" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1237" t="b">
         <v>1</v>
@@ -64051,7 +64048,7 @@
       </c>
       <c r="J1237" s="6"/>
       <c r="L1237" s="3" t="s">
-        <v>2474</v>
+        <v>2473</v>
       </c>
       <c r="M1237">
         <v>2</v>
@@ -64084,7 +64081,7 @@
         <v>2072</v>
       </c>
       <c r="F1238" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1238" t="b">
         <v>1</v>
@@ -64097,7 +64094,7 @@
       </c>
       <c r="J1238" s="6"/>
       <c r="L1238" s="3" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="M1238">
         <v>2</v>
@@ -64130,7 +64127,7 @@
         <v>2073</v>
       </c>
       <c r="F1239" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1239" t="b">
         <v>1</v>
@@ -64143,7 +64140,7 @@
       </c>
       <c r="J1239" s="6"/>
       <c r="L1239" s="3" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="M1239">
         <v>2</v>
@@ -64176,7 +64173,7 @@
         <v>2074</v>
       </c>
       <c r="F1240" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1240" t="b">
         <v>1</v>
@@ -64189,7 +64186,7 @@
       </c>
       <c r="J1240" s="6"/>
       <c r="L1240" s="3" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="M1240">
         <v>2</v>
@@ -64222,7 +64219,7 @@
         <v>2075</v>
       </c>
       <c r="F1241" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1241" t="b">
         <v>1</v>
@@ -64235,7 +64232,7 @@
       </c>
       <c r="J1241" s="6"/>
       <c r="L1241" s="3" t="s">
-        <v>2480</v>
+        <v>2479</v>
       </c>
       <c r="M1241">
         <v>2</v>
@@ -64268,7 +64265,7 @@
         <v>2076</v>
       </c>
       <c r="F1242" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1242" t="b">
         <v>1</v>
@@ -64281,7 +64278,7 @@
       </c>
       <c r="J1242" s="6"/>
       <c r="L1242" s="3" t="s">
-        <v>2481</v>
+        <v>2480</v>
       </c>
       <c r="M1242">
         <v>2</v>
@@ -64314,7 +64311,7 @@
         <v>2077</v>
       </c>
       <c r="F1243" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1243" t="b">
         <v>1</v>
@@ -64327,7 +64324,7 @@
       </c>
       <c r="J1243" s="6"/>
       <c r="L1243" s="3" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="M1243">
         <v>2</v>
@@ -64360,7 +64357,7 @@
         <v>2078</v>
       </c>
       <c r="F1244" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1244" t="b">
         <v>1</v>
@@ -64373,7 +64370,7 @@
       </c>
       <c r="J1244" s="6"/>
       <c r="L1244" s="3" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
       <c r="M1244">
         <v>2</v>
@@ -64406,7 +64403,7 @@
         <v>2079</v>
       </c>
       <c r="F1245" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1245" t="b">
         <v>1</v>
@@ -64419,7 +64416,7 @@
       </c>
       <c r="J1245" s="6"/>
       <c r="L1245" s="3" t="s">
-        <v>2484</v>
+        <v>2483</v>
       </c>
       <c r="M1245">
         <v>2</v>
@@ -64452,7 +64449,7 @@
         <v>2080</v>
       </c>
       <c r="F1246" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1246" t="b">
         <v>1</v>
@@ -64465,7 +64462,7 @@
       </c>
       <c r="J1246" s="6"/>
       <c r="L1246" s="3" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="M1246">
         <v>2</v>
@@ -64498,7 +64495,7 @@
         <v>2081</v>
       </c>
       <c r="F1247" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1247" t="b">
         <v>1</v>
@@ -64511,7 +64508,7 @@
       </c>
       <c r="J1247" s="6"/>
       <c r="L1247" s="3" t="s">
-        <v>2486</v>
+        <v>2485</v>
       </c>
       <c r="M1247">
         <v>2</v>
@@ -64544,7 +64541,7 @@
         <v>2082</v>
       </c>
       <c r="F1248" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1248" t="b">
         <v>1</v>
@@ -64557,7 +64554,7 @@
       </c>
       <c r="J1248" s="6"/>
       <c r="L1248" s="3" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="M1248">
         <v>2</v>
@@ -64590,7 +64587,7 @@
         <v>2083</v>
       </c>
       <c r="F1249" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1249" t="b">
         <v>1</v>
@@ -64603,7 +64600,7 @@
       </c>
       <c r="J1249" s="6"/>
       <c r="L1249" s="3" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="M1249">
         <v>2</v>
@@ -64636,7 +64633,7 @@
         <v>2084</v>
       </c>
       <c r="F1250" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1250" t="b">
         <v>1</v>
@@ -64649,7 +64646,7 @@
       </c>
       <c r="J1250" s="6"/>
       <c r="L1250" s="3" t="s">
-        <v>2487</v>
+        <v>2486</v>
       </c>
       <c r="M1250">
         <v>2</v>
@@ -64682,7 +64679,7 @@
         <v>2085</v>
       </c>
       <c r="F1251" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1251" t="b">
         <v>1</v>
@@ -64695,7 +64692,7 @@
       </c>
       <c r="J1251" s="6"/>
       <c r="L1251" s="3" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
       <c r="M1251">
         <v>2</v>
@@ -64728,7 +64725,7 @@
         <v>2086</v>
       </c>
       <c r="F1252" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1252" t="b">
         <v>1</v>
@@ -64741,7 +64738,7 @@
       </c>
       <c r="J1252" s="6"/>
       <c r="L1252" s="3" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
       <c r="M1252">
         <v>2</v>
@@ -64774,7 +64771,7 @@
         <v>2087</v>
       </c>
       <c r="F1253" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1253" t="b">
         <v>1</v>
@@ -64787,7 +64784,7 @@
       </c>
       <c r="J1253" s="6"/>
       <c r="L1253" s="3" t="s">
-        <v>2490</v>
+        <v>2489</v>
       </c>
       <c r="M1253">
         <v>2</v>
@@ -64820,7 +64817,7 @@
         <v>2088</v>
       </c>
       <c r="F1254" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1254" t="b">
         <v>1</v>
@@ -64833,7 +64830,7 @@
       </c>
       <c r="J1254" s="6"/>
       <c r="L1254" s="3" t="s">
-        <v>2491</v>
+        <v>2490</v>
       </c>
       <c r="M1254">
         <v>2</v>
@@ -64866,7 +64863,7 @@
         <v>2089</v>
       </c>
       <c r="F1255" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1255" t="b">
         <v>1</v>
@@ -64879,7 +64876,7 @@
       </c>
       <c r="J1255" s="6"/>
       <c r="L1255" s="3" t="s">
-        <v>2492</v>
+        <v>2491</v>
       </c>
       <c r="M1255">
         <v>2</v>
@@ -64912,7 +64909,7 @@
         <v>2090</v>
       </c>
       <c r="F1256" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1256" t="b">
         <v>1</v>
@@ -64925,7 +64922,7 @@
       </c>
       <c r="J1256" s="6"/>
       <c r="L1256" s="3" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
       <c r="M1256">
         <v>2</v>
@@ -64958,7 +64955,7 @@
         <v>2091</v>
       </c>
       <c r="F1257" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1257" t="b">
         <v>1</v>
@@ -64971,7 +64968,7 @@
       </c>
       <c r="J1257" s="6"/>
       <c r="L1257" s="3" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="M1257">
         <v>2</v>
@@ -65004,7 +65001,7 @@
         <v>2092</v>
       </c>
       <c r="F1258" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1258" t="b">
         <v>1</v>
@@ -65017,7 +65014,7 @@
       </c>
       <c r="J1258" s="6"/>
       <c r="L1258" s="3" t="s">
-        <v>2499</v>
+        <v>2498</v>
       </c>
       <c r="M1258">
         <v>2</v>
@@ -65050,7 +65047,7 @@
         <v>2093</v>
       </c>
       <c r="F1259" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1259" t="b">
         <v>1</v>
@@ -65063,7 +65060,7 @@
       </c>
       <c r="J1259" s="6"/>
       <c r="L1259" s="3" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="M1259">
         <v>2</v>
@@ -65096,7 +65093,7 @@
         <v>2094</v>
       </c>
       <c r="F1260" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1260" t="b">
         <v>1</v>
@@ -65109,7 +65106,7 @@
       </c>
       <c r="J1260" s="6"/>
       <c r="L1260" s="3" t="s">
-        <v>2493</v>
+        <v>2492</v>
       </c>
       <c r="M1260">
         <v>2</v>
@@ -65142,7 +65139,7 @@
         <v>2095</v>
       </c>
       <c r="F1261" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1261" t="b">
         <v>1</v>
@@ -65155,7 +65152,7 @@
       </c>
       <c r="J1261" s="6"/>
       <c r="L1261" s="3" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="M1261">
         <v>2</v>
@@ -65188,7 +65185,7 @@
         <v>2096</v>
       </c>
       <c r="F1262" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1262" t="b">
         <v>1</v>
@@ -65201,7 +65198,7 @@
       </c>
       <c r="J1262" s="6"/>
       <c r="L1262" s="3" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
       <c r="M1262">
         <v>2</v>
@@ -65234,7 +65231,7 @@
         <v>2097</v>
       </c>
       <c r="F1263" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1263" t="b">
         <v>1</v>
@@ -65247,7 +65244,7 @@
       </c>
       <c r="J1263" s="6"/>
       <c r="L1263" s="3" t="s">
-        <v>2496</v>
+        <v>2495</v>
       </c>
       <c r="M1263">
         <v>2</v>
@@ -65280,7 +65277,7 @@
         <v>2098</v>
       </c>
       <c r="F1264" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1264" t="b">
         <v>1</v>
@@ -65293,7 +65290,7 @@
       </c>
       <c r="J1264" s="6"/>
       <c r="L1264" s="3" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="M1264">
         <v>2</v>
@@ -65326,7 +65323,7 @@
         <v>2099</v>
       </c>
       <c r="F1265" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1265" t="b">
         <v>1</v>
@@ -65339,7 +65336,7 @@
       </c>
       <c r="J1265" s="6"/>
       <c r="L1265" s="3" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="M1265">
         <v>2</v>
@@ -65372,7 +65369,7 @@
         <v>2100</v>
       </c>
       <c r="F1266" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1266" t="b">
         <v>1</v>
@@ -65385,7 +65382,7 @@
       </c>
       <c r="J1266" s="6"/>
       <c r="L1266" s="3" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="M1266">
         <v>2</v>
@@ -65418,7 +65415,7 @@
         <v>2101</v>
       </c>
       <c r="F1267" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1267" t="b">
         <v>1</v>
@@ -65431,7 +65428,7 @@
       </c>
       <c r="J1267" s="6"/>
       <c r="L1267" s="3" t="s">
-        <v>2504</v>
+        <v>2503</v>
       </c>
       <c r="M1267">
         <v>2</v>
@@ -65464,7 +65461,7 @@
         <v>2102</v>
       </c>
       <c r="F1268" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1268" t="b">
         <v>1</v>
@@ -65477,7 +65474,7 @@
       </c>
       <c r="J1268" s="6"/>
       <c r="L1268" s="3" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="M1268">
         <v>2</v>
@@ -65510,7 +65507,7 @@
         <v>2103</v>
       </c>
       <c r="F1269" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1269" t="b">
         <v>1</v>
@@ -65523,7 +65520,7 @@
       </c>
       <c r="J1269" s="6"/>
       <c r="L1269" s="3" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="M1269">
         <v>2</v>
@@ -65556,7 +65553,7 @@
         <v>2104</v>
       </c>
       <c r="F1270" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1270" t="b">
         <v>1</v>
@@ -65569,7 +65566,7 @@
       </c>
       <c r="J1270" s="6"/>
       <c r="L1270" s="3" t="s">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="M1270">
         <v>2</v>
@@ -65602,7 +65599,7 @@
         <v>2105</v>
       </c>
       <c r="F1271" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1271" t="b">
         <v>1</v>
@@ -65615,7 +65612,7 @@
       </c>
       <c r="J1271" s="6"/>
       <c r="L1271" s="3" t="s">
-        <v>2508</v>
+        <v>2507</v>
       </c>
       <c r="M1271">
         <v>2</v>
@@ -65648,7 +65645,7 @@
         <v>2106</v>
       </c>
       <c r="F1272" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1272" t="b">
         <v>1</v>
@@ -65661,7 +65658,7 @@
       </c>
       <c r="J1272" s="6"/>
       <c r="L1272" s="3" t="s">
-        <v>2509</v>
+        <v>2508</v>
       </c>
       <c r="M1272">
         <v>2</v>
@@ -65694,7 +65691,7 @@
         <v>2107</v>
       </c>
       <c r="F1273" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1273" t="b">
         <v>1</v>
@@ -65707,7 +65704,7 @@
       </c>
       <c r="J1273" s="6"/>
       <c r="L1273" s="3" t="s">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="M1273">
         <v>2</v>
@@ -65740,7 +65737,7 @@
         <v>2108</v>
       </c>
       <c r="F1274" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1274" t="b">
         <v>1</v>
@@ -65753,7 +65750,7 @@
       </c>
       <c r="J1274" s="6"/>
       <c r="L1274" s="3" t="s">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="M1274">
         <v>2</v>
@@ -65786,7 +65783,7 @@
         <v>2109</v>
       </c>
       <c r="F1275" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1275" t="b">
         <v>1</v>
@@ -65799,7 +65796,7 @@
       </c>
       <c r="J1275" s="6"/>
       <c r="L1275" s="3" t="s">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="M1275">
         <v>2</v>
@@ -65832,7 +65829,7 @@
         <v>2110</v>
       </c>
       <c r="F1276" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1276" t="b">
         <v>1</v>
@@ -65845,7 +65842,7 @@
       </c>
       <c r="J1276" s="6"/>
       <c r="L1276" s="3" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
       <c r="M1276">
         <v>2</v>
@@ -65878,7 +65875,7 @@
         <v>2111</v>
       </c>
       <c r="F1277" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1277" t="b">
         <v>1</v>
@@ -65891,7 +65888,7 @@
       </c>
       <c r="J1277" s="6"/>
       <c r="L1277" s="3" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
       <c r="M1277">
         <v>2</v>
@@ -65924,7 +65921,7 @@
         <v>2112</v>
       </c>
       <c r="F1278" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1278" t="b">
         <v>1</v>
@@ -65937,7 +65934,7 @@
       </c>
       <c r="J1278" s="6"/>
       <c r="L1278" s="3" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="M1278">
         <v>2</v>
@@ -65970,7 +65967,7 @@
         <v>2113</v>
       </c>
       <c r="F1279" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1279" t="b">
         <v>1</v>
@@ -65983,7 +65980,7 @@
       </c>
       <c r="J1279" s="6"/>
       <c r="L1279" s="3" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="M1279">
         <v>2</v>
@@ -66016,7 +66013,7 @@
         <v>2114</v>
       </c>
       <c r="F1280" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1280" t="b">
         <v>1</v>
@@ -66029,7 +66026,7 @@
       </c>
       <c r="J1280" s="6"/>
       <c r="L1280" s="3" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
       <c r="M1280">
         <v>2</v>
@@ -66062,7 +66059,7 @@
         <v>2115</v>
       </c>
       <c r="F1281" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1281" t="b">
         <v>1</v>
@@ -66075,7 +66072,7 @@
       </c>
       <c r="J1281" s="6"/>
       <c r="L1281" s="3" t="s">
-        <v>2518</v>
+        <v>2517</v>
       </c>
       <c r="M1281">
         <v>2</v>
@@ -66108,7 +66105,7 @@
         <v>2116</v>
       </c>
       <c r="F1282" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1282" t="b">
         <v>1</v>
@@ -66121,7 +66118,7 @@
       </c>
       <c r="J1282" s="6"/>
       <c r="L1282" s="3" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
       <c r="M1282">
         <v>2</v>
@@ -66154,7 +66151,7 @@
         <v>2117</v>
       </c>
       <c r="F1283" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1283" t="b">
         <v>1</v>
@@ -66167,7 +66164,7 @@
       </c>
       <c r="J1283" s="6"/>
       <c r="L1283" s="3" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="M1283">
         <v>2</v>
@@ -66200,7 +66197,7 @@
         <v>2118</v>
       </c>
       <c r="F1284" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1284" t="b">
         <v>1</v>
@@ -66213,7 +66210,7 @@
       </c>
       <c r="J1284" s="6"/>
       <c r="L1284" s="3" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
       <c r="M1284">
         <v>2</v>
@@ -66246,7 +66243,7 @@
         <v>2119</v>
       </c>
       <c r="F1285" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1285" t="b">
         <v>1</v>
@@ -66259,7 +66256,7 @@
       </c>
       <c r="J1285" s="6"/>
       <c r="L1285" s="3" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="M1285">
         <v>2</v>
@@ -66292,7 +66289,7 @@
         <v>2120</v>
       </c>
       <c r="F1286" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1286" t="b">
         <v>1</v>
@@ -66305,7 +66302,7 @@
       </c>
       <c r="J1286" s="6"/>
       <c r="L1286" s="3" t="s">
-        <v>2523</v>
+        <v>2522</v>
       </c>
       <c r="M1286">
         <v>2</v>
@@ -66338,7 +66335,7 @@
         <v>2121</v>
       </c>
       <c r="F1287" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1287" t="b">
         <v>1</v>
@@ -66351,7 +66348,7 @@
       </c>
       <c r="J1287" s="6"/>
       <c r="L1287" s="3" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
       <c r="M1287">
         <v>2</v>
@@ -66384,7 +66381,7 @@
         <v>2122</v>
       </c>
       <c r="F1288" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1288" t="b">
         <v>1</v>
@@ -66397,7 +66394,7 @@
       </c>
       <c r="J1288" s="6"/>
       <c r="L1288" s="3" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
       <c r="M1288">
         <v>2</v>
@@ -66430,7 +66427,7 @@
         <v>2123</v>
       </c>
       <c r="F1289" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1289" t="b">
         <v>1</v>
@@ -66443,7 +66440,7 @@
       </c>
       <c r="J1289" s="6"/>
       <c r="L1289" s="3" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
       <c r="M1289">
         <v>2</v>
@@ -66476,7 +66473,7 @@
         <v>2124</v>
       </c>
       <c r="F1290" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1290" t="b">
         <v>1</v>
@@ -66489,7 +66486,7 @@
       </c>
       <c r="J1290" s="6"/>
       <c r="L1290" s="3" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
       <c r="M1290">
         <v>2</v>
@@ -66522,7 +66519,7 @@
         <v>2125</v>
       </c>
       <c r="F1291" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1291" t="b">
         <v>1</v>
@@ -66535,7 +66532,7 @@
       </c>
       <c r="J1291" s="6"/>
       <c r="L1291" s="3" t="s">
-        <v>2528</v>
+        <v>2527</v>
       </c>
       <c r="M1291">
         <v>2</v>
@@ -66568,7 +66565,7 @@
         <v>2126</v>
       </c>
       <c r="F1292" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1292" t="b">
         <v>1</v>
@@ -66581,7 +66578,7 @@
       </c>
       <c r="J1292" s="6"/>
       <c r="L1292" s="3" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="M1292">
         <v>2</v>
@@ -66614,7 +66611,7 @@
         <v>2127</v>
       </c>
       <c r="F1293" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1293" t="b">
         <v>1</v>
@@ -66627,7 +66624,7 @@
       </c>
       <c r="J1293" s="6"/>
       <c r="L1293" s="3" t="s">
-        <v>2530</v>
+        <v>2529</v>
       </c>
       <c r="M1293">
         <v>2</v>
@@ -66660,7 +66657,7 @@
         <v>2128</v>
       </c>
       <c r="F1294" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1294" t="b">
         <v>1</v>
@@ -66673,7 +66670,7 @@
       </c>
       <c r="J1294" s="6"/>
       <c r="L1294" s="3" t="s">
-        <v>2531</v>
+        <v>2530</v>
       </c>
       <c r="M1294">
         <v>2</v>
@@ -66706,7 +66703,7 @@
         <v>2129</v>
       </c>
       <c r="F1295" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1295" t="b">
         <v>1</v>
@@ -66719,7 +66716,7 @@
       </c>
       <c r="J1295" s="6"/>
       <c r="L1295" s="3" t="s">
-        <v>2539</v>
+        <v>2538</v>
       </c>
       <c r="M1295">
         <v>2</v>
@@ -66752,7 +66749,7 @@
         <v>2130</v>
       </c>
       <c r="F1296" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1296" t="b">
         <v>1</v>
@@ -66765,7 +66762,7 @@
       </c>
       <c r="J1296" s="6"/>
       <c r="L1296" s="3" t="s">
-        <v>2532</v>
+        <v>2531</v>
       </c>
       <c r="M1296">
         <v>2</v>
@@ -66798,7 +66795,7 @@
         <v>2131</v>
       </c>
       <c r="F1297" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1297" t="b">
         <v>1</v>
@@ -66811,7 +66808,7 @@
       </c>
       <c r="J1297" s="6"/>
       <c r="L1297" s="3" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
       <c r="M1297">
         <v>2</v>
@@ -66844,7 +66841,7 @@
         <v>2132</v>
       </c>
       <c r="F1298" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1298" t="b">
         <v>1</v>
@@ -66857,7 +66854,7 @@
       </c>
       <c r="J1298" s="6"/>
       <c r="L1298" s="3" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
       <c r="M1298">
         <v>2</v>
@@ -66890,7 +66887,7 @@
         <v>2133</v>
       </c>
       <c r="F1299" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1299" t="b">
         <v>1</v>
@@ -66903,7 +66900,7 @@
       </c>
       <c r="J1299" s="6"/>
       <c r="L1299" s="3" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="M1299">
         <v>2</v>
@@ -66936,7 +66933,7 @@
         <v>2134</v>
       </c>
       <c r="F1300" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1300" t="b">
         <v>1</v>
@@ -66949,7 +66946,7 @@
       </c>
       <c r="J1300" s="6"/>
       <c r="L1300" s="3" t="s">
-        <v>2536</v>
+        <v>2535</v>
       </c>
       <c r="M1300">
         <v>2</v>
@@ -66982,7 +66979,7 @@
         <v>2135</v>
       </c>
       <c r="F1301" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1301" t="b">
         <v>1</v>
@@ -66995,7 +66992,7 @@
       </c>
       <c r="J1301" s="6"/>
       <c r="L1301" s="3" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
       <c r="M1301">
         <v>2</v>
@@ -67028,7 +67025,7 @@
         <v>2136</v>
       </c>
       <c r="F1302" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1302" t="b">
         <v>1</v>
@@ -67041,7 +67038,7 @@
       </c>
       <c r="J1302" s="6"/>
       <c r="L1302" s="3" t="s">
-        <v>2538</v>
+        <v>2537</v>
       </c>
       <c r="M1302">
         <v>2</v>
@@ -67074,7 +67071,7 @@
         <v>2137</v>
       </c>
       <c r="F1303" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1303" t="b">
         <v>1</v>
@@ -67087,7 +67084,7 @@
       </c>
       <c r="J1303" s="6"/>
       <c r="L1303" s="3" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="M1303">
         <v>2</v>
@@ -67120,7 +67117,7 @@
         <v>2138</v>
       </c>
       <c r="F1304" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1304" t="b">
         <v>1</v>
@@ -67133,7 +67130,7 @@
       </c>
       <c r="J1304" s="6"/>
       <c r="L1304" s="3" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="M1304">
         <v>2</v>
@@ -67166,7 +67163,7 @@
         <v>2139</v>
       </c>
       <c r="F1305" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1305" t="b">
         <v>1</v>
@@ -67179,7 +67176,7 @@
       </c>
       <c r="J1305" s="6"/>
       <c r="L1305" s="3" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="M1305">
         <v>2</v>
@@ -67212,7 +67209,7 @@
         <v>2140</v>
       </c>
       <c r="F1306" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1306" t="b">
         <v>1</v>
@@ -67225,7 +67222,7 @@
       </c>
       <c r="J1306" s="6"/>
       <c r="L1306" s="3" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
       <c r="M1306">
         <v>2</v>
@@ -67258,7 +67255,7 @@
         <v>2141</v>
       </c>
       <c r="F1307" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1307" t="b">
         <v>1</v>
@@ -67271,7 +67268,7 @@
       </c>
       <c r="J1307" s="6"/>
       <c r="L1307" s="3" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="M1307">
         <v>2</v>
@@ -67304,7 +67301,7 @@
         <v>2142</v>
       </c>
       <c r="F1308" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1308" t="b">
         <v>1</v>
@@ -67317,7 +67314,7 @@
       </c>
       <c r="J1308" s="6"/>
       <c r="L1308" s="3" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="M1308">
         <v>2</v>
@@ -67350,7 +67347,7 @@
         <v>2143</v>
       </c>
       <c r="F1309" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1309" t="b">
         <v>1</v>
@@ -67363,7 +67360,7 @@
       </c>
       <c r="J1309" s="6"/>
       <c r="L1309" s="3" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="M1309">
         <v>2</v>
@@ -67396,7 +67393,7 @@
         <v>2144</v>
       </c>
       <c r="F1310" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1310" t="b">
         <v>1</v>
@@ -67409,7 +67406,7 @@
       </c>
       <c r="J1310" s="6"/>
       <c r="L1310" s="3" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="M1310">
         <v>2</v>
@@ -67442,7 +67439,7 @@
         <v>2145</v>
       </c>
       <c r="F1311" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1311" t="b">
         <v>1</v>
@@ -67455,7 +67452,7 @@
       </c>
       <c r="J1311" s="6"/>
       <c r="L1311" s="3" t="s">
-        <v>2548</v>
+        <v>2547</v>
       </c>
       <c r="M1311">
         <v>2</v>
@@ -67488,7 +67485,7 @@
         <v>2146</v>
       </c>
       <c r="F1312" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1312" t="b">
         <v>1</v>
@@ -67501,7 +67498,7 @@
       </c>
       <c r="J1312" s="6"/>
       <c r="L1312" s="3" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="M1312">
         <v>2</v>
@@ -67534,7 +67531,7 @@
         <v>2147</v>
       </c>
       <c r="F1313" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1313" t="b">
         <v>1</v>
@@ -67547,7 +67544,7 @@
       </c>
       <c r="J1313" s="6"/>
       <c r="L1313" s="3" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="M1313">
         <v>2</v>
@@ -67580,7 +67577,7 @@
         <v>2148</v>
       </c>
       <c r="F1314" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1314" t="b">
         <v>1</v>
@@ -67593,7 +67590,7 @@
       </c>
       <c r="J1314" s="6"/>
       <c r="L1314" s="3" t="s">
-        <v>2551</v>
+        <v>2550</v>
       </c>
       <c r="M1314">
         <v>2</v>
@@ -67626,7 +67623,7 @@
         <v>2149</v>
       </c>
       <c r="F1315" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1315" t="b">
         <v>1</v>
@@ -67639,7 +67636,7 @@
       </c>
       <c r="J1315" s="6"/>
       <c r="L1315" s="3" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="M1315">
         <v>2</v>
@@ -67672,7 +67669,7 @@
         <v>2150</v>
       </c>
       <c r="F1316" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1316" t="b">
         <v>1</v>
@@ -67685,7 +67682,7 @@
       </c>
       <c r="J1316" s="6"/>
       <c r="L1316" s="3" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="M1316">
         <v>2</v>
@@ -67718,7 +67715,7 @@
         <v>2151</v>
       </c>
       <c r="F1317" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1317" t="b">
         <v>1</v>
@@ -67731,7 +67728,7 @@
       </c>
       <c r="J1317" s="6"/>
       <c r="L1317" s="3" t="s">
-        <v>2554</v>
+        <v>2553</v>
       </c>
       <c r="M1317">
         <v>2</v>
@@ -67764,7 +67761,7 @@
         <v>2152</v>
       </c>
       <c r="F1318" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1318" t="b">
         <v>1</v>
@@ -67777,7 +67774,7 @@
       </c>
       <c r="J1318" s="6"/>
       <c r="L1318" s="3" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="M1318">
         <v>2</v>
@@ -67810,7 +67807,7 @@
         <v>2153</v>
       </c>
       <c r="F1319" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1319" t="b">
         <v>1</v>
@@ -67823,7 +67820,7 @@
       </c>
       <c r="J1319" s="6"/>
       <c r="L1319" s="3" t="s">
-        <v>2556</v>
+        <v>2555</v>
       </c>
       <c r="M1319">
         <v>2</v>
@@ -67856,7 +67853,7 @@
         <v>2154</v>
       </c>
       <c r="F1320" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1320" t="b">
         <v>1</v>
@@ -67869,7 +67866,7 @@
       </c>
       <c r="J1320" s="6"/>
       <c r="L1320" s="3" t="s">
-        <v>2557</v>
+        <v>2556</v>
       </c>
       <c r="M1320">
         <v>2</v>
@@ -67902,7 +67899,7 @@
         <v>2155</v>
       </c>
       <c r="F1321" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1321" t="b">
         <v>1</v>
@@ -67915,7 +67912,7 @@
       </c>
       <c r="J1321" s="6"/>
       <c r="L1321" s="3" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M1321">
         <v>2</v>
@@ -67948,7 +67945,7 @@
         <v>2156</v>
       </c>
       <c r="F1322" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1322" t="b">
         <v>1</v>
@@ -67961,7 +67958,7 @@
       </c>
       <c r="J1322" s="6"/>
       <c r="L1322" s="3" t="s">
-        <v>2559</v>
+        <v>2558</v>
       </c>
       <c r="M1322">
         <v>2</v>
@@ -67994,7 +67991,7 @@
         <v>2157</v>
       </c>
       <c r="F1323" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1323" t="b">
         <v>1</v>
@@ -68007,7 +68004,7 @@
       </c>
       <c r="J1323" s="6"/>
       <c r="L1323" s="3" t="s">
-        <v>2560</v>
+        <v>2559</v>
       </c>
       <c r="M1323">
         <v>2</v>
@@ -68040,7 +68037,7 @@
         <v>2158</v>
       </c>
       <c r="F1324" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1324" t="b">
         <v>1</v>
@@ -68053,7 +68050,7 @@
       </c>
       <c r="J1324" s="6"/>
       <c r="L1324" s="3" t="s">
-        <v>2561</v>
+        <v>2560</v>
       </c>
       <c r="M1324">
         <v>2</v>
@@ -68086,7 +68083,7 @@
         <v>2159</v>
       </c>
       <c r="F1325" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1325" t="b">
         <v>1</v>
@@ -68099,7 +68096,7 @@
       </c>
       <c r="J1325" s="6"/>
       <c r="L1325" s="3" t="s">
-        <v>2562</v>
+        <v>2561</v>
       </c>
       <c r="M1325">
         <v>2</v>
@@ -68132,7 +68129,7 @@
         <v>2160</v>
       </c>
       <c r="F1326" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1326" t="b">
         <v>1</v>
@@ -68145,7 +68142,7 @@
       </c>
       <c r="J1326" s="6"/>
       <c r="L1326" s="3" t="s">
-        <v>2563</v>
+        <v>2562</v>
       </c>
       <c r="M1326">
         <v>2</v>
@@ -68178,7 +68175,7 @@
         <v>2161</v>
       </c>
       <c r="F1327" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1327" t="b">
         <v>1</v>
@@ -68191,7 +68188,7 @@
       </c>
       <c r="J1327" s="6"/>
       <c r="L1327" s="3" t="s">
-        <v>2569</v>
+        <v>2568</v>
       </c>
       <c r="M1327">
         <v>2</v>
@@ -68224,7 +68221,7 @@
         <v>2162</v>
       </c>
       <c r="F1328" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1328" t="b">
         <v>1</v>
@@ -68237,7 +68234,7 @@
       </c>
       <c r="J1328" s="6"/>
       <c r="L1328" s="3" t="s">
-        <v>2564</v>
+        <v>2563</v>
       </c>
       <c r="M1328">
         <v>2</v>
@@ -68270,7 +68267,7 @@
         <v>2163</v>
       </c>
       <c r="F1329" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1329" t="b">
         <v>1</v>
@@ -68283,7 +68280,7 @@
       </c>
       <c r="J1329" s="6"/>
       <c r="L1329" s="3" t="s">
-        <v>2565</v>
+        <v>2564</v>
       </c>
       <c r="M1329">
         <v>2</v>
@@ -68316,7 +68313,7 @@
         <v>2164</v>
       </c>
       <c r="F1330" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1330" t="b">
         <v>1</v>
@@ -68329,7 +68326,7 @@
       </c>
       <c r="J1330" s="6"/>
       <c r="L1330" s="3" t="s">
-        <v>2566</v>
+        <v>2565</v>
       </c>
       <c r="M1330">
         <v>2</v>
@@ -68362,7 +68359,7 @@
         <v>2165</v>
       </c>
       <c r="F1331" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1331" t="b">
         <v>1</v>
@@ -68375,7 +68372,7 @@
       </c>
       <c r="J1331" s="6"/>
       <c r="L1331" s="3" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="M1331">
         <v>2</v>
@@ -68408,7 +68405,7 @@
         <v>2166</v>
       </c>
       <c r="F1332" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1332" t="b">
         <v>1</v>
@@ -68421,7 +68418,7 @@
       </c>
       <c r="J1332" s="6"/>
       <c r="L1332" s="3" t="s">
-        <v>2568</v>
+        <v>2567</v>
       </c>
       <c r="M1332">
         <v>2</v>
@@ -68454,7 +68451,7 @@
         <v>2167</v>
       </c>
       <c r="F1333" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1333" t="b">
         <v>1</v>
@@ -68467,7 +68464,7 @@
       </c>
       <c r="J1333" s="6"/>
       <c r="L1333" s="3" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M1333">
         <v>2</v>
@@ -68500,7 +68497,7 @@
         <v>2168</v>
       </c>
       <c r="F1334" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1334" t="b">
         <v>1</v>
@@ -68513,7 +68510,7 @@
       </c>
       <c r="J1334" s="6"/>
       <c r="L1334" s="3" t="s">
-        <v>2571</v>
+        <v>2570</v>
       </c>
       <c r="M1334">
         <v>2</v>
@@ -68546,7 +68543,7 @@
         <v>2169</v>
       </c>
       <c r="F1335" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1335" t="b">
         <v>1</v>
@@ -68559,7 +68556,7 @@
       </c>
       <c r="J1335" s="6"/>
       <c r="L1335" s="3" t="s">
-        <v>2572</v>
+        <v>2571</v>
       </c>
       <c r="M1335">
         <v>2</v>
@@ -68592,7 +68589,7 @@
         <v>2170</v>
       </c>
       <c r="F1336" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1336" t="b">
         <v>1</v>
@@ -68605,7 +68602,7 @@
       </c>
       <c r="J1336" s="6"/>
       <c r="L1336" s="3" t="s">
-        <v>2573</v>
+        <v>2572</v>
       </c>
       <c r="M1336">
         <v>2</v>
@@ -68638,7 +68635,7 @@
         <v>2171</v>
       </c>
       <c r="F1337" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1337" t="b">
         <v>1</v>
@@ -68651,7 +68648,7 @@
       </c>
       <c r="J1337" s="6"/>
       <c r="L1337" s="3" t="s">
-        <v>2582</v>
+        <v>2581</v>
       </c>
       <c r="M1337">
         <v>2</v>
@@ -68684,7 +68681,7 @@
         <v>2172</v>
       </c>
       <c r="F1338" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1338" t="b">
         <v>1</v>
@@ -68697,7 +68694,7 @@
       </c>
       <c r="J1338" s="6"/>
       <c r="L1338" s="3" t="s">
-        <v>2583</v>
+        <v>2582</v>
       </c>
       <c r="M1338">
         <v>2</v>
@@ -68730,7 +68727,7 @@
         <v>2173</v>
       </c>
       <c r="F1339" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1339" t="b">
         <v>1</v>
@@ -68743,7 +68740,7 @@
       </c>
       <c r="J1339" s="6"/>
       <c r="L1339" s="3" t="s">
-        <v>2584</v>
+        <v>2583</v>
       </c>
       <c r="M1339">
         <v>2</v>
@@ -68776,7 +68773,7 @@
         <v>2174</v>
       </c>
       <c r="F1340" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1340" t="b">
         <v>1</v>
@@ -68789,7 +68786,7 @@
       </c>
       <c r="J1340" s="6"/>
       <c r="L1340" s="3" t="s">
-        <v>2585</v>
+        <v>2584</v>
       </c>
       <c r="M1340">
         <v>2</v>
@@ -68822,7 +68819,7 @@
         <v>2175</v>
       </c>
       <c r="F1341" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1341" t="b">
         <v>1</v>
@@ -68835,7 +68832,7 @@
       </c>
       <c r="J1341" s="6"/>
       <c r="L1341" s="3" t="s">
-        <v>2586</v>
+        <v>2585</v>
       </c>
       <c r="M1341">
         <v>2</v>
@@ -68868,7 +68865,7 @@
         <v>2176</v>
       </c>
       <c r="F1342" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1342" t="b">
         <v>1</v>
@@ -68881,7 +68878,7 @@
       </c>
       <c r="J1342" s="6"/>
       <c r="L1342" s="3" t="s">
-        <v>2587</v>
+        <v>2586</v>
       </c>
       <c r="M1342">
         <v>2</v>
@@ -68914,7 +68911,7 @@
         <v>2177</v>
       </c>
       <c r="F1343" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1343" t="b">
         <v>1</v>
@@ -68927,7 +68924,7 @@
       </c>
       <c r="J1343" s="6"/>
       <c r="L1343" s="3" t="s">
-        <v>2574</v>
+        <v>2573</v>
       </c>
       <c r="M1343">
         <v>2</v>
@@ -68960,7 +68957,7 @@
         <v>2178</v>
       </c>
       <c r="F1344" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1344" t="b">
         <v>1</v>
@@ -68973,7 +68970,7 @@
       </c>
       <c r="J1344" s="6"/>
       <c r="L1344" s="3" t="s">
-        <v>2575</v>
+        <v>2574</v>
       </c>
       <c r="M1344">
         <v>2</v>
@@ -69006,7 +69003,7 @@
         <v>2179</v>
       </c>
       <c r="F1345" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1345" t="b">
         <v>1</v>
@@ -69019,7 +69016,7 @@
       </c>
       <c r="J1345" s="6"/>
       <c r="L1345" s="3" t="s">
-        <v>2576</v>
+        <v>2575</v>
       </c>
       <c r="M1345">
         <v>2</v>
@@ -69052,7 +69049,7 @@
         <v>2180</v>
       </c>
       <c r="F1346" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1346" t="b">
         <v>1</v>
@@ -69065,7 +69062,7 @@
       </c>
       <c r="J1346" s="6"/>
       <c r="L1346" s="3" t="s">
-        <v>2577</v>
+        <v>2576</v>
       </c>
       <c r="M1346">
         <v>2</v>
@@ -69098,7 +69095,7 @@
         <v>2181</v>
       </c>
       <c r="F1347" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1347" t="b">
         <v>1</v>
@@ -69111,7 +69108,7 @@
       </c>
       <c r="J1347" s="6"/>
       <c r="L1347" s="3" t="s">
-        <v>2578</v>
+        <v>2577</v>
       </c>
       <c r="M1347">
         <v>2</v>
@@ -69144,7 +69141,7 @@
         <v>2182</v>
       </c>
       <c r="F1348" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1348" t="b">
         <v>1</v>
@@ -69157,7 +69154,7 @@
       </c>
       <c r="J1348" s="6"/>
       <c r="L1348" s="3" t="s">
-        <v>2579</v>
+        <v>2578</v>
       </c>
       <c r="M1348">
         <v>2</v>
@@ -69190,7 +69187,7 @@
         <v>2183</v>
       </c>
       <c r="F1349" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1349" t="b">
         <v>1</v>
@@ -69203,7 +69200,7 @@
       </c>
       <c r="J1349" s="6"/>
       <c r="L1349" s="3" t="s">
-        <v>2580</v>
+        <v>2579</v>
       </c>
       <c r="M1349">
         <v>2</v>
@@ -69236,7 +69233,7 @@
         <v>2184</v>
       </c>
       <c r="F1350" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1350" t="b">
         <v>1</v>
@@ -69249,7 +69246,7 @@
       </c>
       <c r="J1350" s="6"/>
       <c r="L1350" s="3" t="s">
-        <v>2581</v>
+        <v>2580</v>
       </c>
       <c r="M1350">
         <v>2</v>
@@ -69282,7 +69279,7 @@
         <v>2185</v>
       </c>
       <c r="F1351" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1351" t="b">
         <v>1</v>
@@ -69295,7 +69292,7 @@
       </c>
       <c r="J1351" s="6"/>
       <c r="L1351" s="3" t="s">
-        <v>2588</v>
+        <v>2587</v>
       </c>
       <c r="M1351">
         <v>2</v>
@@ -69328,7 +69325,7 @@
         <v>2186</v>
       </c>
       <c r="F1352" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1352" t="b">
         <v>1</v>
@@ -69341,7 +69338,7 @@
       </c>
       <c r="J1352" s="6"/>
       <c r="L1352" s="3" t="s">
-        <v>2589</v>
+        <v>2588</v>
       </c>
       <c r="M1352">
         <v>2</v>
@@ -69374,7 +69371,7 @@
         <v>2187</v>
       </c>
       <c r="F1353" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1353" t="b">
         <v>1</v>
@@ -69387,7 +69384,7 @@
       </c>
       <c r="J1353" s="6"/>
       <c r="L1353" s="3" t="s">
-        <v>2592</v>
+        <v>2591</v>
       </c>
       <c r="M1353">
         <v>2</v>
@@ -69420,7 +69417,7 @@
         <v>2188</v>
       </c>
       <c r="F1354" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1354" t="b">
         <v>1</v>
@@ -69433,7 +69430,7 @@
       </c>
       <c r="J1354" s="6"/>
       <c r="L1354" s="3" t="s">
-        <v>2593</v>
+        <v>2592</v>
       </c>
       <c r="M1354">
         <v>2</v>
@@ -69466,7 +69463,7 @@
         <v>2189</v>
       </c>
       <c r="F1355" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1355" t="b">
         <v>1</v>
@@ -69479,7 +69476,7 @@
       </c>
       <c r="J1355" s="6"/>
       <c r="L1355" s="3" t="s">
-        <v>2594</v>
+        <v>2593</v>
       </c>
       <c r="M1355">
         <v>2</v>
@@ -69512,7 +69509,7 @@
         <v>2190</v>
       </c>
       <c r="F1356" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1356" t="b">
         <v>1</v>
@@ -69525,7 +69522,7 @@
       </c>
       <c r="J1356" s="6"/>
       <c r="L1356" s="3" t="s">
-        <v>2595</v>
+        <v>2594</v>
       </c>
       <c r="M1356">
         <v>2</v>
@@ -69558,7 +69555,7 @@
         <v>2191</v>
       </c>
       <c r="F1357" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1357" t="b">
         <v>1</v>
@@ -69571,7 +69568,7 @@
       </c>
       <c r="J1357" s="6"/>
       <c r="L1357" s="3" t="s">
-        <v>2596</v>
+        <v>2595</v>
       </c>
       <c r="M1357">
         <v>2</v>
@@ -69604,7 +69601,7 @@
         <v>2192</v>
       </c>
       <c r="F1358" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1358" t="b">
         <v>1</v>
@@ -69617,7 +69614,7 @@
       </c>
       <c r="J1358" s="6"/>
       <c r="L1358" s="3" t="s">
-        <v>2597</v>
+        <v>2596</v>
       </c>
       <c r="M1358">
         <v>2</v>
@@ -69650,7 +69647,7 @@
         <v>2193</v>
       </c>
       <c r="F1359" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1359" t="b">
         <v>1</v>
@@ -69663,7 +69660,7 @@
       </c>
       <c r="J1359" s="6"/>
       <c r="L1359" s="3" t="s">
-        <v>2590</v>
+        <v>2589</v>
       </c>
       <c r="M1359">
         <v>2</v>
@@ -69696,7 +69693,7 @@
         <v>2194</v>
       </c>
       <c r="F1360" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1360" t="b">
         <v>1</v>
@@ -69709,7 +69706,7 @@
       </c>
       <c r="J1360" s="6"/>
       <c r="L1360" s="3" t="s">
-        <v>2591</v>
+        <v>2590</v>
       </c>
       <c r="M1360">
         <v>2</v>
@@ -69742,7 +69739,7 @@
         <v>2195</v>
       </c>
       <c r="F1361" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1361" t="b">
         <v>1</v>
@@ -69755,7 +69752,7 @@
       </c>
       <c r="J1361" s="6"/>
       <c r="L1361" s="3" t="s">
-        <v>2598</v>
+        <v>2597</v>
       </c>
       <c r="M1361">
         <v>2</v>
@@ -69788,7 +69785,7 @@
         <v>2196</v>
       </c>
       <c r="F1362" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1362" t="b">
         <v>1</v>
@@ -69801,7 +69798,7 @@
       </c>
       <c r="J1362" s="6"/>
       <c r="L1362" s="3" t="s">
-        <v>2599</v>
+        <v>2598</v>
       </c>
       <c r="M1362">
         <v>2</v>
@@ -69834,7 +69831,7 @@
         <v>2197</v>
       </c>
       <c r="F1363" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1363" t="b">
         <v>1</v>
@@ -69847,7 +69844,7 @@
       </c>
       <c r="J1363" s="6"/>
       <c r="L1363" s="3" t="s">
-        <v>2600</v>
+        <v>2599</v>
       </c>
       <c r="M1363">
         <v>2</v>
@@ -69880,7 +69877,7 @@
         <v>2198</v>
       </c>
       <c r="F1364" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1364" t="b">
         <v>1</v>
@@ -69893,7 +69890,7 @@
       </c>
       <c r="J1364" s="6"/>
       <c r="L1364" s="3" t="s">
-        <v>2601</v>
+        <v>2600</v>
       </c>
       <c r="M1364">
         <v>2</v>
@@ -69926,7 +69923,7 @@
         <v>2199</v>
       </c>
       <c r="F1365" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1365" t="b">
         <v>1</v>
@@ -69939,7 +69936,7 @@
       </c>
       <c r="J1365" s="6"/>
       <c r="L1365" s="3" t="s">
-        <v>2602</v>
+        <v>2601</v>
       </c>
       <c r="M1365">
         <v>2</v>
@@ -69972,7 +69969,7 @@
         <v>2200</v>
       </c>
       <c r="F1366" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1366" t="b">
         <v>1</v>
@@ -69985,7 +69982,7 @@
       </c>
       <c r="J1366" s="6"/>
       <c r="L1366" s="3" t="s">
-        <v>2603</v>
+        <v>2602</v>
       </c>
       <c r="M1366">
         <v>2</v>
@@ -70018,7 +70015,7 @@
         <v>2201</v>
       </c>
       <c r="F1367" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1367" t="b">
         <v>1</v>
@@ -70031,7 +70028,7 @@
       </c>
       <c r="J1367" s="6"/>
       <c r="L1367" s="3" t="s">
-        <v>2604</v>
+        <v>2603</v>
       </c>
       <c r="M1367">
         <v>2</v>
@@ -70064,7 +70061,7 @@
         <v>2202</v>
       </c>
       <c r="F1368" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1368" t="b">
         <v>1</v>
@@ -70077,7 +70074,7 @@
       </c>
       <c r="J1368" s="6"/>
       <c r="L1368" s="3" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
       <c r="M1368">
         <v>2</v>
@@ -70110,7 +70107,7 @@
         <v>2203</v>
       </c>
       <c r="F1369" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1369" t="b">
         <v>1</v>
@@ -70123,7 +70120,7 @@
       </c>
       <c r="J1369" s="6"/>
       <c r="L1369" s="3" t="s">
-        <v>2606</v>
+        <v>2605</v>
       </c>
       <c r="M1369">
         <v>2</v>
@@ -70156,7 +70153,7 @@
         <v>2204</v>
       </c>
       <c r="F1370" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1370" t="b">
         <v>1</v>
@@ -70169,7 +70166,7 @@
       </c>
       <c r="J1370" s="6"/>
       <c r="L1370" s="3" t="s">
-        <v>2607</v>
+        <v>2606</v>
       </c>
       <c r="M1370">
         <v>2</v>
@@ -70202,7 +70199,7 @@
         <v>2205</v>
       </c>
       <c r="F1371" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1371" t="b">
         <v>1</v>
@@ -70215,7 +70212,7 @@
       </c>
       <c r="J1371" s="6"/>
       <c r="L1371" s="3" t="s">
-        <v>2608</v>
+        <v>2607</v>
       </c>
       <c r="M1371">
         <v>2</v>
@@ -70248,7 +70245,7 @@
         <v>2206</v>
       </c>
       <c r="F1372" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1372" t="b">
         <v>1</v>
@@ -70261,7 +70258,7 @@
       </c>
       <c r="J1372" s="6"/>
       <c r="L1372" s="3" t="s">
-        <v>2609</v>
+        <v>2608</v>
       </c>
       <c r="M1372">
         <v>2</v>
@@ -70294,7 +70291,7 @@
         <v>2207</v>
       </c>
       <c r="F1373" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1373" t="b">
         <v>1</v>
@@ -70307,7 +70304,7 @@
       </c>
       <c r="J1373" s="6"/>
       <c r="L1373" s="3" t="s">
-        <v>2610</v>
+        <v>2609</v>
       </c>
       <c r="M1373">
         <v>2</v>
@@ -70340,7 +70337,7 @@
         <v>2208</v>
       </c>
       <c r="F1374" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1374" t="b">
         <v>1</v>
@@ -70353,7 +70350,7 @@
       </c>
       <c r="J1374" s="6"/>
       <c r="L1374" s="3" t="s">
-        <v>2611</v>
+        <v>2610</v>
       </c>
       <c r="M1374">
         <v>2</v>
@@ -70386,7 +70383,7 @@
         <v>2209</v>
       </c>
       <c r="F1375" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1375" t="b">
         <v>1</v>
@@ -70399,7 +70396,7 @@
       </c>
       <c r="J1375" s="6"/>
       <c r="L1375" s="3" t="s">
-        <v>2612</v>
+        <v>2611</v>
       </c>
       <c r="M1375">
         <v>2</v>
@@ -70432,7 +70429,7 @@
         <v>2210</v>
       </c>
       <c r="F1376" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1376" t="b">
         <v>1</v>
@@ -70445,7 +70442,7 @@
       </c>
       <c r="J1376" s="6"/>
       <c r="L1376" s="3" t="s">
-        <v>2613</v>
+        <v>2612</v>
       </c>
       <c r="M1376">
         <v>2</v>
@@ -70478,7 +70475,7 @@
         <v>2211</v>
       </c>
       <c r="F1377" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1377" t="b">
         <v>1</v>
@@ -70491,7 +70488,7 @@
       </c>
       <c r="J1377" s="6"/>
       <c r="L1377" s="3" t="s">
-        <v>2614</v>
+        <v>2613</v>
       </c>
       <c r="M1377">
         <v>2</v>
@@ -70524,7 +70521,7 @@
         <v>2212</v>
       </c>
       <c r="F1378" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1378" t="b">
         <v>1</v>
@@ -70537,7 +70534,7 @@
       </c>
       <c r="J1378" s="6"/>
       <c r="L1378" s="3" t="s">
-        <v>2616</v>
+        <v>2615</v>
       </c>
       <c r="M1378">
         <v>2</v>
@@ -70570,7 +70567,7 @@
         <v>2213</v>
       </c>
       <c r="F1379" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1379" t="b">
         <v>1</v>
@@ -70583,7 +70580,7 @@
       </c>
       <c r="J1379" s="6"/>
       <c r="L1379" s="3" t="s">
-        <v>2617</v>
+        <v>2616</v>
       </c>
       <c r="M1379">
         <v>2</v>
@@ -70616,7 +70613,7 @@
         <v>2214</v>
       </c>
       <c r="F1380" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1380" t="b">
         <v>1</v>
@@ -70629,7 +70626,7 @@
       </c>
       <c r="J1380" s="6"/>
       <c r="L1380" s="3" t="s">
-        <v>2618</v>
+        <v>2617</v>
       </c>
       <c r="M1380">
         <v>2</v>
@@ -70662,7 +70659,7 @@
         <v>2215</v>
       </c>
       <c r="F1381" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1381" t="b">
         <v>1</v>
@@ -70675,7 +70672,7 @@
       </c>
       <c r="J1381" s="6"/>
       <c r="L1381" s="3" t="s">
-        <v>2619</v>
+        <v>2618</v>
       </c>
       <c r="M1381">
         <v>2</v>
@@ -70708,7 +70705,7 @@
         <v>2216</v>
       </c>
       <c r="F1382" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1382" t="b">
         <v>1</v>
@@ -70721,7 +70718,7 @@
       </c>
       <c r="J1382" s="6"/>
       <c r="L1382" s="3" t="s">
-        <v>2615</v>
+        <v>2614</v>
       </c>
       <c r="M1382">
         <v>2</v>
@@ -70754,7 +70751,7 @@
         <v>2217</v>
       </c>
       <c r="F1383" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1383" t="b">
         <v>1</v>
@@ -70767,7 +70764,7 @@
       </c>
       <c r="J1383" s="6"/>
       <c r="L1383" s="3" t="s">
-        <v>2620</v>
+        <v>2619</v>
       </c>
       <c r="M1383">
         <v>2</v>
@@ -70800,7 +70797,7 @@
         <v>2218</v>
       </c>
       <c r="F1384" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1384" t="b">
         <v>1</v>
@@ -70813,7 +70810,7 @@
       </c>
       <c r="J1384" s="6"/>
       <c r="L1384" s="3" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="M1384">
         <v>2</v>
@@ -70846,7 +70843,7 @@
         <v>2219</v>
       </c>
       <c r="F1385" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1385" t="b">
         <v>1</v>
@@ -70859,7 +70856,7 @@
       </c>
       <c r="J1385" s="6"/>
       <c r="L1385" s="3" t="s">
-        <v>2630</v>
+        <v>2629</v>
       </c>
       <c r="M1385">
         <v>2</v>
@@ -70892,7 +70889,7 @@
         <v>2220</v>
       </c>
       <c r="F1386" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1386" t="b">
         <v>1</v>
@@ -70905,7 +70902,7 @@
       </c>
       <c r="J1386" s="6"/>
       <c r="L1386" s="3" t="s">
-        <v>2631</v>
+        <v>2630</v>
       </c>
       <c r="M1386">
         <v>2</v>
@@ -70938,7 +70935,7 @@
         <v>2221</v>
       </c>
       <c r="F1387" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1387" t="b">
         <v>1</v>
@@ -70951,7 +70948,7 @@
       </c>
       <c r="J1387" s="6"/>
       <c r="L1387" s="3" t="s">
-        <v>2632</v>
+        <v>2631</v>
       </c>
       <c r="M1387">
         <v>2</v>
@@ -70984,7 +70981,7 @@
         <v>2222</v>
       </c>
       <c r="F1388" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1388" t="b">
         <v>1</v>
@@ -70997,7 +70994,7 @@
       </c>
       <c r="J1388" s="6"/>
       <c r="L1388" s="3" t="s">
-        <v>2633</v>
+        <v>2632</v>
       </c>
       <c r="M1388">
         <v>2</v>
@@ -71030,7 +71027,7 @@
         <v>2223</v>
       </c>
       <c r="F1389" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1389" t="b">
         <v>1</v>
@@ -71043,7 +71040,7 @@
       </c>
       <c r="J1389" s="6"/>
       <c r="L1389" s="3" t="s">
-        <v>2634</v>
+        <v>2633</v>
       </c>
       <c r="M1389">
         <v>2</v>
@@ -71076,7 +71073,7 @@
         <v>2224</v>
       </c>
       <c r="F1390" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1390" t="b">
         <v>1</v>
@@ -71089,7 +71086,7 @@
       </c>
       <c r="J1390" s="6"/>
       <c r="L1390" s="3" t="s">
-        <v>2635</v>
+        <v>2634</v>
       </c>
       <c r="M1390">
         <v>2</v>
@@ -71122,7 +71119,7 @@
         <v>2225</v>
       </c>
       <c r="F1391" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1391" t="b">
         <v>1</v>
@@ -71135,7 +71132,7 @@
       </c>
       <c r="J1391" s="6"/>
       <c r="L1391" s="3" t="s">
-        <v>2622</v>
+        <v>2621</v>
       </c>
       <c r="M1391">
         <v>2</v>
@@ -71168,7 +71165,7 @@
         <v>2226</v>
       </c>
       <c r="F1392" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1392" t="b">
         <v>1</v>
@@ -71181,7 +71178,7 @@
       </c>
       <c r="J1392" s="6"/>
       <c r="L1392" s="3" t="s">
-        <v>2623</v>
+        <v>2622</v>
       </c>
       <c r="M1392">
         <v>2</v>
@@ -71214,7 +71211,7 @@
         <v>2227</v>
       </c>
       <c r="F1393" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1393" t="b">
         <v>1</v>
@@ -71227,7 +71224,7 @@
       </c>
       <c r="J1393" s="6"/>
       <c r="L1393" s="3" t="s">
-        <v>2624</v>
+        <v>2623</v>
       </c>
       <c r="M1393">
         <v>2</v>
@@ -71260,7 +71257,7 @@
         <v>2228</v>
       </c>
       <c r="F1394" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1394" t="b">
         <v>1</v>
@@ -71273,7 +71270,7 @@
       </c>
       <c r="J1394" s="6"/>
       <c r="L1394" s="3" t="s">
-        <v>2625</v>
+        <v>2624</v>
       </c>
       <c r="M1394">
         <v>2</v>
@@ -71306,7 +71303,7 @@
         <v>2229</v>
       </c>
       <c r="F1395" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1395" t="b">
         <v>1</v>
@@ -71319,7 +71316,7 @@
       </c>
       <c r="J1395" s="6"/>
       <c r="L1395" s="3" t="s">
-        <v>2626</v>
+        <v>2625</v>
       </c>
       <c r="M1395">
         <v>2</v>
@@ -71352,7 +71349,7 @@
         <v>2230</v>
       </c>
       <c r="F1396" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1396" t="b">
         <v>1</v>
@@ -71365,7 +71362,7 @@
       </c>
       <c r="J1396" s="6"/>
       <c r="L1396" s="3" t="s">
-        <v>2627</v>
+        <v>2626</v>
       </c>
       <c r="M1396">
         <v>2</v>
@@ -71398,7 +71395,7 @@
         <v>2231</v>
       </c>
       <c r="F1397" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1397" t="b">
         <v>1</v>
@@ -71411,7 +71408,7 @@
       </c>
       <c r="J1397" s="6"/>
       <c r="L1397" s="3" t="s">
-        <v>2628</v>
+        <v>2627</v>
       </c>
       <c r="M1397">
         <v>2</v>
@@ -71444,7 +71441,7 @@
         <v>2232</v>
       </c>
       <c r="F1398" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1398" t="b">
         <v>1</v>
@@ -71457,7 +71454,7 @@
       </c>
       <c r="J1398" s="6"/>
       <c r="L1398" s="3" t="s">
-        <v>2629</v>
+        <v>2628</v>
       </c>
       <c r="M1398">
         <v>2</v>
@@ -71490,7 +71487,7 @@
         <v>2233</v>
       </c>
       <c r="F1399" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1399" t="b">
         <v>1</v>
@@ -71503,7 +71500,7 @@
       </c>
       <c r="J1399" s="6"/>
       <c r="L1399" s="3" t="s">
-        <v>2636</v>
+        <v>2635</v>
       </c>
       <c r="M1399">
         <v>2</v>
@@ -71536,7 +71533,7 @@
         <v>2234</v>
       </c>
       <c r="F1400" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1400" t="b">
         <v>1</v>
@@ -71549,7 +71546,7 @@
       </c>
       <c r="J1400" s="6"/>
       <c r="L1400" s="3" t="s">
-        <v>2637</v>
+        <v>2636</v>
       </c>
       <c r="M1400">
         <v>2</v>
@@ -71582,7 +71579,7 @@
         <v>2235</v>
       </c>
       <c r="F1401" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1401" t="b">
         <v>1</v>
@@ -71595,7 +71592,7 @@
       </c>
       <c r="J1401" s="6"/>
       <c r="L1401" s="3" t="s">
-        <v>2638</v>
+        <v>2637</v>
       </c>
       <c r="M1401">
         <v>2</v>
@@ -71628,7 +71625,7 @@
         <v>2236</v>
       </c>
       <c r="F1402" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1402" t="b">
         <v>1</v>
@@ -71641,7 +71638,7 @@
       </c>
       <c r="J1402" s="6"/>
       <c r="L1402" s="3" t="s">
-        <v>2639</v>
+        <v>2638</v>
       </c>
       <c r="M1402">
         <v>2</v>
@@ -71674,7 +71671,7 @@
         <v>2237</v>
       </c>
       <c r="F1403" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1403" t="b">
         <v>1</v>
@@ -71687,7 +71684,7 @@
       </c>
       <c r="J1403" s="6"/>
       <c r="L1403" s="3" t="s">
-        <v>2640</v>
+        <v>2639</v>
       </c>
       <c r="M1403">
         <v>2</v>
@@ -71720,7 +71717,7 @@
         <v>2238</v>
       </c>
       <c r="F1404" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1404" t="b">
         <v>1</v>
@@ -71733,7 +71730,7 @@
       </c>
       <c r="J1404" s="6"/>
       <c r="L1404" s="3" t="s">
-        <v>2641</v>
+        <v>2640</v>
       </c>
       <c r="M1404">
         <v>2</v>
@@ -71766,7 +71763,7 @@
         <v>2239</v>
       </c>
       <c r="F1405" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1405" t="b">
         <v>1</v>
@@ -71779,7 +71776,7 @@
       </c>
       <c r="J1405" s="6"/>
       <c r="L1405" s="3" t="s">
-        <v>2645</v>
+        <v>2644</v>
       </c>
       <c r="M1405">
         <v>2</v>
@@ -71812,7 +71809,7 @@
         <v>2240</v>
       </c>
       <c r="F1406" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1406" t="b">
         <v>1</v>
@@ -71825,7 +71822,7 @@
       </c>
       <c r="J1406" s="6"/>
       <c r="L1406" s="3" t="s">
-        <v>2646</v>
+        <v>2645</v>
       </c>
       <c r="M1406">
         <v>2</v>
@@ -71858,7 +71855,7 @@
         <v>2241</v>
       </c>
       <c r="F1407" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1407" t="b">
         <v>1</v>
@@ -71871,7 +71868,7 @@
       </c>
       <c r="J1407" s="6"/>
       <c r="L1407" s="3" t="s">
-        <v>2647</v>
+        <v>2646</v>
       </c>
       <c r="M1407">
         <v>2</v>
@@ -71904,7 +71901,7 @@
         <v>2242</v>
       </c>
       <c r="F1408" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1408" t="b">
         <v>1</v>
@@ -71917,7 +71914,7 @@
       </c>
       <c r="J1408" s="6"/>
       <c r="L1408" s="3" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
       <c r="M1408">
         <v>2</v>
@@ -71950,7 +71947,7 @@
         <v>2243</v>
       </c>
       <c r="F1409" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1409" t="b">
         <v>1</v>
@@ -71963,7 +71960,7 @@
       </c>
       <c r="J1409" s="6"/>
       <c r="L1409" s="3" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="M1409">
         <v>2</v>
@@ -71996,7 +71993,7 @@
         <v>2244</v>
       </c>
       <c r="F1410" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1410" t="b">
         <v>1</v>
@@ -72009,7 +72006,7 @@
       </c>
       <c r="J1410" s="6"/>
       <c r="L1410" s="3" t="s">
-        <v>2644</v>
+        <v>2643</v>
       </c>
       <c r="M1410">
         <v>2</v>
@@ -72042,7 +72039,7 @@
         <v>2245</v>
       </c>
       <c r="F1411" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1411" t="b">
         <v>1</v>
@@ -72055,7 +72052,7 @@
       </c>
       <c r="J1411" s="6"/>
       <c r="L1411" s="3" t="s">
-        <v>2649</v>
+        <v>2648</v>
       </c>
       <c r="M1411">
         <v>2</v>
@@ -72088,7 +72085,7 @@
         <v>2246</v>
       </c>
       <c r="F1412" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1412" t="b">
         <v>1</v>
@@ -72101,7 +72098,7 @@
       </c>
       <c r="J1412" s="6"/>
       <c r="L1412" s="3" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
       <c r="M1412">
         <v>2</v>
@@ -72134,7 +72131,7 @@
         <v>2247</v>
       </c>
       <c r="F1413" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1413" t="b">
         <v>1</v>
@@ -72147,7 +72144,7 @@
       </c>
       <c r="J1413" s="6"/>
       <c r="L1413" s="3" t="s">
-        <v>2651</v>
+        <v>2650</v>
       </c>
       <c r="M1413">
         <v>2</v>
@@ -72180,7 +72177,7 @@
         <v>2248</v>
       </c>
       <c r="F1414" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1414" t="b">
         <v>1</v>
@@ -72193,7 +72190,7 @@
       </c>
       <c r="J1414" s="6"/>
       <c r="L1414" s="3" t="s">
-        <v>2648</v>
+        <v>2647</v>
       </c>
       <c r="M1414">
         <v>2</v>
@@ -72226,7 +72223,7 @@
         <v>2249</v>
       </c>
       <c r="F1415" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1415" t="b">
         <v>1</v>
@@ -72239,7 +72236,7 @@
       </c>
       <c r="J1415" s="6"/>
       <c r="L1415" s="3" t="s">
-        <v>2652</v>
+        <v>2651</v>
       </c>
       <c r="M1415">
         <v>2</v>
@@ -72272,7 +72269,7 @@
         <v>2250</v>
       </c>
       <c r="F1416" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1416" t="b">
         <v>1</v>
@@ -72285,7 +72282,7 @@
       </c>
       <c r="J1416" s="6"/>
       <c r="L1416" s="3" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
       <c r="M1416">
         <v>2</v>
@@ -72318,7 +72315,7 @@
         <v>2251</v>
       </c>
       <c r="F1417" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1417" t="b">
         <v>1</v>
@@ -72331,7 +72328,7 @@
       </c>
       <c r="J1417" s="6"/>
       <c r="L1417" s="3" t="s">
-        <v>2658</v>
+        <v>2657</v>
       </c>
       <c r="M1417">
         <v>2</v>
@@ -72364,7 +72361,7 @@
         <v>2252</v>
       </c>
       <c r="F1418" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1418" t="b">
         <v>1</v>
@@ -72377,7 +72374,7 @@
       </c>
       <c r="J1418" s="6"/>
       <c r="L1418" s="3" t="s">
-        <v>2659</v>
+        <v>2658</v>
       </c>
       <c r="M1418">
         <v>2</v>
@@ -72410,7 +72407,7 @@
         <v>2253</v>
       </c>
       <c r="F1419" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1419" t="b">
         <v>1</v>
@@ -72423,7 +72420,7 @@
       </c>
       <c r="J1419" s="6"/>
       <c r="L1419" s="3" t="s">
-        <v>2660</v>
+        <v>2659</v>
       </c>
       <c r="M1419">
         <v>2</v>
@@ -72456,7 +72453,7 @@
         <v>2254</v>
       </c>
       <c r="F1420" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1420" t="b">
         <v>1</v>
@@ -72469,7 +72466,7 @@
       </c>
       <c r="J1420" s="6"/>
       <c r="L1420" s="3" t="s">
-        <v>2661</v>
+        <v>2660</v>
       </c>
       <c r="M1420">
         <v>2</v>
@@ -72502,7 +72499,7 @@
         <v>2255</v>
       </c>
       <c r="F1421" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1421" t="b">
         <v>1</v>
@@ -72515,7 +72512,7 @@
       </c>
       <c r="J1421" s="6"/>
       <c r="L1421" s="3" t="s">
-        <v>2662</v>
+        <v>2661</v>
       </c>
       <c r="M1421">
         <v>2</v>
@@ -72548,7 +72545,7 @@
         <v>2256</v>
       </c>
       <c r="F1422" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1422" t="b">
         <v>1</v>
@@ -72561,7 +72558,7 @@
       </c>
       <c r="J1422" s="6"/>
       <c r="L1422" s="3" t="s">
-        <v>2654</v>
+        <v>2653</v>
       </c>
       <c r="M1422">
         <v>2</v>
@@ -72594,7 +72591,7 @@
         <v>2257</v>
       </c>
       <c r="F1423" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1423" t="b">
         <v>1</v>
@@ -72607,7 +72604,7 @@
       </c>
       <c r="J1423" s="6"/>
       <c r="L1423" s="3" t="s">
-        <v>2655</v>
+        <v>2654</v>
       </c>
       <c r="M1423">
         <v>2</v>
@@ -72640,7 +72637,7 @@
         <v>2258</v>
       </c>
       <c r="F1424" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1424" t="b">
         <v>1</v>
@@ -72653,7 +72650,7 @@
       </c>
       <c r="J1424" s="6"/>
       <c r="L1424" s="3" t="s">
-        <v>2656</v>
+        <v>2655</v>
       </c>
       <c r="M1424">
         <v>2</v>
@@ -72686,7 +72683,7 @@
         <v>2259</v>
       </c>
       <c r="F1425" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1425" t="b">
         <v>1</v>
@@ -72699,7 +72696,7 @@
       </c>
       <c r="J1425" s="6"/>
       <c r="L1425" s="3" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
       <c r="M1425">
         <v>2</v>
@@ -72732,7 +72729,7 @@
         <v>2260</v>
       </c>
       <c r="F1426" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1426" t="b">
         <v>1</v>
@@ -72745,7 +72742,7 @@
       </c>
       <c r="J1426" s="6"/>
       <c r="L1426" s="3" t="s">
-        <v>2665</v>
+        <v>2664</v>
       </c>
       <c r="M1426">
         <v>2</v>
@@ -72778,7 +72775,7 @@
         <v>2261</v>
       </c>
       <c r="F1427" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1427" t="b">
         <v>1</v>
@@ -72791,7 +72788,7 @@
       </c>
       <c r="J1427" s="6"/>
       <c r="L1427" s="3" t="s">
-        <v>2666</v>
+        <v>2665</v>
       </c>
       <c r="M1427">
         <v>2</v>
@@ -72824,7 +72821,7 @@
         <v>2262</v>
       </c>
       <c r="F1428" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1428" t="b">
         <v>1</v>
@@ -72837,7 +72834,7 @@
       </c>
       <c r="J1428" s="6"/>
       <c r="L1428" s="3" t="s">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="M1428">
         <v>2</v>
@@ -72870,7 +72867,7 @@
         <v>2263</v>
       </c>
       <c r="F1429" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1429" t="b">
         <v>1</v>
@@ -72883,7 +72880,7 @@
       </c>
       <c r="J1429" s="6"/>
       <c r="L1429" s="3" t="s">
-        <v>2663</v>
+        <v>2662</v>
       </c>
       <c r="M1429">
         <v>2</v>
@@ -72916,7 +72913,7 @@
         <v>2264</v>
       </c>
       <c r="F1430" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="G1430" t="b">
         <v>1</v>
@@ -72929,7 +72926,7 @@
       </c>
       <c r="J1430" s="6"/>
       <c r="L1430" s="3" t="s">
-        <v>2664</v>
+        <v>2663</v>
       </c>
       <c r="M1430">
         <v>2</v>
@@ -72962,7 +72959,7 @@
         <v>2265</v>
       </c>
       <c r="F1431" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1431" t="b">
         <v>1</v>
@@ -72975,7 +72972,7 @@
       </c>
       <c r="J1431" s="6"/>
       <c r="L1431" s="3" t="s">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="M1431">
         <v>2</v>
@@ -73008,7 +73005,7 @@
         <v>2266</v>
       </c>
       <c r="F1432" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1432" t="b">
         <v>1</v>
@@ -73021,7 +73018,7 @@
       </c>
       <c r="J1432" s="6"/>
       <c r="L1432" s="3" t="s">
-        <v>2669</v>
+        <v>2668</v>
       </c>
       <c r="M1432">
         <v>2</v>
@@ -73054,7 +73051,7 @@
         <v>2267</v>
       </c>
       <c r="F1433" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1433" t="b">
         <v>1</v>
@@ -73067,7 +73064,7 @@
       </c>
       <c r="J1433" s="6"/>
       <c r="L1433" s="3" t="s">
-        <v>2670</v>
+        <v>2669</v>
       </c>
       <c r="M1433">
         <v>2</v>
@@ -73100,7 +73097,7 @@
         <v>2268</v>
       </c>
       <c r="F1434" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1434" t="b">
         <v>1</v>
@@ -73113,7 +73110,7 @@
       </c>
       <c r="J1434" s="6"/>
       <c r="L1434" s="3" t="s">
-        <v>2671</v>
+        <v>2670</v>
       </c>
       <c r="M1434">
         <v>2</v>
@@ -73146,7 +73143,7 @@
         <v>2269</v>
       </c>
       <c r="F1435" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1435" t="b">
         <v>1</v>
@@ -73159,7 +73156,7 @@
       </c>
       <c r="J1435" s="6"/>
       <c r="L1435" s="3" t="s">
-        <v>2672</v>
+        <v>2671</v>
       </c>
       <c r="M1435">
         <v>2</v>
@@ -73192,7 +73189,7 @@
         <v>2270</v>
       </c>
       <c r="F1436" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1436" t="b">
         <v>1</v>
@@ -73205,7 +73202,7 @@
       </c>
       <c r="J1436" s="6"/>
       <c r="L1436" s="3" t="s">
-        <v>2673</v>
+        <v>2672</v>
       </c>
       <c r="M1436">
         <v>2</v>
@@ -73238,7 +73235,7 @@
         <v>2271</v>
       </c>
       <c r="F1437" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1437" t="b">
         <v>1</v>
@@ -73251,7 +73248,7 @@
       </c>
       <c r="J1437" s="6"/>
       <c r="L1437" s="3" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="M1437">
         <v>2</v>
@@ -73284,7 +73281,7 @@
         <v>2272</v>
       </c>
       <c r="F1438" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1438" t="b">
         <v>1</v>
@@ -73297,7 +73294,7 @@
       </c>
       <c r="J1438" s="6"/>
       <c r="L1438" s="3" t="s">
-        <v>2675</v>
+        <v>2674</v>
       </c>
       <c r="M1438">
         <v>2</v>
@@ -73330,7 +73327,7 @@
         <v>2273</v>
       </c>
       <c r="F1439" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1439" t="b">
         <v>1</v>
@@ -73343,7 +73340,7 @@
       </c>
       <c r="J1439" s="6"/>
       <c r="L1439" s="3" t="s">
-        <v>2676</v>
+        <v>2675</v>
       </c>
       <c r="M1439">
         <v>2</v>
@@ -73376,7 +73373,7 @@
         <v>2274</v>
       </c>
       <c r="F1440" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1440" t="b">
         <v>1</v>
@@ -73389,7 +73386,7 @@
       </c>
       <c r="J1440" s="6"/>
       <c r="L1440" s="3" t="s">
-        <v>2677</v>
+        <v>2676</v>
       </c>
       <c r="M1440">
         <v>2</v>
@@ -73422,7 +73419,7 @@
         <v>2275</v>
       </c>
       <c r="F1441" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1441" t="b">
         <v>1</v>
@@ -73435,7 +73432,7 @@
       </c>
       <c r="J1441" s="6"/>
       <c r="L1441" s="3" t="s">
-        <v>2678</v>
+        <v>2677</v>
       </c>
       <c r="M1441">
         <v>2</v>
@@ -73468,7 +73465,7 @@
         <v>2276</v>
       </c>
       <c r="F1442" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1442" t="b">
         <v>1</v>
@@ -73481,7 +73478,7 @@
       </c>
       <c r="J1442" s="6"/>
       <c r="L1442" s="3" t="s">
-        <v>2679</v>
+        <v>2678</v>
       </c>
       <c r="M1442">
         <v>2</v>
@@ -73514,7 +73511,7 @@
         <v>2277</v>
       </c>
       <c r="F1443" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1443" t="b">
         <v>1</v>
@@ -73527,7 +73524,7 @@
       </c>
       <c r="J1443" s="6"/>
       <c r="L1443" s="3" t="s">
-        <v>2680</v>
+        <v>2679</v>
       </c>
       <c r="M1443">
         <v>2</v>
@@ -73560,7 +73557,7 @@
         <v>2278</v>
       </c>
       <c r="F1444" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1444" t="b">
         <v>1</v>
@@ -73573,7 +73570,7 @@
       </c>
       <c r="J1444" s="6"/>
       <c r="L1444" s="3" t="s">
-        <v>2681</v>
+        <v>2680</v>
       </c>
       <c r="M1444">
         <v>2</v>
@@ -73606,7 +73603,7 @@
         <v>2279</v>
       </c>
       <c r="F1445" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1445" t="b">
         <v>1</v>
@@ -73619,7 +73616,7 @@
       </c>
       <c r="J1445" s="6"/>
       <c r="L1445" s="3" t="s">
-        <v>2682</v>
+        <v>2681</v>
       </c>
       <c r="M1445">
         <v>2</v>
@@ -73652,7 +73649,7 @@
         <v>2280</v>
       </c>
       <c r="F1446" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1446" t="b">
         <v>1</v>
@@ -73665,7 +73662,7 @@
       </c>
       <c r="J1446" s="6"/>
       <c r="L1446" s="3" t="s">
-        <v>2683</v>
+        <v>2682</v>
       </c>
       <c r="M1446">
         <v>2</v>
@@ -73698,7 +73695,7 @@
         <v>2281</v>
       </c>
       <c r="F1447" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1447" t="b">
         <v>1</v>
@@ -73711,7 +73708,7 @@
       </c>
       <c r="J1447" s="6"/>
       <c r="L1447" s="3" t="s">
-        <v>2684</v>
+        <v>2683</v>
       </c>
       <c r="M1447">
         <v>2</v>
@@ -73744,7 +73741,7 @@
         <v>2282</v>
       </c>
       <c r="F1448" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1448" t="b">
         <v>1</v>
@@ -73757,7 +73754,7 @@
       </c>
       <c r="J1448" s="6"/>
       <c r="L1448" s="3" t="s">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="M1448">
         <v>2</v>
@@ -73790,7 +73787,7 @@
         <v>2283</v>
       </c>
       <c r="F1449" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1449" t="b">
         <v>1</v>
@@ -73803,7 +73800,7 @@
       </c>
       <c r="J1449" s="6"/>
       <c r="L1449" s="3" t="s">
-        <v>2686</v>
+        <v>2685</v>
       </c>
       <c r="M1449">
         <v>2</v>
@@ -73836,7 +73833,7 @@
         <v>2284</v>
       </c>
       <c r="F1450" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1450" t="b">
         <v>1</v>
@@ -73849,7 +73846,7 @@
       </c>
       <c r="J1450" s="6"/>
       <c r="L1450" s="3" t="s">
-        <v>2687</v>
+        <v>2686</v>
       </c>
       <c r="M1450">
         <v>2</v>
@@ -73882,7 +73879,7 @@
         <v>2285</v>
       </c>
       <c r="F1451" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1451" t="b">
         <v>1</v>
@@ -73895,7 +73892,7 @@
       </c>
       <c r="J1451" s="6"/>
       <c r="L1451" s="3" t="s">
-        <v>2688</v>
+        <v>2687</v>
       </c>
       <c r="M1451">
         <v>2</v>
@@ -73928,7 +73925,7 @@
         <v>2286</v>
       </c>
       <c r="F1452" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1452" t="b">
         <v>1</v>
@@ -73941,7 +73938,7 @@
       </c>
       <c r="J1452" s="6"/>
       <c r="L1452" s="3" t="s">
-        <v>2689</v>
+        <v>2688</v>
       </c>
       <c r="M1452">
         <v>2</v>
@@ -73974,7 +73971,7 @@
         <v>2287</v>
       </c>
       <c r="F1453" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1453" t="b">
         <v>1</v>
@@ -73987,7 +73984,7 @@
       </c>
       <c r="J1453" s="6"/>
       <c r="L1453" s="3" t="s">
-        <v>2690</v>
+        <v>2689</v>
       </c>
       <c r="M1453">
         <v>2</v>
@@ -74020,7 +74017,7 @@
         <v>2288</v>
       </c>
       <c r="F1454" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1454" t="b">
         <v>1</v>
@@ -74033,7 +74030,7 @@
       </c>
       <c r="J1454" s="6"/>
       <c r="L1454" s="3" t="s">
-        <v>2691</v>
+        <v>2690</v>
       </c>
       <c r="M1454">
         <v>2</v>
@@ -74066,7 +74063,7 @@
         <v>2289</v>
       </c>
       <c r="F1455" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1455" t="b">
         <v>1</v>
@@ -74079,7 +74076,7 @@
       </c>
       <c r="J1455" s="6"/>
       <c r="L1455" s="3" t="s">
-        <v>2692</v>
+        <v>2691</v>
       </c>
       <c r="M1455">
         <v>2</v>
@@ -74112,7 +74109,7 @@
         <v>2290</v>
       </c>
       <c r="F1456" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1456" t="b">
         <v>1</v>
@@ -74125,7 +74122,7 @@
       </c>
       <c r="J1456" s="6"/>
       <c r="L1456" s="3" t="s">
-        <v>2693</v>
+        <v>2692</v>
       </c>
       <c r="M1456">
         <v>2</v>
@@ -74158,7 +74155,7 @@
         <v>2291</v>
       </c>
       <c r="F1457" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1457" t="b">
         <v>1</v>
@@ -74171,7 +74168,7 @@
       </c>
       <c r="J1457" s="6"/>
       <c r="L1457" s="3" t="s">
-        <v>2694</v>
+        <v>2693</v>
       </c>
       <c r="M1457">
         <v>2</v>
@@ -74204,7 +74201,7 @@
         <v>2292</v>
       </c>
       <c r="F1458" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1458" t="b">
         <v>1</v>
@@ -74217,7 +74214,7 @@
       </c>
       <c r="J1458" s="6"/>
       <c r="L1458" s="3" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
       <c r="M1458">
         <v>2</v>
@@ -74250,7 +74247,7 @@
         <v>2293</v>
       </c>
       <c r="F1459" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1459" t="b">
         <v>1</v>
@@ -74263,7 +74260,7 @@
       </c>
       <c r="J1459" s="6"/>
       <c r="L1459" s="3" t="s">
-        <v>2696</v>
+        <v>2695</v>
       </c>
       <c r="M1459">
         <v>2</v>
@@ -74296,7 +74293,7 @@
         <v>2294</v>
       </c>
       <c r="F1460" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1460" t="b">
         <v>1</v>
@@ -74309,7 +74306,7 @@
       </c>
       <c r="J1460" s="6"/>
       <c r="L1460" s="3" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="M1460">
         <v>2</v>
@@ -74342,7 +74339,7 @@
         <v>2295</v>
       </c>
       <c r="F1461" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1461" t="b">
         <v>1</v>
@@ -74355,7 +74352,7 @@
       </c>
       <c r="J1461" s="6"/>
       <c r="L1461" s="3" t="s">
-        <v>2698</v>
+        <v>2697</v>
       </c>
       <c r="M1461">
         <v>2</v>
@@ -74388,7 +74385,7 @@
         <v>2296</v>
       </c>
       <c r="F1462" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1462" t="b">
         <v>1</v>
@@ -74401,7 +74398,7 @@
       </c>
       <c r="J1462" s="6"/>
       <c r="L1462" s="3" t="s">
-        <v>2699</v>
+        <v>2698</v>
       </c>
       <c r="M1462">
         <v>2</v>
@@ -74434,7 +74431,7 @@
         <v>2297</v>
       </c>
       <c r="F1463" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1463" t="b">
         <v>1</v>
@@ -74447,7 +74444,7 @@
       </c>
       <c r="J1463" s="6"/>
       <c r="L1463" s="3" t="s">
-        <v>2700</v>
+        <v>2699</v>
       </c>
       <c r="M1463">
         <v>2</v>
@@ -74480,7 +74477,7 @@
         <v>2298</v>
       </c>
       <c r="F1464" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1464" t="b">
         <v>1</v>
@@ -74493,7 +74490,7 @@
       </c>
       <c r="J1464" s="6"/>
       <c r="L1464" s="3" t="s">
-        <v>2701</v>
+        <v>2700</v>
       </c>
       <c r="M1464">
         <v>2</v>
@@ -74526,7 +74523,7 @@
         <v>2299</v>
       </c>
       <c r="F1465" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1465" t="b">
         <v>1</v>
@@ -74539,7 +74536,7 @@
       </c>
       <c r="J1465" s="6"/>
       <c r="L1465" s="3" t="s">
-        <v>2702</v>
+        <v>2701</v>
       </c>
       <c r="M1465">
         <v>2</v>
@@ -74572,7 +74569,7 @@
         <v>2300</v>
       </c>
       <c r="F1466" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1466" t="b">
         <v>1</v>
@@ -74585,7 +74582,7 @@
       </c>
       <c r="J1466" s="6"/>
       <c r="L1466" s="3" t="s">
-        <v>2703</v>
+        <v>2702</v>
       </c>
       <c r="M1466">
         <v>2</v>
@@ -74618,7 +74615,7 @@
         <v>2301</v>
       </c>
       <c r="F1467" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1467" t="b">
         <v>1</v>
@@ -74631,7 +74628,7 @@
       </c>
       <c r="J1467" s="6"/>
       <c r="L1467" s="3" t="s">
-        <v>2707</v>
+        <v>2706</v>
       </c>
       <c r="M1467">
         <v>2</v>
@@ -74664,7 +74661,7 @@
         <v>2302</v>
       </c>
       <c r="F1468" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1468" t="b">
         <v>1</v>
@@ -74677,7 +74674,7 @@
       </c>
       <c r="J1468" s="6"/>
       <c r="L1468" s="3" t="s">
-        <v>2708</v>
+        <v>2707</v>
       </c>
       <c r="M1468">
         <v>2</v>
@@ -74710,7 +74707,7 @@
         <v>2303</v>
       </c>
       <c r="F1469" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1469" t="b">
         <v>1</v>
@@ -74723,7 +74720,7 @@
       </c>
       <c r="J1469" s="6"/>
       <c r="L1469" s="3" t="s">
-        <v>2709</v>
+        <v>2708</v>
       </c>
       <c r="M1469">
         <v>2</v>
@@ -74756,7 +74753,7 @@
         <v>2304</v>
       </c>
       <c r="F1470" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1470" t="b">
         <v>1</v>
@@ -74769,7 +74766,7 @@
       </c>
       <c r="J1470" s="6"/>
       <c r="L1470" s="3" t="s">
-        <v>2704</v>
+        <v>2703</v>
       </c>
       <c r="M1470">
         <v>2</v>
@@ -74802,7 +74799,7 @@
         <v>2305</v>
       </c>
       <c r="F1471" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1471" t="b">
         <v>1</v>
@@ -74815,7 +74812,7 @@
       </c>
       <c r="J1471" s="6"/>
       <c r="L1471" s="3" t="s">
-        <v>2705</v>
+        <v>2704</v>
       </c>
       <c r="M1471">
         <v>2</v>
@@ -74848,7 +74845,7 @@
         <v>2306</v>
       </c>
       <c r="F1472" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1472" t="b">
         <v>1</v>
@@ -74861,7 +74858,7 @@
       </c>
       <c r="J1472" s="6"/>
       <c r="L1472" s="3" t="s">
-        <v>2706</v>
+        <v>2705</v>
       </c>
       <c r="M1472">
         <v>2</v>
@@ -74894,7 +74891,7 @@
         <v>2307</v>
       </c>
       <c r="F1473" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1473" t="b">
         <v>1</v>
@@ -74907,7 +74904,7 @@
       </c>
       <c r="J1473" s="6"/>
       <c r="L1473" s="3" t="s">
-        <v>2710</v>
+        <v>2709</v>
       </c>
       <c r="M1473">
         <v>2</v>
@@ -74940,7 +74937,7 @@
         <v>2308</v>
       </c>
       <c r="F1474" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1474" t="b">
         <v>1</v>
@@ -74953,7 +74950,7 @@
       </c>
       <c r="J1474" s="6"/>
       <c r="L1474" s="3" t="s">
-        <v>2711</v>
+        <v>2710</v>
       </c>
       <c r="M1474">
         <v>2</v>
@@ -74986,7 +74983,7 @@
         <v>2309</v>
       </c>
       <c r="F1475" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1475" t="b">
         <v>1</v>
@@ -74999,7 +74996,7 @@
       </c>
       <c r="J1475" s="6"/>
       <c r="L1475" s="3" t="s">
-        <v>2712</v>
+        <v>2711</v>
       </c>
       <c r="M1475">
         <v>2</v>
@@ -75032,7 +75029,7 @@
         <v>2310</v>
       </c>
       <c r="F1476" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1476" t="b">
         <v>1</v>
@@ -75045,7 +75042,7 @@
       </c>
       <c r="J1476" s="6"/>
       <c r="L1476" s="3" t="s">
-        <v>2713</v>
+        <v>2712</v>
       </c>
       <c r="M1476">
         <v>2</v>
@@ -75078,7 +75075,7 @@
         <v>2311</v>
       </c>
       <c r="F1477" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1477" t="b">
         <v>1</v>
@@ -75091,7 +75088,7 @@
       </c>
       <c r="J1477" s="6"/>
       <c r="L1477" s="3" t="s">
-        <v>2714</v>
+        <v>2713</v>
       </c>
       <c r="M1477">
         <v>2</v>
@@ -75124,7 +75121,7 @@
         <v>2312</v>
       </c>
       <c r="F1478" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1478" t="b">
         <v>1</v>
@@ -75137,7 +75134,7 @@
       </c>
       <c r="J1478" s="6"/>
       <c r="L1478" s="3" t="s">
-        <v>2715</v>
+        <v>2714</v>
       </c>
       <c r="M1478">
         <v>2</v>
@@ -75170,7 +75167,7 @@
         <v>2313</v>
       </c>
       <c r="F1479" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1479" t="b">
         <v>1</v>
@@ -75183,7 +75180,7 @@
       </c>
       <c r="J1479" s="6"/>
       <c r="L1479" s="3" t="s">
-        <v>2716</v>
+        <v>2715</v>
       </c>
       <c r="M1479">
         <v>2</v>
@@ -75216,7 +75213,7 @@
         <v>2314</v>
       </c>
       <c r="F1480" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1480" t="b">
         <v>1</v>
@@ -75229,7 +75226,7 @@
       </c>
       <c r="J1480" s="6"/>
       <c r="L1480" s="3" t="s">
-        <v>2717</v>
+        <v>2716</v>
       </c>
       <c r="M1480">
         <v>2</v>
@@ -75262,7 +75259,7 @@
         <v>2315</v>
       </c>
       <c r="F1481" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1481" t="b">
         <v>1</v>
@@ -75275,7 +75272,7 @@
       </c>
       <c r="J1481" s="6"/>
       <c r="L1481" s="3" t="s">
-        <v>2718</v>
+        <v>2717</v>
       </c>
       <c r="M1481">
         <v>2</v>
@@ -75308,7 +75305,7 @@
         <v>2316</v>
       </c>
       <c r="F1482" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1482" t="b">
         <v>1</v>
@@ -75321,7 +75318,7 @@
       </c>
       <c r="J1482" s="6"/>
       <c r="L1482" s="3" t="s">
-        <v>2719</v>
+        <v>2718</v>
       </c>
       <c r="M1482">
         <v>2</v>
@@ -75354,7 +75351,7 @@
         <v>2317</v>
       </c>
       <c r="F1483" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1483" t="b">
         <v>1</v>
@@ -75367,7 +75364,7 @@
       </c>
       <c r="J1483" s="6"/>
       <c r="L1483" s="3" t="s">
-        <v>2720</v>
+        <v>2719</v>
       </c>
       <c r="M1483">
         <v>2</v>
@@ -75400,7 +75397,7 @@
         <v>2318</v>
       </c>
       <c r="F1484" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1484" t="b">
         <v>1</v>
@@ -75413,7 +75410,7 @@
       </c>
       <c r="J1484" s="6"/>
       <c r="L1484" s="3" t="s">
-        <v>2721</v>
+        <v>2720</v>
       </c>
       <c r="M1484">
         <v>2</v>
@@ -75446,7 +75443,7 @@
         <v>2319</v>
       </c>
       <c r="F1485" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1485" t="b">
         <v>1</v>
@@ -75459,7 +75456,7 @@
       </c>
       <c r="J1485" s="6"/>
       <c r="L1485" s="3" t="s">
-        <v>2722</v>
+        <v>2721</v>
       </c>
       <c r="M1485">
         <v>2</v>
@@ -75492,7 +75489,7 @@
         <v>2320</v>
       </c>
       <c r="F1486" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1486" t="b">
         <v>1</v>
@@ -75505,7 +75502,7 @@
       </c>
       <c r="J1486" s="6"/>
       <c r="L1486" s="3" t="s">
-        <v>2723</v>
+        <v>2722</v>
       </c>
       <c r="M1486">
         <v>2</v>
@@ -75538,7 +75535,7 @@
         <v>2321</v>
       </c>
       <c r="F1487" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1487" t="b">
         <v>1</v>
@@ -75551,7 +75548,7 @@
       </c>
       <c r="J1487" s="6"/>
       <c r="L1487" s="3" t="s">
-        <v>2724</v>
+        <v>2723</v>
       </c>
       <c r="M1487">
         <v>2</v>
@@ -75584,7 +75581,7 @@
         <v>2322</v>
       </c>
       <c r="F1488" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1488" t="b">
         <v>1</v>
@@ -75597,7 +75594,7 @@
       </c>
       <c r="J1488" s="6"/>
       <c r="L1488" s="3" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="M1488">
         <v>2</v>
@@ -75630,7 +75627,7 @@
         <v>2323</v>
       </c>
       <c r="F1489" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1489" t="b">
         <v>1</v>
@@ -75643,7 +75640,7 @@
       </c>
       <c r="J1489" s="6"/>
       <c r="L1489" s="3" t="s">
-        <v>2726</v>
+        <v>2725</v>
       </c>
       <c r="M1489">
         <v>2</v>
@@ -75676,7 +75673,7 @@
         <v>2324</v>
       </c>
       <c r="F1490" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1490" t="b">
         <v>1</v>
@@ -75689,7 +75686,7 @@
       </c>
       <c r="J1490" s="6"/>
       <c r="L1490" s="3" t="s">
-        <v>2727</v>
+        <v>2726</v>
       </c>
       <c r="M1490">
         <v>2</v>
@@ -75722,7 +75719,7 @@
         <v>2325</v>
       </c>
       <c r="F1491" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1491" t="b">
         <v>1</v>
@@ -75735,7 +75732,7 @@
       </c>
       <c r="J1491" s="6"/>
       <c r="L1491" s="3" t="s">
-        <v>2728</v>
+        <v>2727</v>
       </c>
       <c r="M1491">
         <v>2</v>
@@ -75768,7 +75765,7 @@
         <v>2326</v>
       </c>
       <c r="F1492" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1492" t="b">
         <v>1</v>
@@ -75781,7 +75778,7 @@
       </c>
       <c r="J1492" s="6"/>
       <c r="L1492" s="3" t="s">
-        <v>2729</v>
+        <v>2728</v>
       </c>
       <c r="M1492">
         <v>2</v>
@@ -75814,7 +75811,7 @@
         <v>2327</v>
       </c>
       <c r="F1493" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1493" t="b">
         <v>1</v>
@@ -75827,7 +75824,7 @@
       </c>
       <c r="J1493" s="6"/>
       <c r="L1493" s="3" t="s">
-        <v>2730</v>
+        <v>2729</v>
       </c>
       <c r="M1493">
         <v>2</v>
@@ -75860,7 +75857,7 @@
         <v>2328</v>
       </c>
       <c r="F1494" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1494" t="b">
         <v>1</v>
@@ -75873,7 +75870,7 @@
       </c>
       <c r="J1494" s="6"/>
       <c r="L1494" s="3" t="s">
-        <v>2731</v>
+        <v>2730</v>
       </c>
       <c r="M1494">
         <v>2</v>
@@ -75906,7 +75903,7 @@
         <v>2329</v>
       </c>
       <c r="F1495" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1495" t="b">
         <v>1</v>
@@ -75919,7 +75916,7 @@
       </c>
       <c r="J1495" s="6"/>
       <c r="L1495" s="3" t="s">
-        <v>2732</v>
+        <v>2731</v>
       </c>
       <c r="M1495">
         <v>2</v>
@@ -75952,7 +75949,7 @@
         <v>2330</v>
       </c>
       <c r="F1496" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1496" t="b">
         <v>1</v>
@@ -75965,7 +75962,7 @@
       </c>
       <c r="J1496" s="6"/>
       <c r="L1496" s="3" t="s">
-        <v>2733</v>
+        <v>2732</v>
       </c>
       <c r="M1496">
         <v>2</v>
@@ -75998,7 +75995,7 @@
         <v>2331</v>
       </c>
       <c r="F1497" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1497" t="b">
         <v>1</v>
@@ -76011,7 +76008,7 @@
       </c>
       <c r="J1497" s="6"/>
       <c r="L1497" s="3" t="s">
-        <v>2734</v>
+        <v>2733</v>
       </c>
       <c r="M1497">
         <v>2</v>
@@ -76044,7 +76041,7 @@
         <v>2332</v>
       </c>
       <c r="F1498" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1498" t="b">
         <v>1</v>
@@ -76057,7 +76054,7 @@
       </c>
       <c r="J1498" s="6"/>
       <c r="L1498" s="3" t="s">
-        <v>2735</v>
+        <v>2734</v>
       </c>
       <c r="M1498">
         <v>2</v>
@@ -76090,7 +76087,7 @@
         <v>2333</v>
       </c>
       <c r="F1499" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1499" t="b">
         <v>1</v>
@@ -76103,7 +76100,7 @@
       </c>
       <c r="J1499" s="6"/>
       <c r="L1499" s="3" t="s">
-        <v>2736</v>
+        <v>2735</v>
       </c>
       <c r="M1499">
         <v>2</v>
@@ -76136,7 +76133,7 @@
         <v>2334</v>
       </c>
       <c r="F1500" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1500" t="b">
         <v>1</v>
@@ -76149,7 +76146,7 @@
       </c>
       <c r="J1500" s="6"/>
       <c r="L1500" s="3" t="s">
-        <v>2737</v>
+        <v>2736</v>
       </c>
       <c r="M1500">
         <v>2</v>
@@ -76182,7 +76179,7 @@
         <v>2335</v>
       </c>
       <c r="F1501" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1501" t="b">
         <v>1</v>
@@ -76195,7 +76192,7 @@
       </c>
       <c r="J1501" s="6"/>
       <c r="L1501" s="3" t="s">
-        <v>2738</v>
+        <v>2737</v>
       </c>
       <c r="M1501">
         <v>2</v>
@@ -76228,7 +76225,7 @@
         <v>2336</v>
       </c>
       <c r="F1502" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1502" t="b">
         <v>1</v>
@@ -76241,7 +76238,7 @@
       </c>
       <c r="J1502" s="6"/>
       <c r="L1502" s="3" t="s">
-        <v>2739</v>
+        <v>2738</v>
       </c>
       <c r="M1502">
         <v>2</v>
@@ -76274,7 +76271,7 @@
         <v>2337</v>
       </c>
       <c r="F1503" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1503" t="b">
         <v>1</v>
@@ -76287,7 +76284,7 @@
       </c>
       <c r="J1503" s="6"/>
       <c r="L1503" s="3" t="s">
-        <v>2740</v>
+        <v>2739</v>
       </c>
       <c r="M1503">
         <v>2</v>
@@ -76320,7 +76317,7 @@
         <v>2338</v>
       </c>
       <c r="F1504" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1504" t="b">
         <v>1</v>
@@ -76333,7 +76330,7 @@
       </c>
       <c r="J1504" s="6"/>
       <c r="L1504" s="3" t="s">
-        <v>2741</v>
+        <v>2740</v>
       </c>
       <c r="M1504">
         <v>2</v>
@@ -76366,7 +76363,7 @@
         <v>2339</v>
       </c>
       <c r="F1505" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1505" t="b">
         <v>1</v>
@@ -76379,7 +76376,7 @@
       </c>
       <c r="J1505" s="6"/>
       <c r="L1505" s="3" t="s">
-        <v>2742</v>
+        <v>2741</v>
       </c>
       <c r="M1505">
         <v>2</v>
@@ -76412,7 +76409,7 @@
         <v>2340</v>
       </c>
       <c r="F1506" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1506" t="b">
         <v>1</v>
@@ -76425,7 +76422,7 @@
       </c>
       <c r="J1506" s="6"/>
       <c r="L1506" s="3" t="s">
-        <v>2745</v>
+        <v>2744</v>
       </c>
       <c r="M1506">
         <v>2</v>
@@ -76458,7 +76455,7 @@
         <v>2341</v>
       </c>
       <c r="F1507" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1507" t="b">
         <v>1</v>
@@ -76471,7 +76468,7 @@
       </c>
       <c r="J1507" s="6"/>
       <c r="L1507" s="3" t="s">
-        <v>2743</v>
+        <v>2742</v>
       </c>
       <c r="M1507">
         <v>2</v>
@@ -76504,7 +76501,7 @@
         <v>2342</v>
       </c>
       <c r="F1508" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1508" t="b">
         <v>1</v>
@@ -76517,7 +76514,7 @@
       </c>
       <c r="J1508" s="6"/>
       <c r="L1508" s="3" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
       <c r="M1508">
         <v>2</v>
@@ -76550,7 +76547,7 @@
         <v>2343</v>
       </c>
       <c r="F1509" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1509" t="b">
         <v>1</v>
@@ -76563,7 +76560,7 @@
       </c>
       <c r="J1509" s="6"/>
       <c r="L1509" s="3" t="s">
-        <v>2746</v>
+        <v>2745</v>
       </c>
       <c r="M1509">
         <v>2</v>
@@ -76596,7 +76593,7 @@
         <v>2344</v>
       </c>
       <c r="F1510" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1510" t="b">
         <v>1</v>
@@ -76609,7 +76606,7 @@
       </c>
       <c r="J1510" s="6"/>
       <c r="L1510" s="3" t="s">
-        <v>2747</v>
+        <v>2746</v>
       </c>
       <c r="M1510">
         <v>2</v>
@@ -76642,7 +76639,7 @@
         <v>2345</v>
       </c>
       <c r="F1511" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1511" t="b">
         <v>1</v>
@@ -76655,7 +76652,7 @@
       </c>
       <c r="J1511" s="6"/>
       <c r="L1511" s="3" t="s">
-        <v>2748</v>
+        <v>2747</v>
       </c>
       <c r="M1511">
         <v>2</v>
@@ -76688,7 +76685,7 @@
         <v>2346</v>
       </c>
       <c r="F1512" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1512" t="b">
         <v>1</v>
@@ -76701,7 +76698,7 @@
       </c>
       <c r="J1512" s="6"/>
       <c r="L1512" s="3" t="s">
-        <v>2749</v>
+        <v>2748</v>
       </c>
       <c r="M1512">
         <v>2</v>
@@ -76734,7 +76731,7 @@
         <v>2347</v>
       </c>
       <c r="F1513" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1513" t="b">
         <v>1</v>
@@ -76747,7 +76744,7 @@
       </c>
       <c r="J1513" s="6"/>
       <c r="L1513" s="3" t="s">
-        <v>2750</v>
+        <v>2749</v>
       </c>
       <c r="M1513">
         <v>2</v>
@@ -76780,7 +76777,7 @@
         <v>2348</v>
       </c>
       <c r="F1514" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1514" t="b">
         <v>1</v>
@@ -76793,7 +76790,7 @@
       </c>
       <c r="J1514" s="6"/>
       <c r="L1514" s="3" t="s">
-        <v>2751</v>
+        <v>2750</v>
       </c>
       <c r="M1514">
         <v>2</v>
@@ -76826,7 +76823,7 @@
         <v>2349</v>
       </c>
       <c r="F1515" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="G1515" t="b">
         <v>1</v>
@@ -76839,7 +76836,7 @@
       </c>
       <c r="J1515" s="6"/>
       <c r="L1515" s="3" t="s">
-        <v>2752</v>
+        <v>2751</v>
       </c>
       <c r="M1515">
         <v>2</v>

--- a/pages/apps/uprn-service/config.xlsx
+++ b/pages/apps/uprn-service/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NDSH\GitHub\dsh-content\dev\pages\apps\uprn-service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BA40EF4-E13E-46B0-8E19-04844816C4E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DA961C0-5E0B-4119-B651-FCC3AFC21B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="388" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="388" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="folders" sheetId="1" r:id="rId1"/>
@@ -9063,6 +9063,12 @@
       <c r="G8">
         <v>0</v>
       </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
@@ -9106,6 +9112,12 @@
       <c r="F10" t="s">
         <v>2772</v>
       </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
@@ -9123,6 +9135,12 @@
       <c r="F11" t="s">
         <v>2772</v>
       </c>
+      <c r="I11">
+        <v>2</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
@@ -9140,6 +9158,12 @@
       <c r="F12" t="s">
         <v>2773</v>
       </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
@@ -9156,6 +9180,12 @@
       </c>
       <c r="F13" t="s">
         <v>2773</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.3">
@@ -11659,7 +11689,7 @@
         <v>2</v>
       </c>
       <c r="K45" t="s">
-        <v>2777</v>
+        <v>2774</v>
       </c>
       <c r="L45" t="s">
         <v>219</v>
@@ -11892,7 +11922,7 @@
         <v>1</v>
       </c>
       <c r="J49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K49" t="s">
         <v>2777</v>
@@ -12249,7 +12279,7 @@
         <v>2</v>
       </c>
       <c r="K55" t="s">
-        <v>2776</v>
+        <v>2774</v>
       </c>
       <c r="L55" t="s">
         <v>269</v>

--- a/pages/apps/uprn-service/config.xlsx
+++ b/pages/apps/uprn-service/config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NDSH\GitHub\dsh-content\pages\apps\uprn-service\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NDSH\GitHub\dsh-content\dev\pages\apps\uprn-service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE01DEF-773C-4E6E-804C-70AE9208B9F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC2726EC-3AA9-414F-A809-EDB25F654D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="388" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="388" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="folders" sheetId="1" r:id="rId1"/>
@@ -7992,78 +7992,6 @@
     <t>AQREAN - Ammonium Sulfate in PM2.5 Dry Aerosol (Mass Concentration) (Surface Level) 2003 annual mean timeseries</t>
   </si>
   <si>
-    <t>Non Cover-Weighted Soil Reactivity Indicator for 1990</t>
-  </si>
-  <si>
-    <t>Non Cover-Weighted Soil Reactivity Indicator for the 2015-2019 period</t>
-  </si>
-  <si>
-    <t>Difference in Cover-Weighted Soil Reactivity Indicators between 1990 and the 2015-2019 period</t>
-  </si>
-  <si>
-    <t>Cover-Weighted Soil Reactivity Indicator for 1990</t>
-  </si>
-  <si>
-    <t>Cover-Weighted Soil Reactivity Indicator for the 2015-2019 period</t>
-  </si>
-  <si>
-    <t>Difference in Non Cover-Weighted Soil Fertility Indicators between 1990 and the 2015-2019 period</t>
-  </si>
-  <si>
-    <t>Non Cover-Weighted Soil Fertility Indicator for 1990</t>
-  </si>
-  <si>
-    <t>Non Cover-Weighted Soil Fertility Indicator for the 2015-2019 period</t>
-  </si>
-  <si>
-    <t>Difference in Cover-Weighted Soil Fertility Indicators between 1990 Model and the 2015-2019 period</t>
-  </si>
-  <si>
-    <t>Cover-Weighted Soil Fertility Indicator for 1990</t>
-  </si>
-  <si>
-    <t>Cover-Weighted Soil Fertility Indicator for the 2015-2019 period</t>
-  </si>
-  <si>
-    <t>Difference in Non Cover-Weighted Light Availability Indicators between 1990 and the 2015-2019 period</t>
-  </si>
-  <si>
-    <t>Non Cover-Weighted Light Availability Indicator for 1990</t>
-  </si>
-  <si>
-    <t>Non Cover-Weighted Light Availability Indicator for the 2015-2019 period</t>
-  </si>
-  <si>
-    <t>Difference in Cover-Weighted Light Availability Indicators between 1990 and the 2015-2019 period</t>
-  </si>
-  <si>
-    <t>Cover-Weighted Light Availability Indicator for 1990</t>
-  </si>
-  <si>
-    <t>Cover-Weighted Light Availability Indicator for the 2015-2019 period</t>
-  </si>
-  <si>
-    <t>Difference in Non Cover-Weighted Soil Moisture Indicators between 1990 and the 2015-2019 period</t>
-  </si>
-  <si>
-    <t>Non Cover-Weighted Soil Moisture Indicator for 1990</t>
-  </si>
-  <si>
-    <t>Non Cover-Weighted Soil Moisture Indicator for the 2015-2019 period</t>
-  </si>
-  <si>
-    <t>Difference in Cover-Weighted Soil Moisture Indicators between 1990 and the 2015-2019 period</t>
-  </si>
-  <si>
-    <t>Cover-Weighted Soil Moisture Indicator for 1990</t>
-  </si>
-  <si>
-    <t>Cover-Weighted Soil Moisture Indicator for the 2015-2019 period</t>
-  </si>
-  <si>
-    <t>Difference in Non Cover-Weighted Soil Reactivity Indicators between 1990 and the 2015-2019 period</t>
-  </si>
-  <si>
     <t>Recent past 30 year mean 1990 - 2019 (℃)</t>
   </si>
   <si>
@@ -9628,6 +9556,78 @@
   </si>
   <si>
     <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/CEH/EllenbergVegetationIndicators/ebergf_cwt_15_19__EPSG_27700.json</t>
+  </si>
+  <si>
+    <t>Cover-Weighted Soil Moisture Indicator 1990</t>
+  </si>
+  <si>
+    <t>Cover-Weighted Soil Moisture Indicator 2015-2019</t>
+  </si>
+  <si>
+    <t>Difference in Cover-Weighted Soil Moisture Indicators between 1990 and 2015-2019</t>
+  </si>
+  <si>
+    <t>Non Cover-Weighted Soil Moisture Indicator 2015-2019</t>
+  </si>
+  <si>
+    <t>Difference in Non Cover-Weighted Soil Moisture Indicators between 1990 and 2015-2019</t>
+  </si>
+  <si>
+    <t>Cover-Weighted Light Availability Indicator 2015-2019</t>
+  </si>
+  <si>
+    <t>Cover-Weighted Light Availability Indicator 1990</t>
+  </si>
+  <si>
+    <t>Difference in Cover-Weighted Light Availability Indicators between 1990 and 2015-2019</t>
+  </si>
+  <si>
+    <t>Non Cover-Weighted Light Availability Indicator 1990</t>
+  </si>
+  <si>
+    <t>Difference in Non Cover-Weighted Light Availability Indicators between 1990 and 2015-2019</t>
+  </si>
+  <si>
+    <t>Cover-Weighted Soil Fertility Indicator 1990</t>
+  </si>
+  <si>
+    <t>Difference in Cover-Weighted Soil Fertility Indicators between 1990 and 2015-2019</t>
+  </si>
+  <si>
+    <t>Non Cover-Weighted Soil Fertility Indicator 2015-2019</t>
+  </si>
+  <si>
+    <t>Non Cover-Weighted Soil Fertility Indicator 1990</t>
+  </si>
+  <si>
+    <t>Cover-Weighted Soil Fertility Indicator 2015-2019</t>
+  </si>
+  <si>
+    <t>Non Cover-Weighted Light Availability Indicator 2015-2019</t>
+  </si>
+  <si>
+    <t>Non Cover-Weighted Soil Moisture Indicator 1990</t>
+  </si>
+  <si>
+    <t>Difference in Non Cover-Weighted Soil Fertility Indicators between 1990 and 2015-2019</t>
+  </si>
+  <si>
+    <t>Cover-Weighted Soil Reactivity Indicator 1990</t>
+  </si>
+  <si>
+    <t>Cover-Weighted Soil Reactivity Indicator 2015-2019</t>
+  </si>
+  <si>
+    <t>Difference in Cover-Weighted Soil Reactivity Indicators between 1990 and 2015-2019</t>
+  </si>
+  <si>
+    <t>Non Cover-Weighted Soil Reactivity Indicator 2015-2019</t>
+  </si>
+  <si>
+    <t>Non Cover-Weighted Soil Reactivity Indicator 1990</t>
+  </si>
+  <si>
+    <t>Difference in Non Cover-Weighted Soil Reactivity Indicators between 1990 and 2015-2019</t>
   </si>
 </sst>
 </file>
@@ -9673,7 +9673,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -9716,6 +9716,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -9730,7 +9736,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -9744,6 +9750,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -10086,7 +10093,7 @@
     <col min="3" max="3" width="16.6640625" customWidth="1"/>
     <col min="4" max="4" width="19.21875" customWidth="1"/>
     <col min="5" max="5" width="43.44140625" customWidth="1"/>
-    <col min="6" max="6" width="28.21875" customWidth="1"/>
+    <col min="6" max="6" width="32.21875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.77734375" customWidth="1"/>
     <col min="8" max="8" width="92.77734375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.109375" customWidth="1"/>
@@ -10297,7 +10304,7 @@
         <v>7000</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>3159</v>
+        <v>3135</v>
       </c>
       <c r="I7">
         <v>2</v>
@@ -10326,7 +10333,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>3160</v>
+        <v>3136</v>
       </c>
       <c r="I8">
         <v>2</v>
@@ -10355,7 +10362,7 @@
         <v>100</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>3161</v>
+        <v>3137</v>
       </c>
       <c r="I9">
         <v>2</v>
@@ -10526,7 +10533,7 @@
     <col min="1" max="1" width="5.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="121.5546875" customWidth="1"/>
     <col min="6" max="6" width="109.88671875" style="10" customWidth="1"/>
     <col min="7" max="7" width="41.44140625" style="8" customWidth="1"/>
@@ -12709,7 +12716,7 @@
       <c r="D40" t="s">
         <v>184</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="3" t="s">
         <v>185</v>
       </c>
       <c r="F40" t="s">
@@ -14317,6 +14324,7 @@
     <hyperlink ref="O62" r:id="rId30" xr:uid="{373745D5-336B-46AD-BEF0-FF285433016E}"/>
     <hyperlink ref="O63" r:id="rId31" xr:uid="{356CAD23-03AB-460F-AFCA-EC4BDE2D8AE0}"/>
     <hyperlink ref="O64" r:id="rId32" xr:uid="{4F6B4081-E0D1-4EF1-825D-2153F4EE3414}"/>
+    <hyperlink ref="E40" r:id="rId33" xr:uid="{FD826172-87CB-45B3-A0FC-D8B3114ACB40}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -25393,7 +25401,7 @@
         <v>651</v>
       </c>
       <c r="E278" t="s">
-        <v>3139</v>
+        <v>3115</v>
       </c>
       <c r="G278" t="b">
         <v>1</v>
@@ -26713,7 +26721,7 @@
         <v>716</v>
       </c>
       <c r="E311" t="s">
-        <v>3137</v>
+        <v>3113</v>
       </c>
       <c r="G311" t="b">
         <v>1</v>
@@ -26833,7 +26841,7 @@
         <v>721</v>
       </c>
       <c r="E314" t="s">
-        <v>3144</v>
+        <v>3120</v>
       </c>
       <c r="G314" t="b">
         <v>1</v>
@@ -26913,7 +26921,7 @@
         <v>724</v>
       </c>
       <c r="E316" s="6" t="s">
-        <v>2678</v>
+        <v>2654</v>
       </c>
       <c r="G316" t="b">
         <v>1</v>
@@ -26953,7 +26961,7 @@
         <v>725</v>
       </c>
       <c r="E317" s="6" t="s">
-        <v>3140</v>
+        <v>3116</v>
       </c>
       <c r="G317" t="b">
         <v>1</v>
@@ -26993,7 +27001,7 @@
         <v>726</v>
       </c>
       <c r="E318" s="6" t="s">
-        <v>3141</v>
+        <v>3117</v>
       </c>
       <c r="G318" t="b">
         <v>1</v>
@@ -27033,7 +27041,7 @@
         <v>727</v>
       </c>
       <c r="E319" s="6" t="s">
-        <v>3142</v>
+        <v>3118</v>
       </c>
       <c r="G319" t="b">
         <v>1</v>
@@ -27113,7 +27121,7 @@
         <v>730</v>
       </c>
       <c r="E321" s="6" t="s">
-        <v>2682</v>
+        <v>2658</v>
       </c>
       <c r="G321" t="b">
         <v>1</v>
@@ -27153,7 +27161,7 @@
         <v>731</v>
       </c>
       <c r="E322" s="6" t="s">
-        <v>2683</v>
+        <v>2659</v>
       </c>
       <c r="G322" t="b">
         <v>1</v>
@@ -27193,7 +27201,7 @@
         <v>732</v>
       </c>
       <c r="E323" s="6" t="s">
-        <v>2684</v>
+        <v>2660</v>
       </c>
       <c r="G323" t="b">
         <v>1</v>
@@ -27273,7 +27281,7 @@
         <v>735</v>
       </c>
       <c r="E325" s="6" t="s">
-        <v>2685</v>
+        <v>2661</v>
       </c>
       <c r="G325" t="b">
         <v>1</v>
@@ -27313,7 +27321,7 @@
         <v>736</v>
       </c>
       <c r="E326" s="6" t="s">
-        <v>2686</v>
+        <v>2662</v>
       </c>
       <c r="G326" t="b">
         <v>1</v>
@@ -27353,7 +27361,7 @@
         <v>737</v>
       </c>
       <c r="E327" s="6" t="s">
-        <v>2687</v>
+        <v>2663</v>
       </c>
       <c r="G327" t="b">
         <v>1</v>
@@ -27433,7 +27441,7 @@
         <v>740</v>
       </c>
       <c r="E329" s="6" t="s">
-        <v>2688</v>
+        <v>2664</v>
       </c>
       <c r="G329" t="b">
         <v>1</v>
@@ -27473,7 +27481,7 @@
         <v>741</v>
       </c>
       <c r="E330" s="6" t="s">
-        <v>2689</v>
+        <v>2665</v>
       </c>
       <c r="G330" t="b">
         <v>1</v>
@@ -27513,7 +27521,7 @@
         <v>742</v>
       </c>
       <c r="E331" s="6" t="s">
-        <v>2690</v>
+        <v>2666</v>
       </c>
       <c r="G331" t="b">
         <v>1</v>
@@ -27593,7 +27601,7 @@
         <v>745</v>
       </c>
       <c r="E333" s="6" t="s">
-        <v>2691</v>
+        <v>2667</v>
       </c>
       <c r="G333" t="b">
         <v>1</v>
@@ -27633,7 +27641,7 @@
         <v>746</v>
       </c>
       <c r="E334" s="6" t="s">
-        <v>2692</v>
+        <v>2668</v>
       </c>
       <c r="G334" t="b">
         <v>1</v>
@@ -27673,7 +27681,7 @@
         <v>747</v>
       </c>
       <c r="E335" s="6" t="s">
-        <v>2693</v>
+        <v>2669</v>
       </c>
       <c r="G335" t="b">
         <v>1</v>
@@ -30433,7 +30441,7 @@
         <v>858</v>
       </c>
       <c r="E404" t="s">
-        <v>3143</v>
+        <v>3119</v>
       </c>
       <c r="G404" t="b">
         <v>1</v>
@@ -30753,7 +30761,7 @@
         <v>872</v>
       </c>
       <c r="E412" t="s">
-        <v>3138</v>
+        <v>3114</v>
       </c>
       <c r="G412" t="b">
         <v>1</v>
@@ -47673,7 +47681,7 @@
         <v>1677</v>
       </c>
       <c r="E817" t="s">
-        <v>3129</v>
+        <v>3105</v>
       </c>
       <c r="G817" t="b">
         <v>1</v>
@@ -47713,7 +47721,7 @@
         <v>1678</v>
       </c>
       <c r="E818" t="s">
-        <v>3130</v>
+        <v>3106</v>
       </c>
       <c r="G818" t="b">
         <v>1</v>
@@ -47753,7 +47761,7 @@
         <v>1679</v>
       </c>
       <c r="E819" t="s">
-        <v>3131</v>
+        <v>3107</v>
       </c>
       <c r="G819" t="b">
         <v>1</v>
@@ -47793,7 +47801,7 @@
         <v>1680</v>
       </c>
       <c r="E820" t="s">
-        <v>3132</v>
+        <v>3108</v>
       </c>
       <c r="G820" t="b">
         <v>1</v>
@@ -47833,7 +47841,7 @@
         <v>1681</v>
       </c>
       <c r="E821" t="s">
-        <v>3133</v>
+        <v>3109</v>
       </c>
       <c r="G821" t="b">
         <v>1</v>
@@ -47873,7 +47881,7 @@
         <v>1682</v>
       </c>
       <c r="E822" t="s">
-        <v>3134</v>
+        <v>3110</v>
       </c>
       <c r="G822" t="b">
         <v>1</v>
@@ -47913,7 +47921,7 @@
         <v>1683</v>
       </c>
       <c r="E823" t="s">
-        <v>3135</v>
+        <v>3111</v>
       </c>
       <c r="G823" t="b">
         <v>1</v>
@@ -47953,7 +47961,7 @@
         <v>1684</v>
       </c>
       <c r="E824" t="s">
-        <v>3136</v>
+        <v>3112</v>
       </c>
       <c r="G824" t="b">
         <v>1</v>
@@ -51673,7 +51681,7 @@
         <v>716</v>
       </c>
       <c r="E917" t="s">
-        <v>3137</v>
+        <v>3113</v>
       </c>
       <c r="G917" t="b">
         <v>1</v>
@@ -51993,7 +52001,7 @@
         <v>721</v>
       </c>
       <c r="E925" t="s">
-        <v>3144</v>
+        <v>3120</v>
       </c>
       <c r="G925" t="b">
         <v>1</v>
@@ -52313,7 +52321,7 @@
         <v>724</v>
       </c>
       <c r="E933" s="6" t="s">
-        <v>2678</v>
+        <v>2654</v>
       </c>
       <c r="G933" t="b">
         <v>1</v>
@@ -52353,7 +52361,7 @@
         <v>725</v>
       </c>
       <c r="E934" s="6" t="s">
-        <v>2679</v>
+        <v>2655</v>
       </c>
       <c r="G934" t="b">
         <v>1</v>
@@ -52393,7 +52401,7 @@
         <v>726</v>
       </c>
       <c r="E935" s="6" t="s">
-        <v>2680</v>
+        <v>2656</v>
       </c>
       <c r="G935" t="b">
         <v>1</v>
@@ -52433,7 +52441,7 @@
         <v>727</v>
       </c>
       <c r="E936" s="6" t="s">
-        <v>2681</v>
+        <v>2657</v>
       </c>
       <c r="G936" t="b">
         <v>1</v>
@@ -52513,7 +52521,7 @@
         <v>730</v>
       </c>
       <c r="E938" s="6" t="s">
-        <v>2682</v>
+        <v>2658</v>
       </c>
       <c r="G938" t="b">
         <v>1</v>
@@ -52553,7 +52561,7 @@
         <v>731</v>
       </c>
       <c r="E939" s="6" t="s">
-        <v>2683</v>
+        <v>2659</v>
       </c>
       <c r="G939" t="b">
         <v>1</v>
@@ -52593,7 +52601,7 @@
         <v>732</v>
       </c>
       <c r="E940" s="6" t="s">
-        <v>2684</v>
+        <v>2660</v>
       </c>
       <c r="G940" t="b">
         <v>1</v>
@@ -52673,7 +52681,7 @@
         <v>735</v>
       </c>
       <c r="E942" s="6" t="s">
-        <v>2685</v>
+        <v>2661</v>
       </c>
       <c r="G942" t="b">
         <v>1</v>
@@ -52713,7 +52721,7 @@
         <v>736</v>
       </c>
       <c r="E943" s="6" t="s">
-        <v>2686</v>
+        <v>2662</v>
       </c>
       <c r="G943" t="b">
         <v>1</v>
@@ -52753,7 +52761,7 @@
         <v>737</v>
       </c>
       <c r="E944" s="6" t="s">
-        <v>2687</v>
+        <v>2663</v>
       </c>
       <c r="G944" t="b">
         <v>1</v>
@@ -52833,7 +52841,7 @@
         <v>740</v>
       </c>
       <c r="E946" s="6" t="s">
-        <v>2688</v>
+        <v>2664</v>
       </c>
       <c r="G946" t="b">
         <v>1</v>
@@ -52873,7 +52881,7 @@
         <v>741</v>
       </c>
       <c r="E947" s="6" t="s">
-        <v>2689</v>
+        <v>2665</v>
       </c>
       <c r="G947" t="b">
         <v>1</v>
@@ -52913,7 +52921,7 @@
         <v>742</v>
       </c>
       <c r="E948" s="6" t="s">
-        <v>2690</v>
+        <v>2666</v>
       </c>
       <c r="G948" t="b">
         <v>1</v>
@@ -52993,7 +53001,7 @@
         <v>745</v>
       </c>
       <c r="E950" s="6" t="s">
-        <v>2691</v>
+        <v>2667</v>
       </c>
       <c r="G950" t="b">
         <v>1</v>
@@ -53033,7 +53041,7 @@
         <v>746</v>
       </c>
       <c r="E951" s="6" t="s">
-        <v>2692</v>
+        <v>2668</v>
       </c>
       <c r="G951" t="b">
         <v>1</v>
@@ -53073,7 +53081,7 @@
         <v>747</v>
       </c>
       <c r="E952" s="6" t="s">
-        <v>2693</v>
+        <v>2669</v>
       </c>
       <c r="G952" t="b">
         <v>1</v>
@@ -55713,7 +55721,7 @@
         <v>1</v>
       </c>
       <c r="E1018" t="s">
-        <v>2694</v>
+        <v>2670</v>
       </c>
       <c r="F1018" t="s">
         <v>1857</v>
@@ -55741,7 +55749,7 @@
         <v>0</v>
       </c>
       <c r="R1018" t="s">
-        <v>2735</v>
+        <v>2711</v>
       </c>
     </row>
     <row r="1019" spans="1:18" x14ac:dyDescent="0.3">
@@ -55758,7 +55766,7 @@
         <v>2</v>
       </c>
       <c r="E1019" t="s">
-        <v>2695</v>
+        <v>2671</v>
       </c>
       <c r="F1019" t="s">
         <v>1857</v>
@@ -55786,7 +55794,7 @@
         <v>0</v>
       </c>
       <c r="R1019" t="s">
-        <v>2736</v>
+        <v>2712</v>
       </c>
     </row>
     <row r="1020" spans="1:18" x14ac:dyDescent="0.3">
@@ -55803,7 +55811,7 @@
         <v>3</v>
       </c>
       <c r="E1020" t="s">
-        <v>2696</v>
+        <v>2672</v>
       </c>
       <c r="F1020" t="s">
         <v>1857</v>
@@ -55831,7 +55839,7 @@
         <v>0</v>
       </c>
       <c r="R1020" t="s">
-        <v>2737</v>
+        <v>2713</v>
       </c>
     </row>
     <row r="1021" spans="1:18" x14ac:dyDescent="0.3">
@@ -55848,7 +55856,7 @@
         <v>4</v>
       </c>
       <c r="E1021" t="s">
-        <v>2697</v>
+        <v>2673</v>
       </c>
       <c r="F1021" t="s">
         <v>1857</v>
@@ -55876,7 +55884,7 @@
         <v>0</v>
       </c>
       <c r="R1021" t="s">
-        <v>2738</v>
+        <v>2714</v>
       </c>
     </row>
     <row r="1022" spans="1:18" x14ac:dyDescent="0.3">
@@ -55893,7 +55901,7 @@
         <v>5</v>
       </c>
       <c r="E1022" t="s">
-        <v>2698</v>
+        <v>2674</v>
       </c>
       <c r="F1022" t="s">
         <v>1857</v>
@@ -55921,7 +55929,7 @@
         <v>0</v>
       </c>
       <c r="R1022" t="s">
-        <v>2739</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="1023" spans="1:18" x14ac:dyDescent="0.3">
@@ -55938,7 +55946,7 @@
         <v>6</v>
       </c>
       <c r="E1023" t="s">
-        <v>2699</v>
+        <v>2675</v>
       </c>
       <c r="F1023" t="s">
         <v>1857</v>
@@ -55966,7 +55974,7 @@
         <v>0</v>
       </c>
       <c r="R1023" t="s">
-        <v>2740</v>
+        <v>2716</v>
       </c>
     </row>
     <row r="1024" spans="1:18" x14ac:dyDescent="0.3">
@@ -55983,7 +55991,7 @@
         <v>7</v>
       </c>
       <c r="E1024" t="s">
-        <v>2700</v>
+        <v>2676</v>
       </c>
       <c r="F1024" t="s">
         <v>1857</v>
@@ -56011,7 +56019,7 @@
         <v>0</v>
       </c>
       <c r="R1024" t="s">
-        <v>2741</v>
+        <v>2717</v>
       </c>
     </row>
     <row r="1025" spans="1:18" x14ac:dyDescent="0.3">
@@ -56028,7 +56036,7 @@
         <v>8</v>
       </c>
       <c r="E1025" t="s">
-        <v>2701</v>
+        <v>2677</v>
       </c>
       <c r="F1025" t="s">
         <v>1857</v>
@@ -56056,7 +56064,7 @@
         <v>0</v>
       </c>
       <c r="R1025" t="s">
-        <v>2742</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="1026" spans="1:18" x14ac:dyDescent="0.3">
@@ -56073,7 +56081,7 @@
         <v>9</v>
       </c>
       <c r="E1026" t="s">
-        <v>2702</v>
+        <v>2678</v>
       </c>
       <c r="F1026" t="s">
         <v>1857</v>
@@ -56101,7 +56109,7 @@
         <v>0</v>
       </c>
       <c r="R1026" t="s">
-        <v>2743</v>
+        <v>2719</v>
       </c>
     </row>
     <row r="1027" spans="1:18" x14ac:dyDescent="0.3">
@@ -56118,7 +56126,7 @@
         <v>10</v>
       </c>
       <c r="E1027" t="s">
-        <v>2703</v>
+        <v>2679</v>
       </c>
       <c r="F1027" t="s">
         <v>1857</v>
@@ -56146,7 +56154,7 @@
         <v>0</v>
       </c>
       <c r="R1027" t="s">
-        <v>2744</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="1028" spans="1:18" x14ac:dyDescent="0.3">
@@ -56163,7 +56171,7 @@
         <v>11</v>
       </c>
       <c r="E1028" t="s">
-        <v>2704</v>
+        <v>2680</v>
       </c>
       <c r="F1028" t="s">
         <v>1857</v>
@@ -56191,7 +56199,7 @@
         <v>0</v>
       </c>
       <c r="R1028" t="s">
-        <v>2745</v>
+        <v>2721</v>
       </c>
     </row>
     <row r="1029" spans="1:18" x14ac:dyDescent="0.3">
@@ -56208,7 +56216,7 @@
         <v>12</v>
       </c>
       <c r="E1029" t="s">
-        <v>2705</v>
+        <v>2681</v>
       </c>
       <c r="F1029" t="s">
         <v>1857</v>
@@ -56236,7 +56244,7 @@
         <v>0</v>
       </c>
       <c r="R1029" t="s">
-        <v>2746</v>
+        <v>2722</v>
       </c>
     </row>
     <row r="1030" spans="1:18" x14ac:dyDescent="0.3">
@@ -56253,7 +56261,7 @@
         <v>13</v>
       </c>
       <c r="E1030" t="s">
-        <v>2706</v>
+        <v>2682</v>
       </c>
       <c r="F1030" t="s">
         <v>1857</v>
@@ -56281,7 +56289,7 @@
         <v>0</v>
       </c>
       <c r="R1030" t="s">
-        <v>2747</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="1031" spans="1:18" x14ac:dyDescent="0.3">
@@ -56298,7 +56306,7 @@
         <v>15</v>
       </c>
       <c r="E1031" t="s">
-        <v>2707</v>
+        <v>2683</v>
       </c>
       <c r="F1031" t="s">
         <v>1857</v>
@@ -56343,7 +56351,7 @@
         <v>16</v>
       </c>
       <c r="E1032" t="s">
-        <v>2708</v>
+        <v>2684</v>
       </c>
       <c r="F1032" t="s">
         <v>1857</v>
@@ -56388,7 +56396,7 @@
         <v>32</v>
       </c>
       <c r="E1033" t="s">
-        <v>2709</v>
+        <v>2685</v>
       </c>
       <c r="F1033" t="s">
         <v>1857</v>
@@ -56416,7 +56424,7 @@
         <v>0</v>
       </c>
       <c r="R1033" t="s">
-        <v>2748</v>
+        <v>2724</v>
       </c>
     </row>
     <row r="1034" spans="1:18" x14ac:dyDescent="0.3">
@@ -56433,7 +56441,7 @@
         <v>33</v>
       </c>
       <c r="E1034" t="s">
-        <v>2710</v>
+        <v>2686</v>
       </c>
       <c r="F1034" t="s">
         <v>1857</v>
@@ -56461,7 +56469,7 @@
         <v>0</v>
       </c>
       <c r="R1034" t="s">
-        <v>2749</v>
+        <v>2725</v>
       </c>
     </row>
     <row r="1035" spans="1:18" x14ac:dyDescent="0.3">
@@ -56478,7 +56486,7 @@
         <v>34</v>
       </c>
       <c r="E1035" t="s">
-        <v>2711</v>
+        <v>2687</v>
       </c>
       <c r="F1035" t="s">
         <v>1857</v>
@@ -56506,7 +56514,7 @@
         <v>0</v>
       </c>
       <c r="R1035" t="s">
-        <v>2750</v>
+        <v>2726</v>
       </c>
     </row>
     <row r="1036" spans="1:18" x14ac:dyDescent="0.3">
@@ -56523,7 +56531,7 @@
         <v>35</v>
       </c>
       <c r="E1036" t="s">
-        <v>2712</v>
+        <v>2688</v>
       </c>
       <c r="F1036" t="s">
         <v>1857</v>
@@ -56551,7 +56559,7 @@
         <v>0</v>
       </c>
       <c r="R1036" t="s">
-        <v>2751</v>
+        <v>2727</v>
       </c>
     </row>
     <row r="1037" spans="1:18" x14ac:dyDescent="0.3">
@@ -56568,7 +56576,7 @@
         <v>36</v>
       </c>
       <c r="E1037" t="s">
-        <v>2713</v>
+        <v>2689</v>
       </c>
       <c r="F1037" t="s">
         <v>1857</v>
@@ -56596,7 +56604,7 @@
         <v>0</v>
       </c>
       <c r="R1037" t="s">
-        <v>2752</v>
+        <v>2728</v>
       </c>
     </row>
     <row r="1038" spans="1:18" x14ac:dyDescent="0.3">
@@ -56613,7 +56621,7 @@
         <v>37</v>
       </c>
       <c r="E1038" t="s">
-        <v>2714</v>
+        <v>2690</v>
       </c>
       <c r="F1038" t="s">
         <v>1857</v>
@@ -56641,7 +56649,7 @@
         <v>0</v>
       </c>
       <c r="R1038" t="s">
-        <v>2753</v>
+        <v>2729</v>
       </c>
     </row>
     <row r="1039" spans="1:18" x14ac:dyDescent="0.3">
@@ -56658,7 +56666,7 @@
         <v>38</v>
       </c>
       <c r="E1039" t="s">
-        <v>2715</v>
+        <v>2691</v>
       </c>
       <c r="F1039" t="s">
         <v>1857</v>
@@ -56686,7 +56694,7 @@
         <v>0</v>
       </c>
       <c r="R1039" t="s">
-        <v>2754</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="1040" spans="1:18" x14ac:dyDescent="0.3">
@@ -56703,7 +56711,7 @@
         <v>39</v>
       </c>
       <c r="E1040" t="s">
-        <v>2716</v>
+        <v>2692</v>
       </c>
       <c r="F1040" t="s">
         <v>1857</v>
@@ -56731,7 +56739,7 @@
         <v>0</v>
       </c>
       <c r="R1040" t="s">
-        <v>2755</v>
+        <v>2731</v>
       </c>
     </row>
     <row r="1041" spans="1:18" x14ac:dyDescent="0.3">
@@ -56748,7 +56756,7 @@
         <v>40</v>
       </c>
       <c r="E1041" t="s">
-        <v>2717</v>
+        <v>2693</v>
       </c>
       <c r="F1041" t="s">
         <v>1857</v>
@@ -56776,7 +56784,7 @@
         <v>0</v>
       </c>
       <c r="R1041" t="s">
-        <v>2756</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="1042" spans="1:18" x14ac:dyDescent="0.3">
@@ -56793,7 +56801,7 @@
         <v>41</v>
       </c>
       <c r="E1042" t="s">
-        <v>2718</v>
+        <v>2694</v>
       </c>
       <c r="F1042" t="s">
         <v>1857</v>
@@ -56821,7 +56829,7 @@
         <v>0</v>
       </c>
       <c r="R1042" t="s">
-        <v>2757</v>
+        <v>2733</v>
       </c>
     </row>
     <row r="1043" spans="1:18" x14ac:dyDescent="0.3">
@@ -56838,7 +56846,7 @@
         <v>42</v>
       </c>
       <c r="E1043" t="s">
-        <v>2719</v>
+        <v>2695</v>
       </c>
       <c r="F1043" t="s">
         <v>1857</v>
@@ -56866,7 +56874,7 @@
         <v>0</v>
       </c>
       <c r="R1043" t="s">
-        <v>2758</v>
+        <v>2734</v>
       </c>
     </row>
     <row r="1044" spans="1:18" x14ac:dyDescent="0.3">
@@ -56883,7 +56891,7 @@
         <v>43</v>
       </c>
       <c r="E1044" t="s">
-        <v>2720</v>
+        <v>2696</v>
       </c>
       <c r="F1044" t="s">
         <v>1857</v>
@@ -56911,7 +56919,7 @@
         <v>0</v>
       </c>
       <c r="R1044" t="s">
-        <v>2759</v>
+        <v>2735</v>
       </c>
     </row>
     <row r="1045" spans="1:18" x14ac:dyDescent="0.3">
@@ -56928,7 +56936,7 @@
         <v>44</v>
       </c>
       <c r="E1045" t="s">
-        <v>2721</v>
+        <v>2697</v>
       </c>
       <c r="F1045" t="s">
         <v>1857</v>
@@ -56956,7 +56964,7 @@
         <v>0</v>
       </c>
       <c r="R1045" t="s">
-        <v>2760</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="1046" spans="1:18" x14ac:dyDescent="0.3">
@@ -56973,7 +56981,7 @@
         <v>46</v>
       </c>
       <c r="E1046" t="s">
-        <v>2722</v>
+        <v>2698</v>
       </c>
       <c r="F1046" t="s">
         <v>1857</v>
@@ -57001,7 +57009,7 @@
         <v>0</v>
       </c>
       <c r="R1046" t="s">
-        <v>2761</v>
+        <v>2737</v>
       </c>
     </row>
     <row r="1047" spans="1:18" x14ac:dyDescent="0.3">
@@ -57018,7 +57026,7 @@
         <v>47</v>
       </c>
       <c r="E1047" t="s">
-        <v>2723</v>
+        <v>2699</v>
       </c>
       <c r="F1047" t="s">
         <v>1857</v>
@@ -57046,7 +57054,7 @@
         <v>0</v>
       </c>
       <c r="R1047" t="s">
-        <v>2762</v>
+        <v>2738</v>
       </c>
     </row>
     <row r="1048" spans="1:18" x14ac:dyDescent="0.3">
@@ -57063,7 +57071,7 @@
         <v>48</v>
       </c>
       <c r="E1048" t="s">
-        <v>2724</v>
+        <v>2700</v>
       </c>
       <c r="F1048" t="s">
         <v>1857</v>
@@ -57091,7 +57099,7 @@
         <v>0</v>
       </c>
       <c r="R1048" t="s">
-        <v>2763</v>
+        <v>2739</v>
       </c>
     </row>
     <row r="1049" spans="1:18" x14ac:dyDescent="0.3">
@@ -57108,7 +57116,7 @@
         <v>49</v>
       </c>
       <c r="E1049" t="s">
-        <v>2725</v>
+        <v>2701</v>
       </c>
       <c r="F1049" t="s">
         <v>1857</v>
@@ -57136,7 +57144,7 @@
         <v>0</v>
       </c>
       <c r="R1049" t="s">
-        <v>2764</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="1050" spans="1:18" x14ac:dyDescent="0.3">
@@ -57153,7 +57161,7 @@
         <v>50</v>
       </c>
       <c r="E1050" t="s">
-        <v>2726</v>
+        <v>2702</v>
       </c>
       <c r="F1050" t="s">
         <v>1857</v>
@@ -57181,7 +57189,7 @@
         <v>0</v>
       </c>
       <c r="R1050" t="s">
-        <v>2765</v>
+        <v>2741</v>
       </c>
     </row>
     <row r="1051" spans="1:18" x14ac:dyDescent="0.3">
@@ -57198,7 +57206,7 @@
         <v>51</v>
       </c>
       <c r="E1051" t="s">
-        <v>2727</v>
+        <v>2703</v>
       </c>
       <c r="F1051" t="s">
         <v>1857</v>
@@ -57226,7 +57234,7 @@
         <v>0</v>
       </c>
       <c r="R1051" t="s">
-        <v>2766</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="1052" spans="1:18" x14ac:dyDescent="0.3">
@@ -57243,7 +57251,7 @@
         <v>52</v>
       </c>
       <c r="E1052" t="s">
-        <v>2728</v>
+        <v>2704</v>
       </c>
       <c r="F1052" t="s">
         <v>1857</v>
@@ -57271,7 +57279,7 @@
         <v>0</v>
       </c>
       <c r="R1052" t="s">
-        <v>2767</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="1053" spans="1:18" x14ac:dyDescent="0.3">
@@ -57288,7 +57296,7 @@
         <v>53</v>
       </c>
       <c r="E1053" t="s">
-        <v>2729</v>
+        <v>2705</v>
       </c>
       <c r="F1053" t="s">
         <v>1857</v>
@@ -57316,7 +57324,7 @@
         <v>0</v>
       </c>
       <c r="R1053" t="s">
-        <v>2768</v>
+        <v>2744</v>
       </c>
     </row>
     <row r="1054" spans="1:18" x14ac:dyDescent="0.3">
@@ -57333,7 +57341,7 @@
         <v>54</v>
       </c>
       <c r="E1054" t="s">
-        <v>2730</v>
+        <v>2706</v>
       </c>
       <c r="F1054" t="s">
         <v>1857</v>
@@ -57361,7 +57369,7 @@
         <v>0</v>
       </c>
       <c r="R1054" t="s">
-        <v>2769</v>
+        <v>2745</v>
       </c>
     </row>
     <row r="1055" spans="1:18" x14ac:dyDescent="0.3">
@@ -57378,7 +57386,7 @@
         <v>55</v>
       </c>
       <c r="E1055" t="s">
-        <v>2731</v>
+        <v>2707</v>
       </c>
       <c r="F1055" t="s">
         <v>1857</v>
@@ -57406,7 +57414,7 @@
         <v>0</v>
       </c>
       <c r="R1055" t="s">
-        <v>2770</v>
+        <v>2746</v>
       </c>
     </row>
     <row r="1056" spans="1:18" x14ac:dyDescent="0.3">
@@ -57423,7 +57431,7 @@
         <v>56</v>
       </c>
       <c r="E1056" t="s">
-        <v>2732</v>
+        <v>2708</v>
       </c>
       <c r="F1056" t="s">
         <v>1857</v>
@@ -57451,7 +57459,7 @@
         <v>0</v>
       </c>
       <c r="R1056" t="s">
-        <v>2771</v>
+        <v>2747</v>
       </c>
     </row>
     <row r="1057" spans="1:18" x14ac:dyDescent="0.3">
@@ -57468,7 +57476,7 @@
         <v>57</v>
       </c>
       <c r="E1057" t="s">
-        <v>2733</v>
+        <v>2709</v>
       </c>
       <c r="F1057" t="s">
         <v>1857</v>
@@ -57496,7 +57504,7 @@
         <v>0</v>
       </c>
       <c r="R1057" t="s">
-        <v>2772</v>
+        <v>2748</v>
       </c>
     </row>
     <row r="1058" spans="1:18" x14ac:dyDescent="0.3">
@@ -57513,7 +57521,7 @@
         <v>58</v>
       </c>
       <c r="E1058" t="s">
-        <v>2734</v>
+        <v>2710</v>
       </c>
       <c r="F1058" t="s">
         <v>1857</v>
@@ -57541,7 +57549,7 @@
         <v>0</v>
       </c>
       <c r="R1058" t="s">
-        <v>2773</v>
+        <v>2749</v>
       </c>
     </row>
     <row r="1059" spans="1:18" x14ac:dyDescent="0.3">
@@ -58143,7 +58151,7 @@
         <v>74</v>
       </c>
       <c r="E1072" t="s">
-        <v>2826</v>
+        <v>2802</v>
       </c>
       <c r="F1072" t="s">
         <v>1857</v>
@@ -58171,7 +58179,7 @@
         <v>0</v>
       </c>
       <c r="R1072" t="s">
-        <v>2774</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="1073" spans="1:18" x14ac:dyDescent="0.3">
@@ -58188,7 +58196,7 @@
         <v>75</v>
       </c>
       <c r="E1073" t="s">
-        <v>2827</v>
+        <v>2803</v>
       </c>
       <c r="F1073" t="s">
         <v>1857</v>
@@ -58216,7 +58224,7 @@
         <v>0</v>
       </c>
       <c r="R1073" t="s">
-        <v>2775</v>
+        <v>2751</v>
       </c>
     </row>
     <row r="1074" spans="1:18" x14ac:dyDescent="0.3">
@@ -58233,7 +58241,7 @@
         <v>76</v>
       </c>
       <c r="E1074" t="s">
-        <v>2828</v>
+        <v>2804</v>
       </c>
       <c r="F1074" t="s">
         <v>1857</v>
@@ -58261,7 +58269,7 @@
         <v>0</v>
       </c>
       <c r="R1074" t="s">
-        <v>2776</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="1075" spans="1:18" x14ac:dyDescent="0.3">
@@ -58278,7 +58286,7 @@
         <v>77</v>
       </c>
       <c r="E1075" t="s">
-        <v>2829</v>
+        <v>2805</v>
       </c>
       <c r="F1075" t="s">
         <v>1857</v>
@@ -58306,7 +58314,7 @@
         <v>0</v>
       </c>
       <c r="R1075" t="s">
-        <v>2777</v>
+        <v>2753</v>
       </c>
     </row>
     <row r="1076" spans="1:18" x14ac:dyDescent="0.3">
@@ -58323,7 +58331,7 @@
         <v>78</v>
       </c>
       <c r="E1076" t="s">
-        <v>2830</v>
+        <v>2806</v>
       </c>
       <c r="F1076" t="s">
         <v>1857</v>
@@ -58351,7 +58359,7 @@
         <v>0</v>
       </c>
       <c r="R1076" t="s">
-        <v>2778</v>
+        <v>2754</v>
       </c>
     </row>
     <row r="1077" spans="1:18" x14ac:dyDescent="0.3">
@@ -58368,7 +58376,7 @@
         <v>79</v>
       </c>
       <c r="E1077" t="s">
-        <v>2831</v>
+        <v>2807</v>
       </c>
       <c r="F1077" t="s">
         <v>1857</v>
@@ -58396,7 +58404,7 @@
         <v>0</v>
       </c>
       <c r="R1077" t="s">
-        <v>2779</v>
+        <v>2755</v>
       </c>
     </row>
     <row r="1078" spans="1:18" x14ac:dyDescent="0.3">
@@ -58413,7 +58421,7 @@
         <v>80</v>
       </c>
       <c r="E1078" t="s">
-        <v>2832</v>
+        <v>2808</v>
       </c>
       <c r="F1078" t="s">
         <v>1857</v>
@@ -58441,7 +58449,7 @@
         <v>0</v>
       </c>
       <c r="R1078" t="s">
-        <v>2780</v>
+        <v>2756</v>
       </c>
     </row>
     <row r="1079" spans="1:18" x14ac:dyDescent="0.3">
@@ -58458,7 +58466,7 @@
         <v>81</v>
       </c>
       <c r="E1079" t="s">
-        <v>2833</v>
+        <v>2809</v>
       </c>
       <c r="F1079" t="s">
         <v>1857</v>
@@ -58486,7 +58494,7 @@
         <v>0</v>
       </c>
       <c r="R1079" t="s">
-        <v>2781</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="1080" spans="1:18" x14ac:dyDescent="0.3">
@@ -58503,7 +58511,7 @@
         <v>82</v>
       </c>
       <c r="E1080" t="s">
-        <v>2834</v>
+        <v>2810</v>
       </c>
       <c r="F1080" t="s">
         <v>1857</v>
@@ -58531,7 +58539,7 @@
         <v>0</v>
       </c>
       <c r="R1080" t="s">
-        <v>2782</v>
+        <v>2758</v>
       </c>
     </row>
     <row r="1081" spans="1:18" x14ac:dyDescent="0.3">
@@ -58548,7 +58556,7 @@
         <v>83</v>
       </c>
       <c r="E1081" t="s">
-        <v>2835</v>
+        <v>2811</v>
       </c>
       <c r="F1081" t="s">
         <v>1857</v>
@@ -58576,7 +58584,7 @@
         <v>0</v>
       </c>
       <c r="R1081" t="s">
-        <v>2783</v>
+        <v>2759</v>
       </c>
     </row>
     <row r="1082" spans="1:18" x14ac:dyDescent="0.3">
@@ -58593,7 +58601,7 @@
         <v>84</v>
       </c>
       <c r="E1082" t="s">
-        <v>2836</v>
+        <v>2812</v>
       </c>
       <c r="F1082" t="s">
         <v>1857</v>
@@ -58621,7 +58629,7 @@
         <v>0</v>
       </c>
       <c r="R1082" t="s">
-        <v>2784</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="1083" spans="1:18" x14ac:dyDescent="0.3">
@@ -58638,7 +58646,7 @@
         <v>85</v>
       </c>
       <c r="E1083" t="s">
-        <v>2837</v>
+        <v>2813</v>
       </c>
       <c r="F1083" t="s">
         <v>1857</v>
@@ -58666,7 +58674,7 @@
         <v>0</v>
       </c>
       <c r="R1083" t="s">
-        <v>2785</v>
+        <v>2761</v>
       </c>
     </row>
     <row r="1084" spans="1:18" x14ac:dyDescent="0.3">
@@ -58683,7 +58691,7 @@
         <v>86</v>
       </c>
       <c r="E1084" t="s">
-        <v>2838</v>
+        <v>2814</v>
       </c>
       <c r="F1084" t="s">
         <v>1857</v>
@@ -58711,7 +58719,7 @@
         <v>0</v>
       </c>
       <c r="R1084" t="s">
-        <v>2786</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="1085" spans="1:18" x14ac:dyDescent="0.3">
@@ -58728,7 +58736,7 @@
         <v>60</v>
       </c>
       <c r="E1085" t="s">
-        <v>2839</v>
+        <v>2815</v>
       </c>
       <c r="F1085" t="s">
         <v>1857</v>
@@ -58756,7 +58764,7 @@
         <v>0</v>
       </c>
       <c r="R1085" t="s">
-        <v>2787</v>
+        <v>2763</v>
       </c>
     </row>
     <row r="1086" spans="1:18" x14ac:dyDescent="0.3">
@@ -58773,7 +58781,7 @@
         <v>61</v>
       </c>
       <c r="E1086" t="s">
-        <v>2840</v>
+        <v>2816</v>
       </c>
       <c r="F1086" t="s">
         <v>1857</v>
@@ -58801,7 +58809,7 @@
         <v>0</v>
       </c>
       <c r="R1086" t="s">
-        <v>2788</v>
+        <v>2764</v>
       </c>
     </row>
     <row r="1087" spans="1:18" x14ac:dyDescent="0.3">
@@ -58818,7 +58826,7 @@
         <v>62</v>
       </c>
       <c r="E1087" t="s">
-        <v>2841</v>
+        <v>2817</v>
       </c>
       <c r="F1087" t="s">
         <v>1857</v>
@@ -58846,7 +58854,7 @@
         <v>0</v>
       </c>
       <c r="R1087" t="s">
-        <v>2789</v>
+        <v>2765</v>
       </c>
     </row>
     <row r="1088" spans="1:18" x14ac:dyDescent="0.3">
@@ -58863,7 +58871,7 @@
         <v>63</v>
       </c>
       <c r="E1088" t="s">
-        <v>2842</v>
+        <v>2818</v>
       </c>
       <c r="F1088" t="s">
         <v>1857</v>
@@ -58891,7 +58899,7 @@
         <v>0</v>
       </c>
       <c r="R1088" t="s">
-        <v>2790</v>
+        <v>2766</v>
       </c>
     </row>
     <row r="1089" spans="1:18" x14ac:dyDescent="0.3">
@@ -58908,7 +58916,7 @@
         <v>64</v>
       </c>
       <c r="E1089" t="s">
-        <v>2843</v>
+        <v>2819</v>
       </c>
       <c r="F1089" t="s">
         <v>1857</v>
@@ -58936,7 +58944,7 @@
         <v>0</v>
       </c>
       <c r="R1089" t="s">
-        <v>2791</v>
+        <v>2767</v>
       </c>
     </row>
     <row r="1090" spans="1:18" x14ac:dyDescent="0.3">
@@ -58953,7 +58961,7 @@
         <v>65</v>
       </c>
       <c r="E1090" t="s">
-        <v>2844</v>
+        <v>2820</v>
       </c>
       <c r="F1090" t="s">
         <v>1857</v>
@@ -58981,7 +58989,7 @@
         <v>0</v>
       </c>
       <c r="R1090" t="s">
-        <v>2792</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="1091" spans="1:18" x14ac:dyDescent="0.3">
@@ -58998,7 +59006,7 @@
         <v>66</v>
       </c>
       <c r="E1091" t="s">
-        <v>2845</v>
+        <v>2821</v>
       </c>
       <c r="F1091" t="s">
         <v>1857</v>
@@ -59026,7 +59034,7 @@
         <v>0</v>
       </c>
       <c r="R1091" t="s">
-        <v>2793</v>
+        <v>2769</v>
       </c>
     </row>
     <row r="1092" spans="1:18" x14ac:dyDescent="0.3">
@@ -59043,7 +59051,7 @@
         <v>67</v>
       </c>
       <c r="E1092" t="s">
-        <v>2846</v>
+        <v>2822</v>
       </c>
       <c r="F1092" t="s">
         <v>1857</v>
@@ -59071,7 +59079,7 @@
         <v>0</v>
       </c>
       <c r="R1092" t="s">
-        <v>2794</v>
+        <v>2770</v>
       </c>
     </row>
     <row r="1093" spans="1:18" x14ac:dyDescent="0.3">
@@ -59088,7 +59096,7 @@
         <v>68</v>
       </c>
       <c r="E1093" t="s">
-        <v>2847</v>
+        <v>2823</v>
       </c>
       <c r="F1093" t="s">
         <v>1857</v>
@@ -59116,7 +59124,7 @@
         <v>0</v>
       </c>
       <c r="R1093" t="s">
-        <v>2795</v>
+        <v>2771</v>
       </c>
     </row>
     <row r="1094" spans="1:18" x14ac:dyDescent="0.3">
@@ -59133,7 +59141,7 @@
         <v>69</v>
       </c>
       <c r="E1094" t="s">
-        <v>2848</v>
+        <v>2824</v>
       </c>
       <c r="F1094" t="s">
         <v>1857</v>
@@ -59161,7 +59169,7 @@
         <v>0</v>
       </c>
       <c r="R1094" t="s">
-        <v>2796</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="1095" spans="1:18" x14ac:dyDescent="0.3">
@@ -59178,7 +59186,7 @@
         <v>70</v>
       </c>
       <c r="E1095" t="s">
-        <v>2849</v>
+        <v>2825</v>
       </c>
       <c r="F1095" t="s">
         <v>1857</v>
@@ -59206,7 +59214,7 @@
         <v>0</v>
       </c>
       <c r="R1095" t="s">
-        <v>2797</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="1096" spans="1:18" x14ac:dyDescent="0.3">
@@ -59223,7 +59231,7 @@
         <v>71</v>
       </c>
       <c r="E1096" t="s">
-        <v>2850</v>
+        <v>2826</v>
       </c>
       <c r="F1096" t="s">
         <v>1857</v>
@@ -59251,7 +59259,7 @@
         <v>0</v>
       </c>
       <c r="R1096" t="s">
-        <v>2798</v>
+        <v>2774</v>
       </c>
     </row>
     <row r="1097" spans="1:18" x14ac:dyDescent="0.3">
@@ -59268,7 +59276,7 @@
         <v>72</v>
       </c>
       <c r="E1097" t="s">
-        <v>2851</v>
+        <v>2827</v>
       </c>
       <c r="F1097" t="s">
         <v>1857</v>
@@ -59296,7 +59304,7 @@
         <v>0</v>
       </c>
       <c r="R1097" t="s">
-        <v>2799</v>
+        <v>2775</v>
       </c>
     </row>
     <row r="1098" spans="1:18" x14ac:dyDescent="0.3">
@@ -59313,7 +59321,7 @@
         <v>88</v>
       </c>
       <c r="E1098" t="s">
-        <v>2813</v>
+        <v>2789</v>
       </c>
       <c r="F1098" t="s">
         <v>1857</v>
@@ -59341,7 +59349,7 @@
         <v>0</v>
       </c>
       <c r="R1098" t="s">
-        <v>2800</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="1099" spans="1:18" x14ac:dyDescent="0.3">
@@ -59358,7 +59366,7 @@
         <v>89</v>
       </c>
       <c r="E1099" t="s">
-        <v>2814</v>
+        <v>2790</v>
       </c>
       <c r="F1099" t="s">
         <v>1857</v>
@@ -59386,7 +59394,7 @@
         <v>0</v>
       </c>
       <c r="R1099" t="s">
-        <v>2801</v>
+        <v>2777</v>
       </c>
     </row>
     <row r="1100" spans="1:18" x14ac:dyDescent="0.3">
@@ -59403,7 +59411,7 @@
         <v>90</v>
       </c>
       <c r="E1100" t="s">
-        <v>2815</v>
+        <v>2791</v>
       </c>
       <c r="F1100" t="s">
         <v>1857</v>
@@ -59431,7 +59439,7 @@
         <v>0</v>
       </c>
       <c r="R1100" t="s">
-        <v>2802</v>
+        <v>2778</v>
       </c>
     </row>
     <row r="1101" spans="1:18" x14ac:dyDescent="0.3">
@@ -59448,7 +59456,7 @@
         <v>91</v>
       </c>
       <c r="E1101" t="s">
-        <v>2816</v>
+        <v>2792</v>
       </c>
       <c r="F1101" t="s">
         <v>1857</v>
@@ -59476,7 +59484,7 @@
         <v>0</v>
       </c>
       <c r="R1101" t="s">
-        <v>2803</v>
+        <v>2779</v>
       </c>
     </row>
     <row r="1102" spans="1:18" x14ac:dyDescent="0.3">
@@ -59493,7 +59501,7 @@
         <v>92</v>
       </c>
       <c r="E1102" t="s">
-        <v>2817</v>
+        <v>2793</v>
       </c>
       <c r="F1102" t="s">
         <v>1857</v>
@@ -59521,7 +59529,7 @@
         <v>0</v>
       </c>
       <c r="R1102" t="s">
-        <v>2804</v>
+        <v>2780</v>
       </c>
     </row>
     <row r="1103" spans="1:18" x14ac:dyDescent="0.3">
@@ -59538,7 +59546,7 @@
         <v>93</v>
       </c>
       <c r="E1103" t="s">
-        <v>2818</v>
+        <v>2794</v>
       </c>
       <c r="F1103" t="s">
         <v>1857</v>
@@ -59566,7 +59574,7 @@
         <v>0</v>
       </c>
       <c r="R1103" t="s">
-        <v>2805</v>
+        <v>2781</v>
       </c>
     </row>
     <row r="1104" spans="1:18" x14ac:dyDescent="0.3">
@@ -59583,7 +59591,7 @@
         <v>94</v>
       </c>
       <c r="E1104" t="s">
-        <v>2819</v>
+        <v>2795</v>
       </c>
       <c r="F1104" t="s">
         <v>1857</v>
@@ -59611,7 +59619,7 @@
         <v>0</v>
       </c>
       <c r="R1104" t="s">
-        <v>2806</v>
+        <v>2782</v>
       </c>
     </row>
     <row r="1105" spans="1:18" x14ac:dyDescent="0.3">
@@ -59628,7 +59636,7 @@
         <v>95</v>
       </c>
       <c r="E1105" t="s">
-        <v>2820</v>
+        <v>2796</v>
       </c>
       <c r="F1105" t="s">
         <v>1857</v>
@@ -59656,7 +59664,7 @@
         <v>0</v>
       </c>
       <c r="R1105" t="s">
-        <v>2807</v>
+        <v>2783</v>
       </c>
     </row>
     <row r="1106" spans="1:18" x14ac:dyDescent="0.3">
@@ -59673,7 +59681,7 @@
         <v>96</v>
       </c>
       <c r="E1106" t="s">
-        <v>2821</v>
+        <v>2797</v>
       </c>
       <c r="F1106" t="s">
         <v>1857</v>
@@ -59701,7 +59709,7 @@
         <v>0</v>
       </c>
       <c r="R1106" t="s">
-        <v>2808</v>
+        <v>2784</v>
       </c>
     </row>
     <row r="1107" spans="1:18" x14ac:dyDescent="0.3">
@@ -59718,7 +59726,7 @@
         <v>97</v>
       </c>
       <c r="E1107" t="s">
-        <v>2822</v>
+        <v>2798</v>
       </c>
       <c r="F1107" t="s">
         <v>1857</v>
@@ -59746,7 +59754,7 @@
         <v>0</v>
       </c>
       <c r="R1107" t="s">
-        <v>2809</v>
+        <v>2785</v>
       </c>
     </row>
     <row r="1108" spans="1:18" x14ac:dyDescent="0.3">
@@ -59763,7 +59771,7 @@
         <v>98</v>
       </c>
       <c r="E1108" t="s">
-        <v>2823</v>
+        <v>2799</v>
       </c>
       <c r="F1108" t="s">
         <v>1857</v>
@@ -59791,7 +59799,7 @@
         <v>0</v>
       </c>
       <c r="R1108" t="s">
-        <v>2810</v>
+        <v>2786</v>
       </c>
     </row>
     <row r="1109" spans="1:18" x14ac:dyDescent="0.3">
@@ -59808,7 +59816,7 @@
         <v>99</v>
       </c>
       <c r="E1109" t="s">
-        <v>2824</v>
+        <v>2800</v>
       </c>
       <c r="F1109" t="s">
         <v>1857</v>
@@ -59836,7 +59844,7 @@
         <v>0</v>
       </c>
       <c r="R1109" t="s">
-        <v>2811</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="1110" spans="1:18" x14ac:dyDescent="0.3">
@@ -59853,7 +59861,7 @@
         <v>100</v>
       </c>
       <c r="E1110" t="s">
-        <v>2825</v>
+        <v>2801</v>
       </c>
       <c r="F1110" t="s">
         <v>1857</v>
@@ -59881,7 +59889,7 @@
         <v>0</v>
       </c>
       <c r="R1110" t="s">
-        <v>2812</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="1111" spans="1:18" x14ac:dyDescent="0.3">
@@ -60098,7 +60106,7 @@
         <v>0</v>
       </c>
       <c r="E1116" t="s">
-        <v>3145</v>
+        <v>3121</v>
       </c>
       <c r="F1116" t="s">
         <v>1853</v>
@@ -60114,7 +60122,7 @@
       </c>
       <c r="J1116" s="6"/>
       <c r="L1116" s="3" t="s">
-        <v>3162</v>
+        <v>3138</v>
       </c>
       <c r="M1116">
         <v>2</v>
@@ -60146,7 +60154,7 @@
         <v>1</v>
       </c>
       <c r="E1117" t="s">
-        <v>3146</v>
+        <v>3122</v>
       </c>
       <c r="F1117" t="s">
         <v>1853</v>
@@ -60162,7 +60170,7 @@
       </c>
       <c r="J1117" s="6"/>
       <c r="L1117" s="3" t="s">
-        <v>3163</v>
+        <v>3139</v>
       </c>
       <c r="M1117">
         <v>2</v>
@@ -60194,7 +60202,7 @@
         <v>2</v>
       </c>
       <c r="E1118" t="s">
-        <v>3147</v>
+        <v>3123</v>
       </c>
       <c r="F1118" t="s">
         <v>1853</v>
@@ -60210,7 +60218,7 @@
       </c>
       <c r="J1118" s="6"/>
       <c r="L1118" s="3" t="s">
-        <v>3164</v>
+        <v>3140</v>
       </c>
       <c r="M1118">
         <v>2</v>
@@ -60242,7 +60250,7 @@
         <v>3</v>
       </c>
       <c r="E1119" t="s">
-        <v>3148</v>
+        <v>3124</v>
       </c>
       <c r="F1119" t="s">
         <v>1853</v>
@@ -60258,7 +60266,7 @@
       </c>
       <c r="J1119" s="6"/>
       <c r="L1119" s="3" t="s">
-        <v>3165</v>
+        <v>3141</v>
       </c>
       <c r="M1119">
         <v>2</v>
@@ -60290,7 +60298,7 @@
         <v>4</v>
       </c>
       <c r="E1120" t="s">
-        <v>3149</v>
+        <v>3125</v>
       </c>
       <c r="F1120" t="s">
         <v>1853</v>
@@ -60306,7 +60314,7 @@
       </c>
       <c r="J1120" s="6"/>
       <c r="L1120" s="3" t="s">
-        <v>3166</v>
+        <v>3142</v>
       </c>
       <c r="M1120">
         <v>2</v>
@@ -60338,7 +60346,7 @@
         <v>5</v>
       </c>
       <c r="E1121" t="s">
-        <v>3150</v>
+        <v>3126</v>
       </c>
       <c r="F1121" t="s">
         <v>1853</v>
@@ -60354,7 +60362,7 @@
       </c>
       <c r="J1121" s="6"/>
       <c r="L1121" s="3" t="s">
-        <v>3167</v>
+        <v>3143</v>
       </c>
       <c r="M1121">
         <v>2</v>
@@ -60386,7 +60394,7 @@
         <v>6</v>
       </c>
       <c r="E1122" t="s">
-        <v>3151</v>
+        <v>3127</v>
       </c>
       <c r="F1122" t="s">
         <v>1853</v>
@@ -60402,7 +60410,7 @@
       </c>
       <c r="J1122" s="6"/>
       <c r="L1122" s="3" t="s">
-        <v>3168</v>
+        <v>3144</v>
       </c>
       <c r="M1122">
         <v>2</v>
@@ -60434,7 +60442,7 @@
         <v>7</v>
       </c>
       <c r="E1123" t="s">
-        <v>3152</v>
+        <v>3128</v>
       </c>
       <c r="F1123" t="s">
         <v>1853</v>
@@ -60450,7 +60458,7 @@
       </c>
       <c r="J1123" s="6"/>
       <c r="L1123" s="3" t="s">
-        <v>3169</v>
+        <v>3145</v>
       </c>
       <c r="M1123">
         <v>2</v>
@@ -60482,7 +60490,7 @@
         <v>8</v>
       </c>
       <c r="E1124" t="s">
-        <v>3153</v>
+        <v>3129</v>
       </c>
       <c r="F1124" t="s">
         <v>1853</v>
@@ -60498,7 +60506,7 @@
       </c>
       <c r="J1124" s="6"/>
       <c r="L1124" s="3" t="s">
-        <v>3170</v>
+        <v>3146</v>
       </c>
       <c r="M1124">
         <v>2</v>
@@ -60530,7 +60538,7 @@
         <v>9</v>
       </c>
       <c r="E1125" t="s">
-        <v>3154</v>
+        <v>3130</v>
       </c>
       <c r="F1125" t="s">
         <v>1853</v>
@@ -60546,7 +60554,7 @@
       </c>
       <c r="J1125" s="6"/>
       <c r="L1125" s="3" t="s">
-        <v>3171</v>
+        <v>3147</v>
       </c>
       <c r="M1125">
         <v>2</v>
@@ -60578,7 +60586,7 @@
         <v>10</v>
       </c>
       <c r="E1126" t="s">
-        <v>3155</v>
+        <v>3131</v>
       </c>
       <c r="F1126" t="s">
         <v>1853</v>
@@ -60594,7 +60602,7 @@
       </c>
       <c r="J1126" s="6"/>
       <c r="L1126" s="3" t="s">
-        <v>3172</v>
+        <v>3148</v>
       </c>
       <c r="M1126">
         <v>2</v>
@@ -60626,7 +60634,7 @@
         <v>11</v>
       </c>
       <c r="E1127" t="s">
-        <v>3156</v>
+        <v>3132</v>
       </c>
       <c r="F1127" t="s">
         <v>1853</v>
@@ -60642,7 +60650,7 @@
       </c>
       <c r="J1127" s="6"/>
       <c r="L1127" s="3" t="s">
-        <v>3173</v>
+        <v>3149</v>
       </c>
       <c r="M1127">
         <v>2</v>
@@ -60674,7 +60682,7 @@
         <v>12</v>
       </c>
       <c r="E1128" t="s">
-        <v>3157</v>
+        <v>3133</v>
       </c>
       <c r="F1128" t="s">
         <v>1853</v>
@@ -60690,7 +60698,7 @@
       </c>
       <c r="J1128" s="6"/>
       <c r="L1128" s="3" t="s">
-        <v>3174</v>
+        <v>3150</v>
       </c>
       <c r="M1128">
         <v>2</v>
@@ -60722,7 +60730,7 @@
         <v>13</v>
       </c>
       <c r="E1129" t="s">
-        <v>3158</v>
+        <v>3134</v>
       </c>
       <c r="F1129" t="s">
         <v>1853</v>
@@ -60738,7 +60746,7 @@
       </c>
       <c r="J1129" s="6"/>
       <c r="L1129" s="3" t="s">
-        <v>3175</v>
+        <v>3151</v>
       </c>
       <c r="M1129">
         <v>2</v>
@@ -60970,7 +60978,7 @@
         <v>1</v>
       </c>
       <c r="E1135" t="s">
-        <v>2677</v>
+        <v>3199</v>
       </c>
       <c r="F1135" t="s">
         <v>1854</v>
@@ -60986,7 +60994,7 @@
       </c>
       <c r="J1135" s="6"/>
       <c r="L1135" s="3" t="s">
-        <v>3176</v>
+        <v>3152</v>
       </c>
       <c r="M1135">
         <v>2</v>
@@ -61018,7 +61026,7 @@
         <v>2</v>
       </c>
       <c r="E1136" t="s">
-        <v>2654</v>
+        <v>3198</v>
       </c>
       <c r="F1136" t="s">
         <v>1854</v>
@@ -61034,7 +61042,7 @@
       </c>
       <c r="J1136" s="6"/>
       <c r="L1136" s="3" t="s">
-        <v>3177</v>
+        <v>3153</v>
       </c>
       <c r="M1136">
         <v>2</v>
@@ -61066,7 +61074,7 @@
         <v>3</v>
       </c>
       <c r="E1137" t="s">
-        <v>2655</v>
+        <v>3197</v>
       </c>
       <c r="F1137" t="s">
         <v>1854</v>
@@ -61082,7 +61090,7 @@
       </c>
       <c r="J1137" s="6"/>
       <c r="L1137" s="3" t="s">
-        <v>3178</v>
+        <v>3154</v>
       </c>
       <c r="M1137">
         <v>2</v>
@@ -61114,7 +61122,7 @@
         <v>4</v>
       </c>
       <c r="E1138" t="s">
-        <v>2656</v>
+        <v>3196</v>
       </c>
       <c r="F1138" t="s">
         <v>1854</v>
@@ -61130,7 +61138,7 @@
       </c>
       <c r="J1138" s="6"/>
       <c r="L1138" s="3" t="s">
-        <v>3179</v>
+        <v>3155</v>
       </c>
       <c r="M1138">
         <v>2</v>
@@ -61162,7 +61170,7 @@
         <v>5</v>
       </c>
       <c r="E1139" t="s">
-        <v>2657</v>
+        <v>3194</v>
       </c>
       <c r="F1139" t="s">
         <v>1854</v>
@@ -61178,7 +61186,7 @@
       </c>
       <c r="J1139" s="6"/>
       <c r="L1139" s="3" t="s">
-        <v>3180</v>
+        <v>3156</v>
       </c>
       <c r="M1139">
         <v>2</v>
@@ -61210,7 +61218,7 @@
         <v>6</v>
       </c>
       <c r="E1140" t="s">
-        <v>2658</v>
+        <v>3195</v>
       </c>
       <c r="F1140" t="s">
         <v>1854</v>
@@ -61226,7 +61234,7 @@
       </c>
       <c r="J1140" s="6"/>
       <c r="L1140" s="3" t="s">
-        <v>3181</v>
+        <v>3157</v>
       </c>
       <c r="M1140">
         <v>2</v>
@@ -61258,7 +61266,7 @@
         <v>7</v>
       </c>
       <c r="E1141" t="s">
-        <v>2659</v>
+        <v>3193</v>
       </c>
       <c r="F1141" t="s">
         <v>1854</v>
@@ -61274,7 +61282,7 @@
       </c>
       <c r="J1141" s="6"/>
       <c r="L1141" s="3" t="s">
-        <v>3182</v>
+        <v>3158</v>
       </c>
       <c r="M1141">
         <v>2</v>
@@ -61306,7 +61314,7 @@
         <v>8</v>
       </c>
       <c r="E1142" t="s">
-        <v>2660</v>
+        <v>3189</v>
       </c>
       <c r="F1142" t="s">
         <v>1854</v>
@@ -61322,7 +61330,7 @@
       </c>
       <c r="J1142" s="6"/>
       <c r="L1142" s="3" t="s">
-        <v>3183</v>
+        <v>3159</v>
       </c>
       <c r="M1142">
         <v>2</v>
@@ -61354,7 +61362,7 @@
         <v>9</v>
       </c>
       <c r="E1143" t="s">
-        <v>2661</v>
+        <v>3188</v>
       </c>
       <c r="F1143" t="s">
         <v>1854</v>
@@ -61370,7 +61378,7 @@
       </c>
       <c r="J1143" s="6"/>
       <c r="L1143" s="3" t="s">
-        <v>3184</v>
+        <v>3160</v>
       </c>
       <c r="M1143">
         <v>2</v>
@@ -61402,7 +61410,7 @@
         <v>10</v>
       </c>
       <c r="E1144" t="s">
-        <v>2662</v>
+        <v>3187</v>
       </c>
       <c r="F1144" t="s">
         <v>1854</v>
@@ -61418,7 +61426,7 @@
       </c>
       <c r="J1144" s="6"/>
       <c r="L1144" s="3" t="s">
-        <v>3185</v>
+        <v>3161</v>
       </c>
       <c r="M1144">
         <v>2</v>
@@ -61450,7 +61458,7 @@
         <v>11</v>
       </c>
       <c r="E1145" t="s">
-        <v>2663</v>
+        <v>3186</v>
       </c>
       <c r="F1145" t="s">
         <v>1854</v>
@@ -61466,7 +61474,7 @@
       </c>
       <c r="J1145" s="6"/>
       <c r="L1145" s="3" t="s">
-        <v>3186</v>
+        <v>3162</v>
       </c>
       <c r="M1145">
         <v>2</v>
@@ -61498,7 +61506,7 @@
         <v>12</v>
       </c>
       <c r="E1146" t="s">
-        <v>2664</v>
+        <v>3190</v>
       </c>
       <c r="F1146" t="s">
         <v>1854</v>
@@ -61514,7 +61522,7 @@
       </c>
       <c r="J1146" s="6"/>
       <c r="L1146" s="3" t="s">
-        <v>3187</v>
+        <v>3163</v>
       </c>
       <c r="M1146">
         <v>2</v>
@@ -61546,7 +61554,7 @@
         <v>13</v>
       </c>
       <c r="E1147" t="s">
-        <v>2665</v>
+        <v>3185</v>
       </c>
       <c r="F1147" t="s">
         <v>1854</v>
@@ -61562,7 +61570,7 @@
       </c>
       <c r="J1147" s="6"/>
       <c r="L1147" s="3" t="s">
-        <v>3188</v>
+        <v>3164</v>
       </c>
       <c r="M1147">
         <v>2</v>
@@ -61594,7 +61602,7 @@
         <v>14</v>
       </c>
       <c r="E1148" t="s">
-        <v>2666</v>
+        <v>3184</v>
       </c>
       <c r="F1148" t="s">
         <v>1854</v>
@@ -61610,7 +61618,7 @@
       </c>
       <c r="J1148" s="6"/>
       <c r="L1148" s="3" t="s">
-        <v>3189</v>
+        <v>3165</v>
       </c>
       <c r="M1148">
         <v>2</v>
@@ -61642,7 +61650,7 @@
         <v>15</v>
       </c>
       <c r="E1149" t="s">
-        <v>2667</v>
+        <v>3191</v>
       </c>
       <c r="F1149" t="s">
         <v>1854</v>
@@ -61658,7 +61666,7 @@
       </c>
       <c r="J1149" s="6"/>
       <c r="L1149" s="3" t="s">
-        <v>3190</v>
+        <v>3166</v>
       </c>
       <c r="M1149">
         <v>2</v>
@@ -61690,7 +61698,7 @@
         <v>16</v>
       </c>
       <c r="E1150" t="s">
-        <v>2668</v>
+        <v>3183</v>
       </c>
       <c r="F1150" t="s">
         <v>1854</v>
@@ -61706,7 +61714,7 @@
       </c>
       <c r="J1150" s="6"/>
       <c r="L1150" s="3" t="s">
-        <v>3191</v>
+        <v>3167</v>
       </c>
       <c r="M1150">
         <v>2</v>
@@ -61738,7 +61746,7 @@
         <v>17</v>
       </c>
       <c r="E1151" t="s">
-        <v>2669</v>
+        <v>3182</v>
       </c>
       <c r="F1151" t="s">
         <v>1854</v>
@@ -61754,7 +61762,7 @@
       </c>
       <c r="J1151" s="6"/>
       <c r="L1151" s="3" t="s">
-        <v>3192</v>
+        <v>3168</v>
       </c>
       <c r="M1151">
         <v>2</v>
@@ -61785,8 +61793,8 @@
       <c r="D1152">
         <v>18</v>
       </c>
-      <c r="E1152" t="s">
-        <v>2670</v>
+      <c r="E1152" s="13" t="s">
+        <v>3181</v>
       </c>
       <c r="F1152" t="s">
         <v>1854</v>
@@ -61802,7 +61810,7 @@
       </c>
       <c r="J1152" s="6"/>
       <c r="L1152" s="3" t="s">
-        <v>3193</v>
+        <v>3169</v>
       </c>
       <c r="M1152">
         <v>2</v>
@@ -61833,8 +61841,8 @@
       <c r="D1153">
         <v>19</v>
       </c>
-      <c r="E1153" t="s">
-        <v>2671</v>
+      <c r="E1153" s="13" t="s">
+        <v>3180</v>
       </c>
       <c r="F1153" t="s">
         <v>1854</v>
@@ -61850,7 +61858,7 @@
       </c>
       <c r="J1153" s="6"/>
       <c r="L1153" s="3" t="s">
-        <v>3194</v>
+        <v>3170</v>
       </c>
       <c r="M1153">
         <v>2</v>
@@ -61882,7 +61890,7 @@
         <v>20</v>
       </c>
       <c r="E1154" t="s">
-        <v>2672</v>
+        <v>3192</v>
       </c>
       <c r="F1154" t="s">
         <v>1854</v>
@@ -61898,7 +61906,7 @@
       </c>
       <c r="J1154" s="6"/>
       <c r="L1154" s="3" t="s">
-        <v>3195</v>
+        <v>3171</v>
       </c>
       <c r="M1154">
         <v>2</v>
@@ -61929,8 +61937,8 @@
       <c r="D1155">
         <v>21</v>
       </c>
-      <c r="E1155" t="s">
-        <v>2673</v>
+      <c r="E1155" s="13" t="s">
+        <v>3179</v>
       </c>
       <c r="F1155" t="s">
         <v>1854</v>
@@ -61946,7 +61954,7 @@
       </c>
       <c r="J1155" s="6"/>
       <c r="L1155" s="3" t="s">
-        <v>3196</v>
+        <v>3172</v>
       </c>
       <c r="M1155">
         <v>2</v>
@@ -61977,8 +61985,8 @@
       <c r="D1156">
         <v>22</v>
       </c>
-      <c r="E1156" t="s">
-        <v>2674</v>
+      <c r="E1156" s="13" t="s">
+        <v>3178</v>
       </c>
       <c r="F1156" t="s">
         <v>1854</v>
@@ -61994,7 +62002,7 @@
       </c>
       <c r="J1156" s="6"/>
       <c r="L1156" s="3" t="s">
-        <v>3197</v>
+        <v>3173</v>
       </c>
       <c r="M1156">
         <v>2</v>
@@ -62026,7 +62034,7 @@
         <v>23</v>
       </c>
       <c r="E1157" t="s">
-        <v>2675</v>
+        <v>3176</v>
       </c>
       <c r="F1157" t="s">
         <v>1854</v>
@@ -62042,7 +62050,7 @@
       </c>
       <c r="J1157" s="6"/>
       <c r="L1157" s="3" t="s">
-        <v>3198</v>
+        <v>3174</v>
       </c>
       <c r="M1157">
         <v>2</v>
@@ -62074,7 +62082,7 @@
         <v>24</v>
       </c>
       <c r="E1158" t="s">
-        <v>2676</v>
+        <v>3177</v>
       </c>
       <c r="F1158" t="s">
         <v>1854</v>
@@ -62090,7 +62098,7 @@
       </c>
       <c r="J1158" s="6"/>
       <c r="L1158" s="3" t="s">
-        <v>3199</v>
+        <v>3175</v>
       </c>
       <c r="M1158">
         <v>2</v>
@@ -62122,7 +62130,7 @@
         <v>0</v>
       </c>
       <c r="E1159" t="s">
-        <v>2852</v>
+        <v>2828</v>
       </c>
       <c r="F1159" t="s">
         <v>1855</v>
@@ -62170,7 +62178,7 @@
         <v>1</v>
       </c>
       <c r="E1160" t="s">
-        <v>2853</v>
+        <v>2829</v>
       </c>
       <c r="F1160" t="s">
         <v>1855</v>
@@ -62218,7 +62226,7 @@
         <v>2</v>
       </c>
       <c r="E1161" t="s">
-        <v>2854</v>
+        <v>2830</v>
       </c>
       <c r="F1161" t="s">
         <v>1855</v>
@@ -62266,7 +62274,7 @@
         <v>3</v>
       </c>
       <c r="E1162" t="s">
-        <v>2855</v>
+        <v>2831</v>
       </c>
       <c r="F1162" t="s">
         <v>1855</v>
@@ -62314,7 +62322,7 @@
         <v>4</v>
       </c>
       <c r="E1163" t="s">
-        <v>2856</v>
+        <v>2832</v>
       </c>
       <c r="F1163" t="s">
         <v>1855</v>
@@ -62362,7 +62370,7 @@
         <v>5</v>
       </c>
       <c r="E1164" t="s">
-        <v>2857</v>
+        <v>2833</v>
       </c>
       <c r="F1164" t="s">
         <v>1855</v>
@@ -62410,7 +62418,7 @@
         <v>6</v>
       </c>
       <c r="E1165" t="s">
-        <v>2858</v>
+        <v>2834</v>
       </c>
       <c r="F1165" t="s">
         <v>1855</v>
@@ -62458,7 +62466,7 @@
         <v>7</v>
       </c>
       <c r="E1166" t="s">
-        <v>2859</v>
+        <v>2835</v>
       </c>
       <c r="F1166" t="s">
         <v>1855</v>
@@ -62506,7 +62514,7 @@
         <v>8</v>
       </c>
       <c r="E1167" t="s">
-        <v>2860</v>
+        <v>2836</v>
       </c>
       <c r="F1167" t="s">
         <v>1855</v>
@@ -62554,7 +62562,7 @@
         <v>9</v>
       </c>
       <c r="E1168" t="s">
-        <v>2861</v>
+        <v>2837</v>
       </c>
       <c r="F1168" t="s">
         <v>1855</v>
@@ -62602,7 +62610,7 @@
         <v>10</v>
       </c>
       <c r="E1169" t="s">
-        <v>2862</v>
+        <v>2838</v>
       </c>
       <c r="F1169" t="s">
         <v>1855</v>
@@ -62650,7 +62658,7 @@
         <v>11</v>
       </c>
       <c r="E1170" t="s">
-        <v>2863</v>
+        <v>2839</v>
       </c>
       <c r="F1170" t="s">
         <v>1855</v>
@@ -62698,7 +62706,7 @@
         <v>12</v>
       </c>
       <c r="E1171" t="s">
-        <v>2864</v>
+        <v>2840</v>
       </c>
       <c r="F1171" t="s">
         <v>1855</v>
@@ -62746,7 +62754,7 @@
         <v>13</v>
       </c>
       <c r="E1172" t="s">
-        <v>2865</v>
+        <v>2841</v>
       </c>
       <c r="F1172" t="s">
         <v>1855</v>
@@ -62794,7 +62802,7 @@
         <v>14</v>
       </c>
       <c r="E1173" t="s">
-        <v>2866</v>
+        <v>2842</v>
       </c>
       <c r="F1173" t="s">
         <v>1855</v>
@@ -62842,7 +62850,7 @@
         <v>15</v>
       </c>
       <c r="E1174" t="s">
-        <v>2867</v>
+        <v>2843</v>
       </c>
       <c r="F1174" t="s">
         <v>1855</v>
@@ -62890,7 +62898,7 @@
         <v>0</v>
       </c>
       <c r="E1175" t="s">
-        <v>2868</v>
+        <v>2844</v>
       </c>
       <c r="F1175" t="s">
         <v>1855</v>
@@ -62938,7 +62946,7 @@
         <v>1</v>
       </c>
       <c r="E1176" t="s">
-        <v>2869</v>
+        <v>2845</v>
       </c>
       <c r="F1176" t="s">
         <v>1855</v>
@@ -62986,7 +62994,7 @@
         <v>2</v>
       </c>
       <c r="E1177" t="s">
-        <v>2870</v>
+        <v>2846</v>
       </c>
       <c r="F1177" t="s">
         <v>1855</v>
@@ -63034,7 +63042,7 @@
         <v>3</v>
       </c>
       <c r="E1178" t="s">
-        <v>2871</v>
+        <v>2847</v>
       </c>
       <c r="F1178" t="s">
         <v>1855</v>
@@ -63082,7 +63090,7 @@
         <v>4</v>
       </c>
       <c r="E1179" t="s">
-        <v>2872</v>
+        <v>2848</v>
       </c>
       <c r="F1179" t="s">
         <v>1855</v>
@@ -63130,7 +63138,7 @@
         <v>5</v>
       </c>
       <c r="E1180" t="s">
-        <v>2873</v>
+        <v>2849</v>
       </c>
       <c r="F1180" t="s">
         <v>1855</v>
@@ -63178,7 +63186,7 @@
         <v>6</v>
       </c>
       <c r="E1181" t="s">
-        <v>2874</v>
+        <v>2850</v>
       </c>
       <c r="F1181" t="s">
         <v>1855</v>
@@ -63226,7 +63234,7 @@
         <v>7</v>
       </c>
       <c r="E1182" t="s">
-        <v>2875</v>
+        <v>2851</v>
       </c>
       <c r="F1182" t="s">
         <v>1855</v>
@@ -63274,7 +63282,7 @@
         <v>8</v>
       </c>
       <c r="E1183" t="s">
-        <v>2876</v>
+        <v>2852</v>
       </c>
       <c r="F1183" t="s">
         <v>1855</v>
@@ -63322,7 +63330,7 @@
         <v>9</v>
       </c>
       <c r="E1184" t="s">
-        <v>2877</v>
+        <v>2853</v>
       </c>
       <c r="F1184" t="s">
         <v>1855</v>
@@ -63370,7 +63378,7 @@
         <v>10</v>
       </c>
       <c r="E1185" t="s">
-        <v>2878</v>
+        <v>2854</v>
       </c>
       <c r="F1185" t="s">
         <v>1855</v>
@@ -63418,7 +63426,7 @@
         <v>11</v>
       </c>
       <c r="E1186" t="s">
-        <v>2879</v>
+        <v>2855</v>
       </c>
       <c r="F1186" t="s">
         <v>1855</v>
@@ -63466,7 +63474,7 @@
         <v>12</v>
       </c>
       <c r="E1187" t="s">
-        <v>2880</v>
+        <v>2856</v>
       </c>
       <c r="F1187" t="s">
         <v>1855</v>
@@ -63514,7 +63522,7 @@
         <v>13</v>
       </c>
       <c r="E1188" t="s">
-        <v>2881</v>
+        <v>2857</v>
       </c>
       <c r="F1188" t="s">
         <v>1855</v>
@@ -63562,7 +63570,7 @@
         <v>14</v>
       </c>
       <c r="E1189" t="s">
-        <v>2882</v>
+        <v>2858</v>
       </c>
       <c r="F1189" t="s">
         <v>1855</v>
@@ -63610,7 +63618,7 @@
         <v>15</v>
       </c>
       <c r="E1190" t="s">
-        <v>2883</v>
+        <v>2859</v>
       </c>
       <c r="F1190" t="s">
         <v>1855</v>
@@ -63658,7 +63666,7 @@
         <v>0</v>
       </c>
       <c r="E1191" t="s">
-        <v>2884</v>
+        <v>2860</v>
       </c>
       <c r="F1191" t="s">
         <v>1855</v>
@@ -63706,7 +63714,7 @@
         <v>1</v>
       </c>
       <c r="E1192" t="s">
-        <v>2885</v>
+        <v>2861</v>
       </c>
       <c r="F1192" t="s">
         <v>1855</v>
@@ -63754,7 +63762,7 @@
         <v>2</v>
       </c>
       <c r="E1193" t="s">
-        <v>2886</v>
+        <v>2862</v>
       </c>
       <c r="F1193" t="s">
         <v>1855</v>
@@ -63802,7 +63810,7 @@
         <v>3</v>
       </c>
       <c r="E1194" t="s">
-        <v>2887</v>
+        <v>2863</v>
       </c>
       <c r="F1194" t="s">
         <v>1855</v>
@@ -63850,7 +63858,7 @@
         <v>4</v>
       </c>
       <c r="E1195" t="s">
-        <v>2888</v>
+        <v>2864</v>
       </c>
       <c r="F1195" t="s">
         <v>1855</v>
@@ -63898,7 +63906,7 @@
         <v>5</v>
       </c>
       <c r="E1196" t="s">
-        <v>2889</v>
+        <v>2865</v>
       </c>
       <c r="F1196" t="s">
         <v>1855</v>
@@ -63946,7 +63954,7 @@
         <v>6</v>
       </c>
       <c r="E1197" t="s">
-        <v>2890</v>
+        <v>2866</v>
       </c>
       <c r="F1197" t="s">
         <v>1855</v>
@@ -63994,7 +64002,7 @@
         <v>7</v>
       </c>
       <c r="E1198" t="s">
-        <v>2891</v>
+        <v>2867</v>
       </c>
       <c r="F1198" t="s">
         <v>1855</v>
@@ -64042,7 +64050,7 @@
         <v>8</v>
       </c>
       <c r="E1199" t="s">
-        <v>2892</v>
+        <v>2868</v>
       </c>
       <c r="F1199" t="s">
         <v>1855</v>
@@ -64090,7 +64098,7 @@
         <v>9</v>
       </c>
       <c r="E1200" t="s">
-        <v>2893</v>
+        <v>2869</v>
       </c>
       <c r="F1200" t="s">
         <v>1855</v>
@@ -64138,7 +64146,7 @@
         <v>10</v>
       </c>
       <c r="E1201" t="s">
-        <v>2894</v>
+        <v>2870</v>
       </c>
       <c r="F1201" t="s">
         <v>1855</v>
@@ -64186,7 +64194,7 @@
         <v>11</v>
       </c>
       <c r="E1202" t="s">
-        <v>2895</v>
+        <v>2871</v>
       </c>
       <c r="F1202" t="s">
         <v>1855</v>
@@ -64234,7 +64242,7 @@
         <v>12</v>
       </c>
       <c r="E1203" t="s">
-        <v>2896</v>
+        <v>2872</v>
       </c>
       <c r="F1203" t="s">
         <v>1855</v>
@@ -64282,7 +64290,7 @@
         <v>13</v>
       </c>
       <c r="E1204" t="s">
-        <v>2897</v>
+        <v>2873</v>
       </c>
       <c r="F1204" t="s">
         <v>1855</v>
@@ -64330,7 +64338,7 @@
         <v>14</v>
       </c>
       <c r="E1205" t="s">
-        <v>2898</v>
+        <v>2874</v>
       </c>
       <c r="F1205" t="s">
         <v>1855</v>
@@ -64378,7 +64386,7 @@
         <v>15</v>
       </c>
       <c r="E1206" t="s">
-        <v>2899</v>
+        <v>2875</v>
       </c>
       <c r="F1206" t="s">
         <v>1855</v>
@@ -64426,7 +64434,7 @@
         <v>0</v>
       </c>
       <c r="E1207" t="s">
-        <v>2900</v>
+        <v>2876</v>
       </c>
       <c r="F1207" t="s">
         <v>1855</v>
@@ -64474,7 +64482,7 @@
         <v>1</v>
       </c>
       <c r="E1208" t="s">
-        <v>2901</v>
+        <v>2877</v>
       </c>
       <c r="F1208" t="s">
         <v>1855</v>
@@ -64522,7 +64530,7 @@
         <v>2</v>
       </c>
       <c r="E1209" t="s">
-        <v>2902</v>
+        <v>2878</v>
       </c>
       <c r="F1209" t="s">
         <v>1855</v>
@@ -64570,7 +64578,7 @@
         <v>3</v>
       </c>
       <c r="E1210" t="s">
-        <v>2903</v>
+        <v>2879</v>
       </c>
       <c r="F1210" t="s">
         <v>1855</v>
@@ -64618,7 +64626,7 @@
         <v>4</v>
       </c>
       <c r="E1211" t="s">
-        <v>2904</v>
+        <v>2880</v>
       </c>
       <c r="F1211" t="s">
         <v>1855</v>
@@ -64666,7 +64674,7 @@
         <v>5</v>
       </c>
       <c r="E1212" t="s">
-        <v>2905</v>
+        <v>2881</v>
       </c>
       <c r="F1212" t="s">
         <v>1855</v>
@@ -64714,7 +64722,7 @@
         <v>6</v>
       </c>
       <c r="E1213" t="s">
-        <v>2906</v>
+        <v>2882</v>
       </c>
       <c r="F1213" t="s">
         <v>1855</v>
@@ -64762,7 +64770,7 @@
         <v>7</v>
       </c>
       <c r="E1214" t="s">
-        <v>2907</v>
+        <v>2883</v>
       </c>
       <c r="F1214" t="s">
         <v>1855</v>
@@ -64810,7 +64818,7 @@
         <v>8</v>
       </c>
       <c r="E1215" t="s">
-        <v>2908</v>
+        <v>2884</v>
       </c>
       <c r="F1215" t="s">
         <v>1855</v>
@@ -64858,7 +64866,7 @@
         <v>9</v>
       </c>
       <c r="E1216" t="s">
-        <v>2909</v>
+        <v>2885</v>
       </c>
       <c r="F1216" t="s">
         <v>1855</v>
@@ -64906,7 +64914,7 @@
         <v>10</v>
       </c>
       <c r="E1217" t="s">
-        <v>2910</v>
+        <v>2886</v>
       </c>
       <c r="F1217" t="s">
         <v>1855</v>
@@ -64954,7 +64962,7 @@
         <v>11</v>
       </c>
       <c r="E1218" t="s">
-        <v>2911</v>
+        <v>2887</v>
       </c>
       <c r="F1218" t="s">
         <v>1855</v>
@@ -65002,7 +65010,7 @@
         <v>12</v>
       </c>
       <c r="E1219" t="s">
-        <v>2912</v>
+        <v>2888</v>
       </c>
       <c r="F1219" t="s">
         <v>1855</v>
@@ -65050,7 +65058,7 @@
         <v>13</v>
       </c>
       <c r="E1220" t="s">
-        <v>2913</v>
+        <v>2889</v>
       </c>
       <c r="F1220" t="s">
         <v>1855</v>
@@ -65098,7 +65106,7 @@
         <v>14</v>
       </c>
       <c r="E1221" t="s">
-        <v>2914</v>
+        <v>2890</v>
       </c>
       <c r="F1221" t="s">
         <v>1855</v>
@@ -65146,7 +65154,7 @@
         <v>15</v>
       </c>
       <c r="E1222" t="s">
-        <v>2915</v>
+        <v>2891</v>
       </c>
       <c r="F1222" t="s">
         <v>1855</v>
@@ -65194,7 +65202,7 @@
         <v>0</v>
       </c>
       <c r="E1223" t="s">
-        <v>2916</v>
+        <v>2892</v>
       </c>
       <c r="F1223" t="s">
         <v>1855</v>
@@ -65242,7 +65250,7 @@
         <v>1</v>
       </c>
       <c r="E1224" t="s">
-        <v>2917</v>
+        <v>2893</v>
       </c>
       <c r="F1224" t="s">
         <v>1855</v>
@@ -65290,7 +65298,7 @@
         <v>2</v>
       </c>
       <c r="E1225" t="s">
-        <v>2918</v>
+        <v>2894</v>
       </c>
       <c r="F1225" t="s">
         <v>1855</v>
@@ -65338,7 +65346,7 @@
         <v>3</v>
       </c>
       <c r="E1226" t="s">
-        <v>2919</v>
+        <v>2895</v>
       </c>
       <c r="F1226" t="s">
         <v>1855</v>
@@ -65386,7 +65394,7 @@
         <v>4</v>
       </c>
       <c r="E1227" t="s">
-        <v>2920</v>
+        <v>2896</v>
       </c>
       <c r="F1227" t="s">
         <v>1855</v>
@@ -65434,7 +65442,7 @@
         <v>5</v>
       </c>
       <c r="E1228" t="s">
-        <v>2921</v>
+        <v>2897</v>
       </c>
       <c r="F1228" t="s">
         <v>1855</v>
@@ -65482,7 +65490,7 @@
         <v>6</v>
       </c>
       <c r="E1229" t="s">
-        <v>2922</v>
+        <v>2898</v>
       </c>
       <c r="F1229" t="s">
         <v>1855</v>
@@ -65530,7 +65538,7 @@
         <v>7</v>
       </c>
       <c r="E1230" t="s">
-        <v>2923</v>
+        <v>2899</v>
       </c>
       <c r="F1230" t="s">
         <v>1855</v>
@@ -65578,7 +65586,7 @@
         <v>8</v>
       </c>
       <c r="E1231" t="s">
-        <v>2924</v>
+        <v>2900</v>
       </c>
       <c r="F1231" t="s">
         <v>1855</v>
@@ -65626,7 +65634,7 @@
         <v>9</v>
       </c>
       <c r="E1232" t="s">
-        <v>2925</v>
+        <v>2901</v>
       </c>
       <c r="F1232" t="s">
         <v>1855</v>
@@ -65674,7 +65682,7 @@
         <v>10</v>
       </c>
       <c r="E1233" t="s">
-        <v>2926</v>
+        <v>2902</v>
       </c>
       <c r="F1233" t="s">
         <v>1855</v>
@@ -65722,7 +65730,7 @@
         <v>11</v>
       </c>
       <c r="E1234" t="s">
-        <v>2927</v>
+        <v>2903</v>
       </c>
       <c r="F1234" t="s">
         <v>1855</v>
@@ -65770,7 +65778,7 @@
         <v>12</v>
       </c>
       <c r="E1235" t="s">
-        <v>2928</v>
+        <v>2904</v>
       </c>
       <c r="F1235" t="s">
         <v>1855</v>
@@ -65818,7 +65826,7 @@
         <v>13</v>
       </c>
       <c r="E1236" t="s">
-        <v>2929</v>
+        <v>2905</v>
       </c>
       <c r="F1236" t="s">
         <v>1855</v>
@@ -65866,7 +65874,7 @@
         <v>14</v>
       </c>
       <c r="E1237" t="s">
-        <v>2930</v>
+        <v>2906</v>
       </c>
       <c r="F1237" t="s">
         <v>1855</v>
@@ -65914,7 +65922,7 @@
         <v>15</v>
       </c>
       <c r="E1238" t="s">
-        <v>2931</v>
+        <v>2907</v>
       </c>
       <c r="F1238" t="s">
         <v>1855</v>
@@ -65962,7 +65970,7 @@
         <v>0</v>
       </c>
       <c r="E1239" t="s">
-        <v>2932</v>
+        <v>2908</v>
       </c>
       <c r="F1239" t="s">
         <v>1855</v>
@@ -66010,7 +66018,7 @@
         <v>1</v>
       </c>
       <c r="E1240" t="s">
-        <v>2933</v>
+        <v>2909</v>
       </c>
       <c r="F1240" t="s">
         <v>1855</v>
@@ -66058,7 +66066,7 @@
         <v>2</v>
       </c>
       <c r="E1241" t="s">
-        <v>2934</v>
+        <v>2910</v>
       </c>
       <c r="F1241" t="s">
         <v>1855</v>
@@ -66106,7 +66114,7 @@
         <v>3</v>
       </c>
       <c r="E1242" t="s">
-        <v>2935</v>
+        <v>2911</v>
       </c>
       <c r="F1242" t="s">
         <v>1855</v>
@@ -66154,7 +66162,7 @@
         <v>4</v>
       </c>
       <c r="E1243" t="s">
-        <v>2936</v>
+        <v>2912</v>
       </c>
       <c r="F1243" t="s">
         <v>1855</v>
@@ -66202,7 +66210,7 @@
         <v>5</v>
       </c>
       <c r="E1244" t="s">
-        <v>2937</v>
+        <v>2913</v>
       </c>
       <c r="F1244" t="s">
         <v>1855</v>
@@ -66250,7 +66258,7 @@
         <v>6</v>
       </c>
       <c r="E1245" t="s">
-        <v>2938</v>
+        <v>2914</v>
       </c>
       <c r="F1245" t="s">
         <v>1855</v>
@@ -66298,7 +66306,7 @@
         <v>7</v>
       </c>
       <c r="E1246" t="s">
-        <v>2939</v>
+        <v>2915</v>
       </c>
       <c r="F1246" t="s">
         <v>1855</v>
@@ -66346,7 +66354,7 @@
         <v>8</v>
       </c>
       <c r="E1247" t="s">
-        <v>2940</v>
+        <v>2916</v>
       </c>
       <c r="F1247" t="s">
         <v>1855</v>
@@ -66394,7 +66402,7 @@
         <v>9</v>
       </c>
       <c r="E1248" t="s">
-        <v>2941</v>
+        <v>2917</v>
       </c>
       <c r="F1248" t="s">
         <v>1855</v>
@@ -66442,7 +66450,7 @@
         <v>10</v>
       </c>
       <c r="E1249" t="s">
-        <v>2942</v>
+        <v>2918</v>
       </c>
       <c r="F1249" t="s">
         <v>1855</v>
@@ -66490,7 +66498,7 @@
         <v>11</v>
       </c>
       <c r="E1250" t="s">
-        <v>2943</v>
+        <v>2919</v>
       </c>
       <c r="F1250" t="s">
         <v>1855</v>
@@ -66538,7 +66546,7 @@
         <v>12</v>
       </c>
       <c r="E1251" t="s">
-        <v>2944</v>
+        <v>2920</v>
       </c>
       <c r="F1251" t="s">
         <v>1855</v>
@@ -66586,7 +66594,7 @@
         <v>13</v>
       </c>
       <c r="E1252" t="s">
-        <v>2945</v>
+        <v>2921</v>
       </c>
       <c r="F1252" t="s">
         <v>1855</v>
@@ -66634,7 +66642,7 @@
         <v>14</v>
       </c>
       <c r="E1253" t="s">
-        <v>2946</v>
+        <v>2922</v>
       </c>
       <c r="F1253" t="s">
         <v>1855</v>
@@ -66682,7 +66690,7 @@
         <v>15</v>
       </c>
       <c r="E1254" t="s">
-        <v>2947</v>
+        <v>2923</v>
       </c>
       <c r="F1254" t="s">
         <v>1855</v>
@@ -66730,7 +66738,7 @@
         <v>0</v>
       </c>
       <c r="E1255" t="s">
-        <v>2948</v>
+        <v>2924</v>
       </c>
       <c r="F1255" t="s">
         <v>1855</v>
@@ -66778,7 +66786,7 @@
         <v>1</v>
       </c>
       <c r="E1256" t="s">
-        <v>2949</v>
+        <v>2925</v>
       </c>
       <c r="F1256" t="s">
         <v>1855</v>
@@ -66826,7 +66834,7 @@
         <v>2</v>
       </c>
       <c r="E1257" t="s">
-        <v>2950</v>
+        <v>2926</v>
       </c>
       <c r="F1257" t="s">
         <v>1855</v>
@@ -66874,7 +66882,7 @@
         <v>3</v>
       </c>
       <c r="E1258" t="s">
-        <v>2951</v>
+        <v>2927</v>
       </c>
       <c r="F1258" t="s">
         <v>1855</v>
@@ -66922,7 +66930,7 @@
         <v>4</v>
       </c>
       <c r="E1259" t="s">
-        <v>2952</v>
+        <v>2928</v>
       </c>
       <c r="F1259" t="s">
         <v>1855</v>
@@ -66970,7 +66978,7 @@
         <v>5</v>
       </c>
       <c r="E1260" t="s">
-        <v>2953</v>
+        <v>2929</v>
       </c>
       <c r="F1260" t="s">
         <v>1855</v>
@@ -67018,7 +67026,7 @@
         <v>6</v>
       </c>
       <c r="E1261" t="s">
-        <v>2954</v>
+        <v>2930</v>
       </c>
       <c r="F1261" t="s">
         <v>1855</v>
@@ -67066,7 +67074,7 @@
         <v>7</v>
       </c>
       <c r="E1262" t="s">
-        <v>2955</v>
+        <v>2931</v>
       </c>
       <c r="F1262" t="s">
         <v>1855</v>
@@ -67114,7 +67122,7 @@
         <v>8</v>
       </c>
       <c r="E1263" t="s">
-        <v>2956</v>
+        <v>2932</v>
       </c>
       <c r="F1263" t="s">
         <v>1855</v>
@@ -67162,7 +67170,7 @@
         <v>9</v>
       </c>
       <c r="E1264" t="s">
-        <v>2957</v>
+        <v>2933</v>
       </c>
       <c r="F1264" t="s">
         <v>1855</v>
@@ -67210,7 +67218,7 @@
         <v>10</v>
       </c>
       <c r="E1265" t="s">
-        <v>2958</v>
+        <v>2934</v>
       </c>
       <c r="F1265" t="s">
         <v>1855</v>
@@ -67258,7 +67266,7 @@
         <v>11</v>
       </c>
       <c r="E1266" t="s">
-        <v>2959</v>
+        <v>2935</v>
       </c>
       <c r="F1266" t="s">
         <v>1855</v>
@@ -67306,7 +67314,7 @@
         <v>12</v>
       </c>
       <c r="E1267" t="s">
-        <v>2960</v>
+        <v>2936</v>
       </c>
       <c r="F1267" t="s">
         <v>1855</v>
@@ -67354,7 +67362,7 @@
         <v>13</v>
       </c>
       <c r="E1268" t="s">
-        <v>2961</v>
+        <v>2937</v>
       </c>
       <c r="F1268" t="s">
         <v>1855</v>
@@ -67402,7 +67410,7 @@
         <v>14</v>
       </c>
       <c r="E1269" t="s">
-        <v>2962</v>
+        <v>2938</v>
       </c>
       <c r="F1269" t="s">
         <v>1855</v>
@@ -67450,7 +67458,7 @@
         <v>15</v>
       </c>
       <c r="E1270" t="s">
-        <v>2963</v>
+        <v>2939</v>
       </c>
       <c r="F1270" t="s">
         <v>1855</v>
@@ -67498,7 +67506,7 @@
         <v>0</v>
       </c>
       <c r="E1271" t="s">
-        <v>2964</v>
+        <v>2940</v>
       </c>
       <c r="F1271" t="s">
         <v>1855</v>
@@ -67546,7 +67554,7 @@
         <v>1</v>
       </c>
       <c r="E1272" t="s">
-        <v>2965</v>
+        <v>2941</v>
       </c>
       <c r="F1272" t="s">
         <v>1855</v>
@@ -67594,7 +67602,7 @@
         <v>2</v>
       </c>
       <c r="E1273" t="s">
-        <v>2966</v>
+        <v>2942</v>
       </c>
       <c r="F1273" t="s">
         <v>1855</v>
@@ -67642,7 +67650,7 @@
         <v>3</v>
       </c>
       <c r="E1274" t="s">
-        <v>2967</v>
+        <v>2943</v>
       </c>
       <c r="F1274" t="s">
         <v>1855</v>
@@ -67690,7 +67698,7 @@
         <v>4</v>
       </c>
       <c r="E1275" t="s">
-        <v>2968</v>
+        <v>2944</v>
       </c>
       <c r="F1275" t="s">
         <v>1855</v>
@@ -67738,7 +67746,7 @@
         <v>5</v>
       </c>
       <c r="E1276" t="s">
-        <v>2969</v>
+        <v>2945</v>
       </c>
       <c r="F1276" t="s">
         <v>1855</v>
@@ -67786,7 +67794,7 @@
         <v>6</v>
       </c>
       <c r="E1277" t="s">
-        <v>2970</v>
+        <v>2946</v>
       </c>
       <c r="F1277" t="s">
         <v>1855</v>
@@ -67834,7 +67842,7 @@
         <v>7</v>
       </c>
       <c r="E1278" t="s">
-        <v>2971</v>
+        <v>2947</v>
       </c>
       <c r="F1278" t="s">
         <v>1855</v>
@@ -67882,7 +67890,7 @@
         <v>8</v>
       </c>
       <c r="E1279" t="s">
-        <v>2972</v>
+        <v>2948</v>
       </c>
       <c r="F1279" t="s">
         <v>1855</v>
@@ -67930,7 +67938,7 @@
         <v>9</v>
       </c>
       <c r="E1280" t="s">
-        <v>2973</v>
+        <v>2949</v>
       </c>
       <c r="F1280" t="s">
         <v>1855</v>
@@ -67978,7 +67986,7 @@
         <v>10</v>
       </c>
       <c r="E1281" t="s">
-        <v>2974</v>
+        <v>2950</v>
       </c>
       <c r="F1281" t="s">
         <v>1855</v>
@@ -68026,7 +68034,7 @@
         <v>11</v>
       </c>
       <c r="E1282" t="s">
-        <v>2975</v>
+        <v>2951</v>
       </c>
       <c r="F1282" t="s">
         <v>1855</v>
@@ -68074,7 +68082,7 @@
         <v>12</v>
       </c>
       <c r="E1283" t="s">
-        <v>2976</v>
+        <v>2952</v>
       </c>
       <c r="F1283" t="s">
         <v>1855</v>
@@ -68122,7 +68130,7 @@
         <v>13</v>
       </c>
       <c r="E1284" t="s">
-        <v>2977</v>
+        <v>2953</v>
       </c>
       <c r="F1284" t="s">
         <v>1855</v>
@@ -68170,7 +68178,7 @@
         <v>14</v>
       </c>
       <c r="E1285" t="s">
-        <v>2978</v>
+        <v>2954</v>
       </c>
       <c r="F1285" t="s">
         <v>1855</v>
@@ -68218,7 +68226,7 @@
         <v>15</v>
       </c>
       <c r="E1286" t="s">
-        <v>2979</v>
+        <v>2955</v>
       </c>
       <c r="F1286" t="s">
         <v>1855</v>
@@ -68266,7 +68274,7 @@
         <v>0</v>
       </c>
       <c r="E1287" t="s">
-        <v>2980</v>
+        <v>2956</v>
       </c>
       <c r="F1287" t="s">
         <v>1855</v>
@@ -68314,7 +68322,7 @@
         <v>1</v>
       </c>
       <c r="E1288" t="s">
-        <v>2981</v>
+        <v>2957</v>
       </c>
       <c r="F1288" t="s">
         <v>1855</v>
@@ -68362,7 +68370,7 @@
         <v>2</v>
       </c>
       <c r="E1289" t="s">
-        <v>2982</v>
+        <v>2958</v>
       </c>
       <c r="F1289" t="s">
         <v>1855</v>
@@ -68410,7 +68418,7 @@
         <v>3</v>
       </c>
       <c r="E1290" t="s">
-        <v>2983</v>
+        <v>2959</v>
       </c>
       <c r="F1290" t="s">
         <v>1855</v>
@@ -68458,7 +68466,7 @@
         <v>4</v>
       </c>
       <c r="E1291" t="s">
-        <v>2984</v>
+        <v>2960</v>
       </c>
       <c r="F1291" t="s">
         <v>1855</v>
@@ -68506,7 +68514,7 @@
         <v>5</v>
       </c>
       <c r="E1292" t="s">
-        <v>2985</v>
+        <v>2961</v>
       </c>
       <c r="F1292" t="s">
         <v>1855</v>
@@ -68554,7 +68562,7 @@
         <v>6</v>
       </c>
       <c r="E1293" t="s">
-        <v>2986</v>
+        <v>2962</v>
       </c>
       <c r="F1293" t="s">
         <v>1855</v>
@@ -68602,7 +68610,7 @@
         <v>7</v>
       </c>
       <c r="E1294" t="s">
-        <v>2987</v>
+        <v>2963</v>
       </c>
       <c r="F1294" t="s">
         <v>1855</v>
@@ -68650,7 +68658,7 @@
         <v>8</v>
       </c>
       <c r="E1295" t="s">
-        <v>2988</v>
+        <v>2964</v>
       </c>
       <c r="F1295" t="s">
         <v>1855</v>
@@ -68698,7 +68706,7 @@
         <v>9</v>
       </c>
       <c r="E1296" t="s">
-        <v>2989</v>
+        <v>2965</v>
       </c>
       <c r="F1296" t="s">
         <v>1855</v>
@@ -68746,7 +68754,7 @@
         <v>10</v>
       </c>
       <c r="E1297" t="s">
-        <v>2990</v>
+        <v>2966</v>
       </c>
       <c r="F1297" t="s">
         <v>1855</v>
@@ -68794,7 +68802,7 @@
         <v>11</v>
       </c>
       <c r="E1298" t="s">
-        <v>2991</v>
+        <v>2967</v>
       </c>
       <c r="F1298" t="s">
         <v>1855</v>
@@ -68842,7 +68850,7 @@
         <v>12</v>
       </c>
       <c r="E1299" t="s">
-        <v>2992</v>
+        <v>2968</v>
       </c>
       <c r="F1299" t="s">
         <v>1855</v>
@@ -68890,7 +68898,7 @@
         <v>13</v>
       </c>
       <c r="E1300" t="s">
-        <v>2993</v>
+        <v>2969</v>
       </c>
       <c r="F1300" t="s">
         <v>1855</v>
@@ -68938,7 +68946,7 @@
         <v>14</v>
       </c>
       <c r="E1301" t="s">
-        <v>2994</v>
+        <v>2970</v>
       </c>
       <c r="F1301" t="s">
         <v>1855</v>
@@ -68986,7 +68994,7 @@
         <v>15</v>
       </c>
       <c r="E1302" t="s">
-        <v>2995</v>
+        <v>2971</v>
       </c>
       <c r="F1302" t="s">
         <v>1855</v>
@@ -69034,7 +69042,7 @@
         <v>0</v>
       </c>
       <c r="E1303" t="s">
-        <v>2996</v>
+        <v>2972</v>
       </c>
       <c r="F1303" t="s">
         <v>1855</v>
@@ -69082,7 +69090,7 @@
         <v>1</v>
       </c>
       <c r="E1304" t="s">
-        <v>2997</v>
+        <v>2973</v>
       </c>
       <c r="F1304" t="s">
         <v>1855</v>
@@ -69130,7 +69138,7 @@
         <v>2</v>
       </c>
       <c r="E1305" t="s">
-        <v>2998</v>
+        <v>2974</v>
       </c>
       <c r="F1305" t="s">
         <v>1855</v>
@@ -69178,7 +69186,7 @@
         <v>3</v>
       </c>
       <c r="E1306" t="s">
-        <v>2999</v>
+        <v>2975</v>
       </c>
       <c r="F1306" t="s">
         <v>1855</v>
@@ -69226,7 +69234,7 @@
         <v>4</v>
       </c>
       <c r="E1307" t="s">
-        <v>3000</v>
+        <v>2976</v>
       </c>
       <c r="F1307" t="s">
         <v>1855</v>
@@ -69274,7 +69282,7 @@
         <v>5</v>
       </c>
       <c r="E1308" t="s">
-        <v>3001</v>
+        <v>2977</v>
       </c>
       <c r="F1308" t="s">
         <v>1855</v>
@@ -69322,7 +69330,7 @@
         <v>6</v>
       </c>
       <c r="E1309" t="s">
-        <v>3002</v>
+        <v>2978</v>
       </c>
       <c r="F1309" t="s">
         <v>1855</v>
@@ -69370,7 +69378,7 @@
         <v>7</v>
       </c>
       <c r="E1310" t="s">
-        <v>3003</v>
+        <v>2979</v>
       </c>
       <c r="F1310" t="s">
         <v>1855</v>
@@ -69418,7 +69426,7 @@
         <v>8</v>
       </c>
       <c r="E1311" t="s">
-        <v>3004</v>
+        <v>2980</v>
       </c>
       <c r="F1311" t="s">
         <v>1855</v>
@@ -69466,7 +69474,7 @@
         <v>9</v>
       </c>
       <c r="E1312" t="s">
-        <v>3005</v>
+        <v>2981</v>
       </c>
       <c r="F1312" t="s">
         <v>1855</v>
@@ -69514,7 +69522,7 @@
         <v>10</v>
       </c>
       <c r="E1313" t="s">
-        <v>3006</v>
+        <v>2982</v>
       </c>
       <c r="F1313" t="s">
         <v>1855</v>
@@ -69562,7 +69570,7 @@
         <v>11</v>
       </c>
       <c r="E1314" t="s">
-        <v>3007</v>
+        <v>2983</v>
       </c>
       <c r="F1314" t="s">
         <v>1855</v>
@@ -69610,7 +69618,7 @@
         <v>12</v>
       </c>
       <c r="E1315" t="s">
-        <v>3008</v>
+        <v>2984</v>
       </c>
       <c r="F1315" t="s">
         <v>1855</v>
@@ -69658,7 +69666,7 @@
         <v>13</v>
       </c>
       <c r="E1316" t="s">
-        <v>3009</v>
+        <v>2985</v>
       </c>
       <c r="F1316" t="s">
         <v>1855</v>
@@ -69706,7 +69714,7 @@
         <v>14</v>
       </c>
       <c r="E1317" t="s">
-        <v>3010</v>
+        <v>2986</v>
       </c>
       <c r="F1317" t="s">
         <v>1855</v>
@@ -69754,7 +69762,7 @@
         <v>15</v>
       </c>
       <c r="E1318" t="s">
-        <v>3011</v>
+        <v>2987</v>
       </c>
       <c r="F1318" t="s">
         <v>1855</v>
@@ -69802,7 +69810,7 @@
         <v>0</v>
       </c>
       <c r="E1319" t="s">
-        <v>3012</v>
+        <v>2988</v>
       </c>
       <c r="F1319" t="s">
         <v>1855</v>
@@ -69850,7 +69858,7 @@
         <v>1</v>
       </c>
       <c r="E1320" t="s">
-        <v>3013</v>
+        <v>2989</v>
       </c>
       <c r="F1320" t="s">
         <v>1855</v>
@@ -69898,7 +69906,7 @@
         <v>2</v>
       </c>
       <c r="E1321" t="s">
-        <v>3014</v>
+        <v>2990</v>
       </c>
       <c r="F1321" t="s">
         <v>1855</v>
@@ -69946,7 +69954,7 @@
         <v>3</v>
       </c>
       <c r="E1322" t="s">
-        <v>3015</v>
+        <v>2991</v>
       </c>
       <c r="F1322" t="s">
         <v>1855</v>
@@ -69994,7 +70002,7 @@
         <v>4</v>
       </c>
       <c r="E1323" t="s">
-        <v>3016</v>
+        <v>2992</v>
       </c>
       <c r="F1323" t="s">
         <v>1855</v>
@@ -70042,7 +70050,7 @@
         <v>5</v>
       </c>
       <c r="E1324" t="s">
-        <v>3017</v>
+        <v>2993</v>
       </c>
       <c r="F1324" t="s">
         <v>1855</v>
@@ -70090,7 +70098,7 @@
         <v>6</v>
       </c>
       <c r="E1325" t="s">
-        <v>3018</v>
+        <v>2994</v>
       </c>
       <c r="F1325" t="s">
         <v>1855</v>
@@ -70138,7 +70146,7 @@
         <v>7</v>
       </c>
       <c r="E1326" t="s">
-        <v>3019</v>
+        <v>2995</v>
       </c>
       <c r="F1326" t="s">
         <v>1855</v>
@@ -70186,7 +70194,7 @@
         <v>8</v>
       </c>
       <c r="E1327" t="s">
-        <v>3020</v>
+        <v>2996</v>
       </c>
       <c r="F1327" t="s">
         <v>1855</v>
@@ -70234,7 +70242,7 @@
         <v>9</v>
       </c>
       <c r="E1328" t="s">
-        <v>3021</v>
+        <v>2997</v>
       </c>
       <c r="F1328" t="s">
         <v>1855</v>
@@ -70282,7 +70290,7 @@
         <v>10</v>
       </c>
       <c r="E1329" t="s">
-        <v>3022</v>
+        <v>2998</v>
       </c>
       <c r="F1329" t="s">
         <v>1855</v>
@@ -70330,7 +70338,7 @@
         <v>11</v>
       </c>
       <c r="E1330" t="s">
-        <v>3023</v>
+        <v>2999</v>
       </c>
       <c r="F1330" t="s">
         <v>1855</v>
@@ -70378,7 +70386,7 @@
         <v>12</v>
       </c>
       <c r="E1331" t="s">
-        <v>3024</v>
+        <v>3000</v>
       </c>
       <c r="F1331" t="s">
         <v>1855</v>
@@ -70426,7 +70434,7 @@
         <v>13</v>
       </c>
       <c r="E1332" t="s">
-        <v>3025</v>
+        <v>3001</v>
       </c>
       <c r="F1332" t="s">
         <v>1855</v>
@@ -70474,7 +70482,7 @@
         <v>14</v>
       </c>
       <c r="E1333" t="s">
-        <v>3026</v>
+        <v>3002</v>
       </c>
       <c r="F1333" t="s">
         <v>1855</v>
@@ -70522,7 +70530,7 @@
         <v>15</v>
       </c>
       <c r="E1334" t="s">
-        <v>3027</v>
+        <v>3003</v>
       </c>
       <c r="F1334" t="s">
         <v>1855</v>
@@ -70570,7 +70578,7 @@
         <v>0</v>
       </c>
       <c r="E1335" t="s">
-        <v>3028</v>
+        <v>3004</v>
       </c>
       <c r="F1335" t="s">
         <v>1855</v>
@@ -70618,7 +70626,7 @@
         <v>1</v>
       </c>
       <c r="E1336" t="s">
-        <v>3029</v>
+        <v>3005</v>
       </c>
       <c r="F1336" t="s">
         <v>1855</v>
@@ -70666,7 +70674,7 @@
         <v>2</v>
       </c>
       <c r="E1337" t="s">
-        <v>3030</v>
+        <v>3006</v>
       </c>
       <c r="F1337" t="s">
         <v>1855</v>
@@ -70714,7 +70722,7 @@
         <v>3</v>
       </c>
       <c r="E1338" t="s">
-        <v>3031</v>
+        <v>3007</v>
       </c>
       <c r="F1338" t="s">
         <v>1855</v>
@@ -70762,7 +70770,7 @@
         <v>4</v>
       </c>
       <c r="E1339" t="s">
-        <v>3032</v>
+        <v>3008</v>
       </c>
       <c r="F1339" t="s">
         <v>1855</v>
@@ -70810,7 +70818,7 @@
         <v>5</v>
       </c>
       <c r="E1340" t="s">
-        <v>3033</v>
+        <v>3009</v>
       </c>
       <c r="F1340" t="s">
         <v>1855</v>
@@ -70858,7 +70866,7 @@
         <v>6</v>
       </c>
       <c r="E1341" t="s">
-        <v>3034</v>
+        <v>3010</v>
       </c>
       <c r="F1341" t="s">
         <v>1855</v>
@@ -70906,7 +70914,7 @@
         <v>7</v>
       </c>
       <c r="E1342" t="s">
-        <v>3035</v>
+        <v>3011</v>
       </c>
       <c r="F1342" t="s">
         <v>1855</v>
@@ -70954,7 +70962,7 @@
         <v>8</v>
       </c>
       <c r="E1343" t="s">
-        <v>3036</v>
+        <v>3012</v>
       </c>
       <c r="F1343" t="s">
         <v>1855</v>
@@ -71002,7 +71010,7 @@
         <v>9</v>
       </c>
       <c r="E1344" t="s">
-        <v>3037</v>
+        <v>3013</v>
       </c>
       <c r="F1344" t="s">
         <v>1855</v>
@@ -71050,7 +71058,7 @@
         <v>10</v>
       </c>
       <c r="E1345" t="s">
-        <v>3038</v>
+        <v>3014</v>
       </c>
       <c r="F1345" t="s">
         <v>1855</v>
@@ -71098,7 +71106,7 @@
         <v>11</v>
       </c>
       <c r="E1346" t="s">
-        <v>3039</v>
+        <v>3015</v>
       </c>
       <c r="F1346" t="s">
         <v>1855</v>
@@ -71146,7 +71154,7 @@
         <v>12</v>
       </c>
       <c r="E1347" t="s">
-        <v>3040</v>
+        <v>3016</v>
       </c>
       <c r="F1347" t="s">
         <v>1855</v>
@@ -71194,7 +71202,7 @@
         <v>13</v>
       </c>
       <c r="E1348" t="s">
-        <v>3041</v>
+        <v>3017</v>
       </c>
       <c r="F1348" t="s">
         <v>1855</v>
@@ -71242,7 +71250,7 @@
         <v>14</v>
       </c>
       <c r="E1349" t="s">
-        <v>3042</v>
+        <v>3018</v>
       </c>
       <c r="F1349" t="s">
         <v>1855</v>
@@ -71290,7 +71298,7 @@
         <v>15</v>
       </c>
       <c r="E1350" t="s">
-        <v>3043</v>
+        <v>3019</v>
       </c>
       <c r="F1350" t="s">
         <v>1855</v>
@@ -71338,7 +71346,7 @@
         <v>0</v>
       </c>
       <c r="E1351" t="s">
-        <v>3044</v>
+        <v>3020</v>
       </c>
       <c r="F1351" t="s">
         <v>1855</v>
@@ -71386,7 +71394,7 @@
         <v>1</v>
       </c>
       <c r="E1352" t="s">
-        <v>3045</v>
+        <v>3021</v>
       </c>
       <c r="F1352" t="s">
         <v>1855</v>
@@ -71434,7 +71442,7 @@
         <v>2</v>
       </c>
       <c r="E1353" t="s">
-        <v>3046</v>
+        <v>3022</v>
       </c>
       <c r="F1353" t="s">
         <v>1855</v>
@@ -71482,7 +71490,7 @@
         <v>3</v>
       </c>
       <c r="E1354" t="s">
-        <v>3047</v>
+        <v>3023</v>
       </c>
       <c r="F1354" t="s">
         <v>1855</v>
@@ -71530,7 +71538,7 @@
         <v>4</v>
       </c>
       <c r="E1355" t="s">
-        <v>3048</v>
+        <v>3024</v>
       </c>
       <c r="F1355" t="s">
         <v>1855</v>
@@ -71578,7 +71586,7 @@
         <v>5</v>
       </c>
       <c r="E1356" t="s">
-        <v>3049</v>
+        <v>3025</v>
       </c>
       <c r="F1356" t="s">
         <v>1855</v>
@@ -71626,7 +71634,7 @@
         <v>6</v>
       </c>
       <c r="E1357" t="s">
-        <v>3050</v>
+        <v>3026</v>
       </c>
       <c r="F1357" t="s">
         <v>1855</v>
@@ -71674,7 +71682,7 @@
         <v>7</v>
       </c>
       <c r="E1358" t="s">
-        <v>3051</v>
+        <v>3027</v>
       </c>
       <c r="F1358" t="s">
         <v>1855</v>
@@ -71722,7 +71730,7 @@
         <v>8</v>
       </c>
       <c r="E1359" t="s">
-        <v>3052</v>
+        <v>3028</v>
       </c>
       <c r="F1359" t="s">
         <v>1855</v>
@@ -71770,7 +71778,7 @@
         <v>9</v>
       </c>
       <c r="E1360" t="s">
-        <v>3053</v>
+        <v>3029</v>
       </c>
       <c r="F1360" t="s">
         <v>1855</v>
@@ -71818,7 +71826,7 @@
         <v>10</v>
       </c>
       <c r="E1361" t="s">
-        <v>3054</v>
+        <v>3030</v>
       </c>
       <c r="F1361" t="s">
         <v>1855</v>
@@ -71866,7 +71874,7 @@
         <v>11</v>
       </c>
       <c r="E1362" t="s">
-        <v>3055</v>
+        <v>3031</v>
       </c>
       <c r="F1362" t="s">
         <v>1855</v>
@@ -71914,7 +71922,7 @@
         <v>12</v>
       </c>
       <c r="E1363" t="s">
-        <v>3056</v>
+        <v>3032</v>
       </c>
       <c r="F1363" t="s">
         <v>1855</v>
@@ -71962,7 +71970,7 @@
         <v>13</v>
       </c>
       <c r="E1364" t="s">
-        <v>3057</v>
+        <v>3033</v>
       </c>
       <c r="F1364" t="s">
         <v>1855</v>
@@ -72010,7 +72018,7 @@
         <v>14</v>
       </c>
       <c r="E1365" t="s">
-        <v>3058</v>
+        <v>3034</v>
       </c>
       <c r="F1365" t="s">
         <v>1855</v>
@@ -72058,7 +72066,7 @@
         <v>15</v>
       </c>
       <c r="E1366" t="s">
-        <v>3059</v>
+        <v>3035</v>
       </c>
       <c r="F1366" t="s">
         <v>1855</v>
@@ -72106,7 +72114,7 @@
         <v>0</v>
       </c>
       <c r="E1367" t="s">
-        <v>3060</v>
+        <v>3036</v>
       </c>
       <c r="F1367" t="s">
         <v>1855</v>
@@ -72154,7 +72162,7 @@
         <v>1</v>
       </c>
       <c r="E1368" t="s">
-        <v>3061</v>
+        <v>3037</v>
       </c>
       <c r="F1368" t="s">
         <v>1855</v>
@@ -72202,7 +72210,7 @@
         <v>2</v>
       </c>
       <c r="E1369" t="s">
-        <v>3062</v>
+        <v>3038</v>
       </c>
       <c r="F1369" t="s">
         <v>1855</v>
@@ -72250,7 +72258,7 @@
         <v>3</v>
       </c>
       <c r="E1370" t="s">
-        <v>3063</v>
+        <v>3039</v>
       </c>
       <c r="F1370" t="s">
         <v>1855</v>
@@ -72298,7 +72306,7 @@
         <v>4</v>
       </c>
       <c r="E1371" t="s">
-        <v>3064</v>
+        <v>3040</v>
       </c>
       <c r="F1371" t="s">
         <v>1855</v>
@@ -72346,7 +72354,7 @@
         <v>5</v>
       </c>
       <c r="E1372" t="s">
-        <v>3065</v>
+        <v>3041</v>
       </c>
       <c r="F1372" t="s">
         <v>1855</v>
@@ -72394,7 +72402,7 @@
         <v>6</v>
       </c>
       <c r="E1373" t="s">
-        <v>3066</v>
+        <v>3042</v>
       </c>
       <c r="F1373" t="s">
         <v>1855</v>
@@ -72442,7 +72450,7 @@
         <v>7</v>
       </c>
       <c r="E1374" t="s">
-        <v>3067</v>
+        <v>3043</v>
       </c>
       <c r="F1374" t="s">
         <v>1855</v>
@@ -72490,7 +72498,7 @@
         <v>8</v>
       </c>
       <c r="E1375" t="s">
-        <v>3068</v>
+        <v>3044</v>
       </c>
       <c r="F1375" t="s">
         <v>1855</v>
@@ -72538,7 +72546,7 @@
         <v>9</v>
       </c>
       <c r="E1376" t="s">
-        <v>3069</v>
+        <v>3045</v>
       </c>
       <c r="F1376" t="s">
         <v>1855</v>
@@ -72586,7 +72594,7 @@
         <v>10</v>
       </c>
       <c r="E1377" t="s">
-        <v>3070</v>
+        <v>3046</v>
       </c>
       <c r="F1377" t="s">
         <v>1855</v>
@@ -72634,7 +72642,7 @@
         <v>11</v>
       </c>
       <c r="E1378" t="s">
-        <v>3071</v>
+        <v>3047</v>
       </c>
       <c r="F1378" t="s">
         <v>1855</v>
@@ -72682,7 +72690,7 @@
         <v>12</v>
       </c>
       <c r="E1379" t="s">
-        <v>3072</v>
+        <v>3048</v>
       </c>
       <c r="F1379" t="s">
         <v>1855</v>
@@ -72730,7 +72738,7 @@
         <v>13</v>
       </c>
       <c r="E1380" t="s">
-        <v>3073</v>
+        <v>3049</v>
       </c>
       <c r="F1380" t="s">
         <v>1855</v>
@@ -72778,7 +72786,7 @@
         <v>14</v>
       </c>
       <c r="E1381" t="s">
-        <v>3074</v>
+        <v>3050</v>
       </c>
       <c r="F1381" t="s">
         <v>1855</v>
@@ -72826,7 +72834,7 @@
         <v>15</v>
       </c>
       <c r="E1382" t="s">
-        <v>3075</v>
+        <v>3051</v>
       </c>
       <c r="F1382" t="s">
         <v>1855</v>
@@ -72874,7 +72882,7 @@
         <v>0</v>
       </c>
       <c r="E1383" t="s">
-        <v>3076</v>
+        <v>3052</v>
       </c>
       <c r="F1383" t="s">
         <v>1855</v>
@@ -72922,7 +72930,7 @@
         <v>1</v>
       </c>
       <c r="E1384" t="s">
-        <v>3077</v>
+        <v>3053</v>
       </c>
       <c r="F1384" t="s">
         <v>1855</v>
@@ -72970,7 +72978,7 @@
         <v>2</v>
       </c>
       <c r="E1385" t="s">
-        <v>3078</v>
+        <v>3054</v>
       </c>
       <c r="F1385" t="s">
         <v>1855</v>
@@ -73018,7 +73026,7 @@
         <v>3</v>
       </c>
       <c r="E1386" t="s">
-        <v>3079</v>
+        <v>3055</v>
       </c>
       <c r="F1386" t="s">
         <v>1855</v>
@@ -73066,7 +73074,7 @@
         <v>4</v>
       </c>
       <c r="E1387" t="s">
-        <v>3080</v>
+        <v>3056</v>
       </c>
       <c r="F1387" t="s">
         <v>1855</v>
@@ -73114,7 +73122,7 @@
         <v>5</v>
       </c>
       <c r="E1388" t="s">
-        <v>3081</v>
+        <v>3057</v>
       </c>
       <c r="F1388" t="s">
         <v>1855</v>
@@ -73162,7 +73170,7 @@
         <v>6</v>
       </c>
       <c r="E1389" t="s">
-        <v>3082</v>
+        <v>3058</v>
       </c>
       <c r="F1389" t="s">
         <v>1855</v>
@@ -73210,7 +73218,7 @@
         <v>7</v>
       </c>
       <c r="E1390" t="s">
-        <v>3083</v>
+        <v>3059</v>
       </c>
       <c r="F1390" t="s">
         <v>1855</v>
@@ -73258,7 +73266,7 @@
         <v>8</v>
       </c>
       <c r="E1391" t="s">
-        <v>3084</v>
+        <v>3060</v>
       </c>
       <c r="F1391" t="s">
         <v>1855</v>
@@ -73306,7 +73314,7 @@
         <v>9</v>
       </c>
       <c r="E1392" t="s">
-        <v>3085</v>
+        <v>3061</v>
       </c>
       <c r="F1392" t="s">
         <v>1855</v>
@@ -73354,7 +73362,7 @@
         <v>10</v>
       </c>
       <c r="E1393" t="s">
-        <v>3086</v>
+        <v>3062</v>
       </c>
       <c r="F1393" t="s">
         <v>1855</v>
@@ -73402,7 +73410,7 @@
         <v>11</v>
       </c>
       <c r="E1394" t="s">
-        <v>3087</v>
+        <v>3063</v>
       </c>
       <c r="F1394" t="s">
         <v>1855</v>
@@ -73450,7 +73458,7 @@
         <v>12</v>
       </c>
       <c r="E1395" t="s">
-        <v>3088</v>
+        <v>3064</v>
       </c>
       <c r="F1395" t="s">
         <v>1855</v>
@@ -73498,7 +73506,7 @@
         <v>13</v>
       </c>
       <c r="E1396" t="s">
-        <v>3089</v>
+        <v>3065</v>
       </c>
       <c r="F1396" t="s">
         <v>1855</v>
@@ -73546,7 +73554,7 @@
         <v>14</v>
       </c>
       <c r="E1397" t="s">
-        <v>3090</v>
+        <v>3066</v>
       </c>
       <c r="F1397" t="s">
         <v>1855</v>
@@ -73594,7 +73602,7 @@
         <v>15</v>
       </c>
       <c r="E1398" t="s">
-        <v>3091</v>
+        <v>3067</v>
       </c>
       <c r="F1398" t="s">
         <v>1855</v>
@@ -73642,7 +73650,7 @@
         <v>0</v>
       </c>
       <c r="E1399" t="s">
-        <v>3092</v>
+        <v>3068</v>
       </c>
       <c r="F1399" t="s">
         <v>1855</v>
@@ -73690,7 +73698,7 @@
         <v>1</v>
       </c>
       <c r="E1400" t="s">
-        <v>3093</v>
+        <v>3069</v>
       </c>
       <c r="F1400" t="s">
         <v>1855</v>
@@ -73738,7 +73746,7 @@
         <v>2</v>
       </c>
       <c r="E1401" t="s">
-        <v>3094</v>
+        <v>3070</v>
       </c>
       <c r="F1401" t="s">
         <v>1855</v>
@@ -73786,7 +73794,7 @@
         <v>3</v>
       </c>
       <c r="E1402" t="s">
-        <v>3095</v>
+        <v>3071</v>
       </c>
       <c r="F1402" t="s">
         <v>1855</v>
@@ -73834,7 +73842,7 @@
         <v>4</v>
       </c>
       <c r="E1403" t="s">
-        <v>3096</v>
+        <v>3072</v>
       </c>
       <c r="F1403" t="s">
         <v>1855</v>
@@ -73882,7 +73890,7 @@
         <v>5</v>
       </c>
       <c r="E1404" t="s">
-        <v>3097</v>
+        <v>3073</v>
       </c>
       <c r="F1404" t="s">
         <v>1855</v>
@@ -73930,7 +73938,7 @@
         <v>6</v>
       </c>
       <c r="E1405" t="s">
-        <v>3098</v>
+        <v>3074</v>
       </c>
       <c r="F1405" t="s">
         <v>1855</v>
@@ -73978,7 +73986,7 @@
         <v>7</v>
       </c>
       <c r="E1406" t="s">
-        <v>3099</v>
+        <v>3075</v>
       </c>
       <c r="F1406" t="s">
         <v>1855</v>
@@ -74026,7 +74034,7 @@
         <v>8</v>
       </c>
       <c r="E1407" t="s">
-        <v>3100</v>
+        <v>3076</v>
       </c>
       <c r="F1407" t="s">
         <v>1855</v>
@@ -74074,7 +74082,7 @@
         <v>9</v>
       </c>
       <c r="E1408" t="s">
-        <v>3101</v>
+        <v>3077</v>
       </c>
       <c r="F1408" t="s">
         <v>1855</v>
@@ -74122,7 +74130,7 @@
         <v>10</v>
       </c>
       <c r="E1409" t="s">
-        <v>3102</v>
+        <v>3078</v>
       </c>
       <c r="F1409" t="s">
         <v>1855</v>
@@ -74170,7 +74178,7 @@
         <v>11</v>
       </c>
       <c r="E1410" t="s">
-        <v>3103</v>
+        <v>3079</v>
       </c>
       <c r="F1410" t="s">
         <v>1855</v>
@@ -74218,7 +74226,7 @@
         <v>12</v>
       </c>
       <c r="E1411" t="s">
-        <v>3104</v>
+        <v>3080</v>
       </c>
       <c r="F1411" t="s">
         <v>1855</v>
@@ -74266,7 +74274,7 @@
         <v>13</v>
       </c>
       <c r="E1412" t="s">
-        <v>3105</v>
+        <v>3081</v>
       </c>
       <c r="F1412" t="s">
         <v>1855</v>
@@ -74314,7 +74322,7 @@
         <v>14</v>
       </c>
       <c r="E1413" t="s">
-        <v>3106</v>
+        <v>3082</v>
       </c>
       <c r="F1413" t="s">
         <v>1855</v>
@@ -74362,7 +74370,7 @@
         <v>15</v>
       </c>
       <c r="E1414" t="s">
-        <v>3107</v>
+        <v>3083</v>
       </c>
       <c r="F1414" t="s">
         <v>1855</v>
@@ -74410,7 +74418,7 @@
         <v>0</v>
       </c>
       <c r="E1415" t="s">
-        <v>3108</v>
+        <v>3084</v>
       </c>
       <c r="F1415" t="s">
         <v>1855</v>
@@ -74458,7 +74466,7 @@
         <v>1</v>
       </c>
       <c r="E1416" t="s">
-        <v>3109</v>
+        <v>3085</v>
       </c>
       <c r="F1416" t="s">
         <v>1855</v>
@@ -74506,7 +74514,7 @@
         <v>2</v>
       </c>
       <c r="E1417" t="s">
-        <v>3110</v>
+        <v>3086</v>
       </c>
       <c r="F1417" t="s">
         <v>1855</v>
@@ -74554,7 +74562,7 @@
         <v>3</v>
       </c>
       <c r="E1418" t="s">
-        <v>3111</v>
+        <v>3087</v>
       </c>
       <c r="F1418" t="s">
         <v>1855</v>
@@ -74602,7 +74610,7 @@
         <v>4</v>
       </c>
       <c r="E1419" t="s">
-        <v>3112</v>
+        <v>3088</v>
       </c>
       <c r="F1419" t="s">
         <v>1855</v>
@@ -74650,7 +74658,7 @@
         <v>5</v>
       </c>
       <c r="E1420" t="s">
-        <v>3113</v>
+        <v>3089</v>
       </c>
       <c r="F1420" t="s">
         <v>1855</v>
@@ -74698,7 +74706,7 @@
         <v>6</v>
       </c>
       <c r="E1421" t="s">
-        <v>3114</v>
+        <v>3090</v>
       </c>
       <c r="F1421" t="s">
         <v>1855</v>
@@ -74746,7 +74754,7 @@
         <v>7</v>
       </c>
       <c r="E1422" t="s">
-        <v>3115</v>
+        <v>3091</v>
       </c>
       <c r="F1422" t="s">
         <v>1855</v>
@@ -74794,7 +74802,7 @@
         <v>8</v>
       </c>
       <c r="E1423" t="s">
-        <v>3116</v>
+        <v>3092</v>
       </c>
       <c r="F1423" t="s">
         <v>1855</v>
@@ -74842,7 +74850,7 @@
         <v>9</v>
       </c>
       <c r="E1424" t="s">
-        <v>3117</v>
+        <v>3093</v>
       </c>
       <c r="F1424" t="s">
         <v>1855</v>
@@ -74890,7 +74898,7 @@
         <v>10</v>
       </c>
       <c r="E1425" t="s">
-        <v>3118</v>
+        <v>3094</v>
       </c>
       <c r="F1425" t="s">
         <v>1855</v>
@@ -74938,7 +74946,7 @@
         <v>11</v>
       </c>
       <c r="E1426" t="s">
-        <v>3119</v>
+        <v>3095</v>
       </c>
       <c r="F1426" t="s">
         <v>1855</v>
@@ -74986,7 +74994,7 @@
         <v>12</v>
       </c>
       <c r="E1427" t="s">
-        <v>3120</v>
+        <v>3096</v>
       </c>
       <c r="F1427" t="s">
         <v>1855</v>
@@ -75034,7 +75042,7 @@
         <v>13</v>
       </c>
       <c r="E1428" t="s">
-        <v>3121</v>
+        <v>3097</v>
       </c>
       <c r="F1428" t="s">
         <v>1855</v>
@@ -75082,7 +75090,7 @@
         <v>14</v>
       </c>
       <c r="E1429" t="s">
-        <v>3122</v>
+        <v>3098</v>
       </c>
       <c r="F1429" t="s">
         <v>1855</v>
@@ -75130,7 +75138,7 @@
         <v>15</v>
       </c>
       <c r="E1430" t="s">
-        <v>3123</v>
+        <v>3099</v>
       </c>
       <c r="F1430" t="s">
         <v>1855</v>
@@ -75178,7 +75186,7 @@
         <v>0</v>
       </c>
       <c r="E1431" t="s">
-        <v>2852</v>
+        <v>2828</v>
       </c>
       <c r="F1431" t="s">
         <v>1856</v>
@@ -75226,7 +75234,7 @@
         <v>1</v>
       </c>
       <c r="E1432" t="s">
-        <v>2853</v>
+        <v>2829</v>
       </c>
       <c r="F1432" t="s">
         <v>1856</v>
@@ -75274,7 +75282,7 @@
         <v>2</v>
       </c>
       <c r="E1433" t="s">
-        <v>2854</v>
+        <v>2830</v>
       </c>
       <c r="F1433" t="s">
         <v>1856</v>
@@ -75322,7 +75330,7 @@
         <v>3</v>
       </c>
       <c r="E1434" t="s">
-        <v>2855</v>
+        <v>2831</v>
       </c>
       <c r="F1434" t="s">
         <v>1856</v>
@@ -75370,7 +75378,7 @@
         <v>4</v>
       </c>
       <c r="E1435" t="s">
-        <v>2856</v>
+        <v>2832</v>
       </c>
       <c r="F1435" t="s">
         <v>1856</v>
@@ -75418,7 +75426,7 @@
         <v>5</v>
       </c>
       <c r="E1436" t="s">
-        <v>2857</v>
+        <v>2833</v>
       </c>
       <c r="F1436" t="s">
         <v>1856</v>
@@ -75466,7 +75474,7 @@
         <v>6</v>
       </c>
       <c r="E1437" t="s">
-        <v>3124</v>
+        <v>3100</v>
       </c>
       <c r="F1437" t="s">
         <v>1856</v>
@@ -75514,7 +75522,7 @@
         <v>7</v>
       </c>
       <c r="E1438" t="s">
-        <v>2858</v>
+        <v>2834</v>
       </c>
       <c r="F1438" t="s">
         <v>1856</v>
@@ -75562,7 +75570,7 @@
         <v>8</v>
       </c>
       <c r="E1439" t="s">
-        <v>2859</v>
+        <v>2835</v>
       </c>
       <c r="F1439" t="s">
         <v>1856</v>
@@ -75610,7 +75618,7 @@
         <v>9</v>
       </c>
       <c r="E1440" t="s">
-        <v>2860</v>
+        <v>2836</v>
       </c>
       <c r="F1440" t="s">
         <v>1856</v>
@@ -75658,7 +75666,7 @@
         <v>10</v>
       </c>
       <c r="E1441" t="s">
-        <v>2861</v>
+        <v>2837</v>
       </c>
       <c r="F1441" t="s">
         <v>1856</v>
@@ -75706,7 +75714,7 @@
         <v>11</v>
       </c>
       <c r="E1442" t="s">
-        <v>2862</v>
+        <v>2838</v>
       </c>
       <c r="F1442" t="s">
         <v>1856</v>
@@ -75754,7 +75762,7 @@
         <v>12</v>
       </c>
       <c r="E1443" t="s">
-        <v>2863</v>
+        <v>2839</v>
       </c>
       <c r="F1443" t="s">
         <v>1856</v>
@@ -75802,7 +75810,7 @@
         <v>13</v>
       </c>
       <c r="E1444" t="s">
-        <v>2864</v>
+        <v>2840</v>
       </c>
       <c r="F1444" t="s">
         <v>1856</v>
@@ -75850,7 +75858,7 @@
         <v>14</v>
       </c>
       <c r="E1445" t="s">
-        <v>2865</v>
+        <v>2841</v>
       </c>
       <c r="F1445" t="s">
         <v>1856</v>
@@ -75898,7 +75906,7 @@
         <v>15</v>
       </c>
       <c r="E1446" t="s">
-        <v>2866</v>
+        <v>2842</v>
       </c>
       <c r="F1446" t="s">
         <v>1856</v>
@@ -75946,7 +75954,7 @@
         <v>16</v>
       </c>
       <c r="E1447" t="s">
-        <v>2867</v>
+        <v>2843</v>
       </c>
       <c r="F1447" t="s">
         <v>1856</v>
@@ -75994,7 +76002,7 @@
         <v>0</v>
       </c>
       <c r="E1448" t="s">
-        <v>2868</v>
+        <v>2844</v>
       </c>
       <c r="F1448" t="s">
         <v>1856</v>
@@ -76042,7 +76050,7 @@
         <v>1</v>
       </c>
       <c r="E1449" t="s">
-        <v>2869</v>
+        <v>2845</v>
       </c>
       <c r="F1449" t="s">
         <v>1856</v>
@@ -76090,7 +76098,7 @@
         <v>2</v>
       </c>
       <c r="E1450" t="s">
-        <v>2870</v>
+        <v>2846</v>
       </c>
       <c r="F1450" t="s">
         <v>1856</v>
@@ -76138,7 +76146,7 @@
         <v>3</v>
       </c>
       <c r="E1451" t="s">
-        <v>2871</v>
+        <v>2847</v>
       </c>
       <c r="F1451" t="s">
         <v>1856</v>
@@ -76186,7 +76194,7 @@
         <v>4</v>
       </c>
       <c r="E1452" t="s">
-        <v>2872</v>
+        <v>2848</v>
       </c>
       <c r="F1452" t="s">
         <v>1856</v>
@@ -76234,7 +76242,7 @@
         <v>5</v>
       </c>
       <c r="E1453" t="s">
-        <v>2873</v>
+        <v>2849</v>
       </c>
       <c r="F1453" t="s">
         <v>1856</v>
@@ -76282,7 +76290,7 @@
         <v>6</v>
       </c>
       <c r="E1454" t="s">
-        <v>3125</v>
+        <v>3101</v>
       </c>
       <c r="F1454" t="s">
         <v>1856</v>
@@ -76330,7 +76338,7 @@
         <v>7</v>
       </c>
       <c r="E1455" t="s">
-        <v>2874</v>
+        <v>2850</v>
       </c>
       <c r="F1455" t="s">
         <v>1856</v>
@@ -76378,7 +76386,7 @@
         <v>8</v>
       </c>
       <c r="E1456" t="s">
-        <v>2875</v>
+        <v>2851</v>
       </c>
       <c r="F1456" t="s">
         <v>1856</v>
@@ -76426,7 +76434,7 @@
         <v>9</v>
       </c>
       <c r="E1457" t="s">
-        <v>2876</v>
+        <v>2852</v>
       </c>
       <c r="F1457" t="s">
         <v>1856</v>
@@ -76474,7 +76482,7 @@
         <v>10</v>
       </c>
       <c r="E1458" t="s">
-        <v>2877</v>
+        <v>2853</v>
       </c>
       <c r="F1458" t="s">
         <v>1856</v>
@@ -76522,7 +76530,7 @@
         <v>11</v>
       </c>
       <c r="E1459" t="s">
-        <v>2878</v>
+        <v>2854</v>
       </c>
       <c r="F1459" t="s">
         <v>1856</v>
@@ -76570,7 +76578,7 @@
         <v>12</v>
       </c>
       <c r="E1460" t="s">
-        <v>2879</v>
+        <v>2855</v>
       </c>
       <c r="F1460" t="s">
         <v>1856</v>
@@ -76618,7 +76626,7 @@
         <v>13</v>
       </c>
       <c r="E1461" t="s">
-        <v>2880</v>
+        <v>2856</v>
       </c>
       <c r="F1461" t="s">
         <v>1856</v>
@@ -76666,7 +76674,7 @@
         <v>14</v>
       </c>
       <c r="E1462" t="s">
-        <v>2881</v>
+        <v>2857</v>
       </c>
       <c r="F1462" t="s">
         <v>1856</v>
@@ -76714,7 +76722,7 @@
         <v>15</v>
       </c>
       <c r="E1463" t="s">
-        <v>2882</v>
+        <v>2858</v>
       </c>
       <c r="F1463" t="s">
         <v>1856</v>
@@ -76762,7 +76770,7 @@
         <v>16</v>
       </c>
       <c r="E1464" t="s">
-        <v>2883</v>
+        <v>2859</v>
       </c>
       <c r="F1464" t="s">
         <v>1856</v>
@@ -76810,7 +76818,7 @@
         <v>0</v>
       </c>
       <c r="E1465" t="s">
-        <v>3012</v>
+        <v>2988</v>
       </c>
       <c r="F1465" t="s">
         <v>1856</v>
@@ -76858,7 +76866,7 @@
         <v>1</v>
       </c>
       <c r="E1466" t="s">
-        <v>3013</v>
+        <v>2989</v>
       </c>
       <c r="F1466" t="s">
         <v>1856</v>
@@ -76906,7 +76914,7 @@
         <v>2</v>
       </c>
       <c r="E1467" t="s">
-        <v>3014</v>
+        <v>2990</v>
       </c>
       <c r="F1467" t="s">
         <v>1856</v>
@@ -76954,7 +76962,7 @@
         <v>3</v>
       </c>
       <c r="E1468" t="s">
-        <v>3015</v>
+        <v>2991</v>
       </c>
       <c r="F1468" t="s">
         <v>1856</v>
@@ -77002,7 +77010,7 @@
         <v>4</v>
       </c>
       <c r="E1469" t="s">
-        <v>3016</v>
+        <v>2992</v>
       </c>
       <c r="F1469" t="s">
         <v>1856</v>
@@ -77050,7 +77058,7 @@
         <v>5</v>
       </c>
       <c r="E1470" t="s">
-        <v>3017</v>
+        <v>2993</v>
       </c>
       <c r="F1470" t="s">
         <v>1856</v>
@@ -77098,7 +77106,7 @@
         <v>6</v>
       </c>
       <c r="E1471" t="s">
-        <v>3126</v>
+        <v>3102</v>
       </c>
       <c r="F1471" t="s">
         <v>1856</v>
@@ -77146,7 +77154,7 @@
         <v>7</v>
       </c>
       <c r="E1472" t="s">
-        <v>3018</v>
+        <v>2994</v>
       </c>
       <c r="F1472" t="s">
         <v>1856</v>
@@ -77194,7 +77202,7 @@
         <v>8</v>
       </c>
       <c r="E1473" t="s">
-        <v>3019</v>
+        <v>2995</v>
       </c>
       <c r="F1473" t="s">
         <v>1856</v>
@@ -77242,7 +77250,7 @@
         <v>9</v>
       </c>
       <c r="E1474" t="s">
-        <v>3020</v>
+        <v>2996</v>
       </c>
       <c r="F1474" t="s">
         <v>1856</v>
@@ -77290,7 +77298,7 @@
         <v>10</v>
       </c>
       <c r="E1475" t="s">
-        <v>3021</v>
+        <v>2997</v>
       </c>
       <c r="F1475" t="s">
         <v>1856</v>
@@ -77338,7 +77346,7 @@
         <v>11</v>
       </c>
       <c r="E1476" t="s">
-        <v>3022</v>
+        <v>2998</v>
       </c>
       <c r="F1476" t="s">
         <v>1856</v>
@@ -77386,7 +77394,7 @@
         <v>12</v>
       </c>
       <c r="E1477" t="s">
-        <v>3023</v>
+        <v>2999</v>
       </c>
       <c r="F1477" t="s">
         <v>1856</v>
@@ -77434,7 +77442,7 @@
         <v>13</v>
       </c>
       <c r="E1478" t="s">
-        <v>3024</v>
+        <v>3000</v>
       </c>
       <c r="F1478" t="s">
         <v>1856</v>
@@ -77482,7 +77490,7 @@
         <v>14</v>
       </c>
       <c r="E1479" t="s">
-        <v>3025</v>
+        <v>3001</v>
       </c>
       <c r="F1479" t="s">
         <v>1856</v>
@@ -77530,7 +77538,7 @@
         <v>15</v>
       </c>
       <c r="E1480" t="s">
-        <v>3026</v>
+        <v>3002</v>
       </c>
       <c r="F1480" t="s">
         <v>1856</v>
@@ -77578,7 +77586,7 @@
         <v>16</v>
       </c>
       <c r="E1481" t="s">
-        <v>3027</v>
+        <v>3003</v>
       </c>
       <c r="F1481" t="s">
         <v>1856</v>
@@ -77626,7 +77634,7 @@
         <v>0</v>
       </c>
       <c r="E1482" t="s">
-        <v>3028</v>
+        <v>3004</v>
       </c>
       <c r="F1482" t="s">
         <v>1856</v>
@@ -77674,7 +77682,7 @@
         <v>1</v>
       </c>
       <c r="E1483" t="s">
-        <v>3029</v>
+        <v>3005</v>
       </c>
       <c r="F1483" t="s">
         <v>1856</v>
@@ -77722,7 +77730,7 @@
         <v>2</v>
       </c>
       <c r="E1484" t="s">
-        <v>3030</v>
+        <v>3006</v>
       </c>
       <c r="F1484" t="s">
         <v>1856</v>
@@ -77770,7 +77778,7 @@
         <v>3</v>
       </c>
       <c r="E1485" t="s">
-        <v>3031</v>
+        <v>3007</v>
       </c>
       <c r="F1485" t="s">
         <v>1856</v>
@@ -77818,7 +77826,7 @@
         <v>4</v>
       </c>
       <c r="E1486" t="s">
-        <v>3032</v>
+        <v>3008</v>
       </c>
       <c r="F1486" t="s">
         <v>1856</v>
@@ -77866,7 +77874,7 @@
         <v>5</v>
       </c>
       <c r="E1487" t="s">
-        <v>3033</v>
+        <v>3009</v>
       </c>
       <c r="F1487" t="s">
         <v>1856</v>
@@ -77914,7 +77922,7 @@
         <v>6</v>
       </c>
       <c r="E1488" t="s">
-        <v>3127</v>
+        <v>3103</v>
       </c>
       <c r="F1488" t="s">
         <v>1856</v>
@@ -77962,7 +77970,7 @@
         <v>7</v>
       </c>
       <c r="E1489" t="s">
-        <v>3034</v>
+        <v>3010</v>
       </c>
       <c r="F1489" t="s">
         <v>1856</v>
@@ -78010,7 +78018,7 @@
         <v>8</v>
       </c>
       <c r="E1490" t="s">
-        <v>3035</v>
+        <v>3011</v>
       </c>
       <c r="F1490" t="s">
         <v>1856</v>
@@ -78058,7 +78066,7 @@
         <v>9</v>
       </c>
       <c r="E1491" t="s">
-        <v>3036</v>
+        <v>3012</v>
       </c>
       <c r="F1491" t="s">
         <v>1856</v>
@@ -78106,7 +78114,7 @@
         <v>10</v>
       </c>
       <c r="E1492" t="s">
-        <v>3037</v>
+        <v>3013</v>
       </c>
       <c r="F1492" t="s">
         <v>1856</v>
@@ -78154,7 +78162,7 @@
         <v>11</v>
       </c>
       <c r="E1493" t="s">
-        <v>3038</v>
+        <v>3014</v>
       </c>
       <c r="F1493" t="s">
         <v>1856</v>
@@ -78202,7 +78210,7 @@
         <v>12</v>
       </c>
       <c r="E1494" t="s">
-        <v>3039</v>
+        <v>3015</v>
       </c>
       <c r="F1494" t="s">
         <v>1856</v>
@@ -78250,7 +78258,7 @@
         <v>13</v>
       </c>
       <c r="E1495" t="s">
-        <v>3040</v>
+        <v>3016</v>
       </c>
       <c r="F1495" t="s">
         <v>1856</v>
@@ -78298,7 +78306,7 @@
         <v>14</v>
       </c>
       <c r="E1496" t="s">
-        <v>3041</v>
+        <v>3017</v>
       </c>
       <c r="F1496" t="s">
         <v>1856</v>
@@ -78346,7 +78354,7 @@
         <v>15</v>
       </c>
       <c r="E1497" t="s">
-        <v>3042</v>
+        <v>3018</v>
       </c>
       <c r="F1497" t="s">
         <v>1856</v>
@@ -78394,7 +78402,7 @@
         <v>16</v>
       </c>
       <c r="E1498" t="s">
-        <v>3043</v>
+        <v>3019</v>
       </c>
       <c r="F1498" t="s">
         <v>1856</v>
@@ -78442,7 +78450,7 @@
         <v>0</v>
       </c>
       <c r="E1499" t="s">
-        <v>3108</v>
+        <v>3084</v>
       </c>
       <c r="F1499" t="s">
         <v>1856</v>
@@ -78490,7 +78498,7 @@
         <v>1</v>
       </c>
       <c r="E1500" t="s">
-        <v>3109</v>
+        <v>3085</v>
       </c>
       <c r="F1500" t="s">
         <v>1856</v>
@@ -78538,7 +78546,7 @@
         <v>2</v>
       </c>
       <c r="E1501" t="s">
-        <v>3110</v>
+        <v>3086</v>
       </c>
       <c r="F1501" t="s">
         <v>1856</v>
@@ -78586,7 +78594,7 @@
         <v>3</v>
       </c>
       <c r="E1502" t="s">
-        <v>3111</v>
+        <v>3087</v>
       </c>
       <c r="F1502" t="s">
         <v>1856</v>
@@ -78634,7 +78642,7 @@
         <v>4</v>
       </c>
       <c r="E1503" t="s">
-        <v>3112</v>
+        <v>3088</v>
       </c>
       <c r="F1503" t="s">
         <v>1856</v>
@@ -78682,7 +78690,7 @@
         <v>5</v>
       </c>
       <c r="E1504" t="s">
-        <v>3113</v>
+        <v>3089</v>
       </c>
       <c r="F1504" t="s">
         <v>1856</v>
@@ -78730,7 +78738,7 @@
         <v>6</v>
       </c>
       <c r="E1505" t="s">
-        <v>3128</v>
+        <v>3104</v>
       </c>
       <c r="F1505" t="s">
         <v>1856</v>
@@ -78778,7 +78786,7 @@
         <v>7</v>
       </c>
       <c r="E1506" t="s">
-        <v>3114</v>
+        <v>3090</v>
       </c>
       <c r="F1506" t="s">
         <v>1856</v>
@@ -78826,7 +78834,7 @@
         <v>8</v>
       </c>
       <c r="E1507" t="s">
-        <v>3115</v>
+        <v>3091</v>
       </c>
       <c r="F1507" t="s">
         <v>1856</v>
@@ -78874,7 +78882,7 @@
         <v>9</v>
       </c>
       <c r="E1508" t="s">
-        <v>3116</v>
+        <v>3092</v>
       </c>
       <c r="F1508" t="s">
         <v>1856</v>
@@ -78922,7 +78930,7 @@
         <v>10</v>
       </c>
       <c r="E1509" t="s">
-        <v>3117</v>
+        <v>3093</v>
       </c>
       <c r="F1509" t="s">
         <v>1856</v>
@@ -78970,7 +78978,7 @@
         <v>11</v>
       </c>
       <c r="E1510" t="s">
-        <v>3118</v>
+        <v>3094</v>
       </c>
       <c r="F1510" t="s">
         <v>1856</v>
@@ -79018,7 +79026,7 @@
         <v>12</v>
       </c>
       <c r="E1511" t="s">
-        <v>3119</v>
+        <v>3095</v>
       </c>
       <c r="F1511" t="s">
         <v>1856</v>
@@ -79066,7 +79074,7 @@
         <v>13</v>
       </c>
       <c r="E1512" t="s">
-        <v>3120</v>
+        <v>3096</v>
       </c>
       <c r="F1512" t="s">
         <v>1856</v>
@@ -79114,7 +79122,7 @@
         <v>14</v>
       </c>
       <c r="E1513" t="s">
-        <v>3121</v>
+        <v>3097</v>
       </c>
       <c r="F1513" t="s">
         <v>1856</v>
@@ -79162,7 +79170,7 @@
         <v>15</v>
       </c>
       <c r="E1514" t="s">
-        <v>3122</v>
+        <v>3098</v>
       </c>
       <c r="F1514" t="s">
         <v>1856</v>
@@ -79210,7 +79218,7 @@
         <v>16</v>
       </c>
       <c r="E1515" t="s">
-        <v>3123</v>
+        <v>3099</v>
       </c>
       <c r="F1515" t="s">
         <v>1856</v>

--- a/pages/apps/uprn-service/config.xlsx
+++ b/pages/apps/uprn-service/config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NDSH\GitHub\dsh-content\dev\pages\apps\uprn-service\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NDSH\GitHub\dsh-content\pages\apps\uprn-service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{577D8B87-A935-4E2E-BF9C-D8B5CFECCBDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82EC4F1E-F6BB-44F4-9C2E-4936F42FDC08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="388" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="388" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="folders" sheetId="1" r:id="rId1"/>
@@ -23,12 +23,25 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">datasets!$A$1:$T$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">variables!$A$1:$S$1515</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6490" uniqueCount="3200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6591" uniqueCount="3301">
   <si>
     <t>DbId</t>
   </si>
@@ -9628,6 +9641,309 @@
   </si>
   <si>
     <t>19b02dc323e-layer-276-0</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/so2__anuual_mean__ug_m3_timeseries.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm25__annual_mean__ug_m3__timeseries.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm10__annual_mean__ug_m3__timeseries.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/nox__annual_mean__ug_m3__timeseries.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/dgt_120__timeseries.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/no2__annual_mean__ug_m3__timeseries.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/co__annual_mean__mg_m3__2010.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/co__2010__mil.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/bz__annual_mean__ug_m3__timeseries.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/bz__annual_mean__ug_m3__2022.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/bz__annual_mean__ug_m3__2021.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/bz__annual_mean__ug_m3__2020.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/bz__annual_mean__ug_m3__2019.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/bz__annual_mean__ug_m3__2018.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/bz__annual_mean__ug_m3__2017.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/bz__annual_mean__ug_m3__2016.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/bz__annual_mean__ug_m3__2015.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/bz__annual_mean__ug_m3__2014.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/bz__annual_mean__ug_m3__2013.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/bz__annual_mean__ug_m3__2012.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/bz__annual_mean__ug_m3__2011.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/bz__annual_mean__ug_m3__2010.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/co__max_8hr_mean__mg_m3__2010.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/no2__annual_mean__ug_m3__2022.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/no2__annual_mean__ug_m3__2021.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/no2__annual_mean__ug_m3__2020.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/no2__annual_mean__ug_m3__2019.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/no2__annual_mean__ug_m3__2018.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/no2__annual_mean__ug_m3__2017.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/no2__annual_mean__ug_m3__2016.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/no2__annual_mean__ug_m3__2015.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/no2__annual_mean__ug_m3__2014.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/no2__annual_mean__ug_m3__2011.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/no2__annual_mean__ug_m3__2010.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/no2__annual_mean__ug_m3__2013.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/no2__annual_mean__ug_m3__2012.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/nox__annual_mean__ug_m3__2022.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/nox__annual_mean__ug_m3__2021.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/nox__annual_mean__ug_m3__2020.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/nox__annual_mean__ug_m3__2019.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/nox__annual_mean__ug_m3__2018.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/nox__annual_mean__ug_m3__2017.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/nox__annual_mean__ug_m3__2016.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/nox__annual_mean__ug_m3__2015.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/nox__annual_mean__ug_m3__2014.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/nox__annual_mean__ug_m3__2013.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/nox__annual_mean__ug_m3__2012.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/nox__annual_mean__ug_m3__2011.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/nox__annual_mean__ug_m3__2010.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/dgt_120__2022.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/dgt_120__2021.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/dgt_120__2020.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/dgt_120__2019.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/dgt_120__2018.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/dgt_120__2017.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/dgt_120__2016.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/dgt_120__2015.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/dgt_120__2014.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/dgt_120__2013.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/dgt_120__2012.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/dgt_120__2011.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/dgt_120__2010.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm25__annual_mean__ug_m3__2022_g.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm25__annual_mean__ug_m3__2021_g.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm25__annual_mean__ug_m3__2020_g.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm25__annual_mean__ug_m3__2019_g.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm25__annual_mean__ug_m3__2018_g.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm25__annual_mean__ug_m3__2017_g.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm25__annual_mean__ug_m3__2016_g.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm25__annual_mean__ug_m3__2015_g.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm25__annual_mean__ug_m3__2014_g.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm25__annual_mean__ug_m3__2013_g.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm25__annual_mean__ug_m3__2012_g.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm25__annual_mean__ug_m3__2011_g.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm25__annual_mean__ug_m3__2010_g.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm10__annual_mean__ug_m3__2022_g.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm10__annual_mean__ug_m3__2021_g.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm10__annual_mean__ug_m3__2020_g.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm10__annual_mean__ug_m3__2019_g.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm10__annual_mean__ug_m3__2018_g.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm10__annual_mean__ug_m3__2017_g.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm10__annual_mean__ug_m3__2016_g.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm10__annual_mean__ug_m3__2015_g.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm10__annual_mean__ug_m3__2014_g.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm10__annual_mean__ug_m3__2013_g.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm10__annual_mean__ug_m3__2012_g.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm10__annual_mean__ug_m3__2011_g.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm10__annual_mean__ug_m3__2010_g.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/so2__annual_mean__ug_m3__2022.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/so2__annual_mean__ug_m3__2021.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/so2__annual_mean__ug_m3__2020.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/so2__annual_mean__ug_m3__2019.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/so2__annual_mean__ug_m3__2018.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/so2__annual_mean__ug_m3__2017.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/so2__annual_mean__ug_m3__2016.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/so2__annual_mean__ug_m3__2015.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/so2__annual_mean__ug_m3__2014.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/so2__annual_mean__ug_m3__2013.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/so2__annual_mean__ug_m3__2012.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/so2__annual_mean__ug_m3__2011.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/so2__annual_mean__ug_m3__2010.json</t>
   </si>
 </sst>
 </file>
@@ -12183,6 +12499,9 @@
       <c r="M30">
         <v>4002</v>
       </c>
+      <c r="O30" s="3" t="s">
+        <v>3208</v>
+      </c>
       <c r="P30">
         <v>2</v>
       </c>
@@ -12239,6 +12558,9 @@
       <c r="M31">
         <v>4003</v>
       </c>
+      <c r="O31" s="3" t="s">
+        <v>3207</v>
+      </c>
       <c r="P31">
         <v>2</v>
       </c>
@@ -12295,6 +12617,9 @@
       <c r="M32">
         <v>4004</v>
       </c>
+      <c r="O32" s="3" t="s">
+        <v>3205</v>
+      </c>
       <c r="P32">
         <v>2</v>
       </c>
@@ -12351,6 +12676,9 @@
       <c r="M33">
         <v>4005</v>
       </c>
+      <c r="O33" s="3" t="s">
+        <v>3203</v>
+      </c>
       <c r="P33">
         <v>2</v>
       </c>
@@ -12407,6 +12735,9 @@
       <c r="M34">
         <v>4006</v>
       </c>
+      <c r="O34" s="3" t="s">
+        <v>3204</v>
+      </c>
       <c r="P34">
         <v>2</v>
       </c>
@@ -12463,6 +12794,9 @@
       <c r="M35">
         <v>4007</v>
       </c>
+      <c r="O35" s="3" t="s">
+        <v>3201</v>
+      </c>
       <c r="P35">
         <v>2</v>
       </c>
@@ -12519,6 +12853,9 @@
       <c r="M36">
         <v>4008</v>
       </c>
+      <c r="O36" s="3" t="s">
+        <v>3202</v>
+      </c>
       <c r="P36">
         <v>2</v>
       </c>
@@ -12574,6 +12911,9 @@
       </c>
       <c r="M37">
         <v>4009</v>
+      </c>
+      <c r="O37" s="3" t="s">
+        <v>3200</v>
       </c>
       <c r="P37">
         <v>2</v>
@@ -14325,6 +14665,14 @@
     <hyperlink ref="O63" r:id="rId31" xr:uid="{356CAD23-03AB-460F-AFCA-EC4BDE2D8AE0}"/>
     <hyperlink ref="O64" r:id="rId32" xr:uid="{4F6B4081-E0D1-4EF1-825D-2153F4EE3414}"/>
     <hyperlink ref="E40" r:id="rId33" xr:uid="{FD826172-87CB-45B3-A0FC-D8B3114ACB40}"/>
+    <hyperlink ref="O37" r:id="rId34" xr:uid="{140F4408-E7AA-44B6-A18E-360C0D67CD7D}"/>
+    <hyperlink ref="O35" r:id="rId35" xr:uid="{808E1FD3-625F-468F-B5CE-C7D46AEC377C}"/>
+    <hyperlink ref="O36" r:id="rId36" xr:uid="{EEDF3432-B070-4FF4-BC80-348F20F284B0}"/>
+    <hyperlink ref="O34" r:id="rId37" xr:uid="{92BB371E-C739-4E6E-90A8-536B8C7ABAAB}"/>
+    <hyperlink ref="O33" r:id="rId38" xr:uid="{28DFF9D9-D4E7-49F3-9FF8-53AEB03F1132}"/>
+    <hyperlink ref="O32" r:id="rId39" xr:uid="{B0A928E1-5A9D-4904-925C-B849C701CBE6}"/>
+    <hyperlink ref="O31" r:id="rId40" xr:uid="{DE66E62C-23D8-409B-8828-A2B1F7104694}"/>
+    <hyperlink ref="O30" r:id="rId41" xr:uid="{7F69EBA1-2661-4784-B19E-BB4CCA00E309}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -55736,6 +56084,9 @@
         <v>0</v>
       </c>
       <c r="J1018" s="6"/>
+      <c r="L1018" s="3" t="s">
+        <v>3209</v>
+      </c>
       <c r="M1018">
         <v>2</v>
       </c>
@@ -55781,6 +56132,9 @@
         <v>0</v>
       </c>
       <c r="J1019" s="6"/>
+      <c r="L1019" s="3" t="s">
+        <v>3210</v>
+      </c>
       <c r="M1019">
         <v>2</v>
       </c>
@@ -55826,6 +56180,9 @@
         <v>0</v>
       </c>
       <c r="J1020" s="6"/>
+      <c r="L1020" s="3" t="s">
+        <v>3211</v>
+      </c>
       <c r="M1020">
         <v>2</v>
       </c>
@@ -55871,6 +56228,9 @@
         <v>0</v>
       </c>
       <c r="J1021" s="6"/>
+      <c r="L1021" s="3" t="s">
+        <v>3212</v>
+      </c>
       <c r="M1021">
         <v>2</v>
       </c>
@@ -55916,6 +56276,9 @@
         <v>0</v>
       </c>
       <c r="J1022" s="6"/>
+      <c r="L1022" s="3" t="s">
+        <v>3213</v>
+      </c>
       <c r="M1022">
         <v>2</v>
       </c>
@@ -55961,6 +56324,9 @@
         <v>0</v>
       </c>
       <c r="J1023" s="6"/>
+      <c r="L1023" s="3" t="s">
+        <v>3214</v>
+      </c>
       <c r="M1023">
         <v>2</v>
       </c>
@@ -56006,6 +56372,9 @@
         <v>0</v>
       </c>
       <c r="J1024" s="6"/>
+      <c r="L1024" s="3" t="s">
+        <v>3215</v>
+      </c>
       <c r="M1024">
         <v>2</v>
       </c>
@@ -56051,6 +56420,9 @@
         <v>0</v>
       </c>
       <c r="J1025" s="6"/>
+      <c r="L1025" s="3" t="s">
+        <v>3216</v>
+      </c>
       <c r="M1025">
         <v>2</v>
       </c>
@@ -56096,6 +56468,9 @@
         <v>0</v>
       </c>
       <c r="J1026" s="6"/>
+      <c r="L1026" s="3" t="s">
+        <v>3217</v>
+      </c>
       <c r="M1026">
         <v>2</v>
       </c>
@@ -56141,6 +56516,9 @@
         <v>0</v>
       </c>
       <c r="J1027" s="6"/>
+      <c r="L1027" s="3" t="s">
+        <v>3218</v>
+      </c>
       <c r="M1027">
         <v>2</v>
       </c>
@@ -56186,6 +56564,9 @@
         <v>0</v>
       </c>
       <c r="J1028" s="6"/>
+      <c r="L1028" s="3" t="s">
+        <v>3219</v>
+      </c>
       <c r="M1028">
         <v>2</v>
       </c>
@@ -56231,6 +56612,9 @@
         <v>0</v>
       </c>
       <c r="J1029" s="6"/>
+      <c r="L1029" s="3" t="s">
+        <v>3220</v>
+      </c>
       <c r="M1029">
         <v>2</v>
       </c>
@@ -56276,6 +56660,9 @@
         <v>0</v>
       </c>
       <c r="J1030" s="6"/>
+      <c r="L1030" s="3" t="s">
+        <v>3221</v>
+      </c>
       <c r="M1030">
         <v>2</v>
       </c>
@@ -56321,6 +56708,9 @@
         <v>0</v>
       </c>
       <c r="J1031" s="6"/>
+      <c r="L1031" s="3" t="s">
+        <v>3206</v>
+      </c>
       <c r="M1031">
         <v>2</v>
       </c>
@@ -56366,6 +56756,9 @@
         <v>0</v>
       </c>
       <c r="J1032" s="6"/>
+      <c r="L1032" s="3" t="s">
+        <v>3222</v>
+      </c>
       <c r="M1032">
         <v>2</v>
       </c>
@@ -56411,6 +56804,9 @@
         <v>0</v>
       </c>
       <c r="J1033" s="6"/>
+      <c r="L1033" s="3" t="s">
+        <v>3223</v>
+      </c>
       <c r="M1033">
         <v>2</v>
       </c>
@@ -56456,6 +56852,9 @@
         <v>0</v>
       </c>
       <c r="J1034" s="6"/>
+      <c r="L1034" s="3" t="s">
+        <v>3224</v>
+      </c>
       <c r="M1034">
         <v>2</v>
       </c>
@@ -56501,6 +56900,9 @@
         <v>0</v>
       </c>
       <c r="J1035" s="6"/>
+      <c r="L1035" s="3" t="s">
+        <v>3225</v>
+      </c>
       <c r="M1035">
         <v>2</v>
       </c>
@@ -56546,6 +56948,9 @@
         <v>0</v>
       </c>
       <c r="J1036" s="6"/>
+      <c r="L1036" s="3" t="s">
+        <v>3226</v>
+      </c>
       <c r="M1036">
         <v>2</v>
       </c>
@@ -56591,6 +56996,9 @@
         <v>0</v>
       </c>
       <c r="J1037" s="6"/>
+      <c r="L1037" s="3" t="s">
+        <v>3227</v>
+      </c>
       <c r="M1037">
         <v>2</v>
       </c>
@@ -56636,6 +57044,9 @@
         <v>0</v>
       </c>
       <c r="J1038" s="6"/>
+      <c r="L1038" s="3" t="s">
+        <v>3228</v>
+      </c>
       <c r="M1038">
         <v>2</v>
       </c>
@@ -56681,6 +57092,9 @@
         <v>0</v>
       </c>
       <c r="J1039" s="6"/>
+      <c r="L1039" s="3" t="s">
+        <v>3229</v>
+      </c>
       <c r="M1039">
         <v>2</v>
       </c>
@@ -56726,6 +57140,9 @@
         <v>0</v>
       </c>
       <c r="J1040" s="6"/>
+      <c r="L1040" s="3" t="s">
+        <v>3230</v>
+      </c>
       <c r="M1040">
         <v>2</v>
       </c>
@@ -56771,6 +57188,9 @@
         <v>0</v>
       </c>
       <c r="J1041" s="6"/>
+      <c r="L1041" s="3" t="s">
+        <v>3231</v>
+      </c>
       <c r="M1041">
         <v>2</v>
       </c>
@@ -56816,6 +57236,9 @@
         <v>0</v>
       </c>
       <c r="J1042" s="6"/>
+      <c r="L1042" s="3" t="s">
+        <v>3234</v>
+      </c>
       <c r="M1042">
         <v>2</v>
       </c>
@@ -56861,6 +57284,9 @@
         <v>0</v>
       </c>
       <c r="J1043" s="6"/>
+      <c r="L1043" s="3" t="s">
+        <v>3235</v>
+      </c>
       <c r="M1043">
         <v>2</v>
       </c>
@@ -56906,6 +57332,9 @@
         <v>0</v>
       </c>
       <c r="J1044" s="6"/>
+      <c r="L1044" s="3" t="s">
+        <v>3232</v>
+      </c>
       <c r="M1044">
         <v>2</v>
       </c>
@@ -56951,6 +57380,9 @@
         <v>0</v>
       </c>
       <c r="J1045" s="6"/>
+      <c r="L1045" s="3" t="s">
+        <v>3233</v>
+      </c>
       <c r="M1045">
         <v>2</v>
       </c>
@@ -56996,6 +57428,9 @@
         <v>0</v>
       </c>
       <c r="J1046" s="6"/>
+      <c r="L1046" s="3" t="s">
+        <v>3236</v>
+      </c>
       <c r="M1046">
         <v>2</v>
       </c>
@@ -57041,6 +57476,9 @@
         <v>0</v>
       </c>
       <c r="J1047" s="6"/>
+      <c r="L1047" s="3" t="s">
+        <v>3237</v>
+      </c>
       <c r="M1047">
         <v>2</v>
       </c>
@@ -57086,6 +57524,9 @@
         <v>0</v>
       </c>
       <c r="J1048" s="6"/>
+      <c r="L1048" s="3" t="s">
+        <v>3238</v>
+      </c>
       <c r="M1048">
         <v>2</v>
       </c>
@@ -57131,6 +57572,9 @@
         <v>0</v>
       </c>
       <c r="J1049" s="6"/>
+      <c r="L1049" s="3" t="s">
+        <v>3239</v>
+      </c>
       <c r="M1049">
         <v>2</v>
       </c>
@@ -57176,6 +57620,9 @@
         <v>0</v>
       </c>
       <c r="J1050" s="6"/>
+      <c r="L1050" s="3" t="s">
+        <v>3240</v>
+      </c>
       <c r="M1050">
         <v>2</v>
       </c>
@@ -57221,6 +57668,9 @@
         <v>0</v>
       </c>
       <c r="J1051" s="6"/>
+      <c r="L1051" s="3" t="s">
+        <v>3241</v>
+      </c>
       <c r="M1051">
         <v>2</v>
       </c>
@@ -57266,6 +57716,9 @@
         <v>0</v>
       </c>
       <c r="J1052" s="6"/>
+      <c r="L1052" s="3" t="s">
+        <v>3242</v>
+      </c>
       <c r="M1052">
         <v>2</v>
       </c>
@@ -57311,6 +57764,9 @@
         <v>0</v>
       </c>
       <c r="J1053" s="6"/>
+      <c r="L1053" s="3" t="s">
+        <v>3243</v>
+      </c>
       <c r="M1053">
         <v>2</v>
       </c>
@@ -57356,6 +57812,9 @@
         <v>0</v>
       </c>
       <c r="J1054" s="6"/>
+      <c r="L1054" s="3" t="s">
+        <v>3244</v>
+      </c>
       <c r="M1054">
         <v>2</v>
       </c>
@@ -57401,6 +57860,9 @@
         <v>0</v>
       </c>
       <c r="J1055" s="6"/>
+      <c r="L1055" s="3" t="s">
+        <v>3245</v>
+      </c>
       <c r="M1055">
         <v>2</v>
       </c>
@@ -57446,6 +57908,9 @@
         <v>0</v>
       </c>
       <c r="J1056" s="6"/>
+      <c r="L1056" s="3" t="s">
+        <v>3246</v>
+      </c>
       <c r="M1056">
         <v>2</v>
       </c>
@@ -57491,6 +57956,9 @@
         <v>0</v>
       </c>
       <c r="J1057" s="6"/>
+      <c r="L1057" s="3" t="s">
+        <v>3247</v>
+      </c>
       <c r="M1057">
         <v>2</v>
       </c>
@@ -57536,6 +58004,9 @@
         <v>0</v>
       </c>
       <c r="J1058" s="6"/>
+      <c r="L1058" s="3" t="s">
+        <v>3248</v>
+      </c>
       <c r="M1058">
         <v>2</v>
       </c>
@@ -57581,6 +58052,9 @@
         <v>0</v>
       </c>
       <c r="J1059" s="6"/>
+      <c r="L1059" s="3" t="s">
+        <v>3249</v>
+      </c>
       <c r="M1059">
         <v>2</v>
       </c>
@@ -57626,6 +58100,9 @@
         <v>0</v>
       </c>
       <c r="J1060" s="6"/>
+      <c r="L1060" s="3" t="s">
+        <v>3250</v>
+      </c>
       <c r="M1060">
         <v>2</v>
       </c>
@@ -57671,6 +58148,9 @@
         <v>0</v>
       </c>
       <c r="J1061" s="6"/>
+      <c r="L1061" s="3" t="s">
+        <v>3251</v>
+      </c>
       <c r="M1061">
         <v>2</v>
       </c>
@@ -57716,6 +58196,9 @@
         <v>0</v>
       </c>
       <c r="J1062" s="6"/>
+      <c r="L1062" s="3" t="s">
+        <v>3252</v>
+      </c>
       <c r="M1062">
         <v>2</v>
       </c>
@@ -57761,6 +58244,9 @@
         <v>0</v>
       </c>
       <c r="J1063" s="6"/>
+      <c r="L1063" s="3" t="s">
+        <v>3253</v>
+      </c>
       <c r="M1063">
         <v>2</v>
       </c>
@@ -57806,6 +58292,9 @@
         <v>0</v>
       </c>
       <c r="J1064" s="6"/>
+      <c r="L1064" s="3" t="s">
+        <v>3254</v>
+      </c>
       <c r="M1064">
         <v>2</v>
       </c>
@@ -57851,6 +58340,9 @@
         <v>0</v>
       </c>
       <c r="J1065" s="6"/>
+      <c r="L1065" s="3" t="s">
+        <v>3255</v>
+      </c>
       <c r="M1065">
         <v>2</v>
       </c>
@@ -57896,6 +58388,9 @@
         <v>0</v>
       </c>
       <c r="J1066" s="6"/>
+      <c r="L1066" s="3" t="s">
+        <v>3256</v>
+      </c>
       <c r="M1066">
         <v>2</v>
       </c>
@@ -57941,6 +58436,9 @@
         <v>0</v>
       </c>
       <c r="J1067" s="6"/>
+      <c r="L1067" s="3" t="s">
+        <v>3257</v>
+      </c>
       <c r="M1067">
         <v>2</v>
       </c>
@@ -57986,6 +58484,9 @@
         <v>0</v>
       </c>
       <c r="J1068" s="6"/>
+      <c r="L1068" s="3" t="s">
+        <v>3258</v>
+      </c>
       <c r="M1068">
         <v>2</v>
       </c>
@@ -58031,6 +58532,9 @@
         <v>0</v>
       </c>
       <c r="J1069" s="6"/>
+      <c r="L1069" s="3" t="s">
+        <v>3259</v>
+      </c>
       <c r="M1069">
         <v>2</v>
       </c>
@@ -58076,6 +58580,9 @@
         <v>0</v>
       </c>
       <c r="J1070" s="6"/>
+      <c r="L1070" s="3" t="s">
+        <v>3260</v>
+      </c>
       <c r="M1070">
         <v>2</v>
       </c>
@@ -58121,6 +58628,9 @@
         <v>0</v>
       </c>
       <c r="J1071" s="6"/>
+      <c r="L1071" s="3" t="s">
+        <v>3261</v>
+      </c>
       <c r="M1071">
         <v>2</v>
       </c>
@@ -58166,6 +58676,9 @@
         <v>0</v>
       </c>
       <c r="J1072" s="6"/>
+      <c r="L1072" s="3" t="s">
+        <v>3262</v>
+      </c>
       <c r="M1072">
         <v>2</v>
       </c>
@@ -58211,6 +58724,9 @@
         <v>0</v>
       </c>
       <c r="J1073" s="6"/>
+      <c r="L1073" s="3" t="s">
+        <v>3263</v>
+      </c>
       <c r="M1073">
         <v>2</v>
       </c>
@@ -58256,6 +58772,9 @@
         <v>0</v>
       </c>
       <c r="J1074" s="6"/>
+      <c r="L1074" s="3" t="s">
+        <v>3264</v>
+      </c>
       <c r="M1074">
         <v>2</v>
       </c>
@@ -58301,6 +58820,9 @@
         <v>0</v>
       </c>
       <c r="J1075" s="6"/>
+      <c r="L1075" s="3" t="s">
+        <v>3265</v>
+      </c>
       <c r="M1075">
         <v>2</v>
       </c>
@@ -58346,6 +58868,9 @@
         <v>0</v>
       </c>
       <c r="J1076" s="6"/>
+      <c r="L1076" s="3" t="s">
+        <v>3266</v>
+      </c>
       <c r="M1076">
         <v>2</v>
       </c>
@@ -58391,6 +58916,9 @@
         <v>0</v>
       </c>
       <c r="J1077" s="6"/>
+      <c r="L1077" s="3" t="s">
+        <v>3267</v>
+      </c>
       <c r="M1077">
         <v>2</v>
       </c>
@@ -58436,6 +58964,9 @@
         <v>0</v>
       </c>
       <c r="J1078" s="6"/>
+      <c r="L1078" s="3" t="s">
+        <v>3268</v>
+      </c>
       <c r="M1078">
         <v>2</v>
       </c>
@@ -58481,6 +59012,9 @@
         <v>0</v>
       </c>
       <c r="J1079" s="6"/>
+      <c r="L1079" s="3" t="s">
+        <v>3269</v>
+      </c>
       <c r="M1079">
         <v>2</v>
       </c>
@@ -58526,6 +59060,9 @@
         <v>0</v>
       </c>
       <c r="J1080" s="6"/>
+      <c r="L1080" s="3" t="s">
+        <v>3270</v>
+      </c>
       <c r="M1080">
         <v>2</v>
       </c>
@@ -58571,6 +59108,9 @@
         <v>0</v>
       </c>
       <c r="J1081" s="6"/>
+      <c r="L1081" s="3" t="s">
+        <v>3271</v>
+      </c>
       <c r="M1081">
         <v>2</v>
       </c>
@@ -58616,6 +59156,9 @@
         <v>0</v>
       </c>
       <c r="J1082" s="6"/>
+      <c r="L1082" s="3" t="s">
+        <v>3272</v>
+      </c>
       <c r="M1082">
         <v>2</v>
       </c>
@@ -58661,6 +59204,9 @@
         <v>0</v>
       </c>
       <c r="J1083" s="6"/>
+      <c r="L1083" s="3" t="s">
+        <v>3273</v>
+      </c>
       <c r="M1083">
         <v>2</v>
       </c>
@@ -58706,6 +59252,9 @@
         <v>0</v>
       </c>
       <c r="J1084" s="6"/>
+      <c r="L1084" s="3" t="s">
+        <v>3274</v>
+      </c>
       <c r="M1084">
         <v>2</v>
       </c>
@@ -58751,6 +59300,9 @@
         <v>0</v>
       </c>
       <c r="J1085" s="6"/>
+      <c r="L1085" s="3" t="s">
+        <v>3275</v>
+      </c>
       <c r="M1085">
         <v>2</v>
       </c>
@@ -58796,6 +59348,9 @@
         <v>0</v>
       </c>
       <c r="J1086" s="6"/>
+      <c r="L1086" s="3" t="s">
+        <v>3276</v>
+      </c>
       <c r="M1086">
         <v>2</v>
       </c>
@@ -58841,6 +59396,9 @@
         <v>0</v>
       </c>
       <c r="J1087" s="6"/>
+      <c r="L1087" s="3" t="s">
+        <v>3277</v>
+      </c>
       <c r="M1087">
         <v>2</v>
       </c>
@@ -58886,6 +59444,9 @@
         <v>0</v>
       </c>
       <c r="J1088" s="6"/>
+      <c r="L1088" s="3" t="s">
+        <v>3278</v>
+      </c>
       <c r="M1088">
         <v>2</v>
       </c>
@@ -58931,6 +59492,9 @@
         <v>0</v>
       </c>
       <c r="J1089" s="6"/>
+      <c r="L1089" s="3" t="s">
+        <v>3279</v>
+      </c>
       <c r="M1089">
         <v>2</v>
       </c>
@@ -58976,6 +59540,9 @@
         <v>0</v>
       </c>
       <c r="J1090" s="6"/>
+      <c r="L1090" s="3" t="s">
+        <v>3280</v>
+      </c>
       <c r="M1090">
         <v>2</v>
       </c>
@@ -59021,6 +59588,9 @@
         <v>0</v>
       </c>
       <c r="J1091" s="6"/>
+      <c r="L1091" s="3" t="s">
+        <v>3281</v>
+      </c>
       <c r="M1091">
         <v>2</v>
       </c>
@@ -59066,6 +59636,9 @@
         <v>0</v>
       </c>
       <c r="J1092" s="6"/>
+      <c r="L1092" s="3" t="s">
+        <v>3282</v>
+      </c>
       <c r="M1092">
         <v>2</v>
       </c>
@@ -59111,6 +59684,9 @@
         <v>0</v>
       </c>
       <c r="J1093" s="6"/>
+      <c r="L1093" s="3" t="s">
+        <v>3283</v>
+      </c>
       <c r="M1093">
         <v>2</v>
       </c>
@@ -59156,6 +59732,9 @@
         <v>0</v>
       </c>
       <c r="J1094" s="6"/>
+      <c r="L1094" s="3" t="s">
+        <v>3284</v>
+      </c>
       <c r="M1094">
         <v>2</v>
       </c>
@@ -59201,6 +59780,9 @@
         <v>0</v>
       </c>
       <c r="J1095" s="6"/>
+      <c r="L1095" s="3" t="s">
+        <v>3285</v>
+      </c>
       <c r="M1095">
         <v>2</v>
       </c>
@@ -59246,6 +59828,9 @@
         <v>0</v>
       </c>
       <c r="J1096" s="6"/>
+      <c r="L1096" s="3" t="s">
+        <v>3286</v>
+      </c>
       <c r="M1096">
         <v>2</v>
       </c>
@@ -59291,6 +59876,9 @@
         <v>0</v>
       </c>
       <c r="J1097" s="6"/>
+      <c r="L1097" s="3" t="s">
+        <v>3287</v>
+      </c>
       <c r="M1097">
         <v>2</v>
       </c>
@@ -59336,6 +59924,9 @@
         <v>0</v>
       </c>
       <c r="J1098" s="6"/>
+      <c r="L1098" s="3" t="s">
+        <v>3288</v>
+      </c>
       <c r="M1098">
         <v>2</v>
       </c>
@@ -59381,6 +59972,9 @@
         <v>0</v>
       </c>
       <c r="J1099" s="6"/>
+      <c r="L1099" s="3" t="s">
+        <v>3289</v>
+      </c>
       <c r="M1099">
         <v>2</v>
       </c>
@@ -59426,6 +60020,9 @@
         <v>0</v>
       </c>
       <c r="J1100" s="6"/>
+      <c r="L1100" s="3" t="s">
+        <v>3290</v>
+      </c>
       <c r="M1100">
         <v>2</v>
       </c>
@@ -59471,6 +60068,9 @@
         <v>0</v>
       </c>
       <c r="J1101" s="6"/>
+      <c r="L1101" s="3" t="s">
+        <v>3291</v>
+      </c>
       <c r="M1101">
         <v>2</v>
       </c>
@@ -59516,6 +60116,9 @@
         <v>0</v>
       </c>
       <c r="J1102" s="6"/>
+      <c r="L1102" s="3" t="s">
+        <v>3292</v>
+      </c>
       <c r="M1102">
         <v>2</v>
       </c>
@@ -59561,6 +60164,9 @@
         <v>0</v>
       </c>
       <c r="J1103" s="6"/>
+      <c r="L1103" s="3" t="s">
+        <v>3293</v>
+      </c>
       <c r="M1103">
         <v>2</v>
       </c>
@@ -59606,6 +60212,9 @@
         <v>0</v>
       </c>
       <c r="J1104" s="6"/>
+      <c r="L1104" s="3" t="s">
+        <v>3294</v>
+      </c>
       <c r="M1104">
         <v>2</v>
       </c>
@@ -59651,6 +60260,9 @@
         <v>0</v>
       </c>
       <c r="J1105" s="6"/>
+      <c r="L1105" s="3" t="s">
+        <v>3295</v>
+      </c>
       <c r="M1105">
         <v>2</v>
       </c>
@@ -59696,6 +60308,9 @@
         <v>0</v>
       </c>
       <c r="J1106" s="6"/>
+      <c r="L1106" s="3" t="s">
+        <v>3296</v>
+      </c>
       <c r="M1106">
         <v>2</v>
       </c>
@@ -59741,6 +60356,9 @@
         <v>0</v>
       </c>
       <c r="J1107" s="6"/>
+      <c r="L1107" s="3" t="s">
+        <v>3297</v>
+      </c>
       <c r="M1107">
         <v>2</v>
       </c>
@@ -59786,6 +60404,9 @@
         <v>0</v>
       </c>
       <c r="J1108" s="6"/>
+      <c r="L1108" s="3" t="s">
+        <v>3298</v>
+      </c>
       <c r="M1108">
         <v>2</v>
       </c>
@@ -59831,6 +60452,9 @@
         <v>0</v>
       </c>
       <c r="J1109" s="6"/>
+      <c r="L1109" s="3" t="s">
+        <v>3299</v>
+      </c>
       <c r="M1109">
         <v>2</v>
       </c>
@@ -59876,6 +60500,9 @@
         <v>0</v>
       </c>
       <c r="J1110" s="6"/>
+      <c r="L1110" s="3" t="s">
+        <v>3300</v>
+      </c>
       <c r="M1110">
         <v>2</v>
       </c>
@@ -79726,9 +80353,112 @@
     <hyperlink ref="L1156" r:id="rId445" xr:uid="{4C737807-DA25-4B3C-BE08-C21879564672}"/>
     <hyperlink ref="L1157" r:id="rId446" xr:uid="{CF680533-4ABC-4AF1-9F1F-0B7829E3B08A}"/>
     <hyperlink ref="L1158" r:id="rId447" xr:uid="{C936BFF0-FD22-47E0-B892-5339F7C0D628}"/>
+    <hyperlink ref="L1018" r:id="rId448" xr:uid="{85A9131B-5685-4F66-A9AE-F88E00539263}"/>
+    <hyperlink ref="L1019" r:id="rId449" xr:uid="{FFDB8E7D-8448-41B7-B8D9-574230F80D22}"/>
+    <hyperlink ref="L1020" r:id="rId450" xr:uid="{407FCB5E-F7B8-458A-AA59-FF58FE33EFF2}"/>
+    <hyperlink ref="L1021" r:id="rId451" xr:uid="{7D6D60AB-D5F7-497F-8AB8-F8FBB2FFBFB0}"/>
+    <hyperlink ref="L1022:L1028" r:id="rId452" display="https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/bz__annual_mean__ug_m3__2019.json" xr:uid="{EE5EAAD9-E0E8-4D74-BC25-D631DF31423F}"/>
+    <hyperlink ref="L1022" r:id="rId453" xr:uid="{11588CAA-AE84-4313-AE8B-F0F7AC07E497}"/>
+    <hyperlink ref="L1023" r:id="rId454" xr:uid="{599FDDAA-7684-45EB-8D92-92CD220EB07E}"/>
+    <hyperlink ref="L1024" r:id="rId455" xr:uid="{7A91ACA0-C608-4C23-AD9B-5E81DFD76D4E}"/>
+    <hyperlink ref="L1025" r:id="rId456" xr:uid="{394CF502-435F-419B-ABEF-855604B512BA}"/>
+    <hyperlink ref="L1026" r:id="rId457" xr:uid="{CFD80DA1-C7BE-4F10-805C-25F385386C51}"/>
+    <hyperlink ref="L1027" r:id="rId458" xr:uid="{610ABCFF-4278-48A9-8382-D1BF24F836C0}"/>
+    <hyperlink ref="L1028" r:id="rId459" xr:uid="{6910793A-7FAE-49A0-B25F-537B9449E24B}"/>
+    <hyperlink ref="L1029:L1030" r:id="rId460" display="https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/bz__annual_mean__ug_m3__2019.json" xr:uid="{9D6EBF13-D381-4C67-8782-E91760BAE8A0}"/>
+    <hyperlink ref="L1029" r:id="rId461" xr:uid="{30FE3909-1222-46CC-B07E-D2442EEE8D50}"/>
+    <hyperlink ref="L1030" r:id="rId462" xr:uid="{A678B830-F250-4875-9F60-B6D13E095343}"/>
+    <hyperlink ref="L1031:L1032" r:id="rId463" display="https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/bz__annual_mean__ug_m3__2019.json" xr:uid="{CC3B9A7E-E372-459E-AE6A-7D0263E98CE5}"/>
+    <hyperlink ref="L1031" r:id="rId464" xr:uid="{2A6F2134-A328-4F79-A361-B26927210E5D}"/>
+    <hyperlink ref="L1032" r:id="rId465" xr:uid="{82AA3813-0653-4BEF-912A-6784B2B832D3}"/>
+    <hyperlink ref="L1033" r:id="rId466" xr:uid="{794F9753-A2D0-43B7-B13F-5F18E937DB6B}"/>
+    <hyperlink ref="L1034" r:id="rId467" xr:uid="{F65A3A07-83B7-404F-B557-1921BF9E3D7C}"/>
+    <hyperlink ref="L1035" r:id="rId468" xr:uid="{9EBCA301-F149-47E6-9BA7-8E4C3E4056D9}"/>
+    <hyperlink ref="L1036" r:id="rId469" xr:uid="{2DCBD81D-AD47-46BE-94FA-DAC719864412}"/>
+    <hyperlink ref="L1037:L1043" r:id="rId470" display="https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/no2__annual_mean__ug_m3__2019.json" xr:uid="{786091A8-46C0-46D3-AFA5-100E2A097C6E}"/>
+    <hyperlink ref="L1037" r:id="rId471" xr:uid="{8F4183DC-5003-435C-97A8-776D5CBBD281}"/>
+    <hyperlink ref="L1038" r:id="rId472" xr:uid="{32C36E27-8E82-4EEE-8C8B-DE96B59E0EE3}"/>
+    <hyperlink ref="L1039" r:id="rId473" xr:uid="{EBE9F38A-8A86-4A60-A621-F650B99C78E9}"/>
+    <hyperlink ref="L1040" r:id="rId474" xr:uid="{327BAF9C-4998-42B6-A04C-4CA76B0E33B0}"/>
+    <hyperlink ref="L1041" r:id="rId475" xr:uid="{B65AE598-CF59-4D7A-9A99-CE077F2F8578}"/>
+    <hyperlink ref="L1042" r:id="rId476" xr:uid="{0FDB2EDD-80D2-4D0F-9C46-B5F3027580A3}"/>
+    <hyperlink ref="L1043" r:id="rId477" xr:uid="{BA717DC7-5CB2-4B75-8AF1-6D2F12816342}"/>
+    <hyperlink ref="L1044:L1045" r:id="rId478" display="https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/no2__annual_mean__ug_m3__2019.json" xr:uid="{5F8285EC-E7E9-4D6D-85FA-028031A19235}"/>
+    <hyperlink ref="L1044" r:id="rId479" xr:uid="{1AC75627-89E4-4F6B-8C77-21EF99664C3F}"/>
+    <hyperlink ref="L1045" r:id="rId480" xr:uid="{0A6B3F44-E3EC-4848-AD11-8C2AE2F8CC63}"/>
+    <hyperlink ref="L1046" r:id="rId481" xr:uid="{2AD4BFCD-F484-4234-89EA-C38B1622829F}"/>
+    <hyperlink ref="L1047" r:id="rId482" xr:uid="{BBD37B84-6F8B-4379-841C-A9638C23DAD1}"/>
+    <hyperlink ref="L1048" r:id="rId483" xr:uid="{6842A1D5-36E9-41AC-BABB-59D170A5ECA7}"/>
+    <hyperlink ref="L1049" r:id="rId484" xr:uid="{5B844D9A-A5DB-4ADF-82B1-08E8D86A63AA}"/>
+    <hyperlink ref="L1050" r:id="rId485" xr:uid="{C3B3AC69-894A-44DC-B4B5-CE50C4E3A23E}"/>
+    <hyperlink ref="L1051" r:id="rId486" xr:uid="{52834128-7E33-4EC4-90C2-51970485CD54}"/>
+    <hyperlink ref="L1052" r:id="rId487" xr:uid="{B25D4069-9248-4FE4-9374-BD7EB5B9D2B1}"/>
+    <hyperlink ref="L1053" r:id="rId488" xr:uid="{5EE1E688-0519-4484-8D67-CE819FD710F7}"/>
+    <hyperlink ref="L1054" r:id="rId489" xr:uid="{6799419C-DBBB-48D8-B1C0-84E22C5ECFD7}"/>
+    <hyperlink ref="L1055" r:id="rId490" xr:uid="{C46E2A92-79E2-4DAD-B0C6-A7437DCD2562}"/>
+    <hyperlink ref="L1056" r:id="rId491" xr:uid="{5C2BBE2E-AAF7-4C58-8444-4FB22846ABDB}"/>
+    <hyperlink ref="L1057" r:id="rId492" xr:uid="{0BE1D659-C84A-401F-A9B6-18064BF9C049}"/>
+    <hyperlink ref="L1058" r:id="rId493" xr:uid="{AB0A5D1B-129A-4656-AA8A-16C9ED7853D0}"/>
+    <hyperlink ref="L1059" r:id="rId494" xr:uid="{7D3FF192-8C44-47F4-9877-1D1F8A769EAC}"/>
+    <hyperlink ref="L1060:L1061" r:id="rId495" display="https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/dgt_120__2022.json" xr:uid="{A5612EE1-5A69-405E-A095-2A7F21480433}"/>
+    <hyperlink ref="L1060" r:id="rId496" xr:uid="{D912D51A-19C0-4ED0-A352-B396D744541E}"/>
+    <hyperlink ref="L1061" r:id="rId497" xr:uid="{17D0AEA5-4458-4129-B962-7F2F825A293A}"/>
+    <hyperlink ref="L1062" r:id="rId498" xr:uid="{A2166901-E5BD-4EC2-B11F-9924B8A8A854}"/>
+    <hyperlink ref="L1063:L1067" r:id="rId499" display="https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/dgt_120__2019.json" xr:uid="{634B0DE9-1685-4B7E-A8F9-F418159FEE38}"/>
+    <hyperlink ref="L1063" r:id="rId500" xr:uid="{42DCC152-1EFF-4C84-B2D6-1E890299B126}"/>
+    <hyperlink ref="L1064" r:id="rId501" xr:uid="{AD4F091C-FC4B-402A-BE71-153611DB887F}"/>
+    <hyperlink ref="L1065" r:id="rId502" xr:uid="{A238315C-A63D-436A-BC23-14B881A8EFE6}"/>
+    <hyperlink ref="L1066" r:id="rId503" xr:uid="{940BB13F-28F8-4BAD-9EF7-B170307C33F1}"/>
+    <hyperlink ref="L1067" r:id="rId504" xr:uid="{F5D534C1-3C36-4505-BEBE-EE3CA5DBBD3F}"/>
+    <hyperlink ref="L1068:L1070" r:id="rId505" display="https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/dgt_120__2019.json" xr:uid="{2C235762-42FD-46AB-A15B-8A758808E074}"/>
+    <hyperlink ref="L1068" r:id="rId506" xr:uid="{6A636136-01E6-4A27-8427-2B8A02EAF8E1}"/>
+    <hyperlink ref="L1069" r:id="rId507" xr:uid="{142DB99F-2B8C-4D04-B4F1-59B094CB000A}"/>
+    <hyperlink ref="L1070" r:id="rId508" xr:uid="{98B44F81-3257-44E9-93EF-2D2680FA9B3F}"/>
+    <hyperlink ref="L1071" r:id="rId509" xr:uid="{F757E6D9-A83F-44BF-866D-E97914A0EEF1}"/>
+    <hyperlink ref="L1072" r:id="rId510" xr:uid="{B7D236C4-CF76-4D9D-8B10-A4537334B2F1}"/>
+    <hyperlink ref="L1073:L1075" r:id="rId511" display="https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm25__annual_mean__ug_m3__2022_g.json" xr:uid="{34FDA581-4BE9-49A9-86AC-29340E2AD4FC}"/>
+    <hyperlink ref="L1073" r:id="rId512" xr:uid="{467FFD2A-0E33-4ABA-A371-4AB2E2D36928}"/>
+    <hyperlink ref="L1074" r:id="rId513" xr:uid="{CF3F3CA1-D8EF-4553-A7D3-38BD4A5CED26}"/>
+    <hyperlink ref="L1075" r:id="rId514" xr:uid="{2E3E4A4D-B041-4900-863F-889B3B496BBB}"/>
+    <hyperlink ref="L1076:L1082" r:id="rId515" display="https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm25__annual_mean__ug_m3__2022_g.json" xr:uid="{D84A3343-37F7-4E63-AED2-FCC9826E5414}"/>
+    <hyperlink ref="L1076" r:id="rId516" xr:uid="{CD9226FC-CCDB-4E10-AD81-EC70F1B66AEB}"/>
+    <hyperlink ref="L1077" r:id="rId517" xr:uid="{6EDE82E7-6307-45A1-89C1-DA43099D65FA}"/>
+    <hyperlink ref="L1078" r:id="rId518" xr:uid="{D0FCA14E-C91D-4152-8401-3958F74B0B87}"/>
+    <hyperlink ref="L1079" r:id="rId519" xr:uid="{0134FAB6-97AD-4F55-8977-9C308F82728B}"/>
+    <hyperlink ref="L1080" r:id="rId520" xr:uid="{F14A7EF9-9F16-463B-898D-E472DEB26252}"/>
+    <hyperlink ref="L1082" r:id="rId521" xr:uid="{102C6100-0479-4C7D-A0B0-153497B43490}"/>
+    <hyperlink ref="L1083:L1084" r:id="rId522" display="https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/pm25__annual_mean__ug_m3__2022_g.json" xr:uid="{5679949B-8FDA-4151-B4B8-6B88F85CA6ED}"/>
+    <hyperlink ref="L1083" r:id="rId523" xr:uid="{AD625A51-2630-4F28-A865-A633B39BA3EF}"/>
+    <hyperlink ref="L1084" r:id="rId524" xr:uid="{FB2C70E0-B553-4430-9F1B-3F16E11E6620}"/>
+    <hyperlink ref="L1085" r:id="rId525" xr:uid="{25885C4B-DDF7-4C70-86D3-B661FC0B9DDE}"/>
+    <hyperlink ref="L1086" r:id="rId526" xr:uid="{05BE2495-501F-40B6-903E-76C754CBFB2D}"/>
+    <hyperlink ref="L1087" r:id="rId527" xr:uid="{AC7022D2-1D7A-4809-B08A-E04C8728D455}"/>
+    <hyperlink ref="L1088" r:id="rId528" xr:uid="{AE7ED104-43A5-4E9C-9FAC-AB5C9B0F282C}"/>
+    <hyperlink ref="L1089" r:id="rId529" xr:uid="{AA81A0A3-AB0B-4966-90A8-C1E5E7CF6FDC}"/>
+    <hyperlink ref="L1090" r:id="rId530" xr:uid="{12DF25B9-5061-4991-9983-7C22A4585FCF}"/>
+    <hyperlink ref="L1091" r:id="rId531" xr:uid="{92E3397B-2C32-4D0C-87CA-8FCAAB9E648E}"/>
+    <hyperlink ref="L1092" r:id="rId532" xr:uid="{6DF878FC-48D0-4F5C-BBBB-F13B3DBECBC9}"/>
+    <hyperlink ref="L1093" r:id="rId533" xr:uid="{6DFB5BF9-BD00-4915-ACA9-D2C3FA96FF1B}"/>
+    <hyperlink ref="L1094" r:id="rId534" xr:uid="{180F5927-0FB7-4F96-ADAC-799B08A16116}"/>
+    <hyperlink ref="L1095" r:id="rId535" xr:uid="{E264D8FB-9808-4B94-9903-732C2582D462}"/>
+    <hyperlink ref="L1096" r:id="rId536" xr:uid="{C9A0B431-D3C8-4633-A6AA-23793FB626AF}"/>
+    <hyperlink ref="L1097" r:id="rId537" xr:uid="{E229DE6F-F669-48EA-A941-887D2A8598DE}"/>
+    <hyperlink ref="L1098" r:id="rId538" xr:uid="{1B96A0A3-7FAF-4F7E-9ABB-6541AFE105EA}"/>
+    <hyperlink ref="L1099" r:id="rId539" xr:uid="{EF5701F3-C866-4F17-9579-AB7E0A801BD3}"/>
+    <hyperlink ref="L1100" r:id="rId540" xr:uid="{DD46443B-1D37-497B-AF17-921EEBF6D131}"/>
+    <hyperlink ref="L1101" r:id="rId541" xr:uid="{2418AE7C-D9E2-4B53-B8E8-00A491BD6B24}"/>
+    <hyperlink ref="L1102" r:id="rId542" xr:uid="{80531937-158B-4D00-8E5D-CFA976C15507}"/>
+    <hyperlink ref="L1103" r:id="rId543" xr:uid="{75720B30-AF9A-48E1-9AB7-0997661F0FA2}"/>
+    <hyperlink ref="L1104" r:id="rId544" xr:uid="{7E3A8FDB-C601-4A66-B837-10A7361BA702}"/>
+    <hyperlink ref="L1105" r:id="rId545" xr:uid="{BF518131-581B-4316-B777-487A583CEFC9}"/>
+    <hyperlink ref="L1106" r:id="rId546" xr:uid="{21150F5A-3051-413A-9A15-92361F513FB5}"/>
+    <hyperlink ref="L1107" r:id="rId547" xr:uid="{643ABB3E-A671-475F-BA65-2247B7CFBF4A}"/>
+    <hyperlink ref="L1108" r:id="rId548" xr:uid="{156E5320-324A-46A9-83F8-B4EFDEECD6C8}"/>
+    <hyperlink ref="L1109" r:id="rId549" xr:uid="{665C61A8-134F-442F-98D5-81FFD9A3B965}"/>
+    <hyperlink ref="L1110" r:id="rId550" xr:uid="{9372FBA2-CD81-4F9B-B049-5FD85AD034A7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId448"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId551"/>
 </worksheet>
 </file>
 

--- a/pages/apps/uprn-service/config.xlsx
+++ b/pages/apps/uprn-service/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NDSH\GitHub\dsh-content\pages\apps\uprn-service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82EC4F1E-F6BB-44F4-9C2E-4936F42FDC08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA96BF9-5874-49A0-8939-464E075D85B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="388" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="388" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="folders" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6591" uniqueCount="3301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6599" uniqueCount="3309">
   <si>
     <t>DbId</t>
   </si>
@@ -9944,6 +9944,30 @@
   </si>
   <si>
     <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/ModelledBackgroundPollution/so2__annual_mean__ug_m3__2010.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/Noise /Level3/EN_Environmental_Noise_Directive_Noise_Mapping_Agglomerations_Round_3.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/Noise /Level3/EN_Road_Noise_Lnight_Round_3.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/Noise /Level3/EN_Road_Noise_Lden_Round_3.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/Noise /Level3/EN_Road_Noise_LAeq_16h_Round_3.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/Noise /Level3/EN_Rail_Noise_Lnight_Round_3.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/Noise /Level3/EN_Rail_Noise_Lden_Round_3.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/Noise /Level3/EN_Rail_Noise_LAeq_16h_Round_3.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/Noise /Level3/EN_Noise_Action_Planning_Important_Areas_Round_3.json</t>
   </si>
 </sst>
 </file>
@@ -10564,6 +10588,9 @@
       <c r="G5">
         <v>3000</v>
       </c>
+      <c r="H5" s="3" t="s">
+        <v>3308</v>
+      </c>
       <c r="I5">
         <v>2</v>
       </c>
@@ -10835,6 +10862,7 @@
     <hyperlink ref="H7" r:id="rId2" xr:uid="{D75E7FAE-D953-4BAD-9FB5-353B5789F8AB}"/>
     <hyperlink ref="H8" r:id="rId3" xr:uid="{B1632C55-A38E-4D56-A2E2-F9D7C9F4331A}"/>
     <hyperlink ref="H9" r:id="rId4" xr:uid="{8C4ADDA5-96A2-4CD2-9BE8-8E08E00E0EE1}"/>
+    <hyperlink ref="H5" r:id="rId5" xr:uid="{FF63FA53-105B-4DCF-9427-D386BFA3F0E8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -12019,6 +12047,7 @@
       <c r="M21">
         <v>2006</v>
       </c>
+      <c r="O21" s="3"/>
       <c r="P21">
         <v>2</v>
       </c>
@@ -12072,6 +12101,9 @@
       <c r="M22">
         <v>3001</v>
       </c>
+      <c r="O22" s="3" t="s">
+        <v>3302</v>
+      </c>
       <c r="P22">
         <v>2</v>
       </c>
@@ -12125,6 +12157,9 @@
       <c r="M23">
         <v>3002</v>
       </c>
+      <c r="O23" s="3" t="s">
+        <v>3303</v>
+      </c>
       <c r="P23">
         <v>2</v>
       </c>
@@ -12178,6 +12213,9 @@
       <c r="M24">
         <v>3003</v>
       </c>
+      <c r="O24" s="3" t="s">
+        <v>3304</v>
+      </c>
       <c r="P24">
         <v>2</v>
       </c>
@@ -12231,6 +12269,9 @@
       <c r="M25">
         <v>3004</v>
       </c>
+      <c r="O25" s="3" t="s">
+        <v>3305</v>
+      </c>
       <c r="P25">
         <v>2</v>
       </c>
@@ -12284,6 +12325,9 @@
       <c r="M26">
         <v>3005</v>
       </c>
+      <c r="O26" s="3" t="s">
+        <v>3306</v>
+      </c>
       <c r="P26">
         <v>2</v>
       </c>
@@ -12337,6 +12381,9 @@
       <c r="M27">
         <v>3006</v>
       </c>
+      <c r="O27" s="3" t="s">
+        <v>3307</v>
+      </c>
       <c r="P27">
         <v>2</v>
       </c>
@@ -12390,6 +12437,9 @@
       <c r="M28">
         <v>3007</v>
       </c>
+      <c r="O28" s="3" t="s">
+        <v>3301</v>
+      </c>
       <c r="P28">
         <v>2</v>
       </c>
@@ -12443,6 +12493,7 @@
       <c r="M29">
         <v>4001</v>
       </c>
+      <c r="O29" s="3"/>
       <c r="P29">
         <v>2</v>
       </c>
@@ -14673,6 +14724,12 @@
     <hyperlink ref="O32" r:id="rId39" xr:uid="{B0A928E1-5A9D-4904-925C-B849C701CBE6}"/>
     <hyperlink ref="O31" r:id="rId40" xr:uid="{DE66E62C-23D8-409B-8828-A2B1F7104694}"/>
     <hyperlink ref="O30" r:id="rId41" xr:uid="{7F69EBA1-2661-4784-B19E-BB4CCA00E309}"/>
+    <hyperlink ref="O28" r:id="rId42" xr:uid="{CF6A1E08-AF38-4E47-BDD3-65A0F83099E2}"/>
+    <hyperlink ref="O23" r:id="rId43" xr:uid="{AB2AEF75-2B89-4336-A0E7-2603A34E2C13}"/>
+    <hyperlink ref="O24" r:id="rId44" xr:uid="{64F05A85-03DC-45CF-8143-21651CEB6A98}"/>
+    <hyperlink ref="O25" r:id="rId45" xr:uid="{E5D04D95-49C3-477F-A7E3-1A8B51774504}"/>
+    <hyperlink ref="O26" r:id="rId46" xr:uid="{2FED63F0-811E-4A6F-9493-69C015A2AC1D}"/>
+    <hyperlink ref="O27" r:id="rId47" xr:uid="{72F2FDFB-8D42-449F-BDA1-2EF6464AB23C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pages/apps/uprn-service/config.xlsx
+++ b/pages/apps/uprn-service/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NDSH\GitHub\dsh-content\pages\apps\uprn-service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA96BF9-5874-49A0-8939-464E075D85B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A5F052-D4F1-4D37-AAE6-C2AB9E342E82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="388" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="388" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="folders" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6599" uniqueCount="3309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6605" uniqueCount="3315">
   <si>
     <t>DbId</t>
   </si>
@@ -9968,6 +9968,24 @@
   </si>
   <si>
     <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/Noise /Level3/EN_Noise_Action_Planning_Important_Areas_Round_3.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/EN_Grid_Heat.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/EN_LSOA_2011_BFC_V3_2022_CJ.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/WA_LSOA_2011_BFC_V3_2022_CJ.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/EN_MSOA_2011_SHVI_CJ.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/UK_Grid_UKCP18_CJ.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/UK_LSOA_2011_Flood_Data_CJ.json</t>
   </si>
 </sst>
 </file>
@@ -11782,6 +11800,9 @@
       <c r="M16">
         <v>2001</v>
       </c>
+      <c r="O16" s="3" t="s">
+        <v>3309</v>
+      </c>
       <c r="P16">
         <v>2</v>
       </c>
@@ -11835,6 +11856,9 @@
       <c r="M17">
         <v>2002</v>
       </c>
+      <c r="O17" s="3" t="s">
+        <v>3310</v>
+      </c>
       <c r="P17">
         <v>2</v>
       </c>
@@ -11888,6 +11912,9 @@
       <c r="M18">
         <v>2003</v>
       </c>
+      <c r="O18" s="3" t="s">
+        <v>3312</v>
+      </c>
       <c r="P18">
         <v>2</v>
       </c>
@@ -11941,6 +11968,9 @@
       <c r="M19">
         <v>2004</v>
       </c>
+      <c r="O19" s="3" t="s">
+        <v>3313</v>
+      </c>
       <c r="P19">
         <v>2</v>
       </c>
@@ -11994,6 +12024,9 @@
       <c r="M20">
         <v>2005</v>
       </c>
+      <c r="O20" s="3" t="s">
+        <v>3314</v>
+      </c>
       <c r="P20">
         <v>2</v>
       </c>
@@ -12047,7 +12080,9 @@
       <c r="M21">
         <v>2006</v>
       </c>
-      <c r="O21" s="3"/>
+      <c r="O21" s="3" t="s">
+        <v>3311</v>
+      </c>
       <c r="P21">
         <v>2</v>
       </c>
@@ -14730,6 +14765,12 @@
     <hyperlink ref="O25" r:id="rId45" xr:uid="{E5D04D95-49C3-477F-A7E3-1A8B51774504}"/>
     <hyperlink ref="O26" r:id="rId46" xr:uid="{2FED63F0-811E-4A6F-9493-69C015A2AC1D}"/>
     <hyperlink ref="O27" r:id="rId47" xr:uid="{72F2FDFB-8D42-449F-BDA1-2EF6464AB23C}"/>
+    <hyperlink ref="O16" r:id="rId48" xr:uid="{3817A9EF-DEC2-42F4-BC65-6C8B01E3147F}"/>
+    <hyperlink ref="O17" r:id="rId49" xr:uid="{0BB7BCDC-3B19-4AD9-ABC8-5F927DB382BD}"/>
+    <hyperlink ref="O18" r:id="rId50" xr:uid="{D43D9927-3B4E-405E-8C05-78E889C82752}"/>
+    <hyperlink ref="O19" r:id="rId51" xr:uid="{D537EB9A-51DD-48F7-9457-FD32A5E9864B}"/>
+    <hyperlink ref="O20" r:id="rId52" xr:uid="{521DDBB9-66B8-4124-AF2F-E5E8F789B155}"/>
+    <hyperlink ref="O21" r:id="rId53" xr:uid="{74B2F229-A063-45D4-8571-63C642C1E2BC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pages/apps/uprn-service/config.xlsx
+++ b/pages/apps/uprn-service/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NDSH\GitHub\dsh-content\dev\pages\apps\uprn-service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE60840-B9A9-4942-B697-92D766CE6589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43D2EFF0-C3AF-4CD9-A13F-86E15B06AE01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="388" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="388" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="folders" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6606" uniqueCount="3316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6635" uniqueCount="3345">
   <si>
     <t>DbId</t>
   </si>
@@ -9989,6 +9989,93 @@
   </si>
   <si>
     <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-101.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-102.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-103.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-104.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-105.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-106.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-107.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-108.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-109.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-110.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-111.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-112.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-113.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-114.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-115.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-116.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-117.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-118.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-119.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-120.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-122.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-123.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-130.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-131.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-132.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-201.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-202.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-203.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-204.json</t>
   </si>
 </sst>
 </file>
@@ -23987,6 +24074,9 @@
         <v>0</v>
       </c>
       <c r="J231" s="6"/>
+      <c r="L231" s="3" t="s">
+        <v>3341</v>
+      </c>
       <c r="M231">
         <v>2</v>
       </c>
@@ -28187,6 +28277,9 @@
         <v>0</v>
       </c>
       <c r="J336" s="6"/>
+      <c r="L336" s="3" t="s">
+        <v>3343</v>
+      </c>
       <c r="M336">
         <v>2</v>
       </c>
@@ -46947,6 +47040,9 @@
         <v>0</v>
       </c>
       <c r="J787" s="6"/>
+      <c r="L787" s="3" t="s">
+        <v>3327</v>
+      </c>
       <c r="M787">
         <v>2</v>
       </c>
@@ -46987,6 +47083,9 @@
         <v>0</v>
       </c>
       <c r="J788" s="6"/>
+      <c r="L788" s="3" t="s">
+        <v>3338</v>
+      </c>
       <c r="M788">
         <v>2</v>
       </c>
@@ -47027,6 +47126,7 @@
         <v>0</v>
       </c>
       <c r="J789" s="6"/>
+      <c r="L789" s="3"/>
       <c r="M789">
         <v>2</v>
       </c>
@@ -47067,6 +47167,7 @@
         <v>0</v>
       </c>
       <c r="J790" s="6"/>
+      <c r="L790" s="3"/>
       <c r="M790">
         <v>2</v>
       </c>
@@ -47107,6 +47208,9 @@
         <v>0</v>
       </c>
       <c r="J791" s="6"/>
+      <c r="L791" s="3" t="s">
+        <v>3325</v>
+      </c>
       <c r="M791">
         <v>2</v>
       </c>
@@ -47267,6 +47371,9 @@
         <v>0</v>
       </c>
       <c r="J795" s="6"/>
+      <c r="L795" s="3" t="s">
+        <v>3337</v>
+      </c>
       <c r="M795">
         <v>2</v>
       </c>
@@ -47307,6 +47414,7 @@
         <v>0</v>
       </c>
       <c r="J796" s="6"/>
+      <c r="L796" s="3"/>
       <c r="M796">
         <v>2</v>
       </c>
@@ -47347,6 +47455,9 @@
         <v>0</v>
       </c>
       <c r="J797" s="6"/>
+      <c r="L797" s="3" t="s">
+        <v>3336</v>
+      </c>
       <c r="M797">
         <v>2</v>
       </c>
@@ -47387,6 +47498,9 @@
         <v>0</v>
       </c>
       <c r="J798" s="6"/>
+      <c r="L798" s="3" t="s">
+        <v>3340</v>
+      </c>
       <c r="M798">
         <v>2</v>
       </c>
@@ -47427,6 +47541,9 @@
         <v>0</v>
       </c>
       <c r="J799" s="6"/>
+      <c r="L799" s="3" t="s">
+        <v>3320</v>
+      </c>
       <c r="M799">
         <v>2</v>
       </c>
@@ -47467,6 +47584,9 @@
         <v>0</v>
       </c>
       <c r="J800" s="6"/>
+      <c r="L800" s="3" t="s">
+        <v>3323</v>
+      </c>
       <c r="M800">
         <v>2</v>
       </c>
@@ -47507,6 +47627,9 @@
         <v>0</v>
       </c>
       <c r="J801" s="6"/>
+      <c r="L801" s="3" t="s">
+        <v>3324</v>
+      </c>
       <c r="M801">
         <v>2</v>
       </c>
@@ -47547,6 +47670,7 @@
         <v>0</v>
       </c>
       <c r="J802" s="6"/>
+      <c r="L802" s="3"/>
       <c r="M802">
         <v>2</v>
       </c>
@@ -47587,6 +47711,9 @@
         <v>0</v>
       </c>
       <c r="J803" s="6"/>
+      <c r="L803" s="3" t="s">
+        <v>3316</v>
+      </c>
       <c r="M803">
         <v>2</v>
       </c>
@@ -47827,6 +47954,9 @@
         <v>0</v>
       </c>
       <c r="J809" s="6"/>
+      <c r="L809" s="3" t="s">
+        <v>3334</v>
+      </c>
       <c r="M809">
         <v>2</v>
       </c>
@@ -47867,6 +47997,9 @@
         <v>0</v>
       </c>
       <c r="J810" s="6"/>
+      <c r="L810" s="3" t="s">
+        <v>3318</v>
+      </c>
       <c r="M810">
         <v>2</v>
       </c>
@@ -47907,6 +48040,9 @@
         <v>0</v>
       </c>
       <c r="J811" s="6"/>
+      <c r="L811" s="3" t="s">
+        <v>3319</v>
+      </c>
       <c r="M811">
         <v>2</v>
       </c>
@@ -47947,6 +48083,9 @@
         <v>0</v>
       </c>
       <c r="J812" s="6"/>
+      <c r="L812" s="3" t="s">
+        <v>3333</v>
+      </c>
       <c r="M812">
         <v>2</v>
       </c>
@@ -47987,6 +48126,9 @@
         <v>0</v>
       </c>
       <c r="J813" s="6"/>
+      <c r="L813" s="3" t="s">
+        <v>3330</v>
+      </c>
       <c r="M813">
         <v>2</v>
       </c>
@@ -48627,6 +48769,9 @@
         <v>0</v>
       </c>
       <c r="J829" s="6"/>
+      <c r="L829" s="3" t="s">
+        <v>3339</v>
+      </c>
       <c r="M829">
         <v>2</v>
       </c>
@@ -48667,6 +48812,9 @@
         <v>0</v>
       </c>
       <c r="J830" s="6"/>
+      <c r="L830" s="3" t="s">
+        <v>3331</v>
+      </c>
       <c r="M830">
         <v>2</v>
       </c>
@@ -48707,6 +48855,9 @@
         <v>0</v>
       </c>
       <c r="J831" s="6"/>
+      <c r="L831" s="3" t="s">
+        <v>3322</v>
+      </c>
       <c r="M831">
         <v>2</v>
       </c>
@@ -48747,6 +48898,7 @@
         <v>0</v>
       </c>
       <c r="J832" s="6"/>
+      <c r="L832" s="3"/>
       <c r="M832">
         <v>2</v>
       </c>
@@ -48787,6 +48939,9 @@
         <v>0</v>
       </c>
       <c r="J833" s="6"/>
+      <c r="L833" s="3" t="s">
+        <v>3335</v>
+      </c>
       <c r="M833">
         <v>2</v>
       </c>
@@ -48827,6 +48982,7 @@
         <v>0</v>
       </c>
       <c r="J834" s="6"/>
+      <c r="L834" s="3"/>
       <c r="M834">
         <v>2</v>
       </c>
@@ -48867,6 +49023,7 @@
         <v>0</v>
       </c>
       <c r="J835" s="6"/>
+      <c r="L835" s="3"/>
       <c r="M835">
         <v>2</v>
       </c>
@@ -48907,6 +49064,9 @@
         <v>0</v>
       </c>
       <c r="J836" s="6"/>
+      <c r="L836" s="3" t="s">
+        <v>3321</v>
+      </c>
       <c r="M836">
         <v>2</v>
       </c>
@@ -48947,6 +49107,9 @@
         <v>0</v>
       </c>
       <c r="J837" s="6"/>
+      <c r="L837" s="3" t="s">
+        <v>3326</v>
+      </c>
       <c r="M837">
         <v>2</v>
       </c>
@@ -48987,6 +49150,9 @@
         <v>0</v>
       </c>
       <c r="J838" s="6"/>
+      <c r="L838" s="3" t="s">
+        <v>3328</v>
+      </c>
       <c r="M838">
         <v>2</v>
       </c>
@@ -49027,6 +49193,9 @@
         <v>0</v>
       </c>
       <c r="J839" s="6"/>
+      <c r="L839" s="3" t="s">
+        <v>3332</v>
+      </c>
       <c r="M839">
         <v>2</v>
       </c>
@@ -49067,6 +49236,7 @@
         <v>0</v>
       </c>
       <c r="J840" s="6"/>
+      <c r="L840" s="3"/>
       <c r="M840">
         <v>2</v>
       </c>
@@ -49107,6 +49277,9 @@
         <v>0</v>
       </c>
       <c r="J841" s="6"/>
+      <c r="L841" s="3" t="s">
+        <v>3329</v>
+      </c>
       <c r="M841">
         <v>2</v>
       </c>
@@ -49147,6 +49320,9 @@
         <v>0</v>
       </c>
       <c r="J842" s="6"/>
+      <c r="L842" s="3" t="s">
+        <v>3317</v>
+      </c>
       <c r="M842">
         <v>2</v>
       </c>
@@ -49667,6 +49843,9 @@
         <v>0</v>
       </c>
       <c r="J855" s="6"/>
+      <c r="L855" s="3" t="s">
+        <v>3342</v>
+      </c>
       <c r="M855">
         <v>2</v>
       </c>
@@ -53787,6 +53966,9 @@
         <v>0</v>
       </c>
       <c r="J958" s="6"/>
+      <c r="L958" s="3" t="s">
+        <v>3344</v>
+      </c>
       <c r="M958">
         <v>2</v>
       </c>
@@ -80562,9 +80744,38 @@
     <hyperlink ref="L1108" r:id="rId548" xr:uid="{156E5320-324A-46A9-83F8-B4EFDEECD6C8}"/>
     <hyperlink ref="L1109" r:id="rId549" xr:uid="{665C61A8-134F-442F-98D5-81FFD9A3B965}"/>
     <hyperlink ref="L1110" r:id="rId550" xr:uid="{9372FBA2-CD81-4F9B-B049-5FD85AD034A7}"/>
+    <hyperlink ref="L803" r:id="rId551" xr:uid="{E7A4C19A-12C2-42A2-8673-C3768AB93009}"/>
+    <hyperlink ref="L842" r:id="rId552" xr:uid="{B8D06407-52A3-45EC-A1F9-1DDB45EC101B}"/>
+    <hyperlink ref="L810" r:id="rId553" xr:uid="{F5708804-9705-46D4-801C-EBD036F5B411}"/>
+    <hyperlink ref="L811" r:id="rId554" xr:uid="{0D29EF0B-288E-49B1-A739-6002748759CF}"/>
+    <hyperlink ref="L799" r:id="rId555" xr:uid="{C51CC765-CEBD-4790-930E-BDA5930D873C}"/>
+    <hyperlink ref="L836" r:id="rId556" xr:uid="{FF818180-4BE8-43AD-9049-CEF4C8939E30}"/>
+    <hyperlink ref="L831" r:id="rId557" xr:uid="{37EFB9A7-9147-4734-932A-83C2E1C2B9EF}"/>
+    <hyperlink ref="L800" r:id="rId558" xr:uid="{5DF17578-F967-4E0A-A51F-BE78DB0DF4B2}"/>
+    <hyperlink ref="L801" r:id="rId559" xr:uid="{DDE2A222-0F0C-419E-B63C-BDBEF7F8CFFA}"/>
+    <hyperlink ref="L791" r:id="rId560" xr:uid="{754831BB-AFEC-4FE4-8452-E6FCE5C23A4C}"/>
+    <hyperlink ref="L837" r:id="rId561" xr:uid="{209779CC-9626-4546-B819-F9AFCB5083C2}"/>
+    <hyperlink ref="L787" r:id="rId562" xr:uid="{B699DB45-A67A-4A59-B809-DE414AB48D14}"/>
+    <hyperlink ref="L838" r:id="rId563" xr:uid="{8177588D-2302-429A-BB6A-86BE04DC90A6}"/>
+    <hyperlink ref="L841" r:id="rId564" xr:uid="{51CAE882-65BC-4394-8F1C-60E1E7C02EBB}"/>
+    <hyperlink ref="L813" r:id="rId565" xr:uid="{7BE4653C-D870-4126-AAA9-23C1DD74403D}"/>
+    <hyperlink ref="L830" r:id="rId566" xr:uid="{10E6B9B1-5D76-4184-8740-7EA70231C735}"/>
+    <hyperlink ref="L839" r:id="rId567" xr:uid="{696BFE12-510C-4CD3-9E47-D0481FD901B7}"/>
+    <hyperlink ref="L812" r:id="rId568" xr:uid="{5ED1529A-5F4E-4308-ACAF-7642BC1D2868}"/>
+    <hyperlink ref="L809" r:id="rId569" xr:uid="{38C05E39-F010-4D1A-8CAC-1699A9C2E280}"/>
+    <hyperlink ref="L833" r:id="rId570" xr:uid="{393D38E2-36D6-4C37-87D8-808AF1F52D0C}"/>
+    <hyperlink ref="L797" r:id="rId571" xr:uid="{F363A484-A9E6-4FD3-BB2F-1C8FA1B9D51E}"/>
+    <hyperlink ref="L795" r:id="rId572" xr:uid="{5F8BD157-A5B0-4DBE-93EA-4FB22CE4C48B}"/>
+    <hyperlink ref="L788" r:id="rId573" xr:uid="{9E44EAF8-5BED-4C0F-A89E-0B6ECD0F06A5}"/>
+    <hyperlink ref="L829" r:id="rId574" xr:uid="{039F1AB2-B467-43C7-A3E2-59F9C5AE09D9}"/>
+    <hyperlink ref="L798" r:id="rId575" xr:uid="{0ED5745A-50E4-49C0-ABDD-4DF7772E2247}"/>
+    <hyperlink ref="L231" r:id="rId576" xr:uid="{5A72733D-5117-4137-87AD-536B0CE04DFF}"/>
+    <hyperlink ref="L855" r:id="rId577" xr:uid="{0EFB5B1D-0695-4F20-8AE2-DE5269E5D19E}"/>
+    <hyperlink ref="L336" r:id="rId578" xr:uid="{D6D10C65-F36A-489A-8707-F63B4D121DEE}"/>
+    <hyperlink ref="L958" r:id="rId579" display="https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-203.json" xr:uid="{121C0C2E-817E-4E76-92E4-761664ADBCCC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId551"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId580"/>
 </worksheet>
 </file>
 

--- a/pages/apps/uprn-service/config.xlsx
+++ b/pages/apps/uprn-service/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NDSH\GitHub\dsh-content\dev\pages\apps\uprn-service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43D2EFF0-C3AF-4CD9-A13F-86E15B06AE01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA4BBED3-E913-4E5B-BEE5-C236757592E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="388" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="388" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="folders" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">datasets!$A$1:$T$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">variables!$A$1:$S$1515</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -9985,9 +9985,6 @@
     <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/Noise/Level3/EN_Environmental_Noise_Directive_Noise_Mapping_Agglomerations_Round_3.json</t>
   </si>
   <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/Noise/Level3/EN_Noise_Action_Planning_Important_Areas_Round_3.json</t>
-  </si>
-  <si>
     <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info.json</t>
   </si>
   <si>
@@ -10076,6 +10073,9 @@
   </si>
   <si>
     <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/info-204.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/DEFRA/Noise/Level3/info.json</t>
   </si>
 </sst>
 </file>
@@ -10671,7 +10671,7 @@
         <v>2000</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>3315</v>
+        <v>3314</v>
       </c>
       <c r="I4">
         <v>2</v>
@@ -10700,7 +10700,7 @@
         <v>3000</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>3314</v>
+        <v>3344</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -24075,7 +24075,7 @@
       </c>
       <c r="J231" s="6"/>
       <c r="L231" s="3" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
       <c r="M231">
         <v>2</v>
@@ -28278,7 +28278,7 @@
       </c>
       <c r="J336" s="6"/>
       <c r="L336" s="3" t="s">
-        <v>3343</v>
+        <v>3342</v>
       </c>
       <c r="M336">
         <v>2</v>
@@ -47041,7 +47041,7 @@
       </c>
       <c r="J787" s="6"/>
       <c r="L787" s="3" t="s">
-        <v>3327</v>
+        <v>3326</v>
       </c>
       <c r="M787">
         <v>2</v>
@@ -47084,7 +47084,7 @@
       </c>
       <c r="J788" s="6"/>
       <c r="L788" s="3" t="s">
-        <v>3338</v>
+        <v>3337</v>
       </c>
       <c r="M788">
         <v>2</v>
@@ -47209,7 +47209,7 @@
       </c>
       <c r="J791" s="6"/>
       <c r="L791" s="3" t="s">
-        <v>3325</v>
+        <v>3324</v>
       </c>
       <c r="M791">
         <v>2</v>
@@ -47372,7 +47372,7 @@
       </c>
       <c r="J795" s="6"/>
       <c r="L795" s="3" t="s">
-        <v>3337</v>
+        <v>3336</v>
       </c>
       <c r="M795">
         <v>2</v>
@@ -47456,7 +47456,7 @@
       </c>
       <c r="J797" s="6"/>
       <c r="L797" s="3" t="s">
-        <v>3336</v>
+        <v>3335</v>
       </c>
       <c r="M797">
         <v>2</v>
@@ -47499,7 +47499,7 @@
       </c>
       <c r="J798" s="6"/>
       <c r="L798" s="3" t="s">
-        <v>3340</v>
+        <v>3339</v>
       </c>
       <c r="M798">
         <v>2</v>
@@ -47542,7 +47542,7 @@
       </c>
       <c r="J799" s="6"/>
       <c r="L799" s="3" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="M799">
         <v>2</v>
@@ -47585,7 +47585,7 @@
       </c>
       <c r="J800" s="6"/>
       <c r="L800" s="3" t="s">
-        <v>3323</v>
+        <v>3322</v>
       </c>
       <c r="M800">
         <v>2</v>
@@ -47628,7 +47628,7 @@
       </c>
       <c r="J801" s="6"/>
       <c r="L801" s="3" t="s">
-        <v>3324</v>
+        <v>3323</v>
       </c>
       <c r="M801">
         <v>2</v>
@@ -47712,7 +47712,7 @@
       </c>
       <c r="J803" s="6"/>
       <c r="L803" s="3" t="s">
-        <v>3316</v>
+        <v>3315</v>
       </c>
       <c r="M803">
         <v>2</v>
@@ -47955,7 +47955,7 @@
       </c>
       <c r="J809" s="6"/>
       <c r="L809" s="3" t="s">
-        <v>3334</v>
+        <v>3333</v>
       </c>
       <c r="M809">
         <v>2</v>
@@ -47998,7 +47998,7 @@
       </c>
       <c r="J810" s="6"/>
       <c r="L810" s="3" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="M810">
         <v>2</v>
@@ -48041,7 +48041,7 @@
       </c>
       <c r="J811" s="6"/>
       <c r="L811" s="3" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="M811">
         <v>2</v>
@@ -48084,7 +48084,7 @@
       </c>
       <c r="J812" s="6"/>
       <c r="L812" s="3" t="s">
-        <v>3333</v>
+        <v>3332</v>
       </c>
       <c r="M812">
         <v>2</v>
@@ -48127,7 +48127,7 @@
       </c>
       <c r="J813" s="6"/>
       <c r="L813" s="3" t="s">
-        <v>3330</v>
+        <v>3329</v>
       </c>
       <c r="M813">
         <v>2</v>
@@ -48770,7 +48770,7 @@
       </c>
       <c r="J829" s="6"/>
       <c r="L829" s="3" t="s">
-        <v>3339</v>
+        <v>3338</v>
       </c>
       <c r="M829">
         <v>2</v>
@@ -48813,7 +48813,7 @@
       </c>
       <c r="J830" s="6"/>
       <c r="L830" s="3" t="s">
-        <v>3331</v>
+        <v>3330</v>
       </c>
       <c r="M830">
         <v>2</v>
@@ -48856,7 +48856,7 @@
       </c>
       <c r="J831" s="6"/>
       <c r="L831" s="3" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="M831">
         <v>2</v>
@@ -48940,7 +48940,7 @@
       </c>
       <c r="J833" s="6"/>
       <c r="L833" s="3" t="s">
-        <v>3335</v>
+        <v>3334</v>
       </c>
       <c r="M833">
         <v>2</v>
@@ -49065,7 +49065,7 @@
       </c>
       <c r="J836" s="6"/>
       <c r="L836" s="3" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="M836">
         <v>2</v>
@@ -49108,7 +49108,7 @@
       </c>
       <c r="J837" s="6"/>
       <c r="L837" s="3" t="s">
-        <v>3326</v>
+        <v>3325</v>
       </c>
       <c r="M837">
         <v>2</v>
@@ -49151,7 +49151,7 @@
       </c>
       <c r="J838" s="6"/>
       <c r="L838" s="3" t="s">
-        <v>3328</v>
+        <v>3327</v>
       </c>
       <c r="M838">
         <v>2</v>
@@ -49194,7 +49194,7 @@
       </c>
       <c r="J839" s="6"/>
       <c r="L839" s="3" t="s">
-        <v>3332</v>
+        <v>3331</v>
       </c>
       <c r="M839">
         <v>2</v>
@@ -49278,7 +49278,7 @@
       </c>
       <c r="J841" s="6"/>
       <c r="L841" s="3" t="s">
-        <v>3329</v>
+        <v>3328</v>
       </c>
       <c r="M841">
         <v>2</v>
@@ -49321,7 +49321,7 @@
       </c>
       <c r="J842" s="6"/>
       <c r="L842" s="3" t="s">
-        <v>3317</v>
+        <v>3316</v>
       </c>
       <c r="M842">
         <v>2</v>
@@ -49844,7 +49844,7 @@
       </c>
       <c r="J855" s="6"/>
       <c r="L855" s="3" t="s">
-        <v>3342</v>
+        <v>3341</v>
       </c>
       <c r="M855">
         <v>2</v>
@@ -53967,7 +53967,7 @@
       </c>
       <c r="J958" s="6"/>
       <c r="L958" s="3" t="s">
-        <v>3344</v>
+        <v>3343</v>
       </c>
       <c r="M958">
         <v>2</v>

--- a/pages/apps/uprn-service/config.xlsx
+++ b/pages/apps/uprn-service/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NDSH\GitHub\dsh-content\dev\pages\apps\uprn-service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E0CCFC3-2063-43A3-8B70-6E86C613614C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2303545A-85F1-4CB0-9ACE-771DAF2666CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="388" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="388" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="folders" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6639" uniqueCount="3349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6639" uniqueCount="3350">
   <si>
     <t>DbId</t>
   </si>
@@ -10088,6 +10088,9 @@
   </si>
   <si>
     <t>The field '% no. of care homes exposed to flooding' measures the percentage of care home facilities within a neighborhood that are physically located in areas identified as prone to flooding. Within the Climate Just framework, this metric serves as an indicator of enhanced exposure. It identifies institutional settings where highly sensitive populations (such as the elderly or those with chronic health conditions) are at direct risk of contact with floodwaters. The physical exposure of these buildings is a critical factor because it can severely undermine a community's ability to respond and recover, as the residents often rely on complex institutional care regimes and may have limited personal mobility during an emergency.</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/MetOffice/AQREAN/Annual/SL/daily_aqi_pm2p5_dry_aerosol/info.json</t>
   </si>
 </sst>
 </file>
@@ -13503,7 +13506,7 @@
         <v>7003</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>1853</v>
+        <v>3349</v>
       </c>
       <c r="P44">
         <v>2</v>

--- a/pages/apps/uprn-service/config.xlsx
+++ b/pages/apps/uprn-service/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NDSH\GitHub\dsh-content\dev\pages\apps\uprn-service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2303545A-85F1-4CB0-9ACE-771DAF2666CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C8C1CE2-BE9B-4E53-A41F-2A843AFD1520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="388" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="388" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="folders" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6639" uniqueCount="3350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6637" uniqueCount="3348">
   <si>
     <t>DbId</t>
   </si>
@@ -10079,12 +10079,6 @@
   </si>
   <si>
     <t>The field 'All pensioner households (%)' (internal field name AllPensioner_HH) represents the percentage of households within a neighborhood (LSOA, Data Zone, or SOA) where all residents are of pensionable age.This metric is a core indicator used to calculate the Neighbourhood Flood Vulnerability Index (NFVI). Within the Climate Just framework, it serves as a measure of sensitivity, identifying populations that may be more susceptible to negative health and welfare impacts during a flood event due to age-related biophysical characteristics</t>
-  </si>
-  <si>
-    <t>The field 'Recent arrivals to UK (% people with &lt;1 yr residency coming from outside UK)' (internal name ArrivalsInUK) represents the percentage of a neighborhood's population that has been resident in the UK for less than one year after arriving from a foreign country. Within the Climate Just framework, this metric is used as an indicator of social vulnerability. It identifies groups that may have a reduced ability to prepare for, respond to, and recover from flooding due to a lack of local knowledge, limited community networks, or unfamiliarity with how to access essential information and public services during an extreme weather event.</t>
-  </si>
-  <si>
-    <t>The field '% caravan or other mobile or temporary structures in all households' (internal name Caravan_HH) represents the percentage of households within a neighborhood (LSOA, Data Zone, or SOA) that reside in non-permanent dwellings. Within the Climate Just framework, this metric is used as an indicator of enhanced exposure related to housing characteristics. Because caravans and temporary structures are typically less resilient to the physical force of water than permanent brick-and-mortar buildings, this indicator identifies areas here the physical environment is likely to accentuate the severity of a flood event's impact on residents.</t>
   </si>
   <si>
     <t>The field '% no. of care homes exposed to flooding' measures the percentage of care home facilities within a neighborhood that are physically located in areas identified as prone to flooding. Within the Climate Just framework, this metric serves as an indicator of enhanced exposure. It identifies institutional settings where highly sensitive populations (such as the elderly or those with chronic health conditions) are at direct risk of contact with floodwaters. The physical exposure of these buildings is a critical factor because it can severely undermine a community's ability to respond and recover, as the residents often rely on complex institutional care regimes and may have limited personal mobility during an emergency.</t>
@@ -13506,7 +13500,7 @@
         <v>7003</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>3349</v>
+        <v>3347</v>
       </c>
       <c r="P44">
         <v>2</v>
@@ -47072,9 +47066,7 @@
       <c r="P787" t="b">
         <v>0</v>
       </c>
-      <c r="R787" t="s">
-        <v>3346</v>
-      </c>
+      <c r="R787"/>
     </row>
     <row r="788" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A788">
@@ -47117,9 +47109,7 @@
       <c r="P788" t="b">
         <v>0</v>
       </c>
-      <c r="R788" t="s">
-        <v>3347</v>
-      </c>
+      <c r="R788"/>
     </row>
     <row r="789" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A789">
@@ -47161,7 +47151,7 @@
         <v>0</v>
       </c>
       <c r="R789" t="s">
-        <v>3348</v>
+        <v>3346</v>
       </c>
     </row>
     <row r="790" spans="1:18" x14ac:dyDescent="0.3">

--- a/pages/apps/uprn-service/config.xlsx
+++ b/pages/apps/uprn-service/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NDSH\GitHub\dsh-content\dev\pages\apps\uprn-service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F129AA7B-BAB6-4325-B2AF-1D5607336F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{832DAB5F-559B-4301-8222-09AB1D2FEAE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="388" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11483,7 +11483,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:W65"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -11583,7 +11582,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -11642,7 +11641,7 @@
         <v>2274</v>
       </c>
     </row>
-    <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>101</v>
       </c>
@@ -11701,7 +11700,7 @@
         <v>2275</v>
       </c>
     </row>
-    <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>201</v>
       </c>
@@ -11760,7 +11759,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="5" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>301</v>
       </c>
@@ -11816,7 +11815,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="6" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>401</v>
       </c>
@@ -11872,7 +11871,7 @@
         <v>2278</v>
       </c>
     </row>
-    <row r="7" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>501</v>
       </c>
@@ -11928,7 +11927,7 @@
         <v>2279</v>
       </c>
     </row>
-    <row r="8" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>601</v>
       </c>
@@ -11984,7 +11983,7 @@
         <v>2280</v>
       </c>
     </row>
-    <row r="9" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>701</v>
       </c>
@@ -12037,7 +12036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>801</v>
       </c>
@@ -12090,7 +12089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>901</v>
       </c>
@@ -12143,7 +12142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>1001</v>
       </c>
@@ -12196,7 +12195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1101</v>
       </c>
@@ -12249,7 +12248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>1201</v>
       </c>
@@ -12302,7 +12301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A15" s="9">
         <v>1301</v>
       </c>
@@ -12358,7 +12357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1401</v>
       </c>
@@ -12414,7 +12413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1501</v>
       </c>
@@ -12470,7 +12469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>1601</v>
       </c>
@@ -12526,7 +12525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1701</v>
       </c>
@@ -12638,7 +12637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>1901</v>
       </c>
@@ -12694,7 +12693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2001</v>
       </c>
@@ -12750,7 +12749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2101</v>
       </c>
@@ -12806,7 +12805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>2201</v>
       </c>
@@ -12862,7 +12861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>2301</v>
       </c>
@@ -12918,7 +12917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2401</v>
       </c>
@@ -12974,7 +12973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2501</v>
       </c>
@@ -13030,7 +13029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>2601</v>
       </c>
@@ -13086,7 +13085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2701</v>
       </c>
@@ -13143,7 +13142,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="30" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>2801</v>
       </c>
@@ -13202,7 +13201,7 @@
         <v>2266</v>
       </c>
     </row>
-    <row r="31" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>2901</v>
       </c>
@@ -13261,7 +13260,7 @@
         <v>2267</v>
       </c>
     </row>
-    <row r="32" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>3001</v>
       </c>
@@ -13320,7 +13319,7 @@
         <v>2268</v>
       </c>
     </row>
-    <row r="33" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>3101</v>
       </c>
@@ -13379,7 +13378,7 @@
         <v>2269</v>
       </c>
     </row>
-    <row r="34" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>3201</v>
       </c>
@@ -13438,7 +13437,7 @@
         <v>2270</v>
       </c>
     </row>
-    <row r="35" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>3301</v>
       </c>
@@ -13497,7 +13496,7 @@
         <v>2271</v>
       </c>
     </row>
-    <row r="36" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>3401</v>
       </c>
@@ -13556,7 +13555,7 @@
         <v>2272</v>
       </c>
     </row>
-    <row r="37" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>3501</v>
       </c>
@@ -13615,7 +13614,7 @@
         <v>2273</v>
       </c>
     </row>
-    <row r="38" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>3601</v>
       </c>
@@ -13674,7 +13673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:22" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A39" s="4">
         <v>3701</v>
       </c>
@@ -13724,7 +13723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>3801</v>
       </c>
@@ -13783,7 +13782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:22" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="4">
         <v>3901</v>
       </c>
@@ -13833,7 +13832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>4001</v>
       </c>
@@ -13889,7 +13888,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="43" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>4101</v>
       </c>
@@ -13951,7 +13950,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="44" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>4201</v>
       </c>
@@ -14013,7 +14012,7 @@
         <v>2226</v>
       </c>
     </row>
-    <row r="45" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>4301</v>
       </c>
@@ -14075,7 +14074,7 @@
         <v>2227</v>
       </c>
     </row>
-    <row r="46" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>4401</v>
       </c>
@@ -14137,7 +14136,7 @@
         <v>2228</v>
       </c>
     </row>
-    <row r="47" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>4501</v>
       </c>
@@ -14199,7 +14198,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="48" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>4601</v>
       </c>
@@ -14261,7 +14260,7 @@
         <v>2230</v>
       </c>
     </row>
-    <row r="49" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>4701</v>
       </c>
@@ -14323,7 +14322,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="50" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>4801</v>
       </c>
@@ -14385,7 +14384,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="51" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>4901</v>
       </c>
@@ -14447,7 +14446,7 @@
         <v>2233</v>
       </c>
     </row>
-    <row r="52" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>5001</v>
       </c>
@@ -14509,7 +14508,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="53" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>5101</v>
       </c>
@@ -14571,7 +14570,7 @@
         <v>2235</v>
       </c>
     </row>
-    <row r="54" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>5201</v>
       </c>
@@ -14633,7 +14632,7 @@
         <v>2236</v>
       </c>
     </row>
-    <row r="55" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>5301</v>
       </c>
@@ -14695,7 +14694,7 @@
         <v>2237</v>
       </c>
     </row>
-    <row r="56" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>5401</v>
       </c>
@@ -14757,7 +14756,7 @@
         <v>2238</v>
       </c>
     </row>
-    <row r="57" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>5501</v>
       </c>
@@ -14819,7 +14818,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="58" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>5601</v>
       </c>
@@ -14881,7 +14880,7 @@
         <v>2240</v>
       </c>
     </row>
-    <row r="59" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>5701</v>
       </c>
@@ -14943,7 +14942,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="60" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>5801</v>
       </c>
@@ -15000,7 +14999,7 @@
         <v>2223</v>
       </c>
     </row>
-    <row r="61" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>5901</v>
       </c>
@@ -15062,7 +15061,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="62" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>6001</v>
       </c>
@@ -15124,7 +15123,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="63" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>6101</v>
       </c>
@@ -15186,7 +15185,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="64" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>6201</v>
       </c>
@@ -15248,7 +15247,7 @@
         <v>2245</v>
       </c>
     </row>
-    <row r="65" spans="1:22" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>6301</v>
       </c>
@@ -15311,13 +15310,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T65" xr:uid="{00000000-0009-0000-0000-000001000000}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="climatejust_lsoas_uk_2011_flood_data"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:T65" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <hyperlinks>
     <hyperlink ref="E22" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
     <hyperlink ref="E29" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>

--- a/pages/apps/uprn-service/config.xlsx
+++ b/pages/apps/uprn-service/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NDSH\GitHub\dsh-content\dev\pages\apps\uprn-service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCF108D0-0F52-4A62-97DF-B770A20FB2F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B8C49A-55BD-48CA-8E28-69C220089573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="388" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="388" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="folders" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6971" uniqueCount="3664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6973" uniqueCount="3666">
   <si>
     <t>DbId</t>
   </si>
@@ -11033,6 +11033,12 @@
   </si>
   <si>
     <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_lsoas_wa_2011_2022_v3_2022_data/128_housingheatvulnerability.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/001_r_hzz_cv1.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/002_r_hzz_cv2.json</t>
   </si>
 </sst>
 </file>
@@ -19985,6 +19991,9 @@
       <c r="J110" s="6" t="s">
         <v>369</v>
       </c>
+      <c r="L110" t="s">
+        <v>3664</v>
+      </c>
       <c r="M110">
         <v>2</v>
       </c>
@@ -20027,6 +20036,9 @@
       <c r="J111" s="6" t="s">
         <v>369</v>
       </c>
+      <c r="L111" t="s">
+        <v>3665</v>
+      </c>
       <c r="M111">
         <v>2</v>
       </c>
@@ -24841,7 +24853,7 @@
         <v>0</v>
       </c>
       <c r="J226" s="6"/>
-      <c r="L226" t="s">
+      <c r="L226" s="3" t="s">
         <v>3354</v>
       </c>
       <c r="M226">
@@ -82716,9 +82728,10 @@
     <hyperlink ref="L1109" r:id="rId549" xr:uid="{665C61A8-134F-442F-98D5-81FFD9A3B965}"/>
     <hyperlink ref="L1110" r:id="rId550" xr:uid="{9372FBA2-CD81-4F9B-B049-5FD85AD034A7}"/>
     <hyperlink ref="L842" r:id="rId551" xr:uid="{888B8DBF-54D3-48FC-BBCE-D30D8A5C2EF7}"/>
+    <hyperlink ref="L226" r:id="rId552" xr:uid="{17799A3C-A04C-4D45-BE2E-BCC0D0D59AB1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId552"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId553"/>
 </worksheet>
 </file>
 

--- a/pages/apps/uprn-service/config.xlsx
+++ b/pages/apps/uprn-service/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NDSH\GitHub\dsh-content\dev\pages\apps\uprn-service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B8C49A-55BD-48CA-8E28-69C220089573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43F758F3-6073-4109-9B2C-EAC641AC834F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="388" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6973" uniqueCount="3666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6975" uniqueCount="3668">
   <si>
     <t>DbId</t>
   </si>
@@ -11039,6 +11039,12 @@
   </si>
   <si>
     <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/002_r_hzz_cv2.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/aa.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/bb.json</t>
   </si>
 </sst>
 </file>
@@ -20081,6 +20087,9 @@
       <c r="J112" s="6" t="s">
         <v>369</v>
       </c>
+      <c r="L112" t="s">
+        <v>3666</v>
+      </c>
       <c r="M112">
         <v>2</v>
       </c>
@@ -20122,6 +20131,9 @@
       </c>
       <c r="J113" s="6" t="s">
         <v>375</v>
+      </c>
+      <c r="L113" t="s">
+        <v>3667</v>
       </c>
       <c r="M113">
         <v>2</v>

--- a/pages/apps/uprn-service/config.xlsx
+++ b/pages/apps/uprn-service/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NDSH\GitHub\dsh-content\dev\pages\apps\uprn-service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43F758F3-6073-4109-9B2C-EAC641AC834F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980BD46C-E886-4206-ABE6-CDFC613FCEA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="388" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6975" uniqueCount="3668">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7439" uniqueCount="4132">
   <si>
     <t>DbId</t>
   </si>
@@ -11041,10 +11041,1402 @@
     <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/002_r_hzz_cv2.json</t>
   </si>
   <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/aa.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/bb.json</t>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/003_r_hzz_cv3.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/004_r_hzz_cv4.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/005_r_hzz_cv5.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/006_r_hzz_cv6.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/007_r_hzz_cv7.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/008_r_hzz_cv8.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/009_r_hzz_cv9.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/010_r_hzz_cv10.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/011_r_hzz_cv11.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/012_r_hzz_cv12.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/013_r_hzz_cv13.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/014_r_hzz_cv14.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/015_r_hzz_cv15.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/016_r_hzz_cv16.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/017_r_hzz_cv17.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/018_r_hzz_cv18.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/019_r_hzz_cv19.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/020_r_hzz_cv20.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/021_r_hzz_cv21.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/022_r_hzz_cv22.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/023_r_hzz_cv23.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/024_r_hzz_cv24.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/025_r_hzz_cv25.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/026_r_hzz_cv26.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/027_r_hzz_cv27.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/028_r_hzz_cv28.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/029_r_hzz_cv29.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/030_r_hzz_cv30.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/031_r_hzz_cv31.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/032_r_hzz_cv32.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/033_r_hzz_cv33.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/034_r_hzz_cv34.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/035_r_hzz_cv35.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/036_r_hzz_cv36.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/037_rwhzz_cv1.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/038_rwhzz_cv2.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/039_rwhzz_cv3.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/040_rwhzz_cv4.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/041_rwhzz_cv5.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/042_rwhzz_cv6.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/043_rwhzz_cv7.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/044_rwhzz_cv8.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/045_rwhzz_cv9.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/046_rwhzz_cv10.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/047_rwhzz_cv11.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/048_rwhzz_cv12.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/049_rwhzz_cv13.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/050_rwhzz_cv14.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/051_rwhzz_cv15.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/052_rwhzz_cv16.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/053_rwhzz_cv17.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/054_rwhzz_cv18.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/055_rwhzz_cv19.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/056_rwhzz_cv20.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/057_rwhzz_cv21.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/058_rwhzz_cv22.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/059_zrwhzz_cv2.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/060_rwhzz_cv24.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/061_rwhzz_cv25.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/062_rwhzz_cv26.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/063_rwhzz_cv27.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/064_rwhzz_cv28.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/065_rwhzz_cv29.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/066_rwhzz_cv30.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/067_rwhzz_cv31.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/068_rwhzz_cv32.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/069_rwhzz_cv33.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/070_rwhzz_cv34.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/071_rwhzz_cv35.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/072_rwhzz_cv36.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/073_zabsh10day.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/074_zabsh50day.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/075_zabsh90day.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/076_zabsl10day.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/077_zabsl50day.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/078_zabsl90day.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/079_zabsm10day.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/080_zabsm50day.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/081_zabsm90day.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/082_zchh10day.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/083_zchh50day.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/084_zchh90day.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/085_zchl10day.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/086_zchl50day.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/087_zchl90day.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/088_zchm10day.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/089_zchm50day.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/090_zchm90day.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/091_zchh10wd.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/092_zchh50wd.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/093_zchh90wd.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/094_zchl10wd.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/095_zchl50wd.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/096_zchl90wd.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/097_zchm10wd.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/098_zchm50wd.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/099_zchm90wd.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/100_zchh10wn.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/101_zchh50wn.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/102_zchh90wn.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/103_zchl10wn.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/104_zchl50wn.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/105_zchl90wn.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/106_zchm10wn.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/107_zchm50wn.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/108_zchm90wn.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/001_tas_rcp26_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/002_tas_rcp26_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/003_tas_rcp26_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/004_tas_rcp26_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/005_tas_rcp26_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/006_tas_rcp26_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/007_tas_rcp26_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/008_tas_rcp26_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/009_tas_rcp26_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/010_tas_rcp45_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/011_tas_rcp45_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/012_tas_rcp45_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/013_tas_rcp45_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/014_tas_rcp45_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/015_tas_rcp45_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/016_tas_rcp45_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/017_tas_rcp45_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/018_tas_rcp45_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/019_tas_rcp60_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/020_tas_rcp60_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/021_tas_rcp60_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/022_tas_rcp60_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/023_tas_rcp60_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/024_tas_rcp60_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/025_tas_rcp60_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/026_tas_rcp60_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/027_tas_rcp60_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/028_tas_rcp85_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/029_tas_rcp85_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/030_tas_rcp85_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/031_tas_rcp85_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/032_tas_rcp85_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/033_tas_rcp85_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/034_tas_rcp85_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/035_tas_rcp85_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/036_tas_rcp85_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/037_tasmax_rcp26_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/038_tasmax_rcp26_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/039_tasmax_rcp26_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/040_tasmax_rcp26_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/041_tasmax_rcp26_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/042_tasmax_rcp26_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/043_tasmax_rcp26_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/044_tasmax_rcp26_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/045_tasmax_rcp26_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/046_tasmax_rcp45_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/047_tasmax_rcp45_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/048_tasmax_rcp45_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/049_tasmax_rcp45_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/050_tasmax_rcp45_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/051_tasmax_rcp45_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/052_tasmax_rcp45_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/053_tasmax_rcp45_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/054_tasmax_rcp45_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/055_tasmax_rcp60_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/056_tasmax_rcp60_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/057_tasmax_rcp60_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/058_tasmax_rcp60_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/059_tasmax_rcp60_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/060_tasmax_rcp60_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/061_tasmax_rcp60_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/062_tasmax_rcp60_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/063_tasmax_rcp60_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/064_tasmax_rcp85_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/065_tasmax_rcp85_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/066_tasmax_rcp85_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/067_tasmax_rcp85_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/068_tasmax_rcp85_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/069_tasmax_rcp85_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/070_tasmax_rcp85_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/071_tasmax_rcp85_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/072_tasmax_rcp85_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/073_z_all_rel_tas_rcp26_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/074_z_all_rel_tas_rcp26_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/075_z_all_rel_tas_rcp26_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/076_z_all_rel_tas_rcp26_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/077_z_all_rel_tas_rcp26_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/078_z_all_rel_tas_rcp26_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/079_z_all_rel_tas_rcp26_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/080_z_all_rel_tas_rcp26_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/081_z_all_rel_tas_rcp26_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/082_z_all_rel_tas_rcp45_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/083_z_all_rel_tas_rcp45_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/084_z_all_rel_tas_rcp45_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/085_z_all_rel_tas_rcp45_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/086_z_all_rel_tas_rcp45_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/087_z_all_rel_tas_rcp45_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/088_z_all_rel_tas_rcp45_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/089_z_all_rel_tas_rcp45_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/090_z_all_rel_tas_rcp45_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/091_z_all_rel_tas_rcp60_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/092_z_all_rel_tas_rcp60_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/093_z_all_rel_tas_rcp60_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/094_z_all_rel_tas_rcp60_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/095_z_all_rel_tas_rcp60_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/096_z_all_rel_tas_rcp60_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/097_z_all_rel_tas_rcp60_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/098_z_all_rel_tas_rcp60_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/099_z_all_rel_tas_rcp60_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/100_z_all_rel_tas_rcp85_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/101_z_all_rel_tas_rcp85_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/102_z_all_rel_tas_rcp85_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/103_z_all_rel_tas_rcp85_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/104_z_all_rel_tas_rcp85_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/105_z_all_rel_tas_rcp85_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/106_z_all_rel_tas_rcp85_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/107_z_all_rel_tas_rcp85_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/108_z_all_rel_tas_rcp85_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/109_z_all_rel_tasmax_rcp26_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/110_z_all_rel_tasmax_rcp26_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/111_z_all_rel_tasmax_rcp26_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/112_z_all_rel_tasmax_rcp26_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/113_z_all_rel_tasmax_rcp26_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/114_z_all_rel_tasmax_rcp26_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/115_z_all_rel_tasmax_rcp26_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/116_z_all_rel_tasmax_rcp26_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/117_z_all_rel_tasmax_rcp26_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/118_z_all_rel_tasmax_rcp45_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/119_z_all_rel_tasmax_rcp45_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/120_z_all_rel_tasmax_rcp45_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/121_z_all_rel_tasmax_rcp45_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/122_z_all_rel_tasmax_rcp45_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/123_z_all_rel_tasmax_rcp45_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/124_z_all_rel_tasmax_rcp45_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/125_z_all_rel_tasmax_rcp45_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/126_z_all_rel_tasmax_rcp45_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/127_z_all_rel_tasmax_rcp60_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/128_z_all_rel_tasmax_rcp60_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/129_z_all_rel_tasmax_rcp60_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/130_z_all_rel_tasmax_rcp60_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/131_z_all_rel_tasmax_rcp60_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/132_z_all_rel_tasmax_rcp60_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/133_z_all_rel_tasmax_rcp60_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/134_z_all_rel_tasmax_rcp60_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/135_z_all_rel_tasmax_rcp60_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/136_z_all_rel_tasmax_rcp85_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/137_z_all_rel_tasmax_rcp85_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/138_z_all_rel_tasmax_rcp85_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/139_z_all_rel_tasmax_rcp85_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/140_z_all_rel_tasmax_rcp85_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/141_z_all_rel_tasmax_rcp85_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/142_z_all_rel_tasmax_rcp85_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/143_z_all_rel_tasmax_rcp85_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/144_z_all_rel_tasmax_rcp85_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/145_tasmax_rcp26_rp20_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/146_tasmax_rcp26_rp20_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/147_tasmax_rcp26_rp20_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/148_tasmax_rcp26_rp20_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/149_tasmax_rcp26_rp20_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/150_tasmax_rcp26_rp20_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/151_tasmax_rcp26_rp20_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/152_tasmax_rcp26_rp20_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/153_tasmax_rcp26_rp20_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/154_tasmax_rcp26_rp50_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/155_tasmax_rcp26_rp50_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/156_tasmax_rcp26_rp50_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/157_tasmax_rcp26_rp50_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/158_tasmax_rcp26_rp50_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/159_tasmax_rcp26_rp50_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/160_tasmax_rcp26_rp50_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/161_tasmax_rcp26_rp50_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/162_tasmax_rcp26_rp50_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/163_tasmax_rcp26_rp100_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/164_tasmax_rcp26_rp100_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/165_tasmax_rcp26_rp100_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/166_tasmax_rcp26_rp100_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/167_tasmax_rcp26_rp100_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/168_tasmax_rcp26_rp100_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/169_tasmax_rcp26_rp100_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/170_tasmax_rcp26_rp100_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/171_tasmax_rcp26_rp100_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/172_tasmax_rcp45_rp20_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/173_tasmax_rcp45_rp20_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/174_tasmax_rcp45_rp20_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/175_tasmax_rcp45_rp20_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/176_tasmax_rcp45_rp20_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/177_tasmax_rcp45_rp20_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/178_tasmax_rcp45_rp20_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/179_tasmax_rcp45_rp20_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/180_tasmax_rcp45_rp20_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/181_tasmax_rcp45_rp50_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/182_tasmax_rcp45_rp50_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/183_tasmax_rcp45_rp50_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/184_tasmax_rcp45_rp50_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/185_tasmax_rcp45_rp50_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/186_tasmax_rcp45_rp50_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/187_tasmax_rcp45_rp50_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/188_tasmax_rcp45_rp50_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/189_tasmax_rcp45_rp50_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/190_tasmax_rcp45_rp100_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/191_tasmax_rcp45_rp100_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/192_tasmax_rcp45_rp100_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/193_tasmax_rcp45_rp100_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/194_tasmax_rcp45_rp100_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/195_tasmax_rcp45_rp100_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/196_tasmax_rcp45_rp100_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/197_tasmax_rcp45_rp100_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/198_tasmax_rcp45_rp100_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/199_tasmax_rcp60_rp20_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/200_tasmax_rcp60_rp20_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/201_tasmax_rcp60_rp20_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/202_tasmax_rcp60_rp20_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/203_tasmax_rcp60_rp20_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/204_tasmax_rcp60_rp20_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/205_tasmax_rcp60_rp20_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/206_tasmax_rcp60_rp20_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/207_tasmax_rcp60_rp20_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/208_tasmax_rcp60_rp50_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/209_tasmax_rcp60_rp50_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/210_tasmax_rcp60_rp50_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/211_tasmax_rcp60_rp50_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/212_tasmax_rcp60_rp50_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/213_tasmax_rcp60_rp50_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/214_tasmax_rcp60_rp50_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/215_tasmax_rcp60_rp50_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/216_tasmax_rcp60_rp50_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/217_tasmax_rcp60_rp100_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/218_tasmax_rcp60_rp100_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/219_tasmax_rcp60_rp100_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/220_tasmax_rcp60_rp100_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/221_tasmax_rcp60_rp100_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/222_tasmax_rcp60_rp100_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/223_tasmax_rcp60_rp100_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/224_tasmax_rcp60_rp100_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/225_tasmax_rcp60_rp100_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/226_tasmax_rcp85_rp20_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/227_tasmax_rcp85_rp20_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/228_tasmax_rcp85_rp20_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/229_tasmax_rcp85_rp20_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/230_tasmax_rcp85_rp20_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/231_tasmax_rcp85_rp20_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/232_tasmax_rcp85_rp20_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/233_tasmax_rcp85_rp20_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/234_tasmax_rcp85_rp20_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/235_tasmax_rcp85_rp50_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/236_tasmax_rcp85_rp50_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/237_tasmax_rcp85_rp50_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/238_tasmax_rcp85_rp50_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/239_tasmax_rcp85_rp50_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/240_tasmax_rcp85_rp50_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/241_tasmax_rcp85_rp50_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/242_tasmax_rcp85_rp50_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/243_tasmax_rcp85_rp50_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/244_tasmax_rcp85_rp100_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/245_tasmax_rcp85_rp100_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/246_tasmax_rcp85_rp100_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/247_tasmax_rcp85_rp100_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/248_tasmax_rcp85_rp100_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/249_tasmax_rcp85_rp100_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/250_tasmax_rcp85_rp100_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/251_tasmax_rcp85_rp100_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/252_tasmax_rcp85_rp100_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/253_z_ar_tasmax_rcp26_rp20_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/254_z_ar_tasmax_rcp26_rp20_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/255_z_ar_tasmax_rcp26_rp20_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/256_z_ar_tasmax_rcp26_rp20_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/257_z_ar_tasmax_rcp26_rp20_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/258_z_ar_tasmax_rcp26_rp20_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/259_z_ar_tasmax_rcp26_rp20_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/260_z_ar_tasmax_rcp26_rp20_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/261_z_ar_tasmax_rcp26_rp20_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/262_z_ar_tasmax_rcp26_rp50_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/263_z_ar_tasmax_rcp26_rp50_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/264_z_ar_tasmax_rcp26_rp50_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/265_z_ar_tasmax_rcp26_rp50_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/266_z_ar_tasmax_rcp26_rp50_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/267_z_ar_tasmax_rcp26_rp50_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/268_z_ar_tasmax_rcp26_rp50_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/269_z_ar_tasmax_rcp26_rp50_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/270_z_ar_tasmax_rcp26_rp50_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/271_z_ar_tasmax_rcp26_rp100_2020_10.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/272_z_ar_tasmax_rcp26_rp100_2020_50.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/273_z_ar_tasmax_rcp26_rp100_2020_90.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/274_z_ar_tasmax_rcp26_rp100_2050_10.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/275_z_ar_tasmax_rcp26_rp100_2050_50.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/276_z_ar_tasmax_rcp26_rp100_2050_90.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/277_z_ar_tasmax_rcp26_rp100_2080_10.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/278_z_ar_tasmax_rcp26_rp100_2080_50.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/279_z_ar_tasmax_rcp26_rp100_2080_90.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/280_z_ar_tasmax_rcp45_rp20_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/281_z_ar_tasmax_rcp45_rp20_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/282_z_ar_tasmax_rcp45_rp20_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/283_z_ar_tasmax_rcp45_rp20_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/284_z_ar_tasmax_rcp45_rp20_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/285_z_ar_tasmax_rcp45_rp20_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/286_z_ar_tasmax_rcp45_rp20_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/287_z_ar_tasmax_rcp45_rp20_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/288_z_ar_tasmax_rcp45_rp20_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/289_z_ar_tasmax_rcp45_rp50_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/290_z_ar_tasmax_rcp45_rp50_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/291_z_ar_tasmax_rcp45_rp50_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/292_z_ar_tasmax_rcp45_rp50_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/293_z_ar_tasmax_rcp45_rp50_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/294_z_ar_tasmax_rcp45_rp50_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/295_z_ar_tasmax_rcp45_rp50_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/296_z_ar_tasmax_rcp45_rp50_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/297_z_ar_tasmax_rcp45_rp50_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/298_z_ar_tasmax_rcp45_rp100_2020_10.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/299_z_ar_tasmax_rcp45_rp100_2020_50.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/300_z_ar_tasmax_rcp45_rp100_2020_90.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/301_z_ar_tasmax_rcp45_rp100_2050_10.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/302_z_ar_tasmax_rcp45_rp100_2050_50.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/303_z_ar_tasmax_rcp45_rp100_2050_90.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/304_z_ar_tasmax_rcp45_rp100_2080_10.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/305_z_ar_tasmax_rcp45_rp100_2080_50.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/306_z_ar_tasmax_rcp45_rp100_2080_90.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/307_z_ar_tasmax_rcp60_rp20_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/308_z_ar_tasmax_rcp60_rp20_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/309_z_ar_tasmax_rcp60_rp20_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/310_z_ar_tasmax_rcp60_rp20_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/311_z_ar_tasmax_rcp60_rp20_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/312_z_ar_tasmax_rcp60_rp20_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/313_z_ar_tasmax_rcp60_rp20_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/314_z_ar_tasmax_rcp60_rp20_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/315_z_ar_tasmax_rcp60_rp20_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/316_z_ar_tasmax_rcp60_rp50_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/317_z_ar_tasmax_rcp60_rp50_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/318_z_ar_tasmax_rcp60_rp50_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/319_z_ar_tasmax_rcp60_rp50_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/320_z_ar_tasmax_rcp60_rp50_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/321_z_ar_tasmax_rcp60_rp50_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/322_z_ar_tasmax_rcp60_rp50_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/323_z_ar_tasmax_rcp60_rp50_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/324_z_ar_tasmax_rcp60_rp50_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/325_z_ar_tasmax_rcp60_rp100_2020_10.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/326_z_ar_tasmax_rcp60_rp100_2020_50.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/327_z_ar_tasmax_rcp60_rp100_2020_90.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/328_z_ar_tasmax_rcp60_rp100_2050_10.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/329_z_ar_tasmax_rcp60_rp100_2050_50.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/330_z_ar_tasmax_rcp60_rp100_2050_90.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/331_z_ar_tasmax_rcp60_rp100_2080_10.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/332_z_ar_tasmax_rcp60_rp100_2080_50.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/333_z_ar_tasmax_rcp60_rp100_2080_90.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/334_z_ar_tasmax_rcp85_rp20_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/335_z_ar_tasmax_rcp85_rp20_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/336_z_ar_tasmax_rcp85_rp20_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/337_z_ar_tasmax_rcp85_rp20_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/338_z_ar_tasmax_rcp85_rp20_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/339_z_ar_tasmax_rcp85_rp20_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/340_z_ar_tasmax_rcp85_rp20_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/341_z_ar_tasmax_rcp85_rp20_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/342_z_ar_tasmax_rcp85_rp20_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/343_z_ar_tasmax_rcp85_rp50_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/344_z_ar_tasmax_rcp85_rp50_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/345_z_ar_tasmax_rcp85_rp50_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/346_z_ar_tasmax_rcp85_rp50_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/347_z_ar_tasmax_rcp85_rp50_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/348_z_ar_tasmax_rcp85_rp50_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/349_z_ar_tasmax_rcp85_rp50_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/350_z_ar_tasmax_rcp85_rp50_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/351_z_ar_tasmax_rcp85_rp50_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/352_z_ar_tasmax_rcp85_rp100_2020_10.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/353_z_ar_tasmax_rcp85_rp100_2020_50.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/354_z_ar_tasmax_rcp85_rp100_2020_90.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/355_z_ar_tasmax_rcp85_rp100_2050_10.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/356_z_ar_tasmax_rcp85_rp100_2050_50.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/357_z_ar_tasmax_rcp85_rp100_2050_90.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/358_z_ar_tasmax_rcp85_rp100_2080_10.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/359_z_ar_tasmax_rcp85_rp100_2080_50.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/360_z_ar_tasmax_rcp85_rp100_2080_90.json</t>
   </si>
 </sst>
 </file>
@@ -20177,6 +21569,9 @@
       <c r="J114" s="6" t="s">
         <v>375</v>
       </c>
+      <c r="L114" t="s">
+        <v>3668</v>
+      </c>
       <c r="M114">
         <v>2</v>
       </c>
@@ -20219,6 +21614,9 @@
       <c r="J115" s="6" t="s">
         <v>375</v>
       </c>
+      <c r="L115" t="s">
+        <v>3669</v>
+      </c>
       <c r="M115">
         <v>2</v>
       </c>
@@ -20261,6 +21659,9 @@
       <c r="J116" s="6" t="s">
         <v>379</v>
       </c>
+      <c r="L116" t="s">
+        <v>3670</v>
+      </c>
       <c r="M116">
         <v>2</v>
       </c>
@@ -20303,6 +21704,9 @@
       <c r="J117" s="6" t="s">
         <v>379</v>
       </c>
+      <c r="L117" t="s">
+        <v>3671</v>
+      </c>
       <c r="M117">
         <v>2</v>
       </c>
@@ -20345,6 +21749,9 @@
       <c r="J118" s="6" t="s">
         <v>379</v>
       </c>
+      <c r="L118" t="s">
+        <v>3672</v>
+      </c>
       <c r="M118">
         <v>2</v>
       </c>
@@ -20387,6 +21794,9 @@
       <c r="J119" s="6" t="s">
         <v>369</v>
       </c>
+      <c r="L119" t="s">
+        <v>3673</v>
+      </c>
       <c r="M119">
         <v>2</v>
       </c>
@@ -20429,6 +21839,9 @@
       <c r="J120" s="6" t="s">
         <v>369</v>
       </c>
+      <c r="L120" t="s">
+        <v>3674</v>
+      </c>
       <c r="M120">
         <v>2</v>
       </c>
@@ -20471,6 +21884,9 @@
       <c r="J121" s="6" t="s">
         <v>369</v>
       </c>
+      <c r="L121" t="s">
+        <v>3675</v>
+      </c>
       <c r="M121">
         <v>2</v>
       </c>
@@ -20513,6 +21929,9 @@
       <c r="J122" s="6" t="s">
         <v>375</v>
       </c>
+      <c r="L122" t="s">
+        <v>3676</v>
+      </c>
       <c r="M122">
         <v>2</v>
       </c>
@@ -20555,6 +21974,9 @@
       <c r="J123" s="6" t="s">
         <v>375</v>
       </c>
+      <c r="L123" t="s">
+        <v>3677</v>
+      </c>
       <c r="M123">
         <v>2</v>
       </c>
@@ -20597,6 +22019,9 @@
       <c r="J124" s="6" t="s">
         <v>375</v>
       </c>
+      <c r="L124" t="s">
+        <v>3678</v>
+      </c>
       <c r="M124">
         <v>2</v>
       </c>
@@ -20639,6 +22064,9 @@
       <c r="J125" s="6" t="s">
         <v>379</v>
       </c>
+      <c r="L125" t="s">
+        <v>3679</v>
+      </c>
       <c r="M125">
         <v>2</v>
       </c>
@@ -20681,6 +22109,9 @@
       <c r="J126" s="6" t="s">
         <v>379</v>
       </c>
+      <c r="L126" t="s">
+        <v>3680</v>
+      </c>
       <c r="M126">
         <v>2</v>
       </c>
@@ -20723,6 +22154,9 @@
       <c r="J127" s="6" t="s">
         <v>379</v>
       </c>
+      <c r="L127" t="s">
+        <v>3681</v>
+      </c>
       <c r="M127">
         <v>2</v>
       </c>
@@ -20765,6 +22199,9 @@
       <c r="J128" s="6" t="s">
         <v>369</v>
       </c>
+      <c r="L128" t="s">
+        <v>3682</v>
+      </c>
       <c r="M128">
         <v>2</v>
       </c>
@@ -20807,6 +22244,9 @@
       <c r="J129" s="6" t="s">
         <v>369</v>
       </c>
+      <c r="L129" t="s">
+        <v>3683</v>
+      </c>
       <c r="M129">
         <v>2</v>
       </c>
@@ -20849,6 +22289,9 @@
       <c r="J130" s="6" t="s">
         <v>369</v>
       </c>
+      <c r="L130" t="s">
+        <v>3684</v>
+      </c>
       <c r="M130">
         <v>2</v>
       </c>
@@ -20891,6 +22334,9 @@
       <c r="J131" s="6" t="s">
         <v>375</v>
       </c>
+      <c r="L131" t="s">
+        <v>3685</v>
+      </c>
       <c r="M131">
         <v>2</v>
       </c>
@@ -20933,6 +22379,9 @@
       <c r="J132" s="6" t="s">
         <v>375</v>
       </c>
+      <c r="L132" t="s">
+        <v>3686</v>
+      </c>
       <c r="M132">
         <v>2</v>
       </c>
@@ -20975,6 +22424,9 @@
       <c r="J133" s="6" t="s">
         <v>375</v>
       </c>
+      <c r="L133" t="s">
+        <v>3687</v>
+      </c>
       <c r="M133">
         <v>2</v>
       </c>
@@ -21017,6 +22469,9 @@
       <c r="J134" s="6" t="s">
         <v>379</v>
       </c>
+      <c r="L134" t="s">
+        <v>3688</v>
+      </c>
       <c r="M134">
         <v>2</v>
       </c>
@@ -21059,6 +22514,9 @@
       <c r="J135" s="6" t="s">
         <v>379</v>
       </c>
+      <c r="L135" t="s">
+        <v>3689</v>
+      </c>
       <c r="M135">
         <v>2</v>
       </c>
@@ -21101,6 +22559,9 @@
       <c r="J136" s="6" t="s">
         <v>379</v>
       </c>
+      <c r="L136" t="s">
+        <v>3690</v>
+      </c>
       <c r="M136">
         <v>2</v>
       </c>
@@ -21143,6 +22604,9 @@
       <c r="J137" s="6" t="s">
         <v>369</v>
       </c>
+      <c r="L137" t="s">
+        <v>3691</v>
+      </c>
       <c r="M137">
         <v>2</v>
       </c>
@@ -21185,6 +22649,9 @@
       <c r="J138" s="6" t="s">
         <v>369</v>
       </c>
+      <c r="L138" t="s">
+        <v>3692</v>
+      </c>
       <c r="M138">
         <v>2</v>
       </c>
@@ -21227,6 +22694,9 @@
       <c r="J139" s="6" t="s">
         <v>369</v>
       </c>
+      <c r="L139" t="s">
+        <v>3693</v>
+      </c>
       <c r="M139">
         <v>2</v>
       </c>
@@ -21269,6 +22739,9 @@
       <c r="J140" s="6" t="s">
         <v>375</v>
       </c>
+      <c r="L140" t="s">
+        <v>3694</v>
+      </c>
       <c r="M140">
         <v>2</v>
       </c>
@@ -21311,6 +22784,9 @@
       <c r="J141" s="6" t="s">
         <v>375</v>
       </c>
+      <c r="L141" t="s">
+        <v>3695</v>
+      </c>
       <c r="M141">
         <v>2</v>
       </c>
@@ -21354,6 +22830,9 @@
       <c r="J142" s="6" t="s">
         <v>375</v>
       </c>
+      <c r="L142" t="s">
+        <v>3696</v>
+      </c>
       <c r="M142">
         <v>2</v>
       </c>
@@ -21396,6 +22875,9 @@
       <c r="J143" s="6" t="s">
         <v>379</v>
       </c>
+      <c r="L143" t="s">
+        <v>3697</v>
+      </c>
       <c r="M143">
         <v>2</v>
       </c>
@@ -21438,6 +22920,9 @@
       <c r="J144" s="6" t="s">
         <v>379</v>
       </c>
+      <c r="L144" t="s">
+        <v>3698</v>
+      </c>
       <c r="M144">
         <v>2</v>
       </c>
@@ -21480,6 +22965,9 @@
       <c r="J145" s="6" t="s">
         <v>379</v>
       </c>
+      <c r="L145" t="s">
+        <v>3699</v>
+      </c>
       <c r="M145">
         <v>2</v>
       </c>
@@ -21522,6 +23010,9 @@
       <c r="J146" s="6" t="s">
         <v>424</v>
       </c>
+      <c r="L146" t="s">
+        <v>3700</v>
+      </c>
       <c r="M146">
         <v>2</v>
       </c>
@@ -21564,6 +23055,9 @@
       <c r="J147" s="6" t="s">
         <v>427</v>
       </c>
+      <c r="L147" t="s">
+        <v>3701</v>
+      </c>
       <c r="M147">
         <v>2</v>
       </c>
@@ -21606,6 +23100,9 @@
       <c r="J148" s="6" t="s">
         <v>424</v>
       </c>
+      <c r="L148" t="s">
+        <v>3702</v>
+      </c>
       <c r="M148">
         <v>2</v>
       </c>
@@ -21648,6 +23145,9 @@
       <c r="J149" s="6" t="s">
         <v>431</v>
       </c>
+      <c r="L149" t="s">
+        <v>3703</v>
+      </c>
       <c r="M149">
         <v>2</v>
       </c>
@@ -21690,6 +23190,9 @@
       <c r="J150" s="6" t="s">
         <v>431</v>
       </c>
+      <c r="L150" t="s">
+        <v>3704</v>
+      </c>
       <c r="M150">
         <v>2</v>
       </c>
@@ -21732,6 +23235,9 @@
       <c r="J151" s="6" t="s">
         <v>431</v>
       </c>
+      <c r="L151" t="s">
+        <v>3705</v>
+      </c>
       <c r="M151">
         <v>2</v>
       </c>
@@ -21774,6 +23280,9 @@
       <c r="J152" s="6" t="s">
         <v>435</v>
       </c>
+      <c r="L152" t="s">
+        <v>3706</v>
+      </c>
       <c r="M152">
         <v>2</v>
       </c>
@@ -21816,6 +23325,9 @@
       <c r="J153" s="6" t="s">
         <v>435</v>
       </c>
+      <c r="L153" t="s">
+        <v>3707</v>
+      </c>
       <c r="M153">
         <v>2</v>
       </c>
@@ -21858,6 +23370,9 @@
       <c r="J154" s="6" t="s">
         <v>435</v>
       </c>
+      <c r="L154" t="s">
+        <v>3708</v>
+      </c>
       <c r="M154">
         <v>2</v>
       </c>
@@ -21900,6 +23415,9 @@
       <c r="J155" s="6" t="s">
         <v>424</v>
       </c>
+      <c r="L155" t="s">
+        <v>3709</v>
+      </c>
       <c r="M155">
         <v>2</v>
       </c>
@@ -21942,6 +23460,9 @@
       <c r="J156" s="6" t="s">
         <v>424</v>
       </c>
+      <c r="L156" t="s">
+        <v>3710</v>
+      </c>
       <c r="M156">
         <v>2</v>
       </c>
@@ -21984,6 +23505,9 @@
       <c r="J157" s="6" t="s">
         <v>424</v>
       </c>
+      <c r="L157" t="s">
+        <v>3711</v>
+      </c>
       <c r="M157">
         <v>2</v>
       </c>
@@ -22026,6 +23550,9 @@
       <c r="J158" s="6" t="s">
         <v>431</v>
       </c>
+      <c r="L158" t="s">
+        <v>3712</v>
+      </c>
       <c r="M158">
         <v>2</v>
       </c>
@@ -22068,6 +23595,9 @@
       <c r="J159" s="6" t="s">
         <v>431</v>
       </c>
+      <c r="L159" t="s">
+        <v>3713</v>
+      </c>
       <c r="M159">
         <v>2</v>
       </c>
@@ -22110,6 +23640,9 @@
       <c r="J160" s="6" t="s">
         <v>431</v>
       </c>
+      <c r="L160" t="s">
+        <v>3714</v>
+      </c>
       <c r="M160">
         <v>2</v>
       </c>
@@ -22152,6 +23685,9 @@
       <c r="J161" s="6" t="s">
         <v>435</v>
       </c>
+      <c r="L161" t="s">
+        <v>3715</v>
+      </c>
       <c r="M161">
         <v>2</v>
       </c>
@@ -22194,6 +23730,9 @@
       <c r="J162" s="6" t="s">
         <v>435</v>
       </c>
+      <c r="L162" t="s">
+        <v>3716</v>
+      </c>
       <c r="M162">
         <v>2</v>
       </c>
@@ -22236,6 +23775,9 @@
       <c r="J163" s="6" t="s">
         <v>435</v>
       </c>
+      <c r="L163" t="s">
+        <v>3717</v>
+      </c>
       <c r="M163">
         <v>2</v>
       </c>
@@ -22278,6 +23820,9 @@
       <c r="J164" s="6" t="s">
         <v>424</v>
       </c>
+      <c r="L164" t="s">
+        <v>3718</v>
+      </c>
       <c r="M164">
         <v>2</v>
       </c>
@@ -22320,6 +23865,9 @@
       <c r="J165" s="6" t="s">
         <v>424</v>
       </c>
+      <c r="L165" t="s">
+        <v>3719</v>
+      </c>
       <c r="M165">
         <v>2</v>
       </c>
@@ -22362,6 +23910,9 @@
       <c r="J166" s="6" t="s">
         <v>424</v>
       </c>
+      <c r="L166" t="s">
+        <v>3720</v>
+      </c>
       <c r="M166">
         <v>2</v>
       </c>
@@ -22404,6 +23955,9 @@
       <c r="J167" s="6" t="s">
         <v>431</v>
       </c>
+      <c r="L167" t="s">
+        <v>3721</v>
+      </c>
       <c r="M167">
         <v>2</v>
       </c>
@@ -22446,6 +24000,9 @@
       <c r="J168" s="6" t="s">
         <v>431</v>
       </c>
+      <c r="L168" t="s">
+        <v>3722</v>
+      </c>
       <c r="M168">
         <v>2</v>
       </c>
@@ -22488,6 +24045,9 @@
       <c r="J169" s="6" t="s">
         <v>431</v>
       </c>
+      <c r="L169" t="s">
+        <v>3723</v>
+      </c>
       <c r="M169">
         <v>2</v>
       </c>
@@ -22530,6 +24090,9 @@
       <c r="J170" s="6" t="s">
         <v>435</v>
       </c>
+      <c r="L170" t="s">
+        <v>3724</v>
+      </c>
       <c r="M170">
         <v>2</v>
       </c>
@@ -22572,6 +24135,9 @@
       <c r="J171" s="6" t="s">
         <v>435</v>
       </c>
+      <c r="L171" t="s">
+        <v>3725</v>
+      </c>
       <c r="M171">
         <v>2</v>
       </c>
@@ -22614,6 +24180,9 @@
       <c r="J172" s="6" t="s">
         <v>435</v>
       </c>
+      <c r="L172" t="s">
+        <v>3726</v>
+      </c>
       <c r="M172">
         <v>2</v>
       </c>
@@ -22656,6 +24225,9 @@
       <c r="J173" s="6" t="s">
         <v>424</v>
       </c>
+      <c r="L173" t="s">
+        <v>3727</v>
+      </c>
       <c r="M173">
         <v>2</v>
       </c>
@@ -22698,6 +24270,9 @@
       <c r="J174" s="6" t="s">
         <v>424</v>
       </c>
+      <c r="L174" t="s">
+        <v>3728</v>
+      </c>
       <c r="M174">
         <v>2</v>
       </c>
@@ -22740,6 +24315,9 @@
       <c r="J175" s="6" t="s">
         <v>424</v>
       </c>
+      <c r="L175" t="s">
+        <v>3729</v>
+      </c>
       <c r="M175">
         <v>2</v>
       </c>
@@ -22782,6 +24360,9 @@
       <c r="J176" s="6" t="s">
         <v>431</v>
       </c>
+      <c r="L176" t="s">
+        <v>3730</v>
+      </c>
       <c r="M176">
         <v>2</v>
       </c>
@@ -22824,6 +24405,9 @@
       <c r="J177" s="6" t="s">
         <v>431</v>
       </c>
+      <c r="L177" t="s">
+        <v>3731</v>
+      </c>
       <c r="M177">
         <v>2</v>
       </c>
@@ -22866,6 +24450,9 @@
       <c r="J178" s="6" t="s">
         <v>431</v>
       </c>
+      <c r="L178" t="s">
+        <v>3732</v>
+      </c>
       <c r="M178">
         <v>2</v>
       </c>
@@ -22908,6 +24495,9 @@
       <c r="J179" s="6" t="s">
         <v>435</v>
       </c>
+      <c r="L179" t="s">
+        <v>3733</v>
+      </c>
       <c r="M179">
         <v>2</v>
       </c>
@@ -22950,6 +24540,9 @@
       <c r="J180" s="6" t="s">
         <v>435</v>
       </c>
+      <c r="L180" t="s">
+        <v>3734</v>
+      </c>
       <c r="M180">
         <v>2</v>
       </c>
@@ -22992,6 +24585,9 @@
       <c r="J181" s="6" t="s">
         <v>435</v>
       </c>
+      <c r="L181" t="s">
+        <v>3735</v>
+      </c>
       <c r="M181">
         <v>2</v>
       </c>
@@ -23034,6 +24630,9 @@
       <c r="J182" s="6" t="s">
         <v>481</v>
       </c>
+      <c r="L182" t="s">
+        <v>3736</v>
+      </c>
       <c r="M182">
         <v>2</v>
       </c>
@@ -23076,6 +24675,9 @@
       <c r="J183" s="6" t="s">
         <v>481</v>
       </c>
+      <c r="L183" t="s">
+        <v>3737</v>
+      </c>
       <c r="M183">
         <v>2</v>
       </c>
@@ -23118,6 +24720,9 @@
       <c r="J184" s="6" t="s">
         <v>481</v>
       </c>
+      <c r="L184" t="s">
+        <v>3738</v>
+      </c>
       <c r="M184">
         <v>2</v>
       </c>
@@ -23160,6 +24765,9 @@
       <c r="J185" s="6" t="s">
         <v>487</v>
       </c>
+      <c r="L185" t="s">
+        <v>3739</v>
+      </c>
       <c r="M185">
         <v>2</v>
       </c>
@@ -23202,6 +24810,9 @@
       <c r="J186" s="6" t="s">
         <v>487</v>
       </c>
+      <c r="L186" t="s">
+        <v>3740</v>
+      </c>
       <c r="M186">
         <v>2</v>
       </c>
@@ -23244,6 +24855,9 @@
       <c r="J187" s="6" t="s">
         <v>487</v>
       </c>
+      <c r="L187" t="s">
+        <v>3741</v>
+      </c>
       <c r="M187">
         <v>2</v>
       </c>
@@ -23286,6 +24900,9 @@
       <c r="J188" s="6" t="s">
         <v>491</v>
       </c>
+      <c r="L188" t="s">
+        <v>3742</v>
+      </c>
       <c r="M188">
         <v>2</v>
       </c>
@@ -23328,6 +24945,9 @@
       <c r="J189" s="6" t="s">
         <v>491</v>
       </c>
+      <c r="L189" t="s">
+        <v>3743</v>
+      </c>
       <c r="M189">
         <v>2</v>
       </c>
@@ -23370,6 +24990,9 @@
       <c r="J190" s="6" t="s">
         <v>491</v>
       </c>
+      <c r="L190" t="s">
+        <v>3744</v>
+      </c>
       <c r="M190">
         <v>2</v>
       </c>
@@ -23412,6 +25035,9 @@
       <c r="J191" s="6" t="s">
         <v>481</v>
       </c>
+      <c r="L191" t="s">
+        <v>3745</v>
+      </c>
       <c r="M191">
         <v>2</v>
       </c>
@@ -23454,6 +25080,9 @@
       <c r="J192" s="6" t="s">
         <v>481</v>
       </c>
+      <c r="L192" t="s">
+        <v>3746</v>
+      </c>
       <c r="M192">
         <v>2</v>
       </c>
@@ -23496,6 +25125,9 @@
       <c r="J193" s="6" t="s">
         <v>481</v>
       </c>
+      <c r="L193" t="s">
+        <v>3747</v>
+      </c>
       <c r="M193">
         <v>2</v>
       </c>
@@ -23538,6 +25170,9 @@
       <c r="J194" s="6" t="s">
         <v>487</v>
       </c>
+      <c r="L194" t="s">
+        <v>3748</v>
+      </c>
       <c r="M194">
         <v>2</v>
       </c>
@@ -23580,6 +25215,9 @@
       <c r="J195" s="6" t="s">
         <v>487</v>
       </c>
+      <c r="L195" t="s">
+        <v>3749</v>
+      </c>
       <c r="M195">
         <v>2</v>
       </c>
@@ -23622,6 +25260,9 @@
       <c r="J196" s="6" t="s">
         <v>487</v>
       </c>
+      <c r="L196" t="s">
+        <v>3750</v>
+      </c>
       <c r="M196">
         <v>2</v>
       </c>
@@ -23664,6 +25305,9 @@
       <c r="J197" s="6" t="s">
         <v>491</v>
       </c>
+      <c r="L197" t="s">
+        <v>3751</v>
+      </c>
       <c r="M197">
         <v>2</v>
       </c>
@@ -23706,6 +25350,9 @@
       <c r="J198" s="6" t="s">
         <v>491</v>
       </c>
+      <c r="L198" t="s">
+        <v>3752</v>
+      </c>
       <c r="M198">
         <v>2</v>
       </c>
@@ -23748,6 +25395,9 @@
       <c r="J199" s="6" t="s">
         <v>491</v>
       </c>
+      <c r="L199" t="s">
+        <v>3753</v>
+      </c>
       <c r="M199">
         <v>2</v>
       </c>
@@ -23790,6 +25440,9 @@
       <c r="J200" s="6" t="s">
         <v>508</v>
       </c>
+      <c r="L200" t="s">
+        <v>3754</v>
+      </c>
       <c r="M200">
         <v>2</v>
       </c>
@@ -23832,6 +25485,9 @@
       <c r="J201" s="6" t="s">
         <v>508</v>
       </c>
+      <c r="L201" t="s">
+        <v>3755</v>
+      </c>
       <c r="M201">
         <v>2</v>
       </c>
@@ -23874,6 +25530,9 @@
       <c r="J202" s="6" t="s">
         <v>508</v>
       </c>
+      <c r="L202" t="s">
+        <v>3756</v>
+      </c>
       <c r="M202">
         <v>2</v>
       </c>
@@ -23916,6 +25575,9 @@
       <c r="J203" s="6" t="s">
         <v>487</v>
       </c>
+      <c r="L203" t="s">
+        <v>3757</v>
+      </c>
       <c r="M203">
         <v>2</v>
       </c>
@@ -23958,6 +25620,9 @@
       <c r="J204" s="6" t="s">
         <v>487</v>
       </c>
+      <c r="L204" t="s">
+        <v>3758</v>
+      </c>
       <c r="M204">
         <v>2</v>
       </c>
@@ -24000,6 +25665,9 @@
       <c r="J205" s="6" t="s">
         <v>487</v>
       </c>
+      <c r="L205" t="s">
+        <v>3759</v>
+      </c>
       <c r="M205">
         <v>2</v>
       </c>
@@ -24042,6 +25710,9 @@
       <c r="J206" s="6" t="s">
         <v>491</v>
       </c>
+      <c r="L206" t="s">
+        <v>3760</v>
+      </c>
       <c r="M206">
         <v>2</v>
       </c>
@@ -24084,6 +25755,9 @@
       <c r="J207" s="6" t="s">
         <v>491</v>
       </c>
+      <c r="L207" t="s">
+        <v>3761</v>
+      </c>
       <c r="M207">
         <v>2</v>
       </c>
@@ -24126,6 +25800,9 @@
       <c r="J208" s="6" t="s">
         <v>491</v>
       </c>
+      <c r="L208" t="s">
+        <v>3762</v>
+      </c>
       <c r="M208">
         <v>2</v>
       </c>
@@ -24168,6 +25845,9 @@
       <c r="J209" s="6" t="s">
         <v>481</v>
       </c>
+      <c r="L209" t="s">
+        <v>3763</v>
+      </c>
       <c r="M209">
         <v>2</v>
       </c>
@@ -24210,6 +25890,9 @@
       <c r="J210" s="6" t="s">
         <v>481</v>
       </c>
+      <c r="L210" t="s">
+        <v>3764</v>
+      </c>
       <c r="M210">
         <v>2</v>
       </c>
@@ -24252,6 +25935,9 @@
       <c r="J211" s="6" t="s">
         <v>481</v>
       </c>
+      <c r="L211" t="s">
+        <v>3765</v>
+      </c>
       <c r="M211">
         <v>2</v>
       </c>
@@ -24294,6 +25980,9 @@
       <c r="J212" s="6" t="s">
         <v>487</v>
       </c>
+      <c r="L212" t="s">
+        <v>3766</v>
+      </c>
       <c r="M212">
         <v>2</v>
       </c>
@@ -24336,6 +26025,9 @@
       <c r="J213" s="6" t="s">
         <v>487</v>
       </c>
+      <c r="L213" t="s">
+        <v>3767</v>
+      </c>
       <c r="M213">
         <v>2</v>
       </c>
@@ -24378,6 +26070,9 @@
       <c r="J214" s="6" t="s">
         <v>487</v>
       </c>
+      <c r="L214" t="s">
+        <v>3768</v>
+      </c>
       <c r="M214">
         <v>2</v>
       </c>
@@ -24420,6 +26115,9 @@
       <c r="J215" s="6" t="s">
         <v>491</v>
       </c>
+      <c r="L215" t="s">
+        <v>3769</v>
+      </c>
       <c r="M215">
         <v>2</v>
       </c>
@@ -24462,6 +26160,9 @@
       <c r="J216" s="6" t="s">
         <v>491</v>
       </c>
+      <c r="L216" t="s">
+        <v>3770</v>
+      </c>
       <c r="M216">
         <v>2</v>
       </c>
@@ -24504,6 +26205,9 @@
       <c r="J217" s="6" t="s">
         <v>491</v>
       </c>
+      <c r="L217" t="s">
+        <v>3771</v>
+      </c>
       <c r="M217">
         <v>2</v>
       </c>
@@ -33129,6 +34833,9 @@
       <c r="J419" s="6" t="s">
         <v>868</v>
       </c>
+      <c r="L419" t="s">
+        <v>3772</v>
+      </c>
       <c r="M419">
         <v>2</v>
       </c>
@@ -33171,6 +34878,9 @@
       <c r="J420" s="6" t="s">
         <v>868</v>
       </c>
+      <c r="L420" t="s">
+        <v>3773</v>
+      </c>
       <c r="M420">
         <v>2</v>
       </c>
@@ -33213,6 +34923,9 @@
       <c r="J421" s="6" t="s">
         <v>868</v>
       </c>
+      <c r="L421" t="s">
+        <v>3774</v>
+      </c>
       <c r="M421">
         <v>2</v>
       </c>
@@ -33255,6 +34968,9 @@
       <c r="J422" s="6" t="s">
         <v>868</v>
       </c>
+      <c r="L422" t="s">
+        <v>3775</v>
+      </c>
       <c r="M422">
         <v>2</v>
       </c>
@@ -33297,6 +35013,9 @@
       <c r="J423" s="6" t="s">
         <v>868</v>
       </c>
+      <c r="L423" t="s">
+        <v>3776</v>
+      </c>
       <c r="M423">
         <v>2</v>
       </c>
@@ -33339,6 +35058,9 @@
       <c r="J424" s="6" t="s">
         <v>868</v>
       </c>
+      <c r="L424" t="s">
+        <v>3777</v>
+      </c>
       <c r="M424">
         <v>2</v>
       </c>
@@ -33381,6 +35103,9 @@
       <c r="J425" s="6" t="s">
         <v>868</v>
       </c>
+      <c r="L425" t="s">
+        <v>3778</v>
+      </c>
       <c r="M425">
         <v>2</v>
       </c>
@@ -33423,6 +35148,9 @@
       <c r="J426" s="6" t="s">
         <v>868</v>
       </c>
+      <c r="L426" t="s">
+        <v>3779</v>
+      </c>
       <c r="M426">
         <v>2</v>
       </c>
@@ -33465,6 +35193,9 @@
       <c r="J427" s="6" t="s">
         <v>868</v>
       </c>
+      <c r="L427" t="s">
+        <v>3780</v>
+      </c>
       <c r="M427">
         <v>2</v>
       </c>
@@ -33507,6 +35238,9 @@
       <c r="J428" s="6" t="s">
         <v>887</v>
       </c>
+      <c r="L428" t="s">
+        <v>3781</v>
+      </c>
       <c r="M428">
         <v>2</v>
       </c>
@@ -33549,6 +35283,9 @@
       <c r="J429" s="6" t="s">
         <v>887</v>
       </c>
+      <c r="L429" t="s">
+        <v>3782</v>
+      </c>
       <c r="M429">
         <v>2</v>
       </c>
@@ -33591,6 +35328,9 @@
       <c r="J430" s="6" t="s">
         <v>887</v>
       </c>
+      <c r="L430" t="s">
+        <v>3783</v>
+      </c>
       <c r="M430">
         <v>2</v>
       </c>
@@ -33633,6 +35373,9 @@
       <c r="J431" s="6" t="s">
         <v>887</v>
       </c>
+      <c r="L431" t="s">
+        <v>3784</v>
+      </c>
       <c r="M431">
         <v>2</v>
       </c>
@@ -33675,6 +35418,9 @@
       <c r="J432" s="6" t="s">
         <v>887</v>
       </c>
+      <c r="L432" t="s">
+        <v>3785</v>
+      </c>
       <c r="M432">
         <v>2</v>
       </c>
@@ -33717,6 +35463,9 @@
       <c r="J433" s="6" t="s">
         <v>887</v>
       </c>
+      <c r="L433" t="s">
+        <v>3786</v>
+      </c>
       <c r="M433">
         <v>2</v>
       </c>
@@ -33759,6 +35508,9 @@
       <c r="J434" s="6" t="s">
         <v>887</v>
       </c>
+      <c r="L434" t="s">
+        <v>3787</v>
+      </c>
       <c r="M434">
         <v>2</v>
       </c>
@@ -33801,6 +35553,9 @@
       <c r="J435" s="6" t="s">
         <v>887</v>
       </c>
+      <c r="L435" t="s">
+        <v>3788</v>
+      </c>
       <c r="M435">
         <v>2</v>
       </c>
@@ -33843,6 +35598,9 @@
       <c r="J436" s="6" t="s">
         <v>887</v>
       </c>
+      <c r="L436" t="s">
+        <v>3789</v>
+      </c>
       <c r="M436">
         <v>2</v>
       </c>
@@ -33885,6 +35643,9 @@
       <c r="J437" s="6" t="s">
         <v>906</v>
       </c>
+      <c r="L437" t="s">
+        <v>3790</v>
+      </c>
       <c r="M437">
         <v>2</v>
       </c>
@@ -33927,6 +35688,9 @@
       <c r="J438" s="6" t="s">
         <v>906</v>
       </c>
+      <c r="L438" t="s">
+        <v>3791</v>
+      </c>
       <c r="M438">
         <v>2</v>
       </c>
@@ -33969,6 +35733,9 @@
       <c r="J439" s="6" t="s">
         <v>906</v>
       </c>
+      <c r="L439" t="s">
+        <v>3792</v>
+      </c>
       <c r="M439">
         <v>2</v>
       </c>
@@ -34011,6 +35778,9 @@
       <c r="J440" s="6" t="s">
         <v>906</v>
       </c>
+      <c r="L440" t="s">
+        <v>3793</v>
+      </c>
       <c r="M440">
         <v>2</v>
       </c>
@@ -34053,6 +35823,9 @@
       <c r="J441" s="6" t="s">
         <v>906</v>
       </c>
+      <c r="L441" t="s">
+        <v>3794</v>
+      </c>
       <c r="M441">
         <v>2</v>
       </c>
@@ -34095,6 +35868,9 @@
       <c r="J442" s="6" t="s">
         <v>906</v>
       </c>
+      <c r="L442" t="s">
+        <v>3795</v>
+      </c>
       <c r="M442">
         <v>2</v>
       </c>
@@ -34137,6 +35913,9 @@
       <c r="J443" s="6" t="s">
         <v>906</v>
       </c>
+      <c r="L443" t="s">
+        <v>3796</v>
+      </c>
       <c r="M443">
         <v>2</v>
       </c>
@@ -34179,6 +35958,9 @@
       <c r="J444" s="6" t="s">
         <v>906</v>
       </c>
+      <c r="L444" t="s">
+        <v>3797</v>
+      </c>
       <c r="M444">
         <v>2</v>
       </c>
@@ -34221,6 +36003,9 @@
       <c r="J445" s="6" t="s">
         <v>906</v>
       </c>
+      <c r="L445" t="s">
+        <v>3798</v>
+      </c>
       <c r="M445">
         <v>2</v>
       </c>
@@ -34263,6 +36048,9 @@
       <c r="J446" s="6" t="s">
         <v>925</v>
       </c>
+      <c r="L446" t="s">
+        <v>3799</v>
+      </c>
       <c r="M446">
         <v>2</v>
       </c>
@@ -34305,6 +36093,9 @@
       <c r="J447" s="6" t="s">
         <v>925</v>
       </c>
+      <c r="L447" t="s">
+        <v>3800</v>
+      </c>
       <c r="M447">
         <v>2</v>
       </c>
@@ -34347,6 +36138,9 @@
       <c r="J448" s="6" t="s">
         <v>925</v>
       </c>
+      <c r="L448" t="s">
+        <v>3801</v>
+      </c>
       <c r="M448">
         <v>2</v>
       </c>
@@ -34389,6 +36183,9 @@
       <c r="J449" s="6" t="s">
         <v>925</v>
       </c>
+      <c r="L449" t="s">
+        <v>3802</v>
+      </c>
       <c r="M449">
         <v>2</v>
       </c>
@@ -34431,6 +36228,9 @@
       <c r="J450" s="6" t="s">
         <v>925</v>
       </c>
+      <c r="L450" t="s">
+        <v>3803</v>
+      </c>
       <c r="M450">
         <v>2</v>
       </c>
@@ -34473,6 +36273,9 @@
       <c r="J451" s="6" t="s">
         <v>925</v>
       </c>
+      <c r="L451" t="s">
+        <v>3804</v>
+      </c>
       <c r="M451">
         <v>2</v>
       </c>
@@ -34515,6 +36318,9 @@
       <c r="J452" s="6" t="s">
         <v>925</v>
       </c>
+      <c r="L452" t="s">
+        <v>3805</v>
+      </c>
       <c r="M452">
         <v>2</v>
       </c>
@@ -34557,6 +36363,9 @@
       <c r="J453" s="6" t="s">
         <v>925</v>
       </c>
+      <c r="L453" t="s">
+        <v>3806</v>
+      </c>
       <c r="M453">
         <v>2</v>
       </c>
@@ -34599,6 +36408,9 @@
       <c r="J454" s="6" t="s">
         <v>925</v>
       </c>
+      <c r="L454" t="s">
+        <v>3807</v>
+      </c>
       <c r="M454">
         <v>2</v>
       </c>
@@ -34641,6 +36453,9 @@
       <c r="J455" s="6" t="s">
         <v>944</v>
       </c>
+      <c r="L455" t="s">
+        <v>3808</v>
+      </c>
       <c r="M455">
         <v>2</v>
       </c>
@@ -34683,6 +36498,9 @@
       <c r="J456" s="6" t="s">
         <v>944</v>
       </c>
+      <c r="L456" t="s">
+        <v>3809</v>
+      </c>
       <c r="M456">
         <v>2</v>
       </c>
@@ -34725,6 +36543,9 @@
       <c r="J457" s="6" t="s">
         <v>944</v>
       </c>
+      <c r="L457" t="s">
+        <v>3810</v>
+      </c>
       <c r="M457">
         <v>2</v>
       </c>
@@ -34767,6 +36588,9 @@
       <c r="J458" s="6" t="s">
         <v>944</v>
       </c>
+      <c r="L458" t="s">
+        <v>3811</v>
+      </c>
       <c r="M458">
         <v>2</v>
       </c>
@@ -34809,6 +36633,9 @@
       <c r="J459" s="6" t="s">
         <v>944</v>
       </c>
+      <c r="L459" t="s">
+        <v>3812</v>
+      </c>
       <c r="M459">
         <v>2</v>
       </c>
@@ -34851,6 +36678,9 @@
       <c r="J460" s="6" t="s">
         <v>944</v>
       </c>
+      <c r="L460" t="s">
+        <v>3813</v>
+      </c>
       <c r="M460">
         <v>2</v>
       </c>
@@ -34893,6 +36723,9 @@
       <c r="J461" s="6" t="s">
         <v>944</v>
       </c>
+      <c r="L461" t="s">
+        <v>3814</v>
+      </c>
       <c r="M461">
         <v>2</v>
       </c>
@@ -34935,6 +36768,9 @@
       <c r="J462" s="6" t="s">
         <v>944</v>
       </c>
+      <c r="L462" t="s">
+        <v>3815</v>
+      </c>
       <c r="M462">
         <v>2</v>
       </c>
@@ -34977,6 +36813,9 @@
       <c r="J463" s="6" t="s">
         <v>944</v>
       </c>
+      <c r="L463" t="s">
+        <v>3816</v>
+      </c>
       <c r="M463">
         <v>2</v>
       </c>
@@ -35019,6 +36858,9 @@
       <c r="J464" s="6" t="s">
         <v>963</v>
       </c>
+      <c r="L464" t="s">
+        <v>3817</v>
+      </c>
       <c r="M464">
         <v>2</v>
       </c>
@@ -35061,6 +36903,9 @@
       <c r="J465" s="6" t="s">
         <v>963</v>
       </c>
+      <c r="L465" t="s">
+        <v>3818</v>
+      </c>
       <c r="M465">
         <v>2</v>
       </c>
@@ -35103,6 +36948,9 @@
       <c r="J466" s="6" t="s">
         <v>963</v>
       </c>
+      <c r="L466" t="s">
+        <v>3819</v>
+      </c>
       <c r="M466">
         <v>2</v>
       </c>
@@ -35145,6 +36993,9 @@
       <c r="J467" s="6" t="s">
         <v>963</v>
       </c>
+      <c r="L467" t="s">
+        <v>3820</v>
+      </c>
       <c r="M467">
         <v>2</v>
       </c>
@@ -35187,6 +37038,9 @@
       <c r="J468" s="6" t="s">
         <v>963</v>
       </c>
+      <c r="L468" t="s">
+        <v>3821</v>
+      </c>
       <c r="M468">
         <v>2</v>
       </c>
@@ -35229,6 +37083,9 @@
       <c r="J469" s="6" t="s">
         <v>963</v>
       </c>
+      <c r="L469" t="s">
+        <v>3822</v>
+      </c>
       <c r="M469">
         <v>2</v>
       </c>
@@ -35271,6 +37128,9 @@
       <c r="J470" s="6" t="s">
         <v>963</v>
       </c>
+      <c r="L470" t="s">
+        <v>3823</v>
+      </c>
       <c r="M470">
         <v>2</v>
       </c>
@@ -35313,6 +37173,9 @@
       <c r="J471" s="6" t="s">
         <v>963</v>
       </c>
+      <c r="L471" t="s">
+        <v>3824</v>
+      </c>
       <c r="M471">
         <v>2</v>
       </c>
@@ -35355,6 +37218,9 @@
       <c r="J472" s="6" t="s">
         <v>963</v>
       </c>
+      <c r="L472" t="s">
+        <v>3825</v>
+      </c>
       <c r="M472">
         <v>2</v>
       </c>
@@ -35397,6 +37263,9 @@
       <c r="J473" s="6" t="s">
         <v>982</v>
       </c>
+      <c r="L473" t="s">
+        <v>3826</v>
+      </c>
       <c r="M473">
         <v>2</v>
       </c>
@@ -35439,6 +37308,9 @@
       <c r="J474" s="6" t="s">
         <v>982</v>
       </c>
+      <c r="L474" t="s">
+        <v>3827</v>
+      </c>
       <c r="M474">
         <v>2</v>
       </c>
@@ -35481,6 +37353,9 @@
       <c r="J475" s="6" t="s">
         <v>982</v>
       </c>
+      <c r="L475" t="s">
+        <v>3828</v>
+      </c>
       <c r="M475">
         <v>2</v>
       </c>
@@ -35523,6 +37398,9 @@
       <c r="J476" s="6" t="s">
         <v>982</v>
       </c>
+      <c r="L476" t="s">
+        <v>3829</v>
+      </c>
       <c r="M476">
         <v>2</v>
       </c>
@@ -35565,6 +37443,9 @@
       <c r="J477" s="6" t="s">
         <v>982</v>
       </c>
+      <c r="L477" t="s">
+        <v>3830</v>
+      </c>
       <c r="M477">
         <v>2</v>
       </c>
@@ -35607,6 +37488,9 @@
       <c r="J478" s="6" t="s">
         <v>982</v>
       </c>
+      <c r="L478" t="s">
+        <v>3831</v>
+      </c>
       <c r="M478">
         <v>2</v>
       </c>
@@ -35649,6 +37533,9 @@
       <c r="J479" s="6" t="s">
         <v>982</v>
       </c>
+      <c r="L479" t="s">
+        <v>3832</v>
+      </c>
       <c r="M479">
         <v>2</v>
       </c>
@@ -35691,6 +37578,9 @@
       <c r="J480" s="6" t="s">
         <v>982</v>
       </c>
+      <c r="L480" t="s">
+        <v>3833</v>
+      </c>
       <c r="M480">
         <v>2</v>
       </c>
@@ -35733,6 +37623,9 @@
       <c r="J481" s="6" t="s">
         <v>982</v>
       </c>
+      <c r="L481" t="s">
+        <v>3834</v>
+      </c>
       <c r="M481">
         <v>2</v>
       </c>
@@ -35775,6 +37668,9 @@
       <c r="J482" s="6" t="s">
         <v>1001</v>
       </c>
+      <c r="L482" t="s">
+        <v>3835</v>
+      </c>
       <c r="M482">
         <v>2</v>
       </c>
@@ -35817,6 +37713,9 @@
       <c r="J483" s="6" t="s">
         <v>1001</v>
       </c>
+      <c r="L483" t="s">
+        <v>3836</v>
+      </c>
       <c r="M483">
         <v>2</v>
       </c>
@@ -35859,6 +37758,9 @@
       <c r="J484" s="6" t="s">
         <v>1001</v>
       </c>
+      <c r="L484" t="s">
+        <v>3837</v>
+      </c>
       <c r="M484">
         <v>2</v>
       </c>
@@ -35901,6 +37803,9 @@
       <c r="J485" s="6" t="s">
         <v>1001</v>
       </c>
+      <c r="L485" t="s">
+        <v>3838</v>
+      </c>
       <c r="M485">
         <v>2</v>
       </c>
@@ -35943,6 +37848,9 @@
       <c r="J486" s="6" t="s">
         <v>1001</v>
       </c>
+      <c r="L486" t="s">
+        <v>3839</v>
+      </c>
       <c r="M486">
         <v>2</v>
       </c>
@@ -35985,6 +37893,9 @@
       <c r="J487" s="6" t="s">
         <v>1001</v>
       </c>
+      <c r="L487" t="s">
+        <v>3840</v>
+      </c>
       <c r="M487">
         <v>2</v>
       </c>
@@ -36027,6 +37938,9 @@
       <c r="J488" s="6" t="s">
         <v>1001</v>
       </c>
+      <c r="L488" t="s">
+        <v>3841</v>
+      </c>
       <c r="M488">
         <v>2</v>
       </c>
@@ -36069,6 +37983,9 @@
       <c r="J489" s="6" t="s">
         <v>1001</v>
       </c>
+      <c r="L489" t="s">
+        <v>3842</v>
+      </c>
       <c r="M489">
         <v>2</v>
       </c>
@@ -36111,6 +38028,9 @@
       <c r="J490" s="6" t="s">
         <v>1001</v>
       </c>
+      <c r="L490" t="s">
+        <v>3843</v>
+      </c>
       <c r="M490">
         <v>2</v>
       </c>
@@ -36153,6 +38073,9 @@
       <c r="J491" s="6" t="s">
         <v>1020</v>
       </c>
+      <c r="L491" t="s">
+        <v>3844</v>
+      </c>
       <c r="M491">
         <v>2</v>
       </c>
@@ -36195,6 +38118,9 @@
       <c r="J492" s="6" t="s">
         <v>1020</v>
       </c>
+      <c r="L492" t="s">
+        <v>3845</v>
+      </c>
       <c r="M492">
         <v>2</v>
       </c>
@@ -36237,6 +38163,9 @@
       <c r="J493" s="6" t="s">
         <v>1020</v>
       </c>
+      <c r="L493" t="s">
+        <v>3846</v>
+      </c>
       <c r="M493">
         <v>2</v>
       </c>
@@ -36279,6 +38208,9 @@
       <c r="J494" s="6" t="s">
         <v>1020</v>
       </c>
+      <c r="L494" t="s">
+        <v>3847</v>
+      </c>
       <c r="M494">
         <v>2</v>
       </c>
@@ -36321,6 +38253,9 @@
       <c r="J495" s="6" t="s">
         <v>1020</v>
       </c>
+      <c r="L495" t="s">
+        <v>3848</v>
+      </c>
       <c r="M495">
         <v>2</v>
       </c>
@@ -36363,6 +38298,9 @@
       <c r="J496" s="6" t="s">
         <v>1020</v>
       </c>
+      <c r="L496" t="s">
+        <v>3849</v>
+      </c>
       <c r="M496">
         <v>2</v>
       </c>
@@ -36405,6 +38343,9 @@
       <c r="J497" s="6" t="s">
         <v>1020</v>
       </c>
+      <c r="L497" t="s">
+        <v>3850</v>
+      </c>
       <c r="M497">
         <v>2</v>
       </c>
@@ -36447,6 +38388,9 @@
       <c r="J498" s="6" t="s">
         <v>1020</v>
       </c>
+      <c r="L498" t="s">
+        <v>3851</v>
+      </c>
       <c r="M498">
         <v>2</v>
       </c>
@@ -36489,6 +38433,9 @@
       <c r="J499" s="6" t="s">
         <v>1020</v>
       </c>
+      <c r="L499" t="s">
+        <v>3852</v>
+      </c>
       <c r="M499">
         <v>2</v>
       </c>
@@ -36531,6 +38478,9 @@
       <c r="J500" s="6" t="s">
         <v>1039</v>
       </c>
+      <c r="L500" t="s">
+        <v>3853</v>
+      </c>
       <c r="M500">
         <v>2</v>
       </c>
@@ -36573,6 +38523,9 @@
       <c r="J501" s="6" t="s">
         <v>1039</v>
       </c>
+      <c r="L501" t="s">
+        <v>3854</v>
+      </c>
       <c r="M501">
         <v>2</v>
       </c>
@@ -36615,6 +38568,9 @@
       <c r="J502" s="6" t="s">
         <v>1039</v>
       </c>
+      <c r="L502" t="s">
+        <v>3855</v>
+      </c>
       <c r="M502">
         <v>2</v>
       </c>
@@ -36657,6 +38613,9 @@
       <c r="J503" s="6" t="s">
         <v>1039</v>
       </c>
+      <c r="L503" t="s">
+        <v>3856</v>
+      </c>
       <c r="M503">
         <v>2</v>
       </c>
@@ -36699,6 +38658,9 @@
       <c r="J504" s="6" t="s">
         <v>1039</v>
       </c>
+      <c r="L504" t="s">
+        <v>3857</v>
+      </c>
       <c r="M504">
         <v>2</v>
       </c>
@@ -36741,6 +38703,9 @@
       <c r="J505" s="6" t="s">
         <v>1039</v>
       </c>
+      <c r="L505" t="s">
+        <v>3858</v>
+      </c>
       <c r="M505">
         <v>2</v>
       </c>
@@ -36783,6 +38748,9 @@
       <c r="J506" s="6" t="s">
         <v>1039</v>
       </c>
+      <c r="L506" t="s">
+        <v>3859</v>
+      </c>
       <c r="M506">
         <v>2</v>
       </c>
@@ -36825,6 +38793,9 @@
       <c r="J507" s="6" t="s">
         <v>1039</v>
       </c>
+      <c r="L507" t="s">
+        <v>3860</v>
+      </c>
       <c r="M507">
         <v>2</v>
       </c>
@@ -36867,6 +38838,9 @@
       <c r="J508" s="6" t="s">
         <v>1039</v>
       </c>
+      <c r="L508" t="s">
+        <v>3861</v>
+      </c>
       <c r="M508">
         <v>2</v>
       </c>
@@ -36909,6 +38883,9 @@
       <c r="J509" s="6" t="s">
         <v>1058</v>
       </c>
+      <c r="L509" t="s">
+        <v>3862</v>
+      </c>
       <c r="M509">
         <v>2</v>
       </c>
@@ -36951,6 +38928,9 @@
       <c r="J510" s="6" t="s">
         <v>1058</v>
       </c>
+      <c r="L510" t="s">
+        <v>3863</v>
+      </c>
       <c r="M510">
         <v>2</v>
       </c>
@@ -36993,6 +38973,9 @@
       <c r="J511" s="6" t="s">
         <v>1058</v>
       </c>
+      <c r="L511" t="s">
+        <v>3864</v>
+      </c>
       <c r="M511">
         <v>2</v>
       </c>
@@ -37035,6 +39018,9 @@
       <c r="J512" s="6" t="s">
         <v>1058</v>
       </c>
+      <c r="L512" t="s">
+        <v>3865</v>
+      </c>
       <c r="M512">
         <v>2</v>
       </c>
@@ -37077,6 +39063,9 @@
       <c r="J513" s="6" t="s">
         <v>1058</v>
       </c>
+      <c r="L513" t="s">
+        <v>3866</v>
+      </c>
       <c r="M513">
         <v>2</v>
       </c>
@@ -37119,6 +39108,9 @@
       <c r="J514" s="6" t="s">
         <v>1058</v>
       </c>
+      <c r="L514" t="s">
+        <v>3867</v>
+      </c>
       <c r="M514">
         <v>2</v>
       </c>
@@ -37161,6 +39153,9 @@
       <c r="J515" s="6" t="s">
         <v>1058</v>
       </c>
+      <c r="L515" t="s">
+        <v>3868</v>
+      </c>
       <c r="M515">
         <v>2</v>
       </c>
@@ -37203,6 +39198,9 @@
       <c r="J516" s="6" t="s">
         <v>1058</v>
       </c>
+      <c r="L516" t="s">
+        <v>3869</v>
+      </c>
       <c r="M516">
         <v>2</v>
       </c>
@@ -37245,6 +39243,9 @@
       <c r="J517" s="6" t="s">
         <v>1058</v>
       </c>
+      <c r="L517" t="s">
+        <v>3870</v>
+      </c>
       <c r="M517">
         <v>2</v>
       </c>
@@ -37287,6 +39288,9 @@
       <c r="J518" s="6" t="s">
         <v>1077</v>
       </c>
+      <c r="L518" t="s">
+        <v>3871</v>
+      </c>
       <c r="M518">
         <v>2</v>
       </c>
@@ -37329,6 +39333,9 @@
       <c r="J519" s="6" t="s">
         <v>1077</v>
       </c>
+      <c r="L519" t="s">
+        <v>3872</v>
+      </c>
       <c r="M519">
         <v>2</v>
       </c>
@@ -37371,6 +39378,9 @@
       <c r="J520" s="6" t="s">
         <v>1077</v>
       </c>
+      <c r="L520" t="s">
+        <v>3873</v>
+      </c>
       <c r="M520">
         <v>2</v>
       </c>
@@ -37413,6 +39423,9 @@
       <c r="J521" s="6" t="s">
         <v>1077</v>
       </c>
+      <c r="L521" t="s">
+        <v>3874</v>
+      </c>
       <c r="M521">
         <v>2</v>
       </c>
@@ -37455,6 +39468,9 @@
       <c r="J522" s="6" t="s">
         <v>1077</v>
       </c>
+      <c r="L522" t="s">
+        <v>3875</v>
+      </c>
       <c r="M522">
         <v>2</v>
       </c>
@@ -37497,6 +39513,9 @@
       <c r="J523" s="6" t="s">
         <v>1077</v>
       </c>
+      <c r="L523" t="s">
+        <v>3876</v>
+      </c>
       <c r="M523">
         <v>2</v>
       </c>
@@ -37539,6 +39558,9 @@
       <c r="J524" s="6" t="s">
         <v>1077</v>
       </c>
+      <c r="L524" t="s">
+        <v>3877</v>
+      </c>
       <c r="M524">
         <v>2</v>
       </c>
@@ -37581,6 +39603,9 @@
       <c r="J525" s="6" t="s">
         <v>1077</v>
       </c>
+      <c r="L525" t="s">
+        <v>3878</v>
+      </c>
       <c r="M525">
         <v>2</v>
       </c>
@@ -37623,6 +39648,9 @@
       <c r="J526" s="6" t="s">
         <v>1077</v>
       </c>
+      <c r="L526" t="s">
+        <v>3879</v>
+      </c>
       <c r="M526">
         <v>2</v>
       </c>
@@ -37665,6 +39693,9 @@
       <c r="J527" s="6" t="s">
         <v>1096</v>
       </c>
+      <c r="L527" t="s">
+        <v>3880</v>
+      </c>
       <c r="M527">
         <v>2</v>
       </c>
@@ -37707,6 +39738,9 @@
       <c r="J528" s="6" t="s">
         <v>1096</v>
       </c>
+      <c r="L528" t="s">
+        <v>3881</v>
+      </c>
       <c r="M528">
         <v>2</v>
       </c>
@@ -37749,6 +39783,9 @@
       <c r="J529" s="6" t="s">
         <v>1096</v>
       </c>
+      <c r="L529" t="s">
+        <v>3882</v>
+      </c>
       <c r="M529">
         <v>2</v>
       </c>
@@ -37791,6 +39828,9 @@
       <c r="J530" s="6" t="s">
         <v>1096</v>
       </c>
+      <c r="L530" t="s">
+        <v>3883</v>
+      </c>
       <c r="M530">
         <v>2</v>
       </c>
@@ -37833,6 +39873,9 @@
       <c r="J531" s="6" t="s">
         <v>1096</v>
       </c>
+      <c r="L531" t="s">
+        <v>3884</v>
+      </c>
       <c r="M531">
         <v>2</v>
       </c>
@@ -37875,6 +39918,9 @@
       <c r="J532" s="6" t="s">
         <v>1096</v>
       </c>
+      <c r="L532" t="s">
+        <v>3885</v>
+      </c>
       <c r="M532">
         <v>2</v>
       </c>
@@ -37917,6 +39963,9 @@
       <c r="J533" s="6" t="s">
         <v>1096</v>
       </c>
+      <c r="L533" t="s">
+        <v>3886</v>
+      </c>
       <c r="M533">
         <v>2</v>
       </c>
@@ -37959,6 +40008,9 @@
       <c r="J534" s="6" t="s">
         <v>1096</v>
       </c>
+      <c r="L534" t="s">
+        <v>3887</v>
+      </c>
       <c r="M534">
         <v>2</v>
       </c>
@@ -38001,6 +40053,9 @@
       <c r="J535" s="6" t="s">
         <v>1096</v>
       </c>
+      <c r="L535" t="s">
+        <v>3888</v>
+      </c>
       <c r="M535">
         <v>2</v>
       </c>
@@ -38043,6 +40098,9 @@
       <c r="J536" s="6" t="s">
         <v>1115</v>
       </c>
+      <c r="L536" t="s">
+        <v>3889</v>
+      </c>
       <c r="M536">
         <v>2</v>
       </c>
@@ -38085,6 +40143,9 @@
       <c r="J537" s="6" t="s">
         <v>1115</v>
       </c>
+      <c r="L537" t="s">
+        <v>3890</v>
+      </c>
       <c r="M537">
         <v>2</v>
       </c>
@@ -38127,6 +40188,9 @@
       <c r="J538" s="6" t="s">
         <v>1115</v>
       </c>
+      <c r="L538" t="s">
+        <v>3891</v>
+      </c>
       <c r="M538">
         <v>2</v>
       </c>
@@ -38169,6 +40233,9 @@
       <c r="J539" s="6" t="s">
         <v>1115</v>
       </c>
+      <c r="L539" t="s">
+        <v>3892</v>
+      </c>
       <c r="M539">
         <v>2</v>
       </c>
@@ -38211,6 +40278,9 @@
       <c r="J540" s="6" t="s">
         <v>1115</v>
       </c>
+      <c r="L540" t="s">
+        <v>3893</v>
+      </c>
       <c r="M540">
         <v>2</v>
       </c>
@@ -38253,6 +40323,9 @@
       <c r="J541" s="6" t="s">
         <v>1115</v>
       </c>
+      <c r="L541" t="s">
+        <v>3894</v>
+      </c>
       <c r="M541">
         <v>2</v>
       </c>
@@ -38295,6 +40368,9 @@
       <c r="J542" s="6" t="s">
         <v>1115</v>
       </c>
+      <c r="L542" t="s">
+        <v>3895</v>
+      </c>
       <c r="M542">
         <v>2</v>
       </c>
@@ -38337,6 +40413,9 @@
       <c r="J543" s="6" t="s">
         <v>1115</v>
       </c>
+      <c r="L543" t="s">
+        <v>3896</v>
+      </c>
       <c r="M543">
         <v>2</v>
       </c>
@@ -38379,6 +40458,9 @@
       <c r="J544" s="6" t="s">
         <v>1115</v>
       </c>
+      <c r="L544" t="s">
+        <v>3897</v>
+      </c>
       <c r="M544">
         <v>2</v>
       </c>
@@ -38421,6 +40503,9 @@
       <c r="J545" s="6" t="s">
         <v>1134</v>
       </c>
+      <c r="L545" t="s">
+        <v>3898</v>
+      </c>
       <c r="M545">
         <v>2</v>
       </c>
@@ -38463,6 +40548,9 @@
       <c r="J546" s="6" t="s">
         <v>1134</v>
       </c>
+      <c r="L546" t="s">
+        <v>3899</v>
+      </c>
       <c r="M546">
         <v>2</v>
       </c>
@@ -38505,6 +40593,9 @@
       <c r="J547" s="6" t="s">
         <v>1134</v>
       </c>
+      <c r="L547" t="s">
+        <v>3900</v>
+      </c>
       <c r="M547">
         <v>2</v>
       </c>
@@ -38547,6 +40638,9 @@
       <c r="J548" s="6" t="s">
         <v>1134</v>
       </c>
+      <c r="L548" t="s">
+        <v>3901</v>
+      </c>
       <c r="M548">
         <v>2</v>
       </c>
@@ -38589,6 +40683,9 @@
       <c r="J549" s="6" t="s">
         <v>1134</v>
       </c>
+      <c r="L549" t="s">
+        <v>3902</v>
+      </c>
       <c r="M549">
         <v>2</v>
       </c>
@@ -38631,6 +40728,9 @@
       <c r="J550" s="6" t="s">
         <v>1134</v>
       </c>
+      <c r="L550" t="s">
+        <v>3903</v>
+      </c>
       <c r="M550">
         <v>2</v>
       </c>
@@ -38673,6 +40773,9 @@
       <c r="J551" s="6" t="s">
         <v>1134</v>
       </c>
+      <c r="L551" t="s">
+        <v>3904</v>
+      </c>
       <c r="M551">
         <v>2</v>
       </c>
@@ -38715,6 +40818,9 @@
       <c r="J552" s="6" t="s">
         <v>1134</v>
       </c>
+      <c r="L552" t="s">
+        <v>3905</v>
+      </c>
       <c r="M552">
         <v>2</v>
       </c>
@@ -38757,6 +40863,9 @@
       <c r="J553" s="6" t="s">
         <v>1134</v>
       </c>
+      <c r="L553" t="s">
+        <v>3906</v>
+      </c>
       <c r="M553">
         <v>2</v>
       </c>
@@ -38799,6 +40908,9 @@
       <c r="J554" s="6" t="s">
         <v>1153</v>
       </c>
+      <c r="L554" t="s">
+        <v>3907</v>
+      </c>
       <c r="M554">
         <v>2</v>
       </c>
@@ -38841,6 +40953,9 @@
       <c r="J555" s="6" t="s">
         <v>1153</v>
       </c>
+      <c r="L555" t="s">
+        <v>3908</v>
+      </c>
       <c r="M555">
         <v>2</v>
       </c>
@@ -38883,6 +40998,9 @@
       <c r="J556" s="6" t="s">
         <v>1153</v>
       </c>
+      <c r="L556" t="s">
+        <v>3909</v>
+      </c>
       <c r="M556">
         <v>2</v>
       </c>
@@ -38925,6 +41043,9 @@
       <c r="J557" s="6" t="s">
         <v>1153</v>
       </c>
+      <c r="L557" t="s">
+        <v>3910</v>
+      </c>
       <c r="M557">
         <v>2</v>
       </c>
@@ -38967,6 +41088,9 @@
       <c r="J558" s="6" t="s">
         <v>1153</v>
       </c>
+      <c r="L558" t="s">
+        <v>3911</v>
+      </c>
       <c r="M558">
         <v>2</v>
       </c>
@@ -39009,6 +41133,9 @@
       <c r="J559" s="6" t="s">
         <v>1153</v>
       </c>
+      <c r="L559" t="s">
+        <v>3912</v>
+      </c>
       <c r="M559">
         <v>2</v>
       </c>
@@ -39051,6 +41178,9 @@
       <c r="J560" s="6" t="s">
         <v>1153</v>
       </c>
+      <c r="L560" t="s">
+        <v>3913</v>
+      </c>
       <c r="M560">
         <v>2</v>
       </c>
@@ -39093,6 +41223,9 @@
       <c r="J561" s="6" t="s">
         <v>1153</v>
       </c>
+      <c r="L561" t="s">
+        <v>3914</v>
+      </c>
       <c r="M561">
         <v>2</v>
       </c>
@@ -39135,6 +41268,9 @@
       <c r="J562" s="6" t="s">
         <v>1153</v>
       </c>
+      <c r="L562" t="s">
+        <v>3915</v>
+      </c>
       <c r="M562">
         <v>2</v>
       </c>
@@ -39177,6 +41313,9 @@
       <c r="J563" s="6" t="s">
         <v>1172</v>
       </c>
+      <c r="L563" t="s">
+        <v>3916</v>
+      </c>
       <c r="M563">
         <v>2</v>
       </c>
@@ -39219,6 +41358,9 @@
       <c r="J564" s="6" t="s">
         <v>1172</v>
       </c>
+      <c r="L564" t="s">
+        <v>3917</v>
+      </c>
       <c r="M564">
         <v>2</v>
       </c>
@@ -39261,6 +41403,9 @@
       <c r="J565" s="6" t="s">
         <v>1172</v>
       </c>
+      <c r="L565" t="s">
+        <v>3918</v>
+      </c>
       <c r="M565">
         <v>2</v>
       </c>
@@ -39303,6 +41448,9 @@
       <c r="J566" s="6" t="s">
         <v>1172</v>
       </c>
+      <c r="L566" t="s">
+        <v>3919</v>
+      </c>
       <c r="M566">
         <v>2</v>
       </c>
@@ -39345,6 +41493,9 @@
       <c r="J567" s="6" t="s">
         <v>1172</v>
       </c>
+      <c r="L567" t="s">
+        <v>3920</v>
+      </c>
       <c r="M567">
         <v>2</v>
       </c>
@@ -39387,6 +41538,9 @@
       <c r="J568" s="6" t="s">
         <v>1172</v>
       </c>
+      <c r="L568" t="s">
+        <v>3921</v>
+      </c>
       <c r="M568">
         <v>2</v>
       </c>
@@ -39429,6 +41583,9 @@
       <c r="J569" s="6" t="s">
         <v>1172</v>
       </c>
+      <c r="L569" t="s">
+        <v>3922</v>
+      </c>
       <c r="M569">
         <v>2</v>
       </c>
@@ -39471,6 +41628,9 @@
       <c r="J570" s="6" t="s">
         <v>1172</v>
       </c>
+      <c r="L570" t="s">
+        <v>3923</v>
+      </c>
       <c r="M570">
         <v>2</v>
       </c>
@@ -39513,6 +41673,9 @@
       <c r="J571" s="6" t="s">
         <v>1172</v>
       </c>
+      <c r="L571" t="s">
+        <v>3924</v>
+      </c>
       <c r="M571">
         <v>2</v>
       </c>
@@ -39555,6 +41718,9 @@
       <c r="J572" s="6" t="s">
         <v>1172</v>
       </c>
+      <c r="L572" t="s">
+        <v>3925</v>
+      </c>
       <c r="M572">
         <v>2</v>
       </c>
@@ -39597,6 +41763,9 @@
       <c r="J573" s="6" t="s">
         <v>1172</v>
       </c>
+      <c r="L573" t="s">
+        <v>3926</v>
+      </c>
       <c r="M573">
         <v>2</v>
       </c>
@@ -39639,6 +41808,9 @@
       <c r="J574" s="6" t="s">
         <v>1172</v>
       </c>
+      <c r="L574" t="s">
+        <v>3927</v>
+      </c>
       <c r="M574">
         <v>2</v>
       </c>
@@ -39681,6 +41853,9 @@
       <c r="J575" s="6" t="s">
         <v>1172</v>
       </c>
+      <c r="L575" t="s">
+        <v>3928</v>
+      </c>
       <c r="M575">
         <v>2</v>
       </c>
@@ -39723,6 +41898,9 @@
       <c r="J576" s="6" t="s">
         <v>1172</v>
       </c>
+      <c r="L576" t="s">
+        <v>3929</v>
+      </c>
       <c r="M576">
         <v>2</v>
       </c>
@@ -39765,6 +41943,9 @@
       <c r="J577" s="6" t="s">
         <v>1172</v>
       </c>
+      <c r="L577" t="s">
+        <v>3930</v>
+      </c>
       <c r="M577">
         <v>2</v>
       </c>
@@ -39807,6 +41988,9 @@
       <c r="J578" s="6" t="s">
         <v>1172</v>
       </c>
+      <c r="L578" t="s">
+        <v>3931</v>
+      </c>
       <c r="M578">
         <v>2</v>
       </c>
@@ -39849,6 +42033,9 @@
       <c r="J579" s="6" t="s">
         <v>1172</v>
       </c>
+      <c r="L579" t="s">
+        <v>3932</v>
+      </c>
       <c r="M579">
         <v>2</v>
       </c>
@@ -39891,6 +42078,9 @@
       <c r="J580" s="6" t="s">
         <v>1172</v>
       </c>
+      <c r="L580" t="s">
+        <v>3933</v>
+      </c>
       <c r="M580">
         <v>2</v>
       </c>
@@ -39933,6 +42123,9 @@
       <c r="J581" s="6" t="s">
         <v>1172</v>
       </c>
+      <c r="L581" t="s">
+        <v>3934</v>
+      </c>
       <c r="M581">
         <v>2</v>
       </c>
@@ -39975,6 +42168,9 @@
       <c r="J582" s="6" t="s">
         <v>1172</v>
       </c>
+      <c r="L582" t="s">
+        <v>3935</v>
+      </c>
       <c r="M582">
         <v>2</v>
       </c>
@@ -40017,6 +42213,9 @@
       <c r="J583" s="6" t="s">
         <v>1172</v>
       </c>
+      <c r="L583" t="s">
+        <v>3936</v>
+      </c>
       <c r="M583">
         <v>2</v>
       </c>
@@ -40059,6 +42258,9 @@
       <c r="J584" s="6" t="s">
         <v>1172</v>
       </c>
+      <c r="L584" t="s">
+        <v>3937</v>
+      </c>
       <c r="M584">
         <v>2</v>
       </c>
@@ -40101,6 +42303,9 @@
       <c r="J585" s="6" t="s">
         <v>1172</v>
       </c>
+      <c r="L585" t="s">
+        <v>3938</v>
+      </c>
       <c r="M585">
         <v>2</v>
       </c>
@@ -40143,6 +42348,9 @@
       <c r="J586" s="6" t="s">
         <v>1172</v>
       </c>
+      <c r="L586" t="s">
+        <v>3939</v>
+      </c>
       <c r="M586">
         <v>2</v>
       </c>
@@ -40185,6 +42393,9 @@
       <c r="J587" s="6" t="s">
         <v>1172</v>
       </c>
+      <c r="L587" t="s">
+        <v>3940</v>
+      </c>
       <c r="M587">
         <v>2</v>
       </c>
@@ -40227,6 +42438,9 @@
       <c r="J588" s="6" t="s">
         <v>1172</v>
       </c>
+      <c r="L588" t="s">
+        <v>3941</v>
+      </c>
       <c r="M588">
         <v>2</v>
       </c>
@@ -40269,6 +42483,9 @@
       <c r="J589" s="6" t="s">
         <v>1172</v>
       </c>
+      <c r="L589" t="s">
+        <v>3942</v>
+      </c>
       <c r="M589">
         <v>2</v>
       </c>
@@ -40311,6 +42528,9 @@
       <c r="J590" s="6" t="s">
         <v>1227</v>
       </c>
+      <c r="L590" t="s">
+        <v>3943</v>
+      </c>
       <c r="M590">
         <v>2</v>
       </c>
@@ -40353,6 +42573,9 @@
       <c r="J591" s="6" t="s">
         <v>1227</v>
       </c>
+      <c r="L591" t="s">
+        <v>3944</v>
+      </c>
       <c r="M591">
         <v>2</v>
       </c>
@@ -40395,6 +42618,9 @@
       <c r="J592" s="6" t="s">
         <v>1227</v>
       </c>
+      <c r="L592" t="s">
+        <v>3945</v>
+      </c>
       <c r="M592">
         <v>2</v>
       </c>
@@ -40437,6 +42663,9 @@
       <c r="J593" s="6" t="s">
         <v>1227</v>
       </c>
+      <c r="L593" t="s">
+        <v>3946</v>
+      </c>
       <c r="M593">
         <v>2</v>
       </c>
@@ -40479,6 +42708,9 @@
       <c r="J594" s="6" t="s">
         <v>1227</v>
       </c>
+      <c r="L594" t="s">
+        <v>3947</v>
+      </c>
       <c r="M594">
         <v>2</v>
       </c>
@@ -40521,6 +42753,9 @@
       <c r="J595" s="6" t="s">
         <v>1227</v>
       </c>
+      <c r="L595" t="s">
+        <v>3948</v>
+      </c>
       <c r="M595">
         <v>2</v>
       </c>
@@ -40563,6 +42798,9 @@
       <c r="J596" s="6" t="s">
         <v>1227</v>
       </c>
+      <c r="L596" t="s">
+        <v>3949</v>
+      </c>
       <c r="M596">
         <v>2</v>
       </c>
@@ -40605,6 +42843,9 @@
       <c r="J597" s="6" t="s">
         <v>1227</v>
       </c>
+      <c r="L597" t="s">
+        <v>3950</v>
+      </c>
       <c r="M597">
         <v>2</v>
       </c>
@@ -40647,6 +42888,9 @@
       <c r="J598" s="6" t="s">
         <v>1227</v>
       </c>
+      <c r="L598" t="s">
+        <v>3951</v>
+      </c>
       <c r="M598">
         <v>2</v>
       </c>
@@ -40689,6 +42933,9 @@
       <c r="J599" s="6" t="s">
         <v>1227</v>
       </c>
+      <c r="L599" t="s">
+        <v>3952</v>
+      </c>
       <c r="M599">
         <v>2</v>
       </c>
@@ -40731,6 +42978,9 @@
       <c r="J600" s="6" t="s">
         <v>1227</v>
       </c>
+      <c r="L600" t="s">
+        <v>3953</v>
+      </c>
       <c r="M600">
         <v>2</v>
       </c>
@@ -40773,6 +43023,9 @@
       <c r="J601" s="6" t="s">
         <v>1227</v>
       </c>
+      <c r="L601" t="s">
+        <v>3954</v>
+      </c>
       <c r="M601">
         <v>2</v>
       </c>
@@ -40815,6 +43068,9 @@
       <c r="J602" s="6" t="s">
         <v>1227</v>
       </c>
+      <c r="L602" t="s">
+        <v>3955</v>
+      </c>
       <c r="M602">
         <v>2</v>
       </c>
@@ -40857,6 +43113,9 @@
       <c r="J603" s="6" t="s">
         <v>1227</v>
       </c>
+      <c r="L603" t="s">
+        <v>3956</v>
+      </c>
       <c r="M603">
         <v>2</v>
       </c>
@@ -40899,6 +43158,9 @@
       <c r="J604" s="6" t="s">
         <v>1227</v>
       </c>
+      <c r="L604" t="s">
+        <v>3957</v>
+      </c>
       <c r="M604">
         <v>2</v>
       </c>
@@ -40941,6 +43203,9 @@
       <c r="J605" s="6" t="s">
         <v>1227</v>
       </c>
+      <c r="L605" t="s">
+        <v>3958</v>
+      </c>
       <c r="M605">
         <v>2</v>
       </c>
@@ -40983,6 +43248,9 @@
       <c r="J606" s="6" t="s">
         <v>1227</v>
       </c>
+      <c r="L606" t="s">
+        <v>3959</v>
+      </c>
       <c r="M606">
         <v>2</v>
       </c>
@@ -41025,6 +43293,9 @@
       <c r="J607" s="6" t="s">
         <v>1227</v>
       </c>
+      <c r="L607" t="s">
+        <v>3960</v>
+      </c>
       <c r="M607">
         <v>2</v>
       </c>
@@ -41067,6 +43338,9 @@
       <c r="J608" s="6" t="s">
         <v>1227</v>
       </c>
+      <c r="L608" t="s">
+        <v>3961</v>
+      </c>
       <c r="M608">
         <v>2</v>
       </c>
@@ -41109,6 +43383,9 @@
       <c r="J609" s="6" t="s">
         <v>1227</v>
       </c>
+      <c r="L609" t="s">
+        <v>3962</v>
+      </c>
       <c r="M609">
         <v>2</v>
       </c>
@@ -41151,6 +43428,9 @@
       <c r="J610" s="6" t="s">
         <v>1227</v>
       </c>
+      <c r="L610" t="s">
+        <v>3963</v>
+      </c>
       <c r="M610">
         <v>2</v>
       </c>
@@ -41193,6 +43473,9 @@
       <c r="J611" s="6" t="s">
         <v>1227</v>
       </c>
+      <c r="L611" t="s">
+        <v>3964</v>
+      </c>
       <c r="M611">
         <v>2</v>
       </c>
@@ -41235,6 +43518,9 @@
       <c r="J612" s="6" t="s">
         <v>1227</v>
       </c>
+      <c r="L612" t="s">
+        <v>3965</v>
+      </c>
       <c r="M612">
         <v>2</v>
       </c>
@@ -41277,6 +43563,9 @@
       <c r="J613" s="6" t="s">
         <v>1227</v>
       </c>
+      <c r="L613" t="s">
+        <v>3966</v>
+      </c>
       <c r="M613">
         <v>2</v>
       </c>
@@ -41319,6 +43608,9 @@
       <c r="J614" s="6" t="s">
         <v>1227</v>
       </c>
+      <c r="L614" t="s">
+        <v>3967</v>
+      </c>
       <c r="M614">
         <v>2</v>
       </c>
@@ -41361,6 +43653,9 @@
       <c r="J615" s="6" t="s">
         <v>1227</v>
       </c>
+      <c r="L615" t="s">
+        <v>3968</v>
+      </c>
       <c r="M615">
         <v>2</v>
       </c>
@@ -41403,6 +43698,9 @@
       <c r="J616" s="6" t="s">
         <v>1227</v>
       </c>
+      <c r="L616" t="s">
+        <v>3969</v>
+      </c>
       <c r="M616">
         <v>2</v>
       </c>
@@ -41445,6 +43743,9 @@
       <c r="J617" s="6" t="s">
         <v>1282</v>
       </c>
+      <c r="L617" t="s">
+        <v>3970</v>
+      </c>
       <c r="M617">
         <v>2</v>
       </c>
@@ -41487,6 +43788,9 @@
       <c r="J618" s="6" t="s">
         <v>1282</v>
       </c>
+      <c r="L618" t="s">
+        <v>3971</v>
+      </c>
       <c r="M618">
         <v>2</v>
       </c>
@@ -41529,6 +43833,9 @@
       <c r="J619" s="6" t="s">
         <v>1282</v>
       </c>
+      <c r="L619" t="s">
+        <v>3972</v>
+      </c>
       <c r="M619">
         <v>2</v>
       </c>
@@ -41571,6 +43878,9 @@
       <c r="J620" s="6" t="s">
         <v>1282</v>
       </c>
+      <c r="L620" t="s">
+        <v>3973</v>
+      </c>
       <c r="M620">
         <v>2</v>
       </c>
@@ -41613,6 +43923,9 @@
       <c r="J621" s="6" t="s">
         <v>1282</v>
       </c>
+      <c r="L621" t="s">
+        <v>3974</v>
+      </c>
       <c r="M621">
         <v>2</v>
       </c>
@@ -41655,6 +43968,9 @@
       <c r="J622" s="6" t="s">
         <v>1282</v>
       </c>
+      <c r="L622" t="s">
+        <v>3975</v>
+      </c>
       <c r="M622">
         <v>2</v>
       </c>
@@ -41697,6 +44013,9 @@
       <c r="J623" s="6" t="s">
         <v>1282</v>
       </c>
+      <c r="L623" t="s">
+        <v>3976</v>
+      </c>
       <c r="M623">
         <v>2</v>
       </c>
@@ -41739,6 +44058,9 @@
       <c r="J624" s="6" t="s">
         <v>1282</v>
       </c>
+      <c r="L624" t="s">
+        <v>3977</v>
+      </c>
       <c r="M624">
         <v>2</v>
       </c>
@@ -41781,6 +44103,9 @@
       <c r="J625" s="6" t="s">
         <v>1282</v>
       </c>
+      <c r="L625" t="s">
+        <v>3978</v>
+      </c>
       <c r="M625">
         <v>2</v>
       </c>
@@ -41823,6 +44148,9 @@
       <c r="J626" s="6" t="s">
         <v>1282</v>
       </c>
+      <c r="L626" t="s">
+        <v>3979</v>
+      </c>
       <c r="M626">
         <v>2</v>
       </c>
@@ -41865,6 +44193,9 @@
       <c r="J627" s="6" t="s">
         <v>1282</v>
       </c>
+      <c r="L627" t="s">
+        <v>3980</v>
+      </c>
       <c r="M627">
         <v>2</v>
       </c>
@@ -41907,6 +44238,9 @@
       <c r="J628" s="6" t="s">
         <v>1282</v>
       </c>
+      <c r="L628" t="s">
+        <v>3981</v>
+      </c>
       <c r="M628">
         <v>2</v>
       </c>
@@ -41949,6 +44283,9 @@
       <c r="J629" s="6" t="s">
         <v>1282</v>
       </c>
+      <c r="L629" t="s">
+        <v>3982</v>
+      </c>
       <c r="M629">
         <v>2</v>
       </c>
@@ -41991,6 +44328,9 @@
       <c r="J630" s="6" t="s">
         <v>1282</v>
       </c>
+      <c r="L630" t="s">
+        <v>3983</v>
+      </c>
       <c r="M630">
         <v>2</v>
       </c>
@@ -42033,6 +44373,9 @@
       <c r="J631" s="6" t="s">
         <v>1282</v>
       </c>
+      <c r="L631" t="s">
+        <v>3984</v>
+      </c>
       <c r="M631">
         <v>2</v>
       </c>
@@ -42075,6 +44418,9 @@
       <c r="J632" s="6" t="s">
         <v>1282</v>
       </c>
+      <c r="L632" t="s">
+        <v>3985</v>
+      </c>
       <c r="M632">
         <v>2</v>
       </c>
@@ -42117,6 +44463,9 @@
       <c r="J633" s="6" t="s">
         <v>1282</v>
       </c>
+      <c r="L633" t="s">
+        <v>3986</v>
+      </c>
       <c r="M633">
         <v>2</v>
       </c>
@@ -42159,6 +44508,9 @@
       <c r="J634" s="6" t="s">
         <v>1282</v>
       </c>
+      <c r="L634" t="s">
+        <v>3987</v>
+      </c>
       <c r="M634">
         <v>2</v>
       </c>
@@ -42201,6 +44553,9 @@
       <c r="J635" s="6" t="s">
         <v>1282</v>
       </c>
+      <c r="L635" t="s">
+        <v>3988</v>
+      </c>
       <c r="M635">
         <v>2</v>
       </c>
@@ -42243,6 +44598,9 @@
       <c r="J636" s="6" t="s">
         <v>1282</v>
       </c>
+      <c r="L636" t="s">
+        <v>3989</v>
+      </c>
       <c r="M636">
         <v>2</v>
       </c>
@@ -42285,6 +44643,9 @@
       <c r="J637" s="6" t="s">
         <v>1282</v>
       </c>
+      <c r="L637" t="s">
+        <v>3990</v>
+      </c>
       <c r="M637">
         <v>2</v>
       </c>
@@ -42327,6 +44688,9 @@
       <c r="J638" s="6" t="s">
         <v>1282</v>
       </c>
+      <c r="L638" t="s">
+        <v>3991</v>
+      </c>
       <c r="M638">
         <v>2</v>
       </c>
@@ -42369,6 +44733,9 @@
       <c r="J639" s="6" t="s">
         <v>1282</v>
       </c>
+      <c r="L639" t="s">
+        <v>3992</v>
+      </c>
       <c r="M639">
         <v>2</v>
       </c>
@@ -42411,6 +44778,9 @@
       <c r="J640" s="6" t="s">
         <v>1282</v>
       </c>
+      <c r="L640" t="s">
+        <v>3993</v>
+      </c>
       <c r="M640">
         <v>2</v>
       </c>
@@ -42453,6 +44823,9 @@
       <c r="J641" s="6" t="s">
         <v>1282</v>
       </c>
+      <c r="L641" t="s">
+        <v>3994</v>
+      </c>
       <c r="M641">
         <v>2</v>
       </c>
@@ -42495,6 +44868,9 @@
       <c r="J642" s="6" t="s">
         <v>1282</v>
       </c>
+      <c r="L642" t="s">
+        <v>3995</v>
+      </c>
       <c r="M642">
         <v>2</v>
       </c>
@@ -42537,6 +44913,9 @@
       <c r="J643" s="6" t="s">
         <v>1282</v>
       </c>
+      <c r="L643" t="s">
+        <v>3996</v>
+      </c>
       <c r="M643">
         <v>2</v>
       </c>
@@ -42579,6 +44958,9 @@
       <c r="J644" s="6" t="s">
         <v>1337</v>
       </c>
+      <c r="L644" t="s">
+        <v>3997</v>
+      </c>
       <c r="M644">
         <v>2</v>
       </c>
@@ -42621,6 +45003,9 @@
       <c r="J645" s="6" t="s">
         <v>1337</v>
       </c>
+      <c r="L645" t="s">
+        <v>3998</v>
+      </c>
       <c r="M645">
         <v>2</v>
       </c>
@@ -42663,6 +45048,9 @@
       <c r="J646" s="6" t="s">
         <v>1337</v>
       </c>
+      <c r="L646" t="s">
+        <v>3999</v>
+      </c>
       <c r="M646">
         <v>2</v>
       </c>
@@ -42705,6 +45093,9 @@
       <c r="J647" s="6" t="s">
         <v>1337</v>
       </c>
+      <c r="L647" t="s">
+        <v>4000</v>
+      </c>
       <c r="M647">
         <v>2</v>
       </c>
@@ -42747,6 +45138,9 @@
       <c r="J648" s="6" t="s">
         <v>1337</v>
       </c>
+      <c r="L648" t="s">
+        <v>4001</v>
+      </c>
       <c r="M648">
         <v>2</v>
       </c>
@@ -42789,6 +45183,9 @@
       <c r="J649" s="6" t="s">
         <v>1337</v>
       </c>
+      <c r="L649" t="s">
+        <v>4002</v>
+      </c>
       <c r="M649">
         <v>2</v>
       </c>
@@ -42831,6 +45228,9 @@
       <c r="J650" s="6" t="s">
         <v>1337</v>
       </c>
+      <c r="L650" t="s">
+        <v>4003</v>
+      </c>
       <c r="M650">
         <v>2</v>
       </c>
@@ -42873,6 +45273,9 @@
       <c r="J651" s="6" t="s">
         <v>1337</v>
       </c>
+      <c r="L651" t="s">
+        <v>4004</v>
+      </c>
       <c r="M651">
         <v>2</v>
       </c>
@@ -42915,6 +45318,9 @@
       <c r="J652" s="6" t="s">
         <v>1337</v>
       </c>
+      <c r="L652" t="s">
+        <v>4005</v>
+      </c>
       <c r="M652">
         <v>2</v>
       </c>
@@ -42957,6 +45363,9 @@
       <c r="J653" s="6" t="s">
         <v>1337</v>
       </c>
+      <c r="L653" t="s">
+        <v>4006</v>
+      </c>
       <c r="M653">
         <v>2</v>
       </c>
@@ -42999,6 +45408,9 @@
       <c r="J654" s="6" t="s">
         <v>1337</v>
       </c>
+      <c r="L654" t="s">
+        <v>4007</v>
+      </c>
       <c r="M654">
         <v>2</v>
       </c>
@@ -43041,6 +45453,9 @@
       <c r="J655" s="6" t="s">
         <v>1337</v>
       </c>
+      <c r="L655" t="s">
+        <v>4008</v>
+      </c>
       <c r="M655">
         <v>2</v>
       </c>
@@ -43083,6 +45498,9 @@
       <c r="J656" s="6" t="s">
         <v>1337</v>
       </c>
+      <c r="L656" t="s">
+        <v>4009</v>
+      </c>
       <c r="M656">
         <v>2</v>
       </c>
@@ -43125,6 +45543,9 @@
       <c r="J657" s="6" t="s">
         <v>1337</v>
       </c>
+      <c r="L657" t="s">
+        <v>4010</v>
+      </c>
       <c r="M657">
         <v>2</v>
       </c>
@@ -43167,6 +45588,9 @@
       <c r="J658" s="6" t="s">
         <v>1337</v>
       </c>
+      <c r="L658" t="s">
+        <v>4011</v>
+      </c>
       <c r="M658">
         <v>2</v>
       </c>
@@ -43209,6 +45633,9 @@
       <c r="J659" s="6" t="s">
         <v>1337</v>
       </c>
+      <c r="L659" t="s">
+        <v>4012</v>
+      </c>
       <c r="M659">
         <v>2</v>
       </c>
@@ -43251,6 +45678,9 @@
       <c r="J660" s="6" t="s">
         <v>1337</v>
       </c>
+      <c r="L660" t="s">
+        <v>4013</v>
+      </c>
       <c r="M660">
         <v>2</v>
       </c>
@@ -43293,6 +45723,9 @@
       <c r="J661" s="6" t="s">
         <v>1337</v>
       </c>
+      <c r="L661" t="s">
+        <v>4014</v>
+      </c>
       <c r="M661">
         <v>2</v>
       </c>
@@ -43335,6 +45768,9 @@
       <c r="J662" s="6" t="s">
         <v>1337</v>
       </c>
+      <c r="L662" t="s">
+        <v>4015</v>
+      </c>
       <c r="M662">
         <v>2</v>
       </c>
@@ -43377,6 +45813,9 @@
       <c r="J663" s="6" t="s">
         <v>1337</v>
       </c>
+      <c r="L663" t="s">
+        <v>4016</v>
+      </c>
       <c r="M663">
         <v>2</v>
       </c>
@@ -43419,6 +45858,9 @@
       <c r="J664" s="6" t="s">
         <v>1337</v>
       </c>
+      <c r="L664" t="s">
+        <v>4017</v>
+      </c>
       <c r="M664">
         <v>2</v>
       </c>
@@ -43461,6 +45903,9 @@
       <c r="J665" s="6" t="s">
         <v>1337</v>
       </c>
+      <c r="L665" t="s">
+        <v>4018</v>
+      </c>
       <c r="M665">
         <v>2</v>
       </c>
@@ -43503,6 +45948,9 @@
       <c r="J666" s="6" t="s">
         <v>1337</v>
       </c>
+      <c r="L666" t="s">
+        <v>4019</v>
+      </c>
       <c r="M666">
         <v>2</v>
       </c>
@@ -43545,6 +45993,9 @@
       <c r="J667" s="6" t="s">
         <v>1337</v>
       </c>
+      <c r="L667" t="s">
+        <v>4020</v>
+      </c>
       <c r="M667">
         <v>2</v>
       </c>
@@ -43587,6 +46038,9 @@
       <c r="J668" s="6" t="s">
         <v>1337</v>
       </c>
+      <c r="L668" t="s">
+        <v>4021</v>
+      </c>
       <c r="M668">
         <v>2</v>
       </c>
@@ -43629,6 +46083,9 @@
       <c r="J669" s="6" t="s">
         <v>1337</v>
       </c>
+      <c r="L669" t="s">
+        <v>4022</v>
+      </c>
       <c r="M669">
         <v>2</v>
       </c>
@@ -43671,6 +46128,9 @@
       <c r="J670" s="6" t="s">
         <v>1337</v>
       </c>
+      <c r="L670" t="s">
+        <v>4023</v>
+      </c>
       <c r="M670">
         <v>2</v>
       </c>
@@ -43713,6 +46173,9 @@
       <c r="J671" s="6" t="s">
         <v>1392</v>
       </c>
+      <c r="L671" t="s">
+        <v>4024</v>
+      </c>
       <c r="M671">
         <v>2</v>
       </c>
@@ -43755,6 +46218,9 @@
       <c r="J672" s="6" t="s">
         <v>1392</v>
       </c>
+      <c r="L672" t="s">
+        <v>4025</v>
+      </c>
       <c r="M672">
         <v>2</v>
       </c>
@@ -43797,6 +46263,9 @@
       <c r="J673" s="6" t="s">
         <v>1392</v>
       </c>
+      <c r="L673" t="s">
+        <v>4026</v>
+      </c>
       <c r="M673">
         <v>2</v>
       </c>
@@ -43839,6 +46308,9 @@
       <c r="J674" s="6" t="s">
         <v>1392</v>
       </c>
+      <c r="L674" t="s">
+        <v>4027</v>
+      </c>
       <c r="M674">
         <v>2</v>
       </c>
@@ -43881,6 +46353,9 @@
       <c r="J675" s="6" t="s">
         <v>1392</v>
       </c>
+      <c r="L675" t="s">
+        <v>4028</v>
+      </c>
       <c r="M675">
         <v>2</v>
       </c>
@@ -43923,6 +46398,9 @@
       <c r="J676" s="6" t="s">
         <v>1392</v>
       </c>
+      <c r="L676" t="s">
+        <v>4029</v>
+      </c>
       <c r="M676">
         <v>2</v>
       </c>
@@ -43965,6 +46443,9 @@
       <c r="J677" s="6" t="s">
         <v>1392</v>
       </c>
+      <c r="L677" t="s">
+        <v>4030</v>
+      </c>
       <c r="M677">
         <v>2</v>
       </c>
@@ -44007,6 +46488,9 @@
       <c r="J678" s="6" t="s">
         <v>1392</v>
       </c>
+      <c r="L678" t="s">
+        <v>4031</v>
+      </c>
       <c r="M678">
         <v>2</v>
       </c>
@@ -44049,6 +46533,9 @@
       <c r="J679" s="6" t="s">
         <v>1392</v>
       </c>
+      <c r="L679" t="s">
+        <v>4032</v>
+      </c>
       <c r="M679">
         <v>2</v>
       </c>
@@ -44091,6 +46578,9 @@
       <c r="J680" s="6" t="s">
         <v>1392</v>
       </c>
+      <c r="L680" t="s">
+        <v>4033</v>
+      </c>
       <c r="M680">
         <v>2</v>
       </c>
@@ -44133,6 +46623,9 @@
       <c r="J681" s="6" t="s">
         <v>1392</v>
       </c>
+      <c r="L681" t="s">
+        <v>4034</v>
+      </c>
       <c r="M681">
         <v>2</v>
       </c>
@@ -44175,6 +46668,9 @@
       <c r="J682" s="6" t="s">
         <v>1392</v>
       </c>
+      <c r="L682" t="s">
+        <v>4035</v>
+      </c>
       <c r="M682">
         <v>2</v>
       </c>
@@ -44217,6 +46713,9 @@
       <c r="J683" s="6" t="s">
         <v>1392</v>
       </c>
+      <c r="L683" t="s">
+        <v>4036</v>
+      </c>
       <c r="M683">
         <v>2</v>
       </c>
@@ -44259,6 +46758,9 @@
       <c r="J684" s="6" t="s">
         <v>1392</v>
       </c>
+      <c r="L684" t="s">
+        <v>4037</v>
+      </c>
       <c r="M684">
         <v>2</v>
       </c>
@@ -44301,6 +46803,9 @@
       <c r="J685" s="6" t="s">
         <v>1392</v>
       </c>
+      <c r="L685" t="s">
+        <v>4038</v>
+      </c>
       <c r="M685">
         <v>2</v>
       </c>
@@ -44343,6 +46848,9 @@
       <c r="J686" s="6" t="s">
         <v>1392</v>
       </c>
+      <c r="L686" t="s">
+        <v>4039</v>
+      </c>
       <c r="M686">
         <v>2</v>
       </c>
@@ -44385,6 +46893,9 @@
       <c r="J687" s="6" t="s">
         <v>1392</v>
       </c>
+      <c r="L687" t="s">
+        <v>4040</v>
+      </c>
       <c r="M687">
         <v>2</v>
       </c>
@@ -44427,6 +46938,9 @@
       <c r="J688" s="6" t="s">
         <v>1392</v>
       </c>
+      <c r="L688" t="s">
+        <v>4041</v>
+      </c>
       <c r="M688">
         <v>2</v>
       </c>
@@ -44469,6 +46983,9 @@
       <c r="J689" s="6" t="s">
         <v>1392</v>
       </c>
+      <c r="L689" t="s">
+        <v>4042</v>
+      </c>
       <c r="M689">
         <v>2</v>
       </c>
@@ -44511,6 +47028,9 @@
       <c r="J690" s="6" t="s">
         <v>1392</v>
       </c>
+      <c r="L690" t="s">
+        <v>4043</v>
+      </c>
       <c r="M690">
         <v>2</v>
       </c>
@@ -44553,6 +47073,9 @@
       <c r="J691" s="6" t="s">
         <v>1392</v>
       </c>
+      <c r="L691" t="s">
+        <v>4044</v>
+      </c>
       <c r="M691">
         <v>2</v>
       </c>
@@ -44595,6 +47118,9 @@
       <c r="J692" s="6" t="s">
         <v>1392</v>
       </c>
+      <c r="L692" t="s">
+        <v>4045</v>
+      </c>
       <c r="M692">
         <v>2</v>
       </c>
@@ -44637,6 +47163,9 @@
       <c r="J693" s="6" t="s">
         <v>1392</v>
       </c>
+      <c r="L693" t="s">
+        <v>4046</v>
+      </c>
       <c r="M693">
         <v>2</v>
       </c>
@@ -44679,6 +47208,9 @@
       <c r="J694" s="6" t="s">
         <v>1392</v>
       </c>
+      <c r="L694" t="s">
+        <v>4047</v>
+      </c>
       <c r="M694">
         <v>2</v>
       </c>
@@ -44721,6 +47253,9 @@
       <c r="J695" s="6" t="s">
         <v>1392</v>
       </c>
+      <c r="L695" t="s">
+        <v>4048</v>
+      </c>
       <c r="M695">
         <v>2</v>
       </c>
@@ -44763,6 +47298,9 @@
       <c r="J696" s="6" t="s">
         <v>1392</v>
       </c>
+      <c r="L696" t="s">
+        <v>4049</v>
+      </c>
       <c r="M696">
         <v>2</v>
       </c>
@@ -44805,6 +47343,9 @@
       <c r="J697" s="6" t="s">
         <v>1392</v>
       </c>
+      <c r="L697" t="s">
+        <v>4050</v>
+      </c>
       <c r="M697">
         <v>2</v>
       </c>
@@ -44847,6 +47388,9 @@
       <c r="J698" s="6" t="s">
         <v>1447</v>
       </c>
+      <c r="L698" t="s">
+        <v>4051</v>
+      </c>
       <c r="M698">
         <v>2</v>
       </c>
@@ -44889,6 +47433,9 @@
       <c r="J699" s="6" t="s">
         <v>1447</v>
       </c>
+      <c r="L699" t="s">
+        <v>4052</v>
+      </c>
       <c r="M699">
         <v>2</v>
       </c>
@@ -44931,6 +47478,9 @@
       <c r="J700" s="6" t="s">
         <v>1447</v>
       </c>
+      <c r="L700" t="s">
+        <v>4053</v>
+      </c>
       <c r="M700">
         <v>2</v>
       </c>
@@ -44973,6 +47523,9 @@
       <c r="J701" s="6" t="s">
         <v>1447</v>
       </c>
+      <c r="L701" t="s">
+        <v>4054</v>
+      </c>
       <c r="M701">
         <v>2</v>
       </c>
@@ -45015,6 +47568,9 @@
       <c r="J702" s="6" t="s">
         <v>1447</v>
       </c>
+      <c r="L702" t="s">
+        <v>4055</v>
+      </c>
       <c r="M702">
         <v>2</v>
       </c>
@@ -45057,6 +47613,9 @@
       <c r="J703" s="6" t="s">
         <v>1447</v>
       </c>
+      <c r="L703" t="s">
+        <v>4056</v>
+      </c>
       <c r="M703">
         <v>2</v>
       </c>
@@ -45099,6 +47658,9 @@
       <c r="J704" s="6" t="s">
         <v>1447</v>
       </c>
+      <c r="L704" t="s">
+        <v>4057</v>
+      </c>
       <c r="M704">
         <v>2</v>
       </c>
@@ -45141,6 +47703,9 @@
       <c r="J705" s="6" t="s">
         <v>1447</v>
       </c>
+      <c r="L705" t="s">
+        <v>4058</v>
+      </c>
       <c r="M705">
         <v>2</v>
       </c>
@@ -45183,6 +47748,9 @@
       <c r="J706" s="6" t="s">
         <v>1447</v>
       </c>
+      <c r="L706" t="s">
+        <v>4059</v>
+      </c>
       <c r="M706">
         <v>2</v>
       </c>
@@ -45225,6 +47793,9 @@
       <c r="J707" s="6" t="s">
         <v>1447</v>
       </c>
+      <c r="L707" t="s">
+        <v>4060</v>
+      </c>
       <c r="M707">
         <v>2</v>
       </c>
@@ -45267,6 +47838,9 @@
       <c r="J708" s="6" t="s">
         <v>1447</v>
       </c>
+      <c r="L708" t="s">
+        <v>4061</v>
+      </c>
       <c r="M708">
         <v>2</v>
       </c>
@@ -45309,6 +47883,9 @@
       <c r="J709" s="6" t="s">
         <v>1447</v>
       </c>
+      <c r="L709" t="s">
+        <v>4062</v>
+      </c>
       <c r="M709">
         <v>2</v>
       </c>
@@ -45351,6 +47928,9 @@
       <c r="J710" s="6" t="s">
         <v>1447</v>
       </c>
+      <c r="L710" t="s">
+        <v>4063</v>
+      </c>
       <c r="M710">
         <v>2</v>
       </c>
@@ -45393,6 +47973,9 @@
       <c r="J711" s="6" t="s">
         <v>1447</v>
       </c>
+      <c r="L711" t="s">
+        <v>4064</v>
+      </c>
       <c r="M711">
         <v>2</v>
       </c>
@@ -45435,6 +48018,9 @@
       <c r="J712" s="6" t="s">
         <v>1447</v>
       </c>
+      <c r="L712" t="s">
+        <v>4065</v>
+      </c>
       <c r="M712">
         <v>2</v>
       </c>
@@ -45477,6 +48063,9 @@
       <c r="J713" s="6" t="s">
         <v>1447</v>
       </c>
+      <c r="L713" t="s">
+        <v>4066</v>
+      </c>
       <c r="M713">
         <v>2</v>
       </c>
@@ -45519,6 +48108,9 @@
       <c r="J714" s="6" t="s">
         <v>1447</v>
       </c>
+      <c r="L714" t="s">
+        <v>4067</v>
+      </c>
       <c r="M714">
         <v>2</v>
       </c>
@@ -45561,6 +48153,9 @@
       <c r="J715" s="6" t="s">
         <v>1447</v>
       </c>
+      <c r="L715" t="s">
+        <v>4068</v>
+      </c>
       <c r="M715">
         <v>2</v>
       </c>
@@ -45603,6 +48198,9 @@
       <c r="J716" s="6" t="s">
         <v>1447</v>
       </c>
+      <c r="L716" t="s">
+        <v>4069</v>
+      </c>
       <c r="M716">
         <v>2</v>
       </c>
@@ -45645,6 +48243,9 @@
       <c r="J717" s="6" t="s">
         <v>1447</v>
       </c>
+      <c r="L717" t="s">
+        <v>4070</v>
+      </c>
       <c r="M717">
         <v>2</v>
       </c>
@@ -45687,6 +48288,9 @@
       <c r="J718" s="6" t="s">
         <v>1447</v>
       </c>
+      <c r="L718" t="s">
+        <v>4071</v>
+      </c>
       <c r="M718">
         <v>2</v>
       </c>
@@ -45729,6 +48333,9 @@
       <c r="J719" s="6" t="s">
         <v>1447</v>
       </c>
+      <c r="L719" t="s">
+        <v>4072</v>
+      </c>
       <c r="M719">
         <v>2</v>
       </c>
@@ -45771,6 +48378,9 @@
       <c r="J720" s="6" t="s">
         <v>1447</v>
       </c>
+      <c r="L720" t="s">
+        <v>4073</v>
+      </c>
       <c r="M720">
         <v>2</v>
       </c>
@@ -45813,6 +48423,9 @@
       <c r="J721" s="6" t="s">
         <v>1447</v>
       </c>
+      <c r="L721" t="s">
+        <v>4074</v>
+      </c>
       <c r="M721">
         <v>2</v>
       </c>
@@ -45855,6 +48468,9 @@
       <c r="J722" s="6" t="s">
         <v>1447</v>
       </c>
+      <c r="L722" t="s">
+        <v>4075</v>
+      </c>
       <c r="M722">
         <v>2</v>
       </c>
@@ -45897,6 +48513,9 @@
       <c r="J723" s="6" t="s">
         <v>1447</v>
       </c>
+      <c r="L723" t="s">
+        <v>4076</v>
+      </c>
       <c r="M723">
         <v>2</v>
       </c>
@@ -45939,6 +48558,9 @@
       <c r="J724" s="6" t="s">
         <v>1447</v>
       </c>
+      <c r="L724" t="s">
+        <v>4077</v>
+      </c>
       <c r="M724">
         <v>2</v>
       </c>
@@ -45981,6 +48603,9 @@
       <c r="J725" s="6" t="s">
         <v>1502</v>
       </c>
+      <c r="L725" t="s">
+        <v>4078</v>
+      </c>
       <c r="M725">
         <v>2</v>
       </c>
@@ -46023,6 +48648,9 @@
       <c r="J726" s="6" t="s">
         <v>1502</v>
       </c>
+      <c r="L726" t="s">
+        <v>4079</v>
+      </c>
       <c r="M726">
         <v>2</v>
       </c>
@@ -46065,6 +48693,9 @@
       <c r="J727" s="6" t="s">
         <v>1502</v>
       </c>
+      <c r="L727" t="s">
+        <v>4080</v>
+      </c>
       <c r="M727">
         <v>2</v>
       </c>
@@ -46107,6 +48738,9 @@
       <c r="J728" s="6" t="s">
         <v>1502</v>
       </c>
+      <c r="L728" t="s">
+        <v>4081</v>
+      </c>
       <c r="M728">
         <v>2</v>
       </c>
@@ -46149,6 +48783,9 @@
       <c r="J729" s="6" t="s">
         <v>1502</v>
       </c>
+      <c r="L729" t="s">
+        <v>4082</v>
+      </c>
       <c r="M729">
         <v>2</v>
       </c>
@@ -46191,6 +48828,9 @@
       <c r="J730" s="6" t="s">
         <v>1502</v>
       </c>
+      <c r="L730" t="s">
+        <v>4083</v>
+      </c>
       <c r="M730">
         <v>2</v>
       </c>
@@ -46233,6 +48873,9 @@
       <c r="J731" s="6" t="s">
         <v>1502</v>
       </c>
+      <c r="L731" t="s">
+        <v>4084</v>
+      </c>
       <c r="M731">
         <v>2</v>
       </c>
@@ -46275,6 +48918,9 @@
       <c r="J732" s="6" t="s">
         <v>1502</v>
       </c>
+      <c r="L732" t="s">
+        <v>4085</v>
+      </c>
       <c r="M732">
         <v>2</v>
       </c>
@@ -46317,6 +48963,9 @@
       <c r="J733" s="6" t="s">
         <v>1502</v>
       </c>
+      <c r="L733" t="s">
+        <v>4086</v>
+      </c>
       <c r="M733">
         <v>2</v>
       </c>
@@ -46359,6 +49008,9 @@
       <c r="J734" s="6" t="s">
         <v>1502</v>
       </c>
+      <c r="L734" t="s">
+        <v>4087</v>
+      </c>
       <c r="M734">
         <v>2</v>
       </c>
@@ -46401,6 +49053,9 @@
       <c r="J735" s="6" t="s">
         <v>1502</v>
       </c>
+      <c r="L735" t="s">
+        <v>4088</v>
+      </c>
       <c r="M735">
         <v>2</v>
       </c>
@@ -46443,6 +49098,9 @@
       <c r="J736" s="6" t="s">
         <v>1502</v>
       </c>
+      <c r="L736" t="s">
+        <v>4089</v>
+      </c>
       <c r="M736">
         <v>2</v>
       </c>
@@ -46485,6 +49143,9 @@
       <c r="J737" s="6" t="s">
         <v>1502</v>
       </c>
+      <c r="L737" t="s">
+        <v>4090</v>
+      </c>
       <c r="M737">
         <v>2</v>
       </c>
@@ -46527,6 +49188,9 @@
       <c r="J738" s="6" t="s">
         <v>1502</v>
       </c>
+      <c r="L738" t="s">
+        <v>4091</v>
+      </c>
       <c r="M738">
         <v>2</v>
       </c>
@@ -46569,6 +49233,9 @@
       <c r="J739" s="6" t="s">
         <v>1502</v>
       </c>
+      <c r="L739" t="s">
+        <v>4092</v>
+      </c>
       <c r="M739">
         <v>2</v>
       </c>
@@ -46611,6 +49278,9 @@
       <c r="J740" s="6" t="s">
         <v>1502</v>
       </c>
+      <c r="L740" t="s">
+        <v>4093</v>
+      </c>
       <c r="M740">
         <v>2</v>
       </c>
@@ -46653,6 +49323,9 @@
       <c r="J741" s="6" t="s">
         <v>1502</v>
       </c>
+      <c r="L741" t="s">
+        <v>4094</v>
+      </c>
       <c r="M741">
         <v>2</v>
       </c>
@@ -46695,6 +49368,9 @@
       <c r="J742" s="6" t="s">
         <v>1502</v>
       </c>
+      <c r="L742" t="s">
+        <v>4095</v>
+      </c>
       <c r="M742">
         <v>2</v>
       </c>
@@ -46737,6 +49413,9 @@
       <c r="J743" s="6" t="s">
         <v>1502</v>
       </c>
+      <c r="L743" t="s">
+        <v>4096</v>
+      </c>
       <c r="M743">
         <v>2</v>
       </c>
@@ -46779,6 +49458,9 @@
       <c r="J744" s="6" t="s">
         <v>1502</v>
       </c>
+      <c r="L744" t="s">
+        <v>4097</v>
+      </c>
       <c r="M744">
         <v>2</v>
       </c>
@@ -46821,6 +49503,9 @@
       <c r="J745" s="6" t="s">
         <v>1502</v>
       </c>
+      <c r="L745" t="s">
+        <v>4098</v>
+      </c>
       <c r="M745">
         <v>2</v>
       </c>
@@ -46863,6 +49548,9 @@
       <c r="J746" s="6" t="s">
         <v>1502</v>
       </c>
+      <c r="L746" t="s">
+        <v>4099</v>
+      </c>
       <c r="M746">
         <v>2</v>
       </c>
@@ -46905,6 +49593,9 @@
       <c r="J747" s="6" t="s">
         <v>1502</v>
       </c>
+      <c r="L747" t="s">
+        <v>4100</v>
+      </c>
       <c r="M747">
         <v>2</v>
       </c>
@@ -46947,6 +49638,9 @@
       <c r="J748" s="6" t="s">
         <v>1502</v>
       </c>
+      <c r="L748" t="s">
+        <v>4101</v>
+      </c>
       <c r="M748">
         <v>2</v>
       </c>
@@ -46989,6 +49683,9 @@
       <c r="J749" s="6" t="s">
         <v>1502</v>
       </c>
+      <c r="L749" t="s">
+        <v>4102</v>
+      </c>
       <c r="M749">
         <v>2</v>
       </c>
@@ -47031,6 +49728,9 @@
       <c r="J750" s="6" t="s">
         <v>1502</v>
       </c>
+      <c r="L750" t="s">
+        <v>4103</v>
+      </c>
       <c r="M750">
         <v>2</v>
       </c>
@@ -47073,6 +49773,9 @@
       <c r="J751" s="6" t="s">
         <v>1502</v>
       </c>
+      <c r="L751" t="s">
+        <v>4104</v>
+      </c>
       <c r="M751">
         <v>2</v>
       </c>
@@ -47115,6 +49818,9 @@
       <c r="J752" s="6" t="s">
         <v>1557</v>
       </c>
+      <c r="L752" t="s">
+        <v>4105</v>
+      </c>
       <c r="M752">
         <v>2</v>
       </c>
@@ -47157,6 +49863,9 @@
       <c r="J753" s="6" t="s">
         <v>1557</v>
       </c>
+      <c r="L753" t="s">
+        <v>4106</v>
+      </c>
       <c r="M753">
         <v>2</v>
       </c>
@@ -47199,6 +49908,9 @@
       <c r="J754" s="6" t="s">
         <v>1557</v>
       </c>
+      <c r="L754" t="s">
+        <v>4107</v>
+      </c>
       <c r="M754">
         <v>2</v>
       </c>
@@ -47241,6 +49953,9 @@
       <c r="J755" s="6" t="s">
         <v>1557</v>
       </c>
+      <c r="L755" t="s">
+        <v>4108</v>
+      </c>
       <c r="M755">
         <v>2</v>
       </c>
@@ -47283,6 +49998,9 @@
       <c r="J756" s="6" t="s">
         <v>1557</v>
       </c>
+      <c r="L756" t="s">
+        <v>4109</v>
+      </c>
       <c r="M756">
         <v>2</v>
       </c>
@@ -47325,6 +50043,9 @@
       <c r="J757" s="6" t="s">
         <v>1557</v>
       </c>
+      <c r="L757" t="s">
+        <v>4110</v>
+      </c>
       <c r="M757">
         <v>2</v>
       </c>
@@ -47367,6 +50088,9 @@
       <c r="J758" s="6" t="s">
         <v>1557</v>
       </c>
+      <c r="L758" t="s">
+        <v>4111</v>
+      </c>
       <c r="M758">
         <v>2</v>
       </c>
@@ -47409,6 +50133,9 @@
       <c r="J759" s="6" t="s">
         <v>1557</v>
       </c>
+      <c r="L759" t="s">
+        <v>4112</v>
+      </c>
       <c r="M759">
         <v>2</v>
       </c>
@@ -47451,6 +50178,9 @@
       <c r="J760" s="6" t="s">
         <v>1557</v>
       </c>
+      <c r="L760" t="s">
+        <v>4113</v>
+      </c>
       <c r="M760">
         <v>2</v>
       </c>
@@ -47493,6 +50223,9 @@
       <c r="J761" s="6" t="s">
         <v>1557</v>
       </c>
+      <c r="L761" t="s">
+        <v>4114</v>
+      </c>
       <c r="M761">
         <v>2</v>
       </c>
@@ -47535,6 +50268,9 @@
       <c r="J762" s="6" t="s">
         <v>1557</v>
       </c>
+      <c r="L762" t="s">
+        <v>4115</v>
+      </c>
       <c r="M762">
         <v>2</v>
       </c>
@@ -47577,6 +50313,9 @@
       <c r="J763" s="6" t="s">
         <v>1557</v>
       </c>
+      <c r="L763" t="s">
+        <v>4116</v>
+      </c>
       <c r="M763">
         <v>2</v>
       </c>
@@ -47619,6 +50358,9 @@
       <c r="J764" s="6" t="s">
         <v>1557</v>
       </c>
+      <c r="L764" t="s">
+        <v>4117</v>
+      </c>
       <c r="M764">
         <v>2</v>
       </c>
@@ -47661,6 +50403,9 @@
       <c r="J765" s="6" t="s">
         <v>1557</v>
       </c>
+      <c r="L765" t="s">
+        <v>4118</v>
+      </c>
       <c r="M765">
         <v>2</v>
       </c>
@@ -47703,6 +50448,9 @@
       <c r="J766" s="6" t="s">
         <v>1557</v>
       </c>
+      <c r="L766" t="s">
+        <v>4119</v>
+      </c>
       <c r="M766">
         <v>2</v>
       </c>
@@ -47745,6 +50493,9 @@
       <c r="J767" s="6" t="s">
         <v>1557</v>
       </c>
+      <c r="L767" t="s">
+        <v>4120</v>
+      </c>
       <c r="M767">
         <v>2</v>
       </c>
@@ -47787,6 +50538,9 @@
       <c r="J768" s="6" t="s">
         <v>1557</v>
       </c>
+      <c r="L768" t="s">
+        <v>4121</v>
+      </c>
       <c r="M768">
         <v>2</v>
       </c>
@@ -47829,6 +50583,9 @@
       <c r="J769" s="6" t="s">
         <v>1557</v>
       </c>
+      <c r="L769" t="s">
+        <v>4122</v>
+      </c>
       <c r="M769">
         <v>2</v>
       </c>
@@ -47871,6 +50628,9 @@
       <c r="J770" s="6" t="s">
         <v>1557</v>
       </c>
+      <c r="L770" t="s">
+        <v>4123</v>
+      </c>
       <c r="M770">
         <v>2</v>
       </c>
@@ -47913,6 +50673,9 @@
       <c r="J771" s="6" t="s">
         <v>1557</v>
       </c>
+      <c r="L771" t="s">
+        <v>4124</v>
+      </c>
       <c r="M771">
         <v>2</v>
       </c>
@@ -47955,6 +50718,9 @@
       <c r="J772" s="6" t="s">
         <v>1557</v>
       </c>
+      <c r="L772" t="s">
+        <v>4125</v>
+      </c>
       <c r="M772">
         <v>2</v>
       </c>
@@ -47997,6 +50763,9 @@
       <c r="J773" s="6" t="s">
         <v>1557</v>
       </c>
+      <c r="L773" t="s">
+        <v>4126</v>
+      </c>
       <c r="M773">
         <v>2</v>
       </c>
@@ -48039,6 +50808,9 @@
       <c r="J774" s="6" t="s">
         <v>1557</v>
       </c>
+      <c r="L774" t="s">
+        <v>4127</v>
+      </c>
       <c r="M774">
         <v>2</v>
       </c>
@@ -48081,6 +50853,9 @@
       <c r="J775" s="6" t="s">
         <v>1557</v>
       </c>
+      <c r="L775" t="s">
+        <v>4128</v>
+      </c>
       <c r="M775">
         <v>2</v>
       </c>
@@ -48123,6 +50898,9 @@
       <c r="J776" s="6" t="s">
         <v>1557</v>
       </c>
+      <c r="L776" t="s">
+        <v>4129</v>
+      </c>
       <c r="M776">
         <v>2</v>
       </c>
@@ -48165,6 +50943,9 @@
       <c r="J777" s="6" t="s">
         <v>1557</v>
       </c>
+      <c r="L777" t="s">
+        <v>4130</v>
+      </c>
       <c r="M777">
         <v>2</v>
       </c>
@@ -48206,6 +50987,9 @@
       </c>
       <c r="J778" s="6" t="s">
         <v>1557</v>
+      </c>
+      <c r="L778" t="s">
+        <v>4131</v>
       </c>
       <c r="M778">
         <v>2</v>

--- a/pages/apps/uprn-service/config.xlsx
+++ b/pages/apps/uprn-service/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NDSH\GitHub\dsh-content\dev\pages\apps\uprn-service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980BD46C-E886-4206-ABE6-CDFC613FCEA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB49CA5-E29E-4081-AA1A-12C2CC466862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="388" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11359,1084 +11359,1084 @@
     <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_england_heat/108_zchm90wn.json</t>
   </si>
   <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/001_tas_rcp26_2019_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/002_tas_rcp26_2019_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/003_tas_rcp26_2019_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/004_tas_rcp26_2049_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/005_tas_rcp26_2049_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/006_tas_rcp26_2049_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/007_tas_rcp26_2079_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/008_tas_rcp26_2079_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/009_tas_rcp26_2079_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/010_tas_rcp45_2019_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/011_tas_rcp45_2019_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/012_tas_rcp45_2019_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/013_tas_rcp45_2049_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/014_tas_rcp45_2049_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/015_tas_rcp45_2049_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/016_tas_rcp45_2079_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/017_tas_rcp45_2079_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/018_tas_rcp45_2079_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/019_tas_rcp60_2019_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/020_tas_rcp60_2019_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/021_tas_rcp60_2019_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/022_tas_rcp60_2049_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/023_tas_rcp60_2049_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/024_tas_rcp60_2049_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/025_tas_rcp60_2079_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/026_tas_rcp60_2079_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/027_tas_rcp60_2079_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/028_tas_rcp85_2019_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/029_tas_rcp85_2019_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/030_tas_rcp85_2019_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/031_tas_rcp85_2049_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/032_tas_rcp85_2049_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/033_tas_rcp85_2049_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/034_tas_rcp85_2079_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/035_tas_rcp85_2079_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/036_tas_rcp85_2079_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/037_tasmax_rcp26_2019_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/038_tasmax_rcp26_2019_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/039_tasmax_rcp26_2019_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/040_tasmax_rcp26_2049_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/041_tasmax_rcp26_2049_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/042_tasmax_rcp26_2049_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/043_tasmax_rcp26_2079_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/044_tasmax_rcp26_2079_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/045_tasmax_rcp26_2079_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/046_tasmax_rcp45_2019_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/047_tasmax_rcp45_2019_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/048_tasmax_rcp45_2019_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/049_tasmax_rcp45_2049_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/050_tasmax_rcp45_2049_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/051_tasmax_rcp45_2049_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/052_tasmax_rcp45_2079_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/053_tasmax_rcp45_2079_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/054_tasmax_rcp45_2079_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/055_tasmax_rcp60_2019_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/056_tasmax_rcp60_2019_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/057_tasmax_rcp60_2019_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/058_tasmax_rcp60_2049_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/059_tasmax_rcp60_2049_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/060_tasmax_rcp60_2049_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/061_tasmax_rcp60_2079_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/062_tasmax_rcp60_2079_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/063_tasmax_rcp60_2079_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/064_tasmax_rcp85_2019_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/065_tasmax_rcp85_2019_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/066_tasmax_rcp85_2019_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/067_tasmax_rcp85_2049_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/068_tasmax_rcp85_2049_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/069_tasmax_rcp85_2049_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/070_tasmax_rcp85_2079_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/071_tasmax_rcp85_2079_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/072_tasmax_rcp85_2079_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/073_z_all_rel_tas_rcp26_2019_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/074_z_all_rel_tas_rcp26_2019_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/075_z_all_rel_tas_rcp26_2019_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/076_z_all_rel_tas_rcp26_2049_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/077_z_all_rel_tas_rcp26_2049_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/078_z_all_rel_tas_rcp26_2049_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/079_z_all_rel_tas_rcp26_2079_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/080_z_all_rel_tas_rcp26_2079_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/081_z_all_rel_tas_rcp26_2079_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/082_z_all_rel_tas_rcp45_2019_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/083_z_all_rel_tas_rcp45_2019_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/084_z_all_rel_tas_rcp45_2019_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/085_z_all_rel_tas_rcp45_2049_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/086_z_all_rel_tas_rcp45_2049_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/087_z_all_rel_tas_rcp45_2049_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/088_z_all_rel_tas_rcp45_2079_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/089_z_all_rel_tas_rcp45_2079_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/090_z_all_rel_tas_rcp45_2079_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/091_z_all_rel_tas_rcp60_2019_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/092_z_all_rel_tas_rcp60_2019_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/093_z_all_rel_tas_rcp60_2019_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/094_z_all_rel_tas_rcp60_2049_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/095_z_all_rel_tas_rcp60_2049_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/096_z_all_rel_tas_rcp60_2049_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/097_z_all_rel_tas_rcp60_2079_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/098_z_all_rel_tas_rcp60_2079_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/099_z_all_rel_tas_rcp60_2079_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/100_z_all_rel_tas_rcp85_2019_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/101_z_all_rel_tas_rcp85_2019_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/102_z_all_rel_tas_rcp85_2019_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/103_z_all_rel_tas_rcp85_2049_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/104_z_all_rel_tas_rcp85_2049_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/105_z_all_rel_tas_rcp85_2049_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/106_z_all_rel_tas_rcp85_2079_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/107_z_all_rel_tas_rcp85_2079_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/108_z_all_rel_tas_rcp85_2079_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/109_z_all_rel_tasmax_rcp26_2019_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/110_z_all_rel_tasmax_rcp26_2019_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/111_z_all_rel_tasmax_rcp26_2019_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/112_z_all_rel_tasmax_rcp26_2049_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/113_z_all_rel_tasmax_rcp26_2049_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/114_z_all_rel_tasmax_rcp26_2049_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/115_z_all_rel_tasmax_rcp26_2079_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/116_z_all_rel_tasmax_rcp26_2079_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/117_z_all_rel_tasmax_rcp26_2079_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/118_z_all_rel_tasmax_rcp45_2019_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/119_z_all_rel_tasmax_rcp45_2019_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/120_z_all_rel_tasmax_rcp45_2019_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/121_z_all_rel_tasmax_rcp45_2049_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/122_z_all_rel_tasmax_rcp45_2049_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/123_z_all_rel_tasmax_rcp45_2049_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/124_z_all_rel_tasmax_rcp45_2079_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/125_z_all_rel_tasmax_rcp45_2079_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/126_z_all_rel_tasmax_rcp45_2079_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/127_z_all_rel_tasmax_rcp60_2019_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/128_z_all_rel_tasmax_rcp60_2019_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/129_z_all_rel_tasmax_rcp60_2019_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/130_z_all_rel_tasmax_rcp60_2049_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/131_z_all_rel_tasmax_rcp60_2049_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/132_z_all_rel_tasmax_rcp60_2049_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/133_z_all_rel_tasmax_rcp60_2079_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/134_z_all_rel_tasmax_rcp60_2079_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/135_z_all_rel_tasmax_rcp60_2079_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/136_z_all_rel_tasmax_rcp85_2019_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/137_z_all_rel_tasmax_rcp85_2019_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/138_z_all_rel_tasmax_rcp85_2019_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/139_z_all_rel_tasmax_rcp85_2049_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/140_z_all_rel_tasmax_rcp85_2049_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/141_z_all_rel_tasmax_rcp85_2049_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/142_z_all_rel_tasmax_rcp85_2079_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/143_z_all_rel_tasmax_rcp85_2079_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/144_z_all_rel_tasmax_rcp85_2079_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/145_tasmax_rcp26_rp20_2020_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/146_tasmax_rcp26_rp20_2020_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/147_tasmax_rcp26_rp20_2020_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/148_tasmax_rcp26_rp20_2050_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/149_tasmax_rcp26_rp20_2050_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/150_tasmax_rcp26_rp20_2050_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/151_tasmax_rcp26_rp20_2080_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/152_tasmax_rcp26_rp20_2080_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/153_tasmax_rcp26_rp20_2080_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/154_tasmax_rcp26_rp50_2020_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/155_tasmax_rcp26_rp50_2020_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/156_tasmax_rcp26_rp50_2020_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/157_tasmax_rcp26_rp50_2050_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/158_tasmax_rcp26_rp50_2050_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/159_tasmax_rcp26_rp50_2050_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/160_tasmax_rcp26_rp50_2080_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/161_tasmax_rcp26_rp50_2080_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/162_tasmax_rcp26_rp50_2080_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/163_tasmax_rcp26_rp100_2020_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/164_tasmax_rcp26_rp100_2020_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/165_tasmax_rcp26_rp100_2020_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/166_tasmax_rcp26_rp100_2050_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/167_tasmax_rcp26_rp100_2050_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/168_tasmax_rcp26_rp100_2050_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/169_tasmax_rcp26_rp100_2080_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/170_tasmax_rcp26_rp100_2080_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/171_tasmax_rcp26_rp100_2080_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/172_tasmax_rcp45_rp20_2020_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/173_tasmax_rcp45_rp20_2020_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/174_tasmax_rcp45_rp20_2020_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/175_tasmax_rcp45_rp20_2050_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/176_tasmax_rcp45_rp20_2050_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/177_tasmax_rcp45_rp20_2050_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/178_tasmax_rcp45_rp20_2080_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/179_tasmax_rcp45_rp20_2080_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/180_tasmax_rcp45_rp20_2080_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/181_tasmax_rcp45_rp50_2020_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/182_tasmax_rcp45_rp50_2020_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/183_tasmax_rcp45_rp50_2020_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/184_tasmax_rcp45_rp50_2050_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/185_tasmax_rcp45_rp50_2050_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/186_tasmax_rcp45_rp50_2050_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/187_tasmax_rcp45_rp50_2080_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/188_tasmax_rcp45_rp50_2080_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/189_tasmax_rcp45_rp50_2080_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/190_tasmax_rcp45_rp100_2020_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/191_tasmax_rcp45_rp100_2020_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/192_tasmax_rcp45_rp100_2020_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/193_tasmax_rcp45_rp100_2050_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/194_tasmax_rcp45_rp100_2050_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/195_tasmax_rcp45_rp100_2050_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/196_tasmax_rcp45_rp100_2080_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/197_tasmax_rcp45_rp100_2080_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/198_tasmax_rcp45_rp100_2080_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/199_tasmax_rcp60_rp20_2020_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/200_tasmax_rcp60_rp20_2020_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/201_tasmax_rcp60_rp20_2020_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/202_tasmax_rcp60_rp20_2050_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/203_tasmax_rcp60_rp20_2050_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/204_tasmax_rcp60_rp20_2050_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/205_tasmax_rcp60_rp20_2080_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/206_tasmax_rcp60_rp20_2080_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/207_tasmax_rcp60_rp20_2080_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/208_tasmax_rcp60_rp50_2020_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/209_tasmax_rcp60_rp50_2020_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/210_tasmax_rcp60_rp50_2020_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/211_tasmax_rcp60_rp50_2050_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/212_tasmax_rcp60_rp50_2050_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/213_tasmax_rcp60_rp50_2050_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/214_tasmax_rcp60_rp50_2080_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/215_tasmax_rcp60_rp50_2080_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/216_tasmax_rcp60_rp50_2080_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/217_tasmax_rcp60_rp100_2020_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/218_tasmax_rcp60_rp100_2020_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/219_tasmax_rcp60_rp100_2020_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/220_tasmax_rcp60_rp100_2050_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/221_tasmax_rcp60_rp100_2050_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/222_tasmax_rcp60_rp100_2050_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/223_tasmax_rcp60_rp100_2080_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/224_tasmax_rcp60_rp100_2080_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/225_tasmax_rcp60_rp100_2080_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/226_tasmax_rcp85_rp20_2020_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/227_tasmax_rcp85_rp20_2020_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/228_tasmax_rcp85_rp20_2020_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/229_tasmax_rcp85_rp20_2050_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/230_tasmax_rcp85_rp20_2050_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/231_tasmax_rcp85_rp20_2050_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/232_tasmax_rcp85_rp20_2080_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/233_tasmax_rcp85_rp20_2080_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/234_tasmax_rcp85_rp20_2080_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/235_tasmax_rcp85_rp50_2020_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/236_tasmax_rcp85_rp50_2020_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/237_tasmax_rcp85_rp50_2020_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/238_tasmax_rcp85_rp50_2050_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/239_tasmax_rcp85_rp50_2050_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/240_tasmax_rcp85_rp50_2050_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/241_tasmax_rcp85_rp50_2080_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/242_tasmax_rcp85_rp50_2080_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/243_tasmax_rcp85_rp50_2080_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/244_tasmax_rcp85_rp100_2020_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/245_tasmax_rcp85_rp100_2020_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/246_tasmax_rcp85_rp100_2020_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/247_tasmax_rcp85_rp100_2050_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/248_tasmax_rcp85_rp100_2050_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/249_tasmax_rcp85_rp100_2050_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/250_tasmax_rcp85_rp100_2080_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/251_tasmax_rcp85_rp100_2080_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/252_tasmax_rcp85_rp100_2080_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/253_z_ar_tasmax_rcp26_rp20_2020_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/254_z_ar_tasmax_rcp26_rp20_2020_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/255_z_ar_tasmax_rcp26_rp20_2020_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/256_z_ar_tasmax_rcp26_rp20_2050_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/257_z_ar_tasmax_rcp26_rp20_2050_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/258_z_ar_tasmax_rcp26_rp20_2050_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/259_z_ar_tasmax_rcp26_rp20_2080_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/260_z_ar_tasmax_rcp26_rp20_2080_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/261_z_ar_tasmax_rcp26_rp20_2080_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/262_z_ar_tasmax_rcp26_rp50_2020_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/263_z_ar_tasmax_rcp26_rp50_2020_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/264_z_ar_tasmax_rcp26_rp50_2020_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/265_z_ar_tasmax_rcp26_rp50_2050_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/266_z_ar_tasmax_rcp26_rp50_2050_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/267_z_ar_tasmax_rcp26_rp50_2050_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/268_z_ar_tasmax_rcp26_rp50_2080_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/269_z_ar_tasmax_rcp26_rp50_2080_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/270_z_ar_tasmax_rcp26_rp50_2080_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/271_z_ar_tasmax_rcp26_rp100_2020_10.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/272_z_ar_tasmax_rcp26_rp100_2020_50.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/273_z_ar_tasmax_rcp26_rp100_2020_90.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/274_z_ar_tasmax_rcp26_rp100_2050_10.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/275_z_ar_tasmax_rcp26_rp100_2050_50.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/276_z_ar_tasmax_rcp26_rp100_2050_90.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/277_z_ar_tasmax_rcp26_rp100_2080_10.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/278_z_ar_tasmax_rcp26_rp100_2080_50.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/279_z_ar_tasmax_rcp26_rp100_2080_90.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/280_z_ar_tasmax_rcp45_rp20_2020_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/281_z_ar_tasmax_rcp45_rp20_2020_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/282_z_ar_tasmax_rcp45_rp20_2020_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/283_z_ar_tasmax_rcp45_rp20_2050_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/284_z_ar_tasmax_rcp45_rp20_2050_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/285_z_ar_tasmax_rcp45_rp20_2050_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/286_z_ar_tasmax_rcp45_rp20_2080_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/287_z_ar_tasmax_rcp45_rp20_2080_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/288_z_ar_tasmax_rcp45_rp20_2080_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/289_z_ar_tasmax_rcp45_rp50_2020_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/290_z_ar_tasmax_rcp45_rp50_2020_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/291_z_ar_tasmax_rcp45_rp50_2020_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/292_z_ar_tasmax_rcp45_rp50_2050_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/293_z_ar_tasmax_rcp45_rp50_2050_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/294_z_ar_tasmax_rcp45_rp50_2050_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/295_z_ar_tasmax_rcp45_rp50_2080_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/296_z_ar_tasmax_rcp45_rp50_2080_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/297_z_ar_tasmax_rcp45_rp50_2080_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/298_z_ar_tasmax_rcp45_rp100_2020_10.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/299_z_ar_tasmax_rcp45_rp100_2020_50.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/300_z_ar_tasmax_rcp45_rp100_2020_90.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/301_z_ar_tasmax_rcp45_rp100_2050_10.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/302_z_ar_tasmax_rcp45_rp100_2050_50.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/303_z_ar_tasmax_rcp45_rp100_2050_90.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/304_z_ar_tasmax_rcp45_rp100_2080_10.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/305_z_ar_tasmax_rcp45_rp100_2080_50.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/306_z_ar_tasmax_rcp45_rp100_2080_90.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/307_z_ar_tasmax_rcp60_rp20_2020_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/308_z_ar_tasmax_rcp60_rp20_2020_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/309_z_ar_tasmax_rcp60_rp20_2020_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/310_z_ar_tasmax_rcp60_rp20_2050_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/311_z_ar_tasmax_rcp60_rp20_2050_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/312_z_ar_tasmax_rcp60_rp20_2050_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/313_z_ar_tasmax_rcp60_rp20_2080_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/314_z_ar_tasmax_rcp60_rp20_2080_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/315_z_ar_tasmax_rcp60_rp20_2080_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/316_z_ar_tasmax_rcp60_rp50_2020_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/317_z_ar_tasmax_rcp60_rp50_2020_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/318_z_ar_tasmax_rcp60_rp50_2020_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/319_z_ar_tasmax_rcp60_rp50_2050_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/320_z_ar_tasmax_rcp60_rp50_2050_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/321_z_ar_tasmax_rcp60_rp50_2050_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/322_z_ar_tasmax_rcp60_rp50_2080_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/323_z_ar_tasmax_rcp60_rp50_2080_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/324_z_ar_tasmax_rcp60_rp50_2080_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/325_z_ar_tasmax_rcp60_rp100_2020_10.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/326_z_ar_tasmax_rcp60_rp100_2020_50.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/327_z_ar_tasmax_rcp60_rp100_2020_90.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/328_z_ar_tasmax_rcp60_rp100_2050_10.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/329_z_ar_tasmax_rcp60_rp100_2050_50.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/330_z_ar_tasmax_rcp60_rp100_2050_90.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/331_z_ar_tasmax_rcp60_rp100_2080_10.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/332_z_ar_tasmax_rcp60_rp100_2080_50.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/333_z_ar_tasmax_rcp60_rp100_2080_90.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/334_z_ar_tasmax_rcp85_rp20_2020_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/335_z_ar_tasmax_rcp85_rp20_2020_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/336_z_ar_tasmax_rcp85_rp20_2020_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/337_z_ar_tasmax_rcp85_rp20_2050_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/338_z_ar_tasmax_rcp85_rp20_2050_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/339_z_ar_tasmax_rcp85_rp20_2050_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/340_z_ar_tasmax_rcp85_rp20_2080_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/341_z_ar_tasmax_rcp85_rp20_2080_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/342_z_ar_tasmax_rcp85_rp20_2080_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/343_z_ar_tasmax_rcp85_rp50_2020_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/344_z_ar_tasmax_rcp85_rp50_2020_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/345_z_ar_tasmax_rcp85_rp50_2020_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/346_z_ar_tasmax_rcp85_rp50_2050_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/347_z_ar_tasmax_rcp85_rp50_2050_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/348_z_ar_tasmax_rcp85_rp50_2050_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/349_z_ar_tasmax_rcp85_rp50_2080_10p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/350_z_ar_tasmax_rcp85_rp50_2080_50p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/351_z_ar_tasmax_rcp85_rp50_2080_90p.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/352_z_ar_tasmax_rcp85_rp100_2020_10.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/353_z_ar_tasmax_rcp85_rp100_2020_50.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/354_z_ar_tasmax_rcp85_rp100_2020_90.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/355_z_ar_tasmax_rcp85_rp100_2050_10.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/356_z_ar_tasmax_rcp85_rp100_2050_50.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/357_z_ar_tasmax_rcp85_rp100_2050_90.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/358_z_ar_tasmax_rcp85_rp100_2080_10.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/359_z_ar_tasmax_rcp85_rp100_2080_50.json</t>
-  </si>
-  <si>
-    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/climatejust_grid_uk_ukcp18/360_z_ar_tasmax_rcp85_rp100_2080_90.json</t>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/001_tas_rcp26_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/002_tas_rcp26_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/003_tas_rcp26_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/004_tas_rcp26_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/005_tas_rcp26_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/006_tas_rcp26_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/007_tas_rcp26_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/008_tas_rcp26_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/009_tas_rcp26_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/010_tas_rcp45_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/011_tas_rcp45_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/012_tas_rcp45_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/013_tas_rcp45_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/014_tas_rcp45_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/015_tas_rcp45_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/016_tas_rcp45_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/017_tas_rcp45_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/018_tas_rcp45_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/019_tas_rcp60_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/020_tas_rcp60_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/021_tas_rcp60_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/022_tas_rcp60_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/023_tas_rcp60_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/024_tas_rcp60_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/025_tas_rcp60_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/026_tas_rcp60_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/027_tas_rcp60_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/028_tas_rcp85_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/029_tas_rcp85_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/030_tas_rcp85_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/031_tas_rcp85_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/032_tas_rcp85_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/033_tas_rcp85_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/034_tas_rcp85_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/035_tas_rcp85_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/036_tas_rcp85_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/037_tasmax_rcp26_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/038_tasmax_rcp26_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/039_tasmax_rcp26_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/040_tasmax_rcp26_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/041_tasmax_rcp26_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/042_tasmax_rcp26_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/043_tasmax_rcp26_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/044_tasmax_rcp26_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/045_tasmax_rcp26_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/046_tasmax_rcp45_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/047_tasmax_rcp45_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/048_tasmax_rcp45_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/049_tasmax_rcp45_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/050_tasmax_rcp45_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/051_tasmax_rcp45_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/052_tasmax_rcp45_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/053_tasmax_rcp45_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/054_tasmax_rcp45_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/055_tasmax_rcp60_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/056_tasmax_rcp60_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/057_tasmax_rcp60_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/058_tasmax_rcp60_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/059_tasmax_rcp60_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/060_tasmax_rcp60_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/061_tasmax_rcp60_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/062_tasmax_rcp60_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/063_tasmax_rcp60_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/064_tasmax_rcp85_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/065_tasmax_rcp85_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/066_tasmax_rcp85_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/067_tasmax_rcp85_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/068_tasmax_rcp85_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/069_tasmax_rcp85_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/070_tasmax_rcp85_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/071_tasmax_rcp85_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/072_tasmax_rcp85_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/073_z_all_rel_tas_rcp26_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/074_z_all_rel_tas_rcp26_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/075_z_all_rel_tas_rcp26_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/076_z_all_rel_tas_rcp26_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/077_z_all_rel_tas_rcp26_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/078_z_all_rel_tas_rcp26_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/079_z_all_rel_tas_rcp26_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/080_z_all_rel_tas_rcp26_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/081_z_all_rel_tas_rcp26_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/082_z_all_rel_tas_rcp45_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/083_z_all_rel_tas_rcp45_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/084_z_all_rel_tas_rcp45_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/085_z_all_rel_tas_rcp45_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/086_z_all_rel_tas_rcp45_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/087_z_all_rel_tas_rcp45_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/088_z_all_rel_tas_rcp45_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/089_z_all_rel_tas_rcp45_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/090_z_all_rel_tas_rcp45_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/091_z_all_rel_tas_rcp60_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/092_z_all_rel_tas_rcp60_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/093_z_all_rel_tas_rcp60_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/094_z_all_rel_tas_rcp60_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/095_z_all_rel_tas_rcp60_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/096_z_all_rel_tas_rcp60_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/097_z_all_rel_tas_rcp60_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/098_z_all_rel_tas_rcp60_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/099_z_all_rel_tas_rcp60_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/100_z_all_rel_tas_rcp85_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/101_z_all_rel_tas_rcp85_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/102_z_all_rel_tas_rcp85_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/103_z_all_rel_tas_rcp85_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/104_z_all_rel_tas_rcp85_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/105_z_all_rel_tas_rcp85_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/106_z_all_rel_tas_rcp85_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/107_z_all_rel_tas_rcp85_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/108_z_all_rel_tas_rcp85_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/109_z_all_rel_tasmax_rcp26_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/110_z_all_rel_tasmax_rcp26_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/111_z_all_rel_tasmax_rcp26_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/112_z_all_rel_tasmax_rcp26_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/113_z_all_rel_tasmax_rcp26_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/114_z_all_rel_tasmax_rcp26_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/115_z_all_rel_tasmax_rcp26_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/116_z_all_rel_tasmax_rcp26_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/117_z_all_rel_tasmax_rcp26_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/118_z_all_rel_tasmax_rcp45_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/119_z_all_rel_tasmax_rcp45_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/120_z_all_rel_tasmax_rcp45_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/121_z_all_rel_tasmax_rcp45_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/122_z_all_rel_tasmax_rcp45_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/123_z_all_rel_tasmax_rcp45_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/124_z_all_rel_tasmax_rcp45_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/125_z_all_rel_tasmax_rcp45_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/126_z_all_rel_tasmax_rcp45_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/127_z_all_rel_tasmax_rcp60_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/128_z_all_rel_tasmax_rcp60_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/129_z_all_rel_tasmax_rcp60_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/130_z_all_rel_tasmax_rcp60_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/131_z_all_rel_tasmax_rcp60_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/132_z_all_rel_tasmax_rcp60_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/133_z_all_rel_tasmax_rcp60_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/134_z_all_rel_tasmax_rcp60_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/135_z_all_rel_tasmax_rcp60_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/136_z_all_rel_tasmax_rcp85_2019_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/137_z_all_rel_tasmax_rcp85_2019_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/138_z_all_rel_tasmax_rcp85_2019_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/139_z_all_rel_tasmax_rcp85_2049_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/140_z_all_rel_tasmax_rcp85_2049_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/141_z_all_rel_tasmax_rcp85_2049_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/142_z_all_rel_tasmax_rcp85_2079_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/143_z_all_rel_tasmax_rcp85_2079_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/144_z_all_rel_tasmax_rcp85_2079_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/145_tasmax_rcp26_rp20_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/146_tasmax_rcp26_rp20_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/147_tasmax_rcp26_rp20_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/148_tasmax_rcp26_rp20_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/149_tasmax_rcp26_rp20_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/150_tasmax_rcp26_rp20_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/151_tasmax_rcp26_rp20_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/152_tasmax_rcp26_rp20_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/153_tasmax_rcp26_rp20_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/154_tasmax_rcp26_rp50_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/155_tasmax_rcp26_rp50_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/156_tasmax_rcp26_rp50_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/157_tasmax_rcp26_rp50_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/158_tasmax_rcp26_rp50_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/159_tasmax_rcp26_rp50_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/160_tasmax_rcp26_rp50_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/161_tasmax_rcp26_rp50_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/162_tasmax_rcp26_rp50_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/163_tasmax_rcp26_rp100_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/164_tasmax_rcp26_rp100_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/165_tasmax_rcp26_rp100_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/166_tasmax_rcp26_rp100_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/167_tasmax_rcp26_rp100_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/168_tasmax_rcp26_rp100_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/169_tasmax_rcp26_rp100_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/170_tasmax_rcp26_rp100_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/171_tasmax_rcp26_rp100_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/172_tasmax_rcp45_rp20_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/173_tasmax_rcp45_rp20_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/174_tasmax_rcp45_rp20_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/175_tasmax_rcp45_rp20_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/176_tasmax_rcp45_rp20_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/177_tasmax_rcp45_rp20_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/178_tasmax_rcp45_rp20_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/179_tasmax_rcp45_rp20_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/180_tasmax_rcp45_rp20_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/181_tasmax_rcp45_rp50_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/182_tasmax_rcp45_rp50_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/183_tasmax_rcp45_rp50_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/184_tasmax_rcp45_rp50_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/185_tasmax_rcp45_rp50_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/186_tasmax_rcp45_rp50_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/187_tasmax_rcp45_rp50_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/188_tasmax_rcp45_rp50_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/189_tasmax_rcp45_rp50_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/190_tasmax_rcp45_rp100_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/191_tasmax_rcp45_rp100_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/192_tasmax_rcp45_rp100_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/193_tasmax_rcp45_rp100_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/194_tasmax_rcp45_rp100_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/195_tasmax_rcp45_rp100_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/196_tasmax_rcp45_rp100_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/197_tasmax_rcp45_rp100_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/198_tasmax_rcp45_rp100_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/199_tasmax_rcp60_rp20_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/200_tasmax_rcp60_rp20_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/201_tasmax_rcp60_rp20_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/202_tasmax_rcp60_rp20_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/203_tasmax_rcp60_rp20_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/204_tasmax_rcp60_rp20_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/205_tasmax_rcp60_rp20_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/206_tasmax_rcp60_rp20_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/207_tasmax_rcp60_rp20_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/208_tasmax_rcp60_rp50_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/209_tasmax_rcp60_rp50_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/210_tasmax_rcp60_rp50_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/211_tasmax_rcp60_rp50_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/212_tasmax_rcp60_rp50_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/213_tasmax_rcp60_rp50_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/214_tasmax_rcp60_rp50_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/215_tasmax_rcp60_rp50_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/216_tasmax_rcp60_rp50_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/217_tasmax_rcp60_rp100_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/218_tasmax_rcp60_rp100_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/219_tasmax_rcp60_rp100_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/220_tasmax_rcp60_rp100_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/221_tasmax_rcp60_rp100_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/222_tasmax_rcp60_rp100_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/223_tasmax_rcp60_rp100_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/224_tasmax_rcp60_rp100_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/225_tasmax_rcp60_rp100_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/226_tasmax_rcp85_rp20_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/227_tasmax_rcp85_rp20_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/228_tasmax_rcp85_rp20_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/229_tasmax_rcp85_rp20_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/230_tasmax_rcp85_rp20_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/231_tasmax_rcp85_rp20_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/232_tasmax_rcp85_rp20_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/233_tasmax_rcp85_rp20_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/234_tasmax_rcp85_rp20_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/235_tasmax_rcp85_rp50_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/236_tasmax_rcp85_rp50_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/237_tasmax_rcp85_rp50_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/238_tasmax_rcp85_rp50_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/239_tasmax_rcp85_rp50_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/240_tasmax_rcp85_rp50_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/241_tasmax_rcp85_rp50_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/242_tasmax_rcp85_rp50_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/243_tasmax_rcp85_rp50_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/244_tasmax_rcp85_rp100_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/245_tasmax_rcp85_rp100_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/246_tasmax_rcp85_rp100_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/247_tasmax_rcp85_rp100_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/248_tasmax_rcp85_rp100_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/249_tasmax_rcp85_rp100_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/250_tasmax_rcp85_rp100_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/251_tasmax_rcp85_rp100_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/252_tasmax_rcp85_rp100_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/253_z_ar_tasmax_rcp26_rp20_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/254_z_ar_tasmax_rcp26_rp20_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/255_z_ar_tasmax_rcp26_rp20_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/256_z_ar_tasmax_rcp26_rp20_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/257_z_ar_tasmax_rcp26_rp20_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/258_z_ar_tasmax_rcp26_rp20_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/259_z_ar_tasmax_rcp26_rp20_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/260_z_ar_tasmax_rcp26_rp20_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/261_z_ar_tasmax_rcp26_rp20_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/262_z_ar_tasmax_rcp26_rp50_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/263_z_ar_tasmax_rcp26_rp50_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/264_z_ar_tasmax_rcp26_rp50_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/265_z_ar_tasmax_rcp26_rp50_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/266_z_ar_tasmax_rcp26_rp50_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/267_z_ar_tasmax_rcp26_rp50_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/268_z_ar_tasmax_rcp26_rp50_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/269_z_ar_tasmax_rcp26_rp50_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/270_z_ar_tasmax_rcp26_rp50_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/271_z_ar_tasmax_rcp26_rp100_2020_10.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/272_z_ar_tasmax_rcp26_rp100_2020_50.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/273_z_ar_tasmax_rcp26_rp100_2020_90.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/274_z_ar_tasmax_rcp26_rp100_2050_10.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/275_z_ar_tasmax_rcp26_rp100_2050_50.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/276_z_ar_tasmax_rcp26_rp100_2050_90.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/277_z_ar_tasmax_rcp26_rp100_2080_10.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/278_z_ar_tasmax_rcp26_rp100_2080_50.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/279_z_ar_tasmax_rcp26_rp100_2080_90.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/280_z_ar_tasmax_rcp45_rp20_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/281_z_ar_tasmax_rcp45_rp20_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/282_z_ar_tasmax_rcp45_rp20_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/283_z_ar_tasmax_rcp45_rp20_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/284_z_ar_tasmax_rcp45_rp20_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/285_z_ar_tasmax_rcp45_rp20_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/286_z_ar_tasmax_rcp45_rp20_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/287_z_ar_tasmax_rcp45_rp20_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/288_z_ar_tasmax_rcp45_rp20_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/289_z_ar_tasmax_rcp45_rp50_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/290_z_ar_tasmax_rcp45_rp50_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/291_z_ar_tasmax_rcp45_rp50_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/292_z_ar_tasmax_rcp45_rp50_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/293_z_ar_tasmax_rcp45_rp50_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/294_z_ar_tasmax_rcp45_rp50_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/295_z_ar_tasmax_rcp45_rp50_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/296_z_ar_tasmax_rcp45_rp50_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/297_z_ar_tasmax_rcp45_rp50_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/298_z_ar_tasmax_rcp45_rp100_2020_10.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/299_z_ar_tasmax_rcp45_rp100_2020_50.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/300_z_ar_tasmax_rcp45_rp100_2020_90.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/301_z_ar_tasmax_rcp45_rp100_2050_10.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/302_z_ar_tasmax_rcp45_rp100_2050_50.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/303_z_ar_tasmax_rcp45_rp100_2050_90.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/304_z_ar_tasmax_rcp45_rp100_2080_10.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/305_z_ar_tasmax_rcp45_rp100_2080_50.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/306_z_ar_tasmax_rcp45_rp100_2080_90.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/307_z_ar_tasmax_rcp60_rp20_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/308_z_ar_tasmax_rcp60_rp20_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/309_z_ar_tasmax_rcp60_rp20_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/310_z_ar_tasmax_rcp60_rp20_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/311_z_ar_tasmax_rcp60_rp20_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/312_z_ar_tasmax_rcp60_rp20_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/313_z_ar_tasmax_rcp60_rp20_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/314_z_ar_tasmax_rcp60_rp20_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/315_z_ar_tasmax_rcp60_rp20_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/316_z_ar_tasmax_rcp60_rp50_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/317_z_ar_tasmax_rcp60_rp50_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/318_z_ar_tasmax_rcp60_rp50_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/319_z_ar_tasmax_rcp60_rp50_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/320_z_ar_tasmax_rcp60_rp50_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/321_z_ar_tasmax_rcp60_rp50_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/322_z_ar_tasmax_rcp60_rp50_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/323_z_ar_tasmax_rcp60_rp50_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/324_z_ar_tasmax_rcp60_rp50_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/325_z_ar_tasmax_rcp60_rp100_2020_10.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/326_z_ar_tasmax_rcp60_rp100_2020_50.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/327_z_ar_tasmax_rcp60_rp100_2020_90.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/328_z_ar_tasmax_rcp60_rp100_2050_10.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/329_z_ar_tasmax_rcp60_rp100_2050_50.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/330_z_ar_tasmax_rcp60_rp100_2050_90.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/331_z_ar_tasmax_rcp60_rp100_2080_10.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/332_z_ar_tasmax_rcp60_rp100_2080_50.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/333_z_ar_tasmax_rcp60_rp100_2080_90.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/334_z_ar_tasmax_rcp85_rp20_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/335_z_ar_tasmax_rcp85_rp20_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/336_z_ar_tasmax_rcp85_rp20_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/337_z_ar_tasmax_rcp85_rp20_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/338_z_ar_tasmax_rcp85_rp20_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/339_z_ar_tasmax_rcp85_rp20_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/340_z_ar_tasmax_rcp85_rp20_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/341_z_ar_tasmax_rcp85_rp20_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/342_z_ar_tasmax_rcp85_rp20_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/343_z_ar_tasmax_rcp85_rp50_2020_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/344_z_ar_tasmax_rcp85_rp50_2020_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/345_z_ar_tasmax_rcp85_rp50_2020_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/346_z_ar_tasmax_rcp85_rp50_2050_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/347_z_ar_tasmax_rcp85_rp50_2050_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/348_z_ar_tasmax_rcp85_rp50_2050_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/349_z_ar_tasmax_rcp85_rp50_2080_10p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/350_z_ar_tasmax_rcp85_rp50_2080_50p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/351_z_ar_tasmax_rcp85_rp50_2080_90p.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/352_z_ar_tasmax_rcp85_rp100_2020_10.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/353_z_ar_tasmax_rcp85_rp100_2020_50.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/354_z_ar_tasmax_rcp85_rp100_2020_90.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/355_z_ar_tasmax_rcp85_rp100_2050_10.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/356_z_ar_tasmax_rcp85_rp100_2050_50.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/357_z_ar_tasmax_rcp85_rp100_2050_90.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/358_z_ar_tasmax_rcp85_rp100_2080_10.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/359_z_ar_tasmax_rcp85_rp100_2080_50.json</t>
+  </si>
+  <si>
+    <t>https://nerc-digital-solutions-hub.github.io/dsh-metadata/UPRN/ClimateJust/md/climatejust_grid_uk_ukcp18/360_z_ar_tasmax_rcp85_rp100_2080_90.json</t>
   </si>
 </sst>
 </file>

--- a/pages/apps/uprn-service/config.xlsx
+++ b/pages/apps/uprn-service/config.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NDSH\GitHub\dsh-content\dev\pages\apps\uprn-service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12362C1F-B6B9-4DE1-88E1-1C6C9A2B0253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7758E5C-E726-42D2-ABB0-3E340545D61C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="388" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -70193,10 +70193,10 @@
         <v>1834</v>
       </c>
       <c r="G1207" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1207" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1207" t="b">
         <v>0</v>
@@ -70241,10 +70241,10 @@
         <v>1834</v>
       </c>
       <c r="G1208" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1208" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1208" t="b">
         <v>0</v>
@@ -70289,10 +70289,10 @@
         <v>1834</v>
       </c>
       <c r="G1209" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1209" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1209" t="b">
         <v>0</v>
@@ -70337,10 +70337,10 @@
         <v>1834</v>
       </c>
       <c r="G1210" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1210" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1210" t="b">
         <v>0</v>
@@ -70385,10 +70385,10 @@
         <v>1834</v>
       </c>
       <c r="G1211" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1211" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1211" t="b">
         <v>0</v>
@@ -70433,10 +70433,10 @@
         <v>1834</v>
       </c>
       <c r="G1212" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1212" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1212" t="b">
         <v>0</v>
@@ -70481,10 +70481,10 @@
         <v>1834</v>
       </c>
       <c r="G1213" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1213" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1213" t="b">
         <v>0</v>
@@ -70529,10 +70529,10 @@
         <v>1834</v>
       </c>
       <c r="G1214" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1214" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1214" t="b">
         <v>0</v>
@@ -70577,10 +70577,10 @@
         <v>1834</v>
       </c>
       <c r="G1215" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1215" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1215" t="b">
         <v>0</v>
@@ -70625,10 +70625,10 @@
         <v>1834</v>
       </c>
       <c r="G1216" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1216" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1216" t="b">
         <v>0</v>
@@ -70673,10 +70673,10 @@
         <v>1834</v>
       </c>
       <c r="G1217" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1217" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1217" t="b">
         <v>0</v>
@@ -70721,10 +70721,10 @@
         <v>1834</v>
       </c>
       <c r="G1218" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1218" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1218" t="b">
         <v>0</v>
@@ -70769,10 +70769,10 @@
         <v>1834</v>
       </c>
       <c r="G1219" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1219" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1219" t="b">
         <v>0</v>
@@ -70817,10 +70817,10 @@
         <v>1834</v>
       </c>
       <c r="G1220" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1220" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1220" t="b">
         <v>0</v>
@@ -70865,10 +70865,10 @@
         <v>1834</v>
       </c>
       <c r="G1221" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1221" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1221" t="b">
         <v>0</v>
@@ -70913,10 +70913,10 @@
         <v>1834</v>
       </c>
       <c r="G1222" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1222" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1222" t="b">
         <v>0</v>

--- a/pages/apps/uprn-service/config.xlsx
+++ b/pages/apps/uprn-service/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NDSH\GitHub\dsh-content\dev\pages\apps\uprn-service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7758E5C-E726-42D2-ABB0-3E340545D61C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6DF1FA3-D949-47ED-AC24-764547C1198F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="388" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="388" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="folders" sheetId="1" r:id="rId1"/>
@@ -16025,10 +16025,10 @@
         <v>1834</v>
       </c>
       <c r="H46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46">
         <v>2</v>
